--- a/Financial Analysis/SNAP.xlsx
+++ b/Financial Analysis/SNAP.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35E6DEBB-B6C3-45BD-BE82-B603DCB5351E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{599D7D7C-8045-41BE-91A2-8B9633D72A37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{48C45758-2500-4F87-8506-866CB0FEFDEC}"/>
   </bookViews>
@@ -812,14 +812,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="5">
-        <v>7.86</v>
+        <v>8.39</v>
       </c>
       <c r="E3" s="3">
-        <v>45777</v>
+        <v>45804</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45781</v>
+        <v>45804</v>
       </c>
       <c r="G3" s="3">
         <v>45867</v>
@@ -843,7 +843,7 @@
       </c>
       <c r="D5" s="4">
         <f>D3*D4</f>
-        <v>13332.918</v>
+        <v>14231.957</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -885,7 +885,7 @@
       </c>
       <c r="D9" s="4">
         <f>D5-D8</f>
-        <v>13738.918</v>
+        <v>14637.957</v>
       </c>
     </row>
   </sheetData>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BE27" s="5">
         <f>Main!D3</f>
-        <v>7.86</v>
+        <v>8.39</v>
       </c>
     </row>
     <row r="28" spans="2:57" x14ac:dyDescent="0.3">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="BE28" s="10">
         <f>BE26/BE27-1</f>
-        <v>-0.7532020829253403</v>
+        <v>-0.76879241618512217</v>
       </c>
     </row>
     <row r="29" spans="2:57" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -7509,13 +7509,13 @@
     <row r="53" spans="57:57" x14ac:dyDescent="0.3">
       <c r="BE53" s="5">
         <f>Main!D3</f>
-        <v>7.86</v>
+        <v>8.39</v>
       </c>
     </row>
     <row r="54" spans="57:57" x14ac:dyDescent="0.3">
       <c r="BE54" s="10">
         <f>BE52/BE53-1</f>
-        <v>-0.33764030354459329</v>
+        <v>-0.37948185767109699</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/SNAP.xlsx
+++ b/Financial Analysis/SNAP.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{599D7D7C-8045-41BE-91A2-8B9633D72A37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EB81D1D-BA17-41E2-BCC5-163A9D437D69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{48C45758-2500-4F87-8506-866CB0FEFDEC}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="89">
   <si>
     <t>SNAP</t>
   </si>
@@ -290,6 +290,9 @@
   </si>
   <si>
     <t>FCF</t>
+  </si>
+  <si>
+    <t>Q225 8K</t>
   </si>
 </sst>
 </file>
@@ -389,13 +392,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>31</xdr:col>
+      <xdr:col>32</xdr:col>
       <xdr:colOff>30480</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>31</xdr:col>
+      <xdr:col>32</xdr:col>
       <xdr:colOff>30480</xdr:colOff>
       <xdr:row>50</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
@@ -413,7 +416,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="19362420" y="0"/>
+          <a:off x="19972020" y="0"/>
           <a:ext cx="0" cy="9304020"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -812,17 +815,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="5">
-        <v>8.39</v>
+        <v>7.86</v>
       </c>
       <c r="E3" s="3">
-        <v>45804</v>
+        <v>45875</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45804</v>
+        <v>45909</v>
       </c>
       <c r="G3" s="3">
-        <v>45867</v>
+        <v>45958</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -830,11 +833,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="4">
-        <f>1442.2+22.5+231.6</f>
-        <v>1696.3</v>
+        <f>1674.9</f>
+        <v>1674.9</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -843,7 +846,7 @@
       </c>
       <c r="D5" s="4">
         <f>D3*D4</f>
-        <v>14231.957</v>
+        <v>13164.714000000002</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -851,11 +854,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="4">
-        <f>911.2+2295.7</f>
-        <v>3206.8999999999996</v>
+        <f>926+1967.1</f>
+        <v>2893.1</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -863,11 +866,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="4">
-        <f>36.2+3576.7</f>
-        <v>3612.8999999999996</v>
+        <f>3576</f>
+        <v>3576</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -876,7 +879,7 @@
       </c>
       <c r="D8" s="4">
         <f>D6-D7</f>
-        <v>-406</v>
+        <v>-682.90000000000009</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -885,7 +888,7 @@
       </c>
       <c r="D9" s="4">
         <f>D5-D8</f>
-        <v>14637.957</v>
+        <v>13847.614000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1151,16 +1154,15 @@
         <v>1363.2</v>
       </c>
       <c r="AF3" s="8">
-        <f>AB3*1.12</f>
-        <v>1385.2160000000001</v>
+        <v>1344.9</v>
       </c>
       <c r="AG3" s="8">
-        <f>AC3*1.1</f>
-        <v>1509.7500000000002</v>
+        <f>AC3*1.08</f>
+        <v>1482.3000000000002</v>
       </c>
       <c r="AH3" s="8">
-        <f>AD3*1.1</f>
-        <v>1713.0300000000002</v>
+        <f>AD3*1.06</f>
+        <v>1650.7380000000001</v>
       </c>
       <c r="AI3" s="8"/>
       <c r="AK3" s="8">
@@ -1193,47 +1195,47 @@
       </c>
       <c r="AR3" s="8">
         <f>SUM(AE3:AH3)</f>
-        <v>5971.1959999999999</v>
+        <v>5841.1380000000008</v>
       </c>
       <c r="AS3" s="8">
-        <f>AR3*1.08</f>
-        <v>6448.8916800000006</v>
+        <f>AR3*1.05</f>
+        <v>6133.1949000000013</v>
       </c>
       <c r="AT3" s="8">
-        <f>AS3*1.06</f>
-        <v>6835.8251808000014</v>
+        <f>AS3*1.04</f>
+        <v>6378.5226960000018</v>
       </c>
       <c r="AU3" s="8">
-        <f>AT3*1.05</f>
-        <v>7177.6164398400015</v>
+        <f>AT3*1.04</f>
+        <v>6633.663603840002</v>
       </c>
       <c r="AV3" s="8">
         <f>AU3*1.04</f>
-        <v>7464.7210974336022</v>
+        <v>6899.010147993602</v>
       </c>
       <c r="AW3" s="8">
         <f>AV3*1.03</f>
-        <v>7688.6627303566102</v>
+        <v>7105.9804524334104</v>
       </c>
       <c r="AX3" s="8">
-        <f>AW3*1.02</f>
-        <v>7842.4359849637422</v>
+        <f t="shared" ref="AX3:BB3" si="0">AW3*1.03</f>
+        <v>7319.1598660064128</v>
       </c>
       <c r="AY3" s="8">
-        <f>AX3*1.02</f>
-        <v>7999.2847046630168</v>
+        <f t="shared" si="0"/>
+        <v>7538.7346619866057</v>
       </c>
       <c r="AZ3" s="8">
-        <f t="shared" ref="AZ3:BB3" si="0">AY3*1.02</f>
-        <v>8159.2703987562772</v>
+        <f t="shared" si="0"/>
+        <v>7764.8967018462045</v>
       </c>
       <c r="BA3" s="8">
         <f t="shared" si="0"/>
-        <v>8322.4558067314028</v>
+        <v>7997.8436029015911</v>
       </c>
       <c r="BB3" s="8">
         <f t="shared" si="0"/>
-        <v>8488.9049228660315</v>
+        <v>8237.7789109886398</v>
       </c>
     </row>
     <row r="4" spans="2:167" x14ac:dyDescent="0.3">
@@ -1328,16 +1330,15 @@
         <v>639.6</v>
       </c>
       <c r="AF4" s="4">
-        <f t="shared" ref="AF4:AG4" si="1">AF3-AF5</f>
-        <v>637.19935999999996</v>
+        <v>653.29999999999995</v>
       </c>
       <c r="AG4" s="4">
-        <f t="shared" si="1"/>
-        <v>694.48500000000001</v>
+        <f t="shared" ref="AG4" si="1">AG3-AG5</f>
+        <v>681.85800000000006</v>
       </c>
       <c r="AH4" s="4">
         <f>AH3-AH5</f>
-        <v>736.6029000000002</v>
+        <v>709.81734000000006</v>
       </c>
       <c r="AI4" s="4"/>
       <c r="AK4" s="4">
@@ -1370,47 +1371,47 @@
       </c>
       <c r="AR4" s="4">
         <f>SUM(AE4:AH4)</f>
-        <v>2707.8872600000004</v>
+        <v>2684.5753400000003</v>
       </c>
       <c r="AS4" s="4">
         <f t="shared" ref="AS4:AW4" si="2">AS3-AS5</f>
-        <v>2837.5123392</v>
+        <v>2698.6057560000004</v>
       </c>
       <c r="AT4" s="4">
         <f t="shared" si="2"/>
-        <v>3007.7630795520004</v>
+        <v>2806.5499862400006</v>
       </c>
       <c r="AU4" s="4">
         <f t="shared" si="2"/>
-        <v>3158.1512335296002</v>
+        <v>2918.8119856896005</v>
       </c>
       <c r="AV4" s="4">
         <f t="shared" si="2"/>
-        <v>3284.4772828707846</v>
+        <v>3035.5644651171847</v>
       </c>
       <c r="AW4" s="4">
         <f t="shared" si="2"/>
-        <v>3383.0116013569077</v>
+        <v>3126.6313990707004</v>
       </c>
       <c r="AX4" s="4">
         <f t="shared" ref="AX4:BB4" si="3">AX3-AX5</f>
-        <v>3450.6718333840463</v>
+        <v>3220.4303410428211</v>
       </c>
       <c r="AY4" s="4">
         <f t="shared" si="3"/>
-        <v>3519.6852700517265</v>
+        <v>3317.0432512741063</v>
       </c>
       <c r="AZ4" s="4">
         <f t="shared" si="3"/>
-        <v>3590.0789754527614</v>
+        <v>3416.5545488123298</v>
       </c>
       <c r="BA4" s="4">
         <f t="shared" si="3"/>
-        <v>3661.8805549618164</v>
+        <v>3519.0511852766995</v>
       </c>
       <c r="BB4" s="4">
         <f t="shared" si="3"/>
-        <v>3735.1181660610537</v>
+        <v>3624.622720835001</v>
       </c>
     </row>
     <row r="5" spans="2:167" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1518,7 +1519,7 @@
         <v>620.09999999999991</v>
       </c>
       <c r="AB5" s="8">
-        <f t="shared" ref="AB5:AE5" si="12">AB3-AB4</f>
+        <f t="shared" ref="AB5:AF5" si="12">AB3-AB4</f>
         <v>647.9</v>
       </c>
       <c r="AC5" s="8">
@@ -1534,16 +1535,16 @@
         <v>723.6</v>
       </c>
       <c r="AF5" s="8">
-        <f t="shared" ref="AF5:AG5" si="13">AF3*0.54</f>
-        <v>748.01664000000017</v>
+        <f t="shared" si="12"/>
+        <v>691.60000000000014</v>
       </c>
       <c r="AG5" s="8">
-        <f t="shared" si="13"/>
-        <v>815.26500000000021</v>
+        <f t="shared" ref="AG5" si="13">AG3*0.54</f>
+        <v>800.44200000000012</v>
       </c>
       <c r="AH5" s="8">
         <f>AH3*0.57</f>
-        <v>976.4271</v>
+        <v>940.92066</v>
       </c>
       <c r="AI5" s="8"/>
       <c r="AJ5" s="8"/>
@@ -1577,47 +1578,47 @@
       </c>
       <c r="AR5" s="8">
         <f t="shared" si="14"/>
-        <v>3263.3087399999995</v>
+        <v>3156.5626600000005</v>
       </c>
       <c r="AS5" s="8">
         <f>AS3*0.56</f>
-        <v>3611.3793408000006</v>
+        <v>3434.5891440000009</v>
       </c>
       <c r="AT5" s="8">
         <f t="shared" ref="AT5:BB5" si="15">AT3*0.56</f>
-        <v>3828.062101248001</v>
+        <v>3571.9727097600012</v>
       </c>
       <c r="AU5" s="8">
         <f t="shared" si="15"/>
-        <v>4019.4652063104013</v>
+        <v>3714.8516181504015</v>
       </c>
       <c r="AV5" s="8">
         <f t="shared" si="15"/>
-        <v>4180.2438145628175</v>
+        <v>3863.4456828764173</v>
       </c>
       <c r="AW5" s="8">
         <f t="shared" si="15"/>
-        <v>4305.6511289997025</v>
+        <v>3979.34905336271</v>
       </c>
       <c r="AX5" s="8">
         <f t="shared" si="15"/>
-        <v>4391.7641515796959</v>
+        <v>4098.7295249635918</v>
       </c>
       <c r="AY5" s="8">
         <f t="shared" si="15"/>
-        <v>4479.5994346112902</v>
+        <v>4221.6914107124994</v>
       </c>
       <c r="AZ5" s="8">
         <f t="shared" si="15"/>
-        <v>4569.1914233035159</v>
+        <v>4348.3421530338746</v>
       </c>
       <c r="BA5" s="8">
         <f t="shared" si="15"/>
-        <v>4660.5752517695864</v>
+        <v>4478.7924176248916</v>
       </c>
       <c r="BB5" s="8">
         <f t="shared" si="15"/>
-        <v>4753.7867568049778</v>
+        <v>4613.1561901536388</v>
       </c>
     </row>
     <row r="6" spans="2:167" x14ac:dyDescent="0.3">
@@ -1712,16 +1713,15 @@
         <v>424.2</v>
       </c>
       <c r="AF6" s="4">
-        <f>AB6*0.98</f>
-        <v>398.07599999999996</v>
+        <v>443.3</v>
       </c>
       <c r="AG6" s="4">
-        <f t="shared" ref="AG6:AH6" si="16">AC6*0.98</f>
-        <v>404.54399999999998</v>
+        <f>AC6*1.1</f>
+        <v>454.08000000000004</v>
       </c>
       <c r="AH6" s="4">
-        <f t="shared" si="16"/>
-        <v>414.44199999999995</v>
+        <f>AD6*1.1</f>
+        <v>465.19</v>
       </c>
       <c r="AI6" s="4"/>
       <c r="AJ6" s="4"/>
@@ -1734,7 +1734,7 @@
         <v>883.5</v>
       </c>
       <c r="AM6" s="4">
-        <f t="shared" ref="AM6:AM8" si="17">SUM(K6:N6)</f>
+        <f t="shared" ref="AM6:AM8" si="16">SUM(K6:N6)</f>
         <v>1101.5</v>
       </c>
       <c r="AN6" s="4">
@@ -1755,47 +1755,47 @@
       </c>
       <c r="AR6" s="4">
         <f>SUM(AE6:AH6)</f>
-        <v>1641.2619999999999</v>
+        <v>1786.77</v>
       </c>
       <c r="AS6" s="4">
         <f>AR6*1.01</f>
-        <v>1657.67462</v>
+        <v>1804.6377</v>
       </c>
       <c r="AT6" s="4">
-        <f t="shared" ref="AT6:BB6" si="18">AS6*1.01</f>
-        <v>1674.2513662000001</v>
+        <f t="shared" ref="AT6:BB6" si="17">AS6*1.01</f>
+        <v>1822.6840770000001</v>
       </c>
       <c r="AU6" s="4">
-        <f t="shared" si="18"/>
-        <v>1690.9938798620001</v>
+        <f t="shared" si="17"/>
+        <v>1840.9109177700002</v>
       </c>
       <c r="AV6" s="4">
-        <f t="shared" si="18"/>
-        <v>1707.9038186606201</v>
+        <f t="shared" si="17"/>
+        <v>1859.3200269477002</v>
       </c>
       <c r="AW6" s="4">
-        <f t="shared" si="18"/>
-        <v>1724.9828568472262</v>
+        <f t="shared" si="17"/>
+        <v>1877.9132272171771</v>
       </c>
       <c r="AX6" s="4">
-        <f t="shared" si="18"/>
-        <v>1742.2326854156986</v>
+        <f t="shared" si="17"/>
+        <v>1896.692359489349</v>
       </c>
       <c r="AY6" s="4">
-        <f t="shared" si="18"/>
-        <v>1759.6550122698557</v>
+        <f t="shared" si="17"/>
+        <v>1915.6592830842426</v>
       </c>
       <c r="AZ6" s="4">
-        <f t="shared" si="18"/>
-        <v>1777.2515623925542</v>
+        <f t="shared" si="17"/>
+        <v>1934.8158759150851</v>
       </c>
       <c r="BA6" s="4">
-        <f t="shared" si="18"/>
-        <v>1795.0240780164797</v>
+        <f t="shared" si="17"/>
+        <v>1954.1640346742361</v>
       </c>
       <c r="BB6" s="4">
-        <f t="shared" si="18"/>
-        <v>1812.9743187966446</v>
+        <f t="shared" si="17"/>
+        <v>1973.7056750209783</v>
       </c>
     </row>
     <row r="7" spans="2:167" x14ac:dyDescent="0.3">
@@ -1890,16 +1890,15 @@
         <v>258</v>
       </c>
       <c r="AF7" s="4">
-        <f>AF3*0.2</f>
-        <v>277.04320000000001</v>
+        <v>257.89999999999998</v>
       </c>
       <c r="AG7" s="4">
         <f>AG3*0.19</f>
-        <v>286.85250000000002</v>
+        <v>281.63700000000006</v>
       </c>
       <c r="AH7" s="4">
         <f>AH3*0.16</f>
-        <v>274.08480000000003</v>
+        <v>264.11808000000002</v>
       </c>
       <c r="AI7" s="4"/>
       <c r="AK7" s="4">
@@ -1911,7 +1910,7 @@
         <v>458.6</v>
       </c>
       <c r="AM7" s="4">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>555.4</v>
       </c>
       <c r="AN7" s="4">
@@ -1932,47 +1931,47 @@
       </c>
       <c r="AR7" s="4">
         <f>SUM(AE7:AH7)</f>
-        <v>1095.9805000000001</v>
+        <v>1061.65508</v>
       </c>
       <c r="AS7" s="4">
         <f>AS3*0.17</f>
-        <v>1096.3115856000002</v>
+        <v>1042.6431330000003</v>
       </c>
       <c r="AT7" s="4">
         <f>AT3*0.16</f>
-        <v>1093.7320289280003</v>
+        <v>1020.5636313600003</v>
       </c>
       <c r="AU7" s="4">
         <f>AU3*0.16</f>
-        <v>1148.4186303744002</v>
+        <v>1061.3861766144003</v>
       </c>
       <c r="AV7" s="4">
-        <f t="shared" ref="AV7:BB7" si="19">AV3*0.16</f>
-        <v>1194.3553755893763</v>
+        <f t="shared" ref="AV7:BB7" si="18">AV3*0.16</f>
+        <v>1103.8416236789762</v>
       </c>
       <c r="AW7" s="4">
-        <f t="shared" si="19"/>
-        <v>1230.1860368570576</v>
+        <f t="shared" si="18"/>
+        <v>1136.9568723893458</v>
       </c>
       <c r="AX7" s="4">
-        <f t="shared" si="19"/>
-        <v>1254.7897575941988</v>
+        <f t="shared" si="18"/>
+        <v>1171.0655785610261</v>
       </c>
       <c r="AY7" s="4">
-        <f t="shared" si="19"/>
-        <v>1279.8855527460828</v>
+        <f t="shared" si="18"/>
+        <v>1206.197545917857</v>
       </c>
       <c r="AZ7" s="4">
-        <f t="shared" si="19"/>
-        <v>1305.4832638010043</v>
+        <f t="shared" si="18"/>
+        <v>1242.3834722953927</v>
       </c>
       <c r="BA7" s="4">
-        <f t="shared" si="19"/>
-        <v>1331.5929290770246</v>
+        <f t="shared" si="18"/>
+        <v>1279.6549764642546</v>
       </c>
       <c r="BB7" s="4">
-        <f t="shared" si="19"/>
-        <v>1358.224787658565</v>
+        <f t="shared" si="18"/>
+        <v>1318.0446257581823</v>
       </c>
     </row>
     <row r="8" spans="2:167" x14ac:dyDescent="0.3">
@@ -2067,16 +2066,15 @@
         <v>235.4</v>
       </c>
       <c r="AF8" s="4">
-        <f t="shared" ref="AF8:AH8" si="20">AB8*1.02</f>
-        <v>233.88600000000002</v>
+        <v>250.1</v>
       </c>
       <c r="AG8" s="4">
-        <f t="shared" si="20"/>
-        <v>225.42000000000002</v>
+        <f>AC8*1.1</f>
+        <v>243.10000000000002</v>
       </c>
       <c r="AH8" s="4">
-        <f t="shared" si="20"/>
-        <v>246.126</v>
+        <f>AD8*1.1</f>
+        <v>265.43</v>
       </c>
       <c r="AI8" s="4"/>
       <c r="AK8" s="4">
@@ -2088,7 +2086,7 @@
         <v>580.9</v>
       </c>
       <c r="AM8" s="4">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>529.1</v>
       </c>
       <c r="AN8" s="4">
@@ -2109,47 +2107,47 @@
       </c>
       <c r="AR8" s="4">
         <f>SUM(AE8:AH8)</f>
-        <v>940.83200000000011</v>
+        <v>994.03</v>
       </c>
       <c r="AS8" s="4">
         <f>AR8*1.04</f>
-        <v>978.46528000000012</v>
+        <v>1033.7912000000001</v>
       </c>
       <c r="AT8" s="4">
         <f>AS8*1.03</f>
-        <v>1007.8192384000001</v>
+        <v>1064.8049360000002</v>
       </c>
       <c r="AU8" s="4">
-        <f t="shared" ref="AU8:AW8" si="21">AT8*1.02</f>
-        <v>1027.9756231680001</v>
+        <f t="shared" ref="AU8:AW8" si="19">AT8*1.02</f>
+        <v>1086.1010347200001</v>
       </c>
       <c r="AV8" s="4">
-        <f t="shared" si="21"/>
-        <v>1048.5351356313602</v>
+        <f t="shared" si="19"/>
+        <v>1107.8230554144002</v>
       </c>
       <c r="AW8" s="4">
-        <f t="shared" si="21"/>
-        <v>1069.5058383439873</v>
+        <f t="shared" si="19"/>
+        <v>1129.9795165226883</v>
       </c>
       <c r="AX8" s="4">
         <f>AW8*1.01</f>
-        <v>1080.2008967274271</v>
+        <v>1141.2793116879152</v>
       </c>
       <c r="AY8" s="4">
-        <f t="shared" ref="AY8:BB8" si="22">AX8*1.01</f>
-        <v>1091.0029056947014</v>
+        <f t="shared" ref="AY8:BB8" si="20">AX8*1.01</f>
+        <v>1152.6921048047943</v>
       </c>
       <c r="AZ8" s="4">
-        <f t="shared" si="22"/>
-        <v>1101.9129347516484</v>
+        <f t="shared" si="20"/>
+        <v>1164.2190258528424</v>
       </c>
       <c r="BA8" s="4">
-        <f t="shared" si="22"/>
-        <v>1112.932064099165</v>
+        <f t="shared" si="20"/>
+        <v>1175.8612161113708</v>
       </c>
       <c r="BB8" s="4">
-        <f t="shared" si="22"/>
-        <v>1124.0613847401567</v>
+        <f t="shared" si="20"/>
+        <v>1187.6198282724845</v>
       </c>
     </row>
     <row r="9" spans="2:167" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2157,132 +2155,132 @@
         <v>28</v>
       </c>
       <c r="C9" s="8">
-        <f t="shared" ref="C9:Q9" si="23">C5-C6-C7-C8</f>
+        <f t="shared" ref="C9:Q9" si="21">C5-C6-C7-C8</f>
         <v>-392.50000000000006</v>
       </c>
       <c r="D9" s="8">
+        <f t="shared" si="21"/>
+        <v>-357.79999999999995</v>
+      </c>
+      <c r="E9" s="8">
+        <f t="shared" si="21"/>
+        <v>-323.5</v>
+      </c>
+      <c r="F9" s="8">
+        <f t="shared" si="21"/>
+        <v>-194.70000000000005</v>
+      </c>
+      <c r="G9" s="8">
+        <f t="shared" si="21"/>
+        <v>-316.20000000000005</v>
+      </c>
+      <c r="H9" s="8">
+        <f t="shared" si="21"/>
+        <v>-304.79999999999995</v>
+      </c>
+      <c r="I9" s="8">
+        <f t="shared" si="21"/>
+        <v>-228.8</v>
+      </c>
+      <c r="J9" s="8">
+        <f t="shared" si="21"/>
+        <v>-253.5</v>
+      </c>
+      <c r="K9" s="8">
+        <f t="shared" si="21"/>
+        <v>-286.29999999999995</v>
+      </c>
+      <c r="L9" s="8">
+        <f t="shared" si="21"/>
+        <v>-310.59999999999997</v>
+      </c>
+      <c r="M9" s="8">
+        <f t="shared" si="21"/>
+        <v>-167.8</v>
+      </c>
+      <c r="N9" s="8">
+        <f t="shared" si="21"/>
+        <v>-97.100000000000023</v>
+      </c>
+      <c r="O9" s="8">
+        <f t="shared" si="21"/>
+        <v>-303.60000000000002</v>
+      </c>
+      <c r="P9" s="8">
+        <f t="shared" si="21"/>
+        <v>-192.49999999999994</v>
+      </c>
+      <c r="Q9" s="8">
+        <f t="shared" si="21"/>
+        <v>-180.8</v>
+      </c>
+      <c r="R9" s="8">
+        <f t="shared" ref="R9:S9" si="22">R5-R6-R7-R8</f>
+        <v>-25.099999999999937</v>
+      </c>
+      <c r="S9" s="8">
+        <f t="shared" si="22"/>
+        <v>-271.59999999999997</v>
+      </c>
+      <c r="T9" s="8">
+        <f t="shared" ref="T9:U9" si="23">T5-T6-T7-T8</f>
+        <v>-400.99999999999989</v>
+      </c>
+      <c r="U9" s="8">
         <f t="shared" si="23"/>
-        <v>-357.79999999999995</v>
-      </c>
-      <c r="E9" s="8">
-        <f t="shared" si="23"/>
-        <v>-323.5</v>
-      </c>
-      <c r="F9" s="8">
-        <f t="shared" si="23"/>
-        <v>-194.70000000000005</v>
-      </c>
-      <c r="G9" s="8">
-        <f t="shared" si="23"/>
-        <v>-316.20000000000005</v>
-      </c>
-      <c r="H9" s="8">
-        <f t="shared" si="23"/>
-        <v>-304.79999999999995</v>
-      </c>
-      <c r="I9" s="8">
-        <f t="shared" si="23"/>
-        <v>-228.8</v>
-      </c>
-      <c r="J9" s="8">
-        <f t="shared" si="23"/>
-        <v>-253.5</v>
-      </c>
-      <c r="K9" s="8">
-        <f t="shared" si="23"/>
-        <v>-286.29999999999995</v>
-      </c>
-      <c r="L9" s="8">
-        <f t="shared" si="23"/>
-        <v>-310.59999999999997</v>
-      </c>
-      <c r="M9" s="8">
-        <f t="shared" si="23"/>
-        <v>-167.8</v>
-      </c>
-      <c r="N9" s="8">
-        <f t="shared" si="23"/>
-        <v>-97.100000000000023</v>
-      </c>
-      <c r="O9" s="8">
-        <f t="shared" si="23"/>
-        <v>-303.60000000000002</v>
-      </c>
-      <c r="P9" s="8">
-        <f t="shared" si="23"/>
-        <v>-192.49999999999994</v>
-      </c>
-      <c r="Q9" s="8">
-        <f t="shared" si="23"/>
-        <v>-180.8</v>
-      </c>
-      <c r="R9" s="8">
-        <f t="shared" ref="R9:S9" si="24">R5-R6-R7-R8</f>
-        <v>-25.099999999999937</v>
-      </c>
-      <c r="S9" s="8">
-        <f t="shared" si="24"/>
-        <v>-271.59999999999997</v>
-      </c>
-      <c r="T9" s="8">
-        <f t="shared" ref="T9:U9" si="25">T5-T6-T7-T8</f>
-        <v>-400.99999999999989</v>
-      </c>
-      <c r="U9" s="8">
-        <f t="shared" si="25"/>
         <v>-435.2999999999999</v>
       </c>
       <c r="V9" s="8">
-        <f t="shared" ref="V9" si="26">V5-V6-V7-V8</f>
+        <f t="shared" ref="V9" si="24">V5-V6-V7-V8</f>
         <v>-287.59999999999991</v>
       </c>
       <c r="W9" s="8">
-        <f t="shared" ref="W9" si="27">W5-W6-W7-W8</f>
+        <f t="shared" ref="W9" si="25">W5-W6-W7-W8</f>
         <v>-365.2</v>
       </c>
       <c r="X9" s="8">
-        <f t="shared" ref="X9:Y9" si="28">X5-X6-X7-X8</f>
+        <f t="shared" ref="X9:Y9" si="26">X5-X6-X7-X8</f>
         <v>-404.4</v>
       </c>
       <c r="Y9" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>-380.20000000000005</v>
       </c>
       <c r="Z9" s="8">
-        <f t="shared" ref="Z9" si="29">Z5-Z6-Z7-Z8</f>
+        <f t="shared" ref="Z9" si="27">Z5-Z6-Z7-Z8</f>
         <v>-248.70000000000005</v>
       </c>
       <c r="AA9" s="8">
-        <f t="shared" ref="AA9" si="30">AA5-AA6-AA7-AA8</f>
+        <f t="shared" ref="AA9" si="28">AA5-AA6-AA7-AA8</f>
         <v>-333.2000000000001</v>
       </c>
       <c r="AB9" s="8">
-        <f t="shared" ref="AB9:AH9" si="31">AB5-AB6-AB7-AB8</f>
+        <f t="shared" ref="AB9:AH9" si="29">AB5-AB6-AB7-AB8</f>
         <v>-253.90000000000003</v>
       </c>
       <c r="AC9" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>-173.3</v>
       </c>
       <c r="AD9" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>-26.800000000000068</v>
       </c>
       <c r="AE9" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>-193.99999999999997</v>
       </c>
       <c r="AF9" s="8">
-        <f t="shared" si="31"/>
-        <v>-160.98855999999984</v>
+        <f t="shared" si="29"/>
+        <v>-259.69999999999982</v>
       </c>
       <c r="AG9" s="8">
-        <f t="shared" si="31"/>
-        <v>-101.55149999999981</v>
+        <f t="shared" si="29"/>
+        <v>-178.375</v>
       </c>
       <c r="AH9" s="8">
-        <f t="shared" si="31"/>
-        <v>41.774300000000068</v>
+        <f t="shared" si="29"/>
+        <v>-53.817420000000027</v>
       </c>
       <c r="AI9" s="8"/>
       <c r="AK9" s="8">
@@ -2298,64 +2296,64 @@
         <v>-861.80000000000018</v>
       </c>
       <c r="AN9" s="8">
-        <f t="shared" ref="AN9:AW9" si="32">AN5-AN6-AN7-AN8</f>
+        <f t="shared" ref="AN9:AW9" si="30">AN5-AN6-AN7-AN8</f>
         <v>-701.99999999999989</v>
       </c>
       <c r="AO9" s="8">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>-1395.4999999999995</v>
       </c>
       <c r="AP9" s="8">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>-1398.5</v>
       </c>
       <c r="AQ9" s="8">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>-787.19999999999982</v>
       </c>
       <c r="AR9" s="8">
-        <f t="shared" si="32"/>
-        <v>-414.76576000000068</v>
+        <f t="shared" si="30"/>
+        <v>-685.89241999999945</v>
       </c>
       <c r="AS9" s="8">
-        <f t="shared" si="32"/>
-        <v>-121.07214479999971</v>
+        <f t="shared" si="30"/>
+        <v>-446.48288899999943</v>
       </c>
       <c r="AT9" s="8">
-        <f t="shared" si="32"/>
-        <v>52.25946772000043</v>
+        <f t="shared" si="30"/>
+        <v>-336.07993459999943</v>
       </c>
       <c r="AU9" s="8">
-        <f t="shared" si="32"/>
-        <v>152.07707290600092</v>
+        <f t="shared" si="30"/>
+        <v>-273.54651095399913</v>
       </c>
       <c r="AV9" s="8">
-        <f t="shared" si="32"/>
-        <v>229.44948468146072</v>
+        <f t="shared" si="30"/>
+        <v>-207.53902316465928</v>
       </c>
       <c r="AW9" s="8">
-        <f t="shared" si="32"/>
-        <v>280.9763969514313</v>
+        <f t="shared" si="30"/>
+        <v>-165.50056276650139</v>
       </c>
       <c r="AX9" s="8">
-        <f t="shared" ref="AX9:BB9" si="33">AX5-AX6-AX7-AX8</f>
-        <v>314.54081184237134</v>
+        <f t="shared" ref="AX9:BB9" si="31">AX5-AX6-AX7-AX8</f>
+        <v>-110.30772477469827</v>
       </c>
       <c r="AY9" s="8">
-        <f t="shared" si="33"/>
-        <v>349.05596390065057</v>
+        <f t="shared" si="31"/>
+        <v>-52.857523094394764</v>
       </c>
       <c r="AZ9" s="8">
-        <f t="shared" si="33"/>
-        <v>384.54366235830889</v>
+        <f t="shared" si="31"/>
+        <v>6.9237789705543946</v>
       </c>
       <c r="BA9" s="8">
-        <f t="shared" si="33"/>
-        <v>421.02618057691734</v>
+        <f t="shared" si="31"/>
+        <v>69.112190375030195</v>
       </c>
       <c r="BB9" s="8">
-        <f t="shared" si="33"/>
-        <v>458.52626560961153</v>
+        <f t="shared" si="31"/>
+        <v>133.78606110199348</v>
       </c>
     </row>
     <row r="10" spans="2:167" x14ac:dyDescent="0.3">
@@ -2450,15 +2448,14 @@
         <v>-37</v>
       </c>
       <c r="AF10" s="4">
-        <f t="shared" ref="AF10:AH10" si="34">AB10*1.01</f>
-        <v>-36.865000000000002</v>
+        <v>-33.200000000000003</v>
       </c>
       <c r="AG10" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" ref="AG10:AH10" si="32">AC10*1.01</f>
         <v>-38.884999999999998</v>
       </c>
       <c r="AH10" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>-38.986000000000004</v>
       </c>
       <c r="AI10" s="4"/>
@@ -2471,7 +2468,7 @@
         <v>-35.700000000000003</v>
       </c>
       <c r="AM10" s="4">
-        <f t="shared" ref="AM10:AM12" si="35">SUM(K10:N10)</f>
+        <f t="shared" ref="AM10:AM12" si="33">SUM(K10:N10)</f>
         <v>-18.169</v>
       </c>
       <c r="AN10" s="4">
@@ -2492,47 +2489,47 @@
       </c>
       <c r="AR10" s="4">
         <f>SUM(AE10:AH10)</f>
-        <v>-151.73599999999999</v>
+        <v>-148.07100000000003</v>
       </c>
       <c r="AS10" s="4">
-        <f t="shared" ref="AS10:BB10" si="36">AR10*1.02</f>
-        <v>-154.77071999999998</v>
+        <f t="shared" ref="AS10:BB10" si="34">AR10*1.02</f>
+        <v>-151.03242000000003</v>
       </c>
       <c r="AT10" s="4">
-        <f t="shared" si="36"/>
-        <v>-157.86613439999999</v>
+        <f t="shared" si="34"/>
+        <v>-154.05306840000003</v>
       </c>
       <c r="AU10" s="4">
-        <f t="shared" si="36"/>
-        <v>-161.02345708799999</v>
+        <f t="shared" si="34"/>
+        <v>-157.13412976800004</v>
       </c>
       <c r="AV10" s="4">
-        <f t="shared" si="36"/>
-        <v>-164.24392622975998</v>
+        <f t="shared" si="34"/>
+        <v>-160.27681236336005</v>
       </c>
       <c r="AW10" s="4">
-        <f t="shared" si="36"/>
-        <v>-167.52880475435518</v>
+        <f t="shared" si="34"/>
+        <v>-163.48234861062724</v>
       </c>
       <c r="AX10" s="4">
-        <f t="shared" si="36"/>
-        <v>-170.8793808494423</v>
+        <f t="shared" si="34"/>
+        <v>-166.75199558283978</v>
       </c>
       <c r="AY10" s="4">
-        <f t="shared" si="36"/>
-        <v>-174.29696846643114</v>
+        <f t="shared" si="34"/>
+        <v>-170.08703549449658</v>
       </c>
       <c r="AZ10" s="4">
-        <f t="shared" si="36"/>
-        <v>-177.78290783575977</v>
+        <f t="shared" si="34"/>
+        <v>-173.48877620438651</v>
       </c>
       <c r="BA10" s="4">
-        <f t="shared" si="36"/>
-        <v>-181.33856599247497</v>
+        <f t="shared" si="34"/>
+        <v>-176.95855172847425</v>
       </c>
       <c r="BB10" s="4">
-        <f t="shared" si="36"/>
-        <v>-184.96533731232446</v>
+        <f t="shared" si="34"/>
+        <v>-180.49772276304373</v>
       </c>
     </row>
     <row r="11" spans="2:167" x14ac:dyDescent="0.3">
@@ -2627,7 +2624,7 @@
         <v>23.4</v>
       </c>
       <c r="AF11" s="4">
-        <v>6</v>
+        <v>27.6</v>
       </c>
       <c r="AG11" s="4">
         <v>6</v>
@@ -2645,7 +2642,7 @@
         <v>25.1</v>
       </c>
       <c r="AM11" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>97.2</v>
       </c>
       <c r="AN11" s="4">
@@ -2666,47 +2663,47 @@
       </c>
       <c r="AR11" s="4">
         <f>SUM(AE11:AH11)</f>
-        <v>41.4</v>
+        <v>63</v>
       </c>
       <c r="AS11" s="4">
         <f>AR11*1.03</f>
-        <v>42.642000000000003</v>
+        <v>64.89</v>
       </c>
       <c r="AT11" s="4">
-        <f t="shared" ref="AT11:BB11" si="37">AS11*1.03</f>
-        <v>43.921260000000004</v>
+        <f t="shared" ref="AT11:BB11" si="35">AS11*1.03</f>
+        <v>66.836700000000008</v>
       </c>
       <c r="AU11" s="4">
-        <f t="shared" si="37"/>
-        <v>45.238897800000004</v>
+        <f t="shared" si="35"/>
+        <v>68.841801000000004</v>
       </c>
       <c r="AV11" s="4">
-        <f t="shared" si="37"/>
-        <v>46.596064734000002</v>
+        <f t="shared" si="35"/>
+        <v>70.907055030000009</v>
       </c>
       <c r="AW11" s="4">
-        <f t="shared" si="37"/>
-        <v>47.993946676020002</v>
+        <f t="shared" si="35"/>
+        <v>73.034266680900018</v>
       </c>
       <c r="AX11" s="4">
-        <f t="shared" si="37"/>
-        <v>49.433765076300602</v>
+        <f t="shared" si="35"/>
+        <v>75.225294681327014</v>
       </c>
       <c r="AY11" s="4">
-        <f t="shared" si="37"/>
-        <v>50.916778028589619</v>
+        <f t="shared" si="35"/>
+        <v>77.482053521766829</v>
       </c>
       <c r="AZ11" s="4">
-        <f t="shared" si="37"/>
-        <v>52.44428136944731</v>
+        <f t="shared" si="35"/>
+        <v>79.806515127419843</v>
       </c>
       <c r="BA11" s="4">
-        <f t="shared" si="37"/>
-        <v>54.017609810530729</v>
+        <f t="shared" si="35"/>
+        <v>82.200710581242447</v>
       </c>
       <c r="BB11" s="4">
-        <f t="shared" si="37"/>
-        <v>55.638138104846654</v>
+        <f t="shared" si="35"/>
+        <v>84.666731898679728</v>
       </c>
     </row>
     <row r="12" spans="2:167" x14ac:dyDescent="0.3">
@@ -2801,7 +2798,7 @@
         <v>-49.1</v>
       </c>
       <c r="AF12" s="4">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AG12" s="4">
         <v>0</v>
@@ -2819,7 +2816,7 @@
         <v>-58.9</v>
       </c>
       <c r="AM12" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>-15</v>
       </c>
       <c r="AN12" s="4">
@@ -2840,47 +2837,47 @@
       </c>
       <c r="AR12" s="4">
         <f>SUM(AE12:AH12)</f>
-        <v>-49.1</v>
+        <v>-48.300000000000004</v>
       </c>
       <c r="AS12" s="4">
-        <f t="shared" ref="AS12:AX12" si="38">-AR15*0.02</f>
-        <v>5.1505654400000145</v>
+        <f t="shared" ref="AS12:AX12" si="36">-AR15*0.02</f>
+        <v>11.206106979999991</v>
       </c>
       <c r="AT12" s="4">
-        <f t="shared" si="38"/>
-        <v>0.22550384383999586</v>
+        <f t="shared" si="36"/>
+        <v>5.9447452156799914</v>
       </c>
       <c r="AU12" s="4">
-        <f t="shared" si="38"/>
-        <v>-2.6556614124185671</v>
+        <f t="shared" si="36"/>
+        <v>4.0769329826508702</v>
       </c>
       <c r="AV12" s="4">
-        <f t="shared" si="38"/>
-        <v>-4.3282766977027114</v>
+        <f t="shared" si="36"/>
+        <v>3.0292978426983996</v>
       </c>
       <c r="AW12" s="4">
-        <f t="shared" si="38"/>
-        <v>-5.6228099659987745</v>
+        <f t="shared" si="36"/>
+        <v>1.9391770187839623</v>
       </c>
       <c r="AX12" s="4">
-        <f t="shared" si="38"/>
-        <v>-6.4981450399322442</v>
+        <f t="shared" si="36"/>
+        <v>1.2318665256889301</v>
       </c>
       <c r="AY12" s="4">
-        <f t="shared" ref="AY12" si="39">-AX15*0.02</f>
-        <v>-7.0797531624871253</v>
+        <f t="shared" ref="AY12" si="37">-AX15*0.02</f>
+        <v>0.32020624638199097</v>
       </c>
       <c r="AZ12" s="4">
-        <f t="shared" ref="AZ12" si="40">-AY15*0.02</f>
-        <v>-7.6722545200156675</v>
+        <f t="shared" ref="AZ12" si="38">-AY15*0.02</f>
+        <v>-0.63083604211124777</v>
       </c>
       <c r="BA12" s="4">
-        <f t="shared" ref="BA12" si="41">-AZ15*0.02</f>
-        <v>-8.2808726935141905</v>
+        <f t="shared" ref="BA12" si="39">-AZ15*0.02</f>
+        <v>-1.6197900174341169</v>
       </c>
       <c r="BB12" s="4">
-        <f t="shared" ref="BB12" si="42">-BA15*0.02</f>
-        <v>-8.9060481512380125</v>
+        <f t="shared" ref="BB12" si="40">-BA15*0.02</f>
+        <v>-2.6478371446351376</v>
       </c>
     </row>
     <row r="13" spans="2:167" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2888,132 +2885,132 @@
         <v>30</v>
       </c>
       <c r="C13" s="8">
-        <f t="shared" ref="C13:L13" si="43">C9-C10-C11-C12</f>
+        <f t="shared" ref="C13:L13" si="41">C9-C10-C11-C12</f>
         <v>-384.1</v>
       </c>
       <c r="D13" s="8">
+        <f t="shared" si="41"/>
+        <v>-352.19999999999993</v>
+      </c>
+      <c r="E13" s="8">
+        <f t="shared" si="41"/>
+        <v>-325</v>
+      </c>
+      <c r="F13" s="8">
+        <f t="shared" si="41"/>
+        <v>-192.00000000000003</v>
+      </c>
+      <c r="G13" s="8">
+        <f t="shared" si="41"/>
+        <v>-310.30000000000007</v>
+      </c>
+      <c r="H13" s="8">
+        <f t="shared" si="41"/>
+        <v>-254.2</v>
+      </c>
+      <c r="I13" s="8">
+        <f t="shared" si="41"/>
+        <v>-229</v>
+      </c>
+      <c r="J13" s="8">
+        <f t="shared" si="41"/>
+        <v>-240.3</v>
+      </c>
+      <c r="K13" s="8">
+        <f t="shared" si="41"/>
+        <v>-305.19999999999993</v>
+      </c>
+      <c r="L13" s="8">
+        <f t="shared" si="41"/>
+        <v>-326.89999999999992</v>
+      </c>
+      <c r="M13" s="8">
+        <f t="shared" ref="M13:Q13" si="42">M9-M10-M11-M12</f>
+        <v>-198.89999999999998</v>
+      </c>
+      <c r="N13" s="8">
+        <f t="shared" si="42"/>
+        <v>-94.831000000000031</v>
+      </c>
+      <c r="O13" s="8">
+        <f t="shared" si="42"/>
+        <v>-285.39999999999998</v>
+      </c>
+      <c r="P13" s="8">
+        <f t="shared" si="42"/>
+        <v>-153.49999999999994</v>
+      </c>
+      <c r="Q13" s="8">
+        <f t="shared" si="42"/>
+        <v>-70.900000000000006</v>
+      </c>
+      <c r="R13" s="8">
+        <f t="shared" ref="R13:S13" si="43">R9-R10-R11-R12</f>
+        <v>35.600000000000065</v>
+      </c>
+      <c r="S13" s="8">
         <f t="shared" si="43"/>
-        <v>-352.19999999999993</v>
-      </c>
-      <c r="E13" s="8">
-        <f t="shared" si="43"/>
-        <v>-325</v>
-      </c>
-      <c r="F13" s="8">
-        <f t="shared" si="43"/>
-        <v>-192.00000000000003</v>
-      </c>
-      <c r="G13" s="8">
-        <f t="shared" si="43"/>
-        <v>-310.30000000000007</v>
-      </c>
-      <c r="H13" s="8">
-        <f t="shared" si="43"/>
-        <v>-254.2</v>
-      </c>
-      <c r="I13" s="8">
-        <f t="shared" si="43"/>
-        <v>-229</v>
-      </c>
-      <c r="J13" s="8">
-        <f t="shared" si="43"/>
-        <v>-240.3</v>
-      </c>
-      <c r="K13" s="8">
-        <f t="shared" si="43"/>
-        <v>-305.19999999999993</v>
-      </c>
-      <c r="L13" s="8">
-        <f t="shared" si="43"/>
-        <v>-326.89999999999992</v>
-      </c>
-      <c r="M13" s="8">
-        <f t="shared" ref="M13:Q13" si="44">M9-M10-M11-M12</f>
-        <v>-198.89999999999998</v>
-      </c>
-      <c r="N13" s="8">
+        <v>-351.19999999999993</v>
+      </c>
+      <c r="T13" s="8">
+        <f t="shared" ref="T13:U13" si="44">T9-T10-T11-T12</f>
+        <v>-415.09999999999985</v>
+      </c>
+      <c r="U13" s="8">
         <f t="shared" si="44"/>
-        <v>-94.831000000000031</v>
-      </c>
-      <c r="O13" s="8">
-        <f t="shared" si="44"/>
-        <v>-285.39999999999998</v>
-      </c>
-      <c r="P13" s="8">
-        <f t="shared" si="44"/>
-        <v>-153.49999999999994</v>
-      </c>
-      <c r="Q13" s="8">
-        <f t="shared" si="44"/>
-        <v>-70.900000000000006</v>
-      </c>
-      <c r="R13" s="8">
-        <f t="shared" ref="R13:S13" si="45">R9-R10-R11-R12</f>
-        <v>35.600000000000065</v>
-      </c>
-      <c r="S13" s="8">
-        <f t="shared" si="45"/>
-        <v>-351.19999999999993</v>
-      </c>
-      <c r="T13" s="8">
-        <f t="shared" ref="T13:U13" si="46">T9-T10-T11-T12</f>
-        <v>-415.09999999999985</v>
-      </c>
-      <c r="U13" s="8">
-        <f t="shared" si="46"/>
         <v>-494.2999999999999</v>
       </c>
       <c r="V13" s="8">
-        <f t="shared" ref="V13" si="47">V9-V10-V11-V12</f>
+        <f t="shared" ref="V13" si="45">V9-V10-V11-V12</f>
         <v>-284.19999999999993</v>
       </c>
       <c r="W13" s="8">
-        <f t="shared" ref="W13" si="48">W9-W10-W11-W12</f>
+        <f t="shared" ref="W13" si="46">W9-W10-W11-W12</f>
         <v>-321.8</v>
       </c>
       <c r="X13" s="8">
-        <f t="shared" ref="X13:Y13" si="49">X9-X10-X11-X12</f>
+        <f t="shared" ref="X13:Y13" si="47">X9-X10-X11-X12</f>
         <v>-365.29999999999995</v>
       </c>
       <c r="Y13" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v>-362.50000000000006</v>
       </c>
       <c r="Z13" s="8">
-        <f t="shared" ref="Z13" si="50">Z9-Z10-Z11-Z12</f>
+        <f t="shared" ref="Z13" si="48">Z9-Z10-Z11-Z12</f>
         <v>-244.90000000000006</v>
       </c>
       <c r="AA13" s="8">
-        <f t="shared" ref="AA13" si="51">AA9-AA10-AA11-AA12</f>
+        <f t="shared" ref="AA13" si="49">AA9-AA10-AA11-AA12</f>
         <v>-298.10000000000014</v>
       </c>
       <c r="AB13" s="8">
-        <f t="shared" ref="AB13:AH13" si="52">AB9-AB10-AB11-AB12</f>
+        <f t="shared" ref="AB13:AH13" si="50">AB9-AB10-AB11-AB12</f>
         <v>-243.30000000000004</v>
       </c>
       <c r="AC13" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="50"/>
         <v>-145.10000000000002</v>
       </c>
       <c r="AD13" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="50"/>
         <v>14.399999999999935</v>
       </c>
       <c r="AE13" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="50"/>
         <v>-131.29999999999998</v>
       </c>
       <c r="AF13" s="8">
-        <f t="shared" si="52"/>
-        <v>-130.12355999999983</v>
+        <f t="shared" si="50"/>
+        <v>-254.89999999999984</v>
       </c>
       <c r="AG13" s="8">
-        <f t="shared" si="52"/>
-        <v>-68.666499999999814</v>
+        <f t="shared" si="50"/>
+        <v>-145.49</v>
       </c>
       <c r="AH13" s="8">
-        <f t="shared" si="52"/>
-        <v>74.760300000000072</v>
+        <f t="shared" si="50"/>
+        <v>-20.831420000000023</v>
       </c>
       <c r="AI13" s="8"/>
       <c r="AK13" s="8">
@@ -3029,64 +3026,64 @@
         <v>-925.83100000000024</v>
       </c>
       <c r="AN13" s="8">
-        <f t="shared" ref="AN13:AW13" si="53">AN9-AN10-AN11-AN12</f>
+        <f t="shared" ref="AN13:AW13" si="51">AN9-AN10-AN11-AN12</f>
         <v>-474.2</v>
       </c>
       <c r="AO13" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="51"/>
         <v>-1544.7999999999997</v>
       </c>
       <c r="AP13" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="51"/>
         <v>-1294.5</v>
       </c>
       <c r="AQ13" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="51"/>
         <v>-672.0999999999998</v>
       </c>
       <c r="AR13" s="8">
-        <f t="shared" si="53"/>
-        <v>-255.32976000000068</v>
+        <f t="shared" si="51"/>
+        <v>-552.52141999999947</v>
       </c>
       <c r="AS13" s="8">
-        <f t="shared" si="53"/>
-        <v>-14.093990239999741</v>
+        <f t="shared" si="51"/>
+        <v>-371.54657597999943</v>
       </c>
       <c r="AT13" s="8">
-        <f t="shared" si="53"/>
-        <v>165.97883827616045</v>
+        <f t="shared" si="51"/>
+        <v>-254.80831141567941</v>
       </c>
       <c r="AU13" s="8">
-        <f t="shared" si="53"/>
-        <v>270.51729360641946</v>
+        <f t="shared" si="51"/>
+        <v>-189.33111516864997</v>
       </c>
       <c r="AV13" s="8">
-        <f t="shared" si="53"/>
-        <v>351.42562287492342</v>
+        <f t="shared" si="51"/>
+        <v>-121.19856367399764</v>
       </c>
       <c r="AW13" s="8">
-        <f t="shared" si="53"/>
-        <v>406.13406499576524</v>
+        <f t="shared" si="51"/>
+        <v>-76.991657855558131</v>
       </c>
       <c r="AX13" s="8">
-        <f t="shared" ref="AX13:BB13" si="54">AX9-AX10-AX11-AX12</f>
-        <v>442.48457265544533</v>
+        <f t="shared" ref="AX13:BB13" si="52">AX9-AX10-AX11-AX12</f>
+        <v>-20.012890398874433</v>
       </c>
       <c r="AY13" s="8">
-        <f t="shared" si="54"/>
-        <v>479.51590750097921</v>
+        <f t="shared" si="52"/>
+        <v>39.427252631952989</v>
       </c>
       <c r="AZ13" s="8">
-        <f t="shared" si="54"/>
-        <v>517.55454334463695</v>
+        <f t="shared" si="52"/>
+        <v>101.2368760896323</v>
       </c>
       <c r="BA13" s="8">
-        <f t="shared" si="54"/>
-        <v>556.62800945237575</v>
+        <f t="shared" si="52"/>
+        <v>165.48982153969612</v>
       </c>
       <c r="BB13" s="8">
-        <f t="shared" si="54"/>
-        <v>596.75951296832727</v>
+        <f t="shared" si="52"/>
+        <v>232.26488911099261</v>
       </c>
     </row>
     <row r="14" spans="2:167" x14ac:dyDescent="0.3">
@@ -3181,16 +3178,15 @@
         <v>8.4</v>
       </c>
       <c r="AF14" s="4">
-        <f t="shared" ref="AF14:AH14" si="55">AF13*0.05</f>
-        <v>-6.5061779999999914</v>
+        <v>7.7</v>
       </c>
       <c r="AG14" s="4">
-        <f t="shared" si="55"/>
-        <v>-3.4333249999999911</v>
+        <f t="shared" ref="AG14:AH14" si="53">AG13*0.05</f>
+        <v>-7.2745000000000006</v>
       </c>
       <c r="AH14" s="4">
-        <f t="shared" si="55"/>
-        <v>3.7380150000000039</v>
+        <f t="shared" si="53"/>
+        <v>-1.0415710000000011</v>
       </c>
       <c r="AI14" s="4"/>
       <c r="AK14" s="4">
@@ -3223,47 +3219,47 @@
       </c>
       <c r="AR14" s="4">
         <f>SUM(AE14:AH14)</f>
-        <v>2.1985120000000218</v>
+        <v>7.7839290000000005</v>
       </c>
       <c r="AS14" s="4">
         <f>AS13*0.2</f>
-        <v>-2.8187980479999482</v>
+        <v>-74.309315195999886</v>
       </c>
       <c r="AT14" s="4">
-        <f t="shared" ref="AT14:AW14" si="56">AT13*0.2</f>
-        <v>33.195767655232089</v>
+        <f t="shared" ref="AT14:AW14" si="54">AT13*0.2</f>
+        <v>-50.961662283135887</v>
       </c>
       <c r="AU14" s="4">
-        <f t="shared" si="56"/>
-        <v>54.103458721283893</v>
+        <f t="shared" si="54"/>
+        <v>-37.866223033729995</v>
       </c>
       <c r="AV14" s="4">
-        <f t="shared" si="56"/>
-        <v>70.285124574984692</v>
+        <f t="shared" si="54"/>
+        <v>-24.239712734799529</v>
       </c>
       <c r="AW14" s="4">
-        <f t="shared" si="56"/>
-        <v>81.226812999153054</v>
+        <f t="shared" si="54"/>
+        <v>-15.398331571111626</v>
       </c>
       <c r="AX14" s="4">
-        <f t="shared" ref="AX14:BB14" si="57">AX13*0.2</f>
-        <v>88.496914531089075</v>
+        <f t="shared" ref="AX14:BB14" si="55">AX13*0.2</f>
+        <v>-4.0025780797748869</v>
       </c>
       <c r="AY14" s="4">
-        <f t="shared" si="57"/>
-        <v>95.903181500195842</v>
+        <f t="shared" si="55"/>
+        <v>7.8854505263905983</v>
       </c>
       <c r="AZ14" s="4">
-        <f t="shared" si="57"/>
-        <v>103.5109086689274</v>
+        <f t="shared" si="55"/>
+        <v>20.247375217926461</v>
       </c>
       <c r="BA14" s="4">
-        <f t="shared" si="57"/>
-        <v>111.32560189047516</v>
+        <f t="shared" si="55"/>
+        <v>33.097964307939229</v>
       </c>
       <c r="BB14" s="4">
-        <f t="shared" si="57"/>
-        <v>119.35190259366546</v>
+        <f t="shared" si="55"/>
+        <v>46.452977822198527</v>
       </c>
     </row>
     <row r="15" spans="2:167" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3271,132 +3267,132 @@
         <v>32</v>
       </c>
       <c r="C15" s="8">
-        <f t="shared" ref="C15:L15" si="58">C13-C14</f>
+        <f t="shared" ref="C15:L15" si="56">C13-C14</f>
         <v>-385.70000000000005</v>
       </c>
       <c r="D15" s="8">
+        <f t="shared" si="56"/>
+        <v>-353.29999999999995</v>
+      </c>
+      <c r="E15" s="8">
+        <f t="shared" si="56"/>
+        <v>-325.2</v>
+      </c>
+      <c r="F15" s="8">
+        <f t="shared" si="56"/>
+        <v>-192.40000000000003</v>
+      </c>
+      <c r="G15" s="8">
+        <f t="shared" si="56"/>
+        <v>-310.00000000000006</v>
+      </c>
+      <c r="H15" s="8">
+        <f t="shared" si="56"/>
+        <v>-255.29999999999998</v>
+      </c>
+      <c r="I15" s="8">
+        <f t="shared" si="56"/>
+        <v>-227.7</v>
+      </c>
+      <c r="J15" s="8">
+        <f t="shared" si="56"/>
+        <v>-240.60000000000002</v>
+      </c>
+      <c r="K15" s="8">
+        <f t="shared" si="56"/>
+        <v>-305.89999999999992</v>
+      </c>
+      <c r="L15" s="8">
+        <f t="shared" si="56"/>
+        <v>-325.89999999999992</v>
+      </c>
+      <c r="M15" s="8">
+        <f t="shared" ref="M15:N15" si="57">M13-M14</f>
+        <v>-198.89999999999998</v>
+      </c>
+      <c r="N15" s="8">
+        <f t="shared" si="57"/>
+        <v>-112.93100000000004</v>
+      </c>
+      <c r="O15" s="8">
+        <f t="shared" ref="O15:Q15" si="58">O13-O14</f>
+        <v>-286.79999999999995</v>
+      </c>
+      <c r="P15" s="8">
         <f t="shared" si="58"/>
-        <v>-353.29999999999995</v>
-      </c>
-      <c r="E15" s="8">
+        <v>-151.59999999999994</v>
+      </c>
+      <c r="Q15" s="8">
         <f t="shared" si="58"/>
-        <v>-325.2</v>
-      </c>
-      <c r="F15" s="8">
-        <f t="shared" si="58"/>
-        <v>-192.40000000000003</v>
-      </c>
-      <c r="G15" s="8">
-        <f t="shared" si="58"/>
-        <v>-310.00000000000006</v>
-      </c>
-      <c r="H15" s="8">
-        <f t="shared" si="58"/>
-        <v>-255.29999999999998</v>
-      </c>
-      <c r="I15" s="8">
-        <f t="shared" si="58"/>
-        <v>-227.7</v>
-      </c>
-      <c r="J15" s="8">
-        <f t="shared" si="58"/>
-        <v>-240.60000000000002</v>
-      </c>
-      <c r="K15" s="8">
-        <f t="shared" si="58"/>
-        <v>-305.89999999999992</v>
-      </c>
-      <c r="L15" s="8">
-        <f t="shared" si="58"/>
-        <v>-325.89999999999992</v>
-      </c>
-      <c r="M15" s="8">
-        <f t="shared" ref="M15:N15" si="59">M13-M14</f>
-        <v>-198.89999999999998</v>
-      </c>
-      <c r="N15" s="8">
+        <v>-71.900000000000006</v>
+      </c>
+      <c r="R15" s="8">
+        <f t="shared" ref="R15:S15" si="59">R13-R14</f>
+        <v>22.600000000000065</v>
+      </c>
+      <c r="S15" s="8">
         <f t="shared" si="59"/>
-        <v>-112.93100000000004</v>
-      </c>
-      <c r="O15" s="8">
-        <f t="shared" ref="O15:Q15" si="60">O13-O14</f>
-        <v>-286.79999999999995</v>
-      </c>
-      <c r="P15" s="8">
+        <v>-359.69999999999993</v>
+      </c>
+      <c r="T15" s="8">
+        <f t="shared" ref="T15:U15" si="60">T13-T14</f>
+        <v>-422.09999999999985</v>
+      </c>
+      <c r="U15" s="8">
         <f t="shared" si="60"/>
-        <v>-151.59999999999994</v>
-      </c>
-      <c r="Q15" s="8">
-        <f t="shared" si="60"/>
-        <v>-71.900000000000006</v>
-      </c>
-      <c r="R15" s="8">
-        <f t="shared" ref="R15:S15" si="61">R13-R14</f>
-        <v>22.600000000000065</v>
-      </c>
-      <c r="S15" s="8">
-        <f t="shared" si="61"/>
-        <v>-359.69999999999993</v>
-      </c>
-      <c r="T15" s="8">
-        <f t="shared" ref="T15:U15" si="62">T13-T14</f>
-        <v>-422.09999999999985</v>
-      </c>
-      <c r="U15" s="8">
-        <f t="shared" si="62"/>
         <v>-503.49999999999989</v>
       </c>
       <c r="V15" s="8">
-        <f t="shared" ref="V15" si="63">V13-V14</f>
+        <f t="shared" ref="V15" si="61">V13-V14</f>
         <v>-288.39999999999992</v>
       </c>
       <c r="W15" s="8">
-        <f t="shared" ref="W15" si="64">W13-W14</f>
+        <f t="shared" ref="W15" si="62">W13-W14</f>
         <v>-328.6</v>
       </c>
       <c r="X15" s="8">
-        <f t="shared" ref="X15:Y15" si="65">X13-X14</f>
+        <f t="shared" ref="X15:Y15" si="63">X13-X14</f>
         <v>-377.4</v>
       </c>
       <c r="Y15" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="63"/>
         <v>-368.30000000000007</v>
       </c>
       <c r="Z15" s="8">
-        <f t="shared" ref="Z15" si="66">Z13-Z14</f>
+        <f t="shared" ref="Z15" si="64">Z13-Z14</f>
         <v>-248.20000000000007</v>
       </c>
       <c r="AA15" s="8">
-        <f t="shared" ref="AA15" si="67">AA13-AA14</f>
+        <f t="shared" ref="AA15" si="65">AA13-AA14</f>
         <v>-305.00000000000011</v>
       </c>
       <c r="AB15" s="8">
-        <f t="shared" ref="AB15:AD15" si="68">AB13-AB14</f>
+        <f t="shared" ref="AB15:AD15" si="66">AB13-AB14</f>
         <v>-248.50000000000003</v>
       </c>
       <c r="AC15" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>-153.40000000000003</v>
       </c>
       <c r="AD15" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>9.1999999999999353</v>
       </c>
       <c r="AE15" s="8">
-        <f t="shared" ref="AE15:AH15" si="69">AE13-AE14</f>
+        <f t="shared" ref="AE15:AH15" si="67">AE13-AE14</f>
         <v>-139.69999999999999</v>
       </c>
       <c r="AF15" s="8">
-        <f t="shared" si="69"/>
-        <v>-123.61738199999984</v>
+        <f t="shared" si="67"/>
+        <v>-262.59999999999985</v>
       </c>
       <c r="AG15" s="8">
-        <f t="shared" si="69"/>
-        <v>-65.233174999999818</v>
+        <f t="shared" si="67"/>
+        <v>-138.21550000000002</v>
       </c>
       <c r="AH15" s="8">
-        <f t="shared" si="69"/>
-        <v>71.022285000000068</v>
+        <f t="shared" si="67"/>
+        <v>-19.789849000000022</v>
       </c>
       <c r="AI15" s="8"/>
       <c r="AK15" s="8">
@@ -3412,516 +3408,516 @@
         <v>-943.6310000000002</v>
       </c>
       <c r="AN15" s="8">
-        <f t="shared" ref="AN15:AW15" si="70">AN13-AN14</f>
+        <f t="shared" ref="AN15:AW15" si="68">AN13-AN14</f>
         <v>-487.7</v>
       </c>
       <c r="AO15" s="8">
+        <f t="shared" si="68"/>
+        <v>-1573.6999999999998</v>
+      </c>
+      <c r="AP15" s="8">
+        <f t="shared" si="68"/>
+        <v>-1322.5</v>
+      </c>
+      <c r="AQ15" s="8">
+        <f t="shared" si="68"/>
+        <v>-697.69999999999982</v>
+      </c>
+      <c r="AR15" s="8">
+        <f t="shared" si="68"/>
+        <v>-560.30534899999952</v>
+      </c>
+      <c r="AS15" s="8">
+        <f t="shared" si="68"/>
+        <v>-297.23726078399955</v>
+      </c>
+      <c r="AT15" s="8">
+        <f t="shared" si="68"/>
+        <v>-203.84664913254352</v>
+      </c>
+      <c r="AU15" s="8">
+        <f t="shared" si="68"/>
+        <v>-151.46489213491998</v>
+      </c>
+      <c r="AV15" s="8">
+        <f t="shared" si="68"/>
+        <v>-96.958850939198115</v>
+      </c>
+      <c r="AW15" s="8">
+        <f t="shared" si="68"/>
+        <v>-61.593326284446505</v>
+      </c>
+      <c r="AX15" s="8">
+        <f t="shared" ref="AX15:BB15" si="69">AX13-AX14</f>
+        <v>-16.010312319099548</v>
+      </c>
+      <c r="AY15" s="8">
+        <f t="shared" si="69"/>
+        <v>31.54180210556239</v>
+      </c>
+      <c r="AZ15" s="8">
+        <f t="shared" si="69"/>
+        <v>80.989500871705843</v>
+      </c>
+      <c r="BA15" s="8">
+        <f t="shared" si="69"/>
+        <v>132.39185723175689</v>
+      </c>
+      <c r="BB15" s="8">
+        <f t="shared" si="69"/>
+        <v>185.81191128879408</v>
+      </c>
+      <c r="BC15" s="1">
+        <f t="shared" ref="BC15:CH15" si="70">BB15*(1+$BE$21)</f>
+        <v>183.95379217590613</v>
+      </c>
+      <c r="BD15" s="1">
         <f t="shared" si="70"/>
-        <v>-1573.6999999999998</v>
-      </c>
-      <c r="AP15" s="8">
+        <v>182.11425425414706</v>
+      </c>
+      <c r="BE15" s="1">
         <f t="shared" si="70"/>
-        <v>-1322.5</v>
-      </c>
-      <c r="AQ15" s="8">
+        <v>180.29311171160558</v>
+      </c>
+      <c r="BF15" s="1">
         <f t="shared" si="70"/>
-        <v>-697.69999999999982</v>
-      </c>
-      <c r="AR15" s="8">
+        <v>178.49018059448952</v>
+      </c>
+      <c r="BG15" s="1">
         <f t="shared" si="70"/>
-        <v>-257.5282720000007</v>
-      </c>
-      <c r="AS15" s="8">
+        <v>176.70527878854463</v>
+      </c>
+      <c r="BH15" s="1">
         <f t="shared" si="70"/>
-        <v>-11.275192191999793</v>
-      </c>
-      <c r="AT15" s="8">
+        <v>174.93822600065917</v>
+      </c>
+      <c r="BI15" s="1">
         <f t="shared" si="70"/>
-        <v>132.78307062092836</v>
-      </c>
-      <c r="AU15" s="8">
+        <v>173.18884374065257</v>
+      </c>
+      <c r="BJ15" s="1">
         <f t="shared" si="70"/>
-        <v>216.41383488513557</v>
-      </c>
-      <c r="AV15" s="8">
+        <v>171.45695530324605</v>
+      </c>
+      <c r="BK15" s="1">
         <f t="shared" si="70"/>
-        <v>281.14049829993871</v>
-      </c>
-      <c r="AW15" s="8">
+        <v>169.74238575021357</v>
+      </c>
+      <c r="BL15" s="1">
         <f t="shared" si="70"/>
-        <v>324.90725199661222</v>
-      </c>
-      <c r="AX15" s="8">
-        <f t="shared" ref="AX15:BB15" si="71">AX13-AX14</f>
-        <v>353.98765812435624</v>
-      </c>
-      <c r="AY15" s="8">
+        <v>168.04496189271143</v>
+      </c>
+      <c r="BM15" s="1">
+        <f t="shared" si="70"/>
+        <v>166.3645122737843</v>
+      </c>
+      <c r="BN15" s="1">
+        <f t="shared" si="70"/>
+        <v>164.70086715104645</v>
+      </c>
+      <c r="BO15" s="1">
+        <f t="shared" si="70"/>
+        <v>163.05385847953599</v>
+      </c>
+      <c r="BP15" s="1">
+        <f t="shared" si="70"/>
+        <v>161.42331989474062</v>
+      </c>
+      <c r="BQ15" s="1">
+        <f t="shared" si="70"/>
+        <v>159.80908669579321</v>
+      </c>
+      <c r="BR15" s="1">
+        <f t="shared" si="70"/>
+        <v>158.21099582883528</v>
+      </c>
+      <c r="BS15" s="1">
+        <f t="shared" si="70"/>
+        <v>156.62888587054692</v>
+      </c>
+      <c r="BT15" s="1">
+        <f t="shared" si="70"/>
+        <v>155.06259701184146</v>
+      </c>
+      <c r="BU15" s="1">
+        <f t="shared" si="70"/>
+        <v>153.51197104172306</v>
+      </c>
+      <c r="BV15" s="1">
+        <f t="shared" si="70"/>
+        <v>151.97685133130582</v>
+      </c>
+      <c r="BW15" s="1">
+        <f t="shared" si="70"/>
+        <v>150.45708281799276</v>
+      </c>
+      <c r="BX15" s="1">
+        <f t="shared" si="70"/>
+        <v>148.95251198981282</v>
+      </c>
+      <c r="BY15" s="1">
+        <f t="shared" si="70"/>
+        <v>147.46298686991469</v>
+      </c>
+      <c r="BZ15" s="1">
+        <f t="shared" si="70"/>
+        <v>145.98835700121555</v>
+      </c>
+      <c r="CA15" s="1">
+        <f t="shared" si="70"/>
+        <v>144.52847343120339</v>
+      </c>
+      <c r="CB15" s="1">
+        <f t="shared" si="70"/>
+        <v>143.08318869689137</v>
+      </c>
+      <c r="CC15" s="1">
+        <f t="shared" si="70"/>
+        <v>141.65235680992245</v>
+      </c>
+      <c r="CD15" s="1">
+        <f t="shared" si="70"/>
+        <v>140.23583324182323</v>
+      </c>
+      <c r="CE15" s="1">
+        <f t="shared" si="70"/>
+        <v>138.833474909405</v>
+      </c>
+      <c r="CF15" s="1">
+        <f t="shared" si="70"/>
+        <v>137.44514016031096</v>
+      </c>
+      <c r="CG15" s="1">
+        <f t="shared" si="70"/>
+        <v>136.07068875870783</v>
+      </c>
+      <c r="CH15" s="1">
+        <f t="shared" si="70"/>
+        <v>134.70998187112076</v>
+      </c>
+      <c r="CI15" s="1">
+        <f t="shared" ref="CI15:DN15" si="71">CH15*(1+$BE$21)</f>
+        <v>133.36288205240956</v>
+      </c>
+      <c r="CJ15" s="1">
         <f t="shared" si="71"/>
-        <v>383.61272600078337</v>
-      </c>
-      <c r="AZ15" s="8">
+        <v>132.02925323188546</v>
+      </c>
+      <c r="CK15" s="1">
         <f t="shared" si="71"/>
-        <v>414.04363467570954</v>
-      </c>
-      <c r="BA15" s="8">
+        <v>130.7089606995666</v>
+      </c>
+      <c r="CL15" s="1">
         <f t="shared" si="71"/>
-        <v>445.30240756190062</v>
-      </c>
-      <c r="BB15" s="8">
+        <v>129.40187109257093</v>
+      </c>
+      <c r="CM15" s="1">
         <f t="shared" si="71"/>
-        <v>477.40761037466183</v>
-      </c>
-      <c r="BC15" s="1">
-        <f t="shared" ref="BC15:CH15" si="72">BB15*(1+$BE$21)</f>
-        <v>472.63353427091522</v>
-      </c>
-      <c r="BD15" s="1">
+        <v>128.10785238164522</v>
+      </c>
+      <c r="CN15" s="1">
+        <f t="shared" si="71"/>
+        <v>126.82677385782877</v>
+      </c>
+      <c r="CO15" s="1">
+        <f t="shared" si="71"/>
+        <v>125.55850611925048</v>
+      </c>
+      <c r="CP15" s="1">
+        <f t="shared" si="71"/>
+        <v>124.30292105805798</v>
+      </c>
+      <c r="CQ15" s="1">
+        <f t="shared" si="71"/>
+        <v>123.05989184747739</v>
+      </c>
+      <c r="CR15" s="1">
+        <f t="shared" si="71"/>
+        <v>121.82929292900262</v>
+      </c>
+      <c r="CS15" s="1">
+        <f t="shared" si="71"/>
+        <v>120.61099999971259</v>
+      </c>
+      <c r="CT15" s="1">
+        <f t="shared" si="71"/>
+        <v>119.40488999971546</v>
+      </c>
+      <c r="CU15" s="1">
+        <f t="shared" si="71"/>
+        <v>118.21084109971831</v>
+      </c>
+      <c r="CV15" s="1">
+        <f t="shared" si="71"/>
+        <v>117.02873268872112</v>
+      </c>
+      <c r="CW15" s="1">
+        <f t="shared" si="71"/>
+        <v>115.85844536183392</v>
+      </c>
+      <c r="CX15" s="1">
+        <f t="shared" si="71"/>
+        <v>114.69986090821557</v>
+      </c>
+      <c r="CY15" s="1">
+        <f t="shared" si="71"/>
+        <v>113.55286229913341</v>
+      </c>
+      <c r="CZ15" s="1">
+        <f t="shared" si="71"/>
+        <v>112.41733367614208</v>
+      </c>
+      <c r="DA15" s="1">
+        <f t="shared" si="71"/>
+        <v>111.29316033938066</v>
+      </c>
+      <c r="DB15" s="1">
+        <f t="shared" si="71"/>
+        <v>110.18022873598686</v>
+      </c>
+      <c r="DC15" s="1">
+        <f t="shared" si="71"/>
+        <v>109.07842644862698</v>
+      </c>
+      <c r="DD15" s="1">
+        <f t="shared" si="71"/>
+        <v>107.98764218414071</v>
+      </c>
+      <c r="DE15" s="1">
+        <f t="shared" si="71"/>
+        <v>106.90776576229931</v>
+      </c>
+      <c r="DF15" s="1">
+        <f t="shared" si="71"/>
+        <v>105.83868810467631</v>
+      </c>
+      <c r="DG15" s="1">
+        <f t="shared" si="71"/>
+        <v>104.78030122362955</v>
+      </c>
+      <c r="DH15" s="1">
+        <f t="shared" si="71"/>
+        <v>103.73249821139325</v>
+      </c>
+      <c r="DI15" s="1">
+        <f t="shared" si="71"/>
+        <v>102.69517322927932</v>
+      </c>
+      <c r="DJ15" s="1">
+        <f t="shared" si="71"/>
+        <v>101.66822149698652</v>
+      </c>
+      <c r="DK15" s="1">
+        <f t="shared" si="71"/>
+        <v>100.65153928201666</v>
+      </c>
+      <c r="DL15" s="1">
+        <f t="shared" si="71"/>
+        <v>99.645023889196494</v>
+      </c>
+      <c r="DM15" s="1">
+        <f t="shared" si="71"/>
+        <v>98.648573650304527</v>
+      </c>
+      <c r="DN15" s="1">
+        <f t="shared" si="71"/>
+        <v>97.662087913801486</v>
+      </c>
+      <c r="DO15" s="1">
+        <f t="shared" ref="DO15:ET15" si="72">DN15*(1+$BE$21)</f>
+        <v>96.685467034663475</v>
+      </c>
+      <c r="DP15" s="1">
         <f t="shared" si="72"/>
-        <v>467.90719892820607</v>
-      </c>
-      <c r="BE15" s="1">
+        <v>95.71861236431684</v>
+      </c>
+      <c r="DQ15" s="1">
         <f t="shared" si="72"/>
-        <v>463.22812693892399</v>
-      </c>
-      <c r="BF15" s="1">
+        <v>94.761426240673671</v>
+      </c>
+      <c r="DR15" s="1">
         <f t="shared" si="72"/>
-        <v>458.59584566953475</v>
-      </c>
-      <c r="BG15" s="1">
+        <v>93.813811978266941</v>
+      </c>
+      <c r="DS15" s="1">
         <f t="shared" si="72"/>
-        <v>454.00988721283937</v>
-      </c>
-      <c r="BH15" s="1">
+        <v>92.875673858484276</v>
+      </c>
+      <c r="DT15" s="1">
         <f t="shared" si="72"/>
-        <v>449.46978834071098</v>
-      </c>
-      <c r="BI15" s="1">
+        <v>91.946917119899439</v>
+      </c>
+      <c r="DU15" s="1">
         <f t="shared" si="72"/>
-        <v>444.97509045730385</v>
-      </c>
-      <c r="BJ15" s="1">
+        <v>91.027447948700441</v>
+      </c>
+      <c r="DV15" s="1">
         <f t="shared" si="72"/>
-        <v>440.52533955273083</v>
-      </c>
-      <c r="BK15" s="1">
+        <v>90.117173469213441</v>
+      </c>
+      <c r="DW15" s="1">
         <f t="shared" si="72"/>
-        <v>436.1200861572035</v>
-      </c>
-      <c r="BL15" s="1">
+        <v>89.216001734521299</v>
+      </c>
+      <c r="DX15" s="1">
         <f t="shared" si="72"/>
-        <v>431.75888529563144</v>
-      </c>
-      <c r="BM15" s="1">
+        <v>88.32384171717608</v>
+      </c>
+      <c r="DY15" s="1">
         <f t="shared" si="72"/>
-        <v>427.44129644267514</v>
-      </c>
-      <c r="BN15" s="1">
+        <v>87.440603300004312</v>
+      </c>
+      <c r="DZ15" s="1">
         <f t="shared" si="72"/>
-        <v>423.16688347824839</v>
-      </c>
-      <c r="BO15" s="1">
+        <v>86.56619726700427</v>
+      </c>
+      <c r="EA15" s="1">
         <f t="shared" si="72"/>
-        <v>418.93521464346588</v>
-      </c>
-      <c r="BP15" s="1">
+        <v>85.70053529433423</v>
+      </c>
+      <c r="EB15" s="1">
         <f t="shared" si="72"/>
-        <v>414.74586249703123</v>
-      </c>
-      <c r="BQ15" s="1">
+        <v>84.843529941390884</v>
+      </c>
+      <c r="EC15" s="1">
         <f t="shared" si="72"/>
-        <v>410.59840387206089</v>
-      </c>
-      <c r="BR15" s="1">
+        <v>83.995094641976976</v>
+      </c>
+      <c r="ED15" s="1">
         <f t="shared" si="72"/>
-        <v>406.49241983334025</v>
-      </c>
-      <c r="BS15" s="1">
+        <v>83.1551436955572</v>
+      </c>
+      <c r="EE15" s="1">
         <f t="shared" si="72"/>
-        <v>402.42749563500684</v>
-      </c>
-      <c r="BT15" s="1">
+        <v>82.323592258601622</v>
+      </c>
+      <c r="EF15" s="1">
         <f t="shared" si="72"/>
-        <v>398.40322067865674</v>
-      </c>
-      <c r="BU15" s="1">
+        <v>81.500356336015599</v>
+      </c>
+      <c r="EG15" s="1">
         <f t="shared" si="72"/>
-        <v>394.41918847187014</v>
-      </c>
-      <c r="BV15" s="1">
+        <v>80.685352772655449</v>
+      </c>
+      <c r="EH15" s="1">
         <f t="shared" si="72"/>
-        <v>390.47499658715145</v>
-      </c>
-      <c r="BW15" s="1">
+        <v>79.878499244928889</v>
+      </c>
+      <c r="EI15" s="1">
         <f t="shared" si="72"/>
-        <v>386.57024662127992</v>
-      </c>
-      <c r="BX15" s="1">
+        <v>79.079714252479604</v>
+      </c>
+      <c r="EJ15" s="1">
         <f t="shared" si="72"/>
-        <v>382.70454415506714</v>
-      </c>
-      <c r="BY15" s="1">
+        <v>78.288917109954809</v>
+      </c>
+      <c r="EK15" s="1">
         <f t="shared" si="72"/>
-        <v>378.87749871351645</v>
-      </c>
-      <c r="BZ15" s="1">
+        <v>77.506027938855254</v>
+      </c>
+      <c r="EL15" s="1">
         <f t="shared" si="72"/>
-        <v>375.08872372638126</v>
-      </c>
-      <c r="CA15" s="1">
+        <v>76.7309676594667</v>
+      </c>
+      <c r="EM15" s="1">
         <f t="shared" si="72"/>
-        <v>371.33783648911742</v>
-      </c>
-      <c r="CB15" s="1">
+        <v>75.963657982872036</v>
+      </c>
+      <c r="EN15" s="1">
         <f t="shared" si="72"/>
-        <v>367.62445812422624</v>
-      </c>
-      <c r="CC15" s="1">
+        <v>75.204021403043313</v>
+      </c>
+      <c r="EO15" s="1">
         <f t="shared" si="72"/>
-        <v>363.94821354298398</v>
-      </c>
-      <c r="CD15" s="1">
+        <v>74.451981189012884</v>
+      </c>
+      <c r="EP15" s="1">
         <f t="shared" si="72"/>
-        <v>360.30873140755415</v>
-      </c>
-      <c r="CE15" s="1">
+        <v>73.707461377122755</v>
+      </c>
+      <c r="EQ15" s="1">
         <f t="shared" si="72"/>
-        <v>356.70564409347861</v>
-      </c>
-      <c r="CF15" s="1">
+        <v>72.970386763351527</v>
+      </c>
+      <c r="ER15" s="1">
         <f t="shared" si="72"/>
-        <v>353.13858765254383</v>
-      </c>
-      <c r="CG15" s="1">
+        <v>72.24068289571801</v>
+      </c>
+      <c r="ES15" s="1">
         <f t="shared" si="72"/>
-        <v>349.60720177601837</v>
-      </c>
-      <c r="CH15" s="1">
+        <v>71.518276066760833</v>
+      </c>
+      <c r="ET15" s="1">
         <f t="shared" si="72"/>
-        <v>346.11112975825819</v>
-      </c>
-      <c r="CI15" s="1">
-        <f t="shared" ref="CI15:DN15" si="73">CH15*(1+$BE$21)</f>
-        <v>342.6500184606756</v>
-      </c>
-      <c r="CJ15" s="1">
+        <v>70.803093306093231</v>
+      </c>
+      <c r="EU15" s="1">
+        <f t="shared" ref="EU15:FK15" si="73">ET15*(1+$BE$21)</f>
+        <v>70.095062373032292</v>
+      </c>
+      <c r="EV15" s="1">
         <f t="shared" si="73"/>
-        <v>339.22351827606883</v>
-      </c>
-      <c r="CK15" s="1">
+        <v>69.39411174930197</v>
+      </c>
+      <c r="EW15" s="1">
         <f t="shared" si="73"/>
-        <v>335.83128309330812</v>
-      </c>
-      <c r="CL15" s="1">
+        <v>68.700170631808945</v>
+      </c>
+      <c r="EX15" s="1">
         <f t="shared" si="73"/>
-        <v>332.47297026237504</v>
-      </c>
-      <c r="CM15" s="1">
+        <v>68.013168925490859</v>
+      </c>
+      <c r="EY15" s="1">
         <f t="shared" si="73"/>
-        <v>329.14824055975129</v>
-      </c>
-      <c r="CN15" s="1">
+        <v>67.333037236235953</v>
+      </c>
+      <c r="EZ15" s="1">
         <f t="shared" si="73"/>
-        <v>325.85675815415379</v>
-      </c>
-      <c r="CO15" s="1">
+        <v>66.659706863873595</v>
+      </c>
+      <c r="FA15" s="1">
         <f t="shared" si="73"/>
-        <v>322.59819057261228</v>
-      </c>
-      <c r="CP15" s="1">
+        <v>65.993109795234858</v>
+      </c>
+      <c r="FB15" s="1">
         <f t="shared" si="73"/>
-        <v>319.37220866688614</v>
-      </c>
-      <c r="CQ15" s="1">
+        <v>65.333178697282506</v>
+      </c>
+      <c r="FC15" s="1">
         <f t="shared" si="73"/>
-        <v>316.17848658021728</v>
-      </c>
-      <c r="CR15" s="1">
+        <v>64.679846910309678</v>
+      </c>
+      <c r="FD15" s="1">
         <f t="shared" si="73"/>
-        <v>313.01670171441509</v>
-      </c>
-      <c r="CS15" s="1">
+        <v>64.033048441206574</v>
+      </c>
+      <c r="FE15" s="1">
         <f t="shared" si="73"/>
-        <v>309.88653469727092</v>
-      </c>
-      <c r="CT15" s="1">
+        <v>63.392717956794506</v>
+      </c>
+      <c r="FF15" s="1">
         <f t="shared" si="73"/>
-        <v>306.78766935029819</v>
-      </c>
-      <c r="CU15" s="1">
+        <v>62.758790777226558</v>
+      </c>
+      <c r="FG15" s="1">
         <f t="shared" si="73"/>
-        <v>303.71979265679522</v>
-      </c>
-      <c r="CV15" s="1">
+        <v>62.131202869454292</v>
+      </c>
+      <c r="FH15" s="1">
         <f t="shared" si="73"/>
-        <v>300.68259473022727</v>
-      </c>
-      <c r="CW15" s="1">
+        <v>61.509890840759745</v>
+      </c>
+      <c r="FI15" s="1">
         <f t="shared" si="73"/>
-        <v>297.67576878292499</v>
-      </c>
-      <c r="CX15" s="1">
+        <v>60.894791932352149</v>
+      </c>
+      <c r="FJ15" s="1">
         <f t="shared" si="73"/>
-        <v>294.69901109509573</v>
-      </c>
-      <c r="CY15" s="1">
+        <v>60.28584401302863</v>
+      </c>
+      <c r="FK15" s="1">
         <f t="shared" si="73"/>
-        <v>291.75202098414479</v>
-      </c>
-      <c r="CZ15" s="1">
-        <f t="shared" si="73"/>
-        <v>288.83450077430336</v>
-      </c>
-      <c r="DA15" s="1">
-        <f t="shared" si="73"/>
-        <v>285.94615576656031</v>
-      </c>
-      <c r="DB15" s="1">
-        <f t="shared" si="73"/>
-        <v>283.0866942088947</v>
-      </c>
-      <c r="DC15" s="1">
-        <f t="shared" si="73"/>
-        <v>280.25582726680574</v>
-      </c>
-      <c r="DD15" s="1">
-        <f t="shared" si="73"/>
-        <v>277.45326899413766</v>
-      </c>
-      <c r="DE15" s="1">
-        <f t="shared" si="73"/>
-        <v>274.67873630419626</v>
-      </c>
-      <c r="DF15" s="1">
-        <f t="shared" si="73"/>
-        <v>271.9319489411543</v>
-      </c>
-      <c r="DG15" s="1">
-        <f t="shared" si="73"/>
-        <v>269.21262945174277</v>
-      </c>
-      <c r="DH15" s="1">
-        <f t="shared" si="73"/>
-        <v>266.52050315722533</v>
-      </c>
-      <c r="DI15" s="1">
-        <f t="shared" si="73"/>
-        <v>263.85529812565306</v>
-      </c>
-      <c r="DJ15" s="1">
-        <f t="shared" si="73"/>
-        <v>261.21674514439655</v>
-      </c>
-      <c r="DK15" s="1">
-        <f t="shared" si="73"/>
-        <v>258.6045776929526</v>
-      </c>
-      <c r="DL15" s="1">
-        <f t="shared" si="73"/>
-        <v>256.01853191602305</v>
-      </c>
-      <c r="DM15" s="1">
-        <f t="shared" si="73"/>
-        <v>253.45834659686281</v>
-      </c>
-      <c r="DN15" s="1">
-        <f t="shared" si="73"/>
-        <v>250.92376313089417</v>
-      </c>
-      <c r="DO15" s="1">
-        <f t="shared" ref="DO15:ET15" si="74">DN15*(1+$BE$21)</f>
-        <v>248.41452549958524</v>
-      </c>
-      <c r="DP15" s="1">
-        <f t="shared" si="74"/>
-        <v>245.93038024458937</v>
-      </c>
-      <c r="DQ15" s="1">
-        <f t="shared" si="74"/>
-        <v>243.47107644214347</v>
-      </c>
-      <c r="DR15" s="1">
-        <f t="shared" si="74"/>
-        <v>241.03636567772205</v>
-      </c>
-      <c r="DS15" s="1">
-        <f t="shared" si="74"/>
-        <v>238.62600202094481</v>
-      </c>
-      <c r="DT15" s="1">
-        <f t="shared" si="74"/>
-        <v>236.23974200073536</v>
-      </c>
-      <c r="DU15" s="1">
-        <f t="shared" si="74"/>
-        <v>233.87734458072799</v>
-      </c>
-      <c r="DV15" s="1">
-        <f t="shared" si="74"/>
-        <v>231.53857113492072</v>
-      </c>
-      <c r="DW15" s="1">
-        <f t="shared" si="74"/>
-        <v>229.22318542357149</v>
-      </c>
-      <c r="DX15" s="1">
-        <f t="shared" si="74"/>
-        <v>226.93095356933577</v>
-      </c>
-      <c r="DY15" s="1">
-        <f t="shared" si="74"/>
-        <v>224.6616440336424</v>
-      </c>
-      <c r="DZ15" s="1">
-        <f t="shared" si="74"/>
-        <v>222.41502759330598</v>
-      </c>
-      <c r="EA15" s="1">
-        <f t="shared" si="74"/>
-        <v>220.19087731737292</v>
-      </c>
-      <c r="EB15" s="1">
-        <f t="shared" si="74"/>
-        <v>217.9889685441992</v>
-      </c>
-      <c r="EC15" s="1">
-        <f t="shared" si="74"/>
-        <v>215.8090788587572</v>
-      </c>
-      <c r="ED15" s="1">
-        <f t="shared" si="74"/>
-        <v>213.65098807016963</v>
-      </c>
-      <c r="EE15" s="1">
-        <f t="shared" si="74"/>
-        <v>211.51447818946792</v>
-      </c>
-      <c r="EF15" s="1">
-        <f t="shared" si="74"/>
-        <v>209.39933340757324</v>
-      </c>
-      <c r="EG15" s="1">
-        <f t="shared" si="74"/>
-        <v>207.30534007349749</v>
-      </c>
-      <c r="EH15" s="1">
-        <f t="shared" si="74"/>
-        <v>205.23228667276251</v>
-      </c>
-      <c r="EI15" s="1">
-        <f t="shared" si="74"/>
-        <v>203.17996380603489</v>
-      </c>
-      <c r="EJ15" s="1">
-        <f t="shared" si="74"/>
-        <v>201.14816416797453</v>
-      </c>
-      <c r="EK15" s="1">
-        <f t="shared" si="74"/>
-        <v>199.13668252629478</v>
-      </c>
-      <c r="EL15" s="1">
-        <f t="shared" si="74"/>
-        <v>197.14531570103182</v>
-      </c>
-      <c r="EM15" s="1">
-        <f t="shared" si="74"/>
-        <v>195.17386254402149</v>
-      </c>
-      <c r="EN15" s="1">
-        <f t="shared" si="74"/>
-        <v>193.22212391858127</v>
-      </c>
-      <c r="EO15" s="1">
-        <f t="shared" si="74"/>
-        <v>191.28990267939545</v>
-      </c>
-      <c r="EP15" s="1">
-        <f t="shared" si="74"/>
-        <v>189.3770036526015</v>
-      </c>
-      <c r="EQ15" s="1">
-        <f t="shared" si="74"/>
-        <v>187.48323361607549</v>
-      </c>
-      <c r="ER15" s="1">
-        <f t="shared" si="74"/>
-        <v>185.60840127991474</v>
-      </c>
-      <c r="ES15" s="1">
-        <f t="shared" si="74"/>
-        <v>183.75231726711559</v>
-      </c>
-      <c r="ET15" s="1">
-        <f t="shared" si="74"/>
-        <v>181.91479409444443</v>
-      </c>
-      <c r="EU15" s="1">
-        <f t="shared" ref="EU15:FK15" si="75">ET15*(1+$BE$21)</f>
-        <v>180.09564615349998</v>
-      </c>
-      <c r="EV15" s="1">
-        <f t="shared" si="75"/>
-        <v>178.29468969196498</v>
-      </c>
-      <c r="EW15" s="1">
-        <f t="shared" si="75"/>
-        <v>176.51174279504534</v>
-      </c>
-      <c r="EX15" s="1">
-        <f t="shared" si="75"/>
-        <v>174.74662536709488</v>
-      </c>
-      <c r="EY15" s="1">
-        <f t="shared" si="75"/>
-        <v>172.99915911342393</v>
-      </c>
-      <c r="EZ15" s="1">
-        <f t="shared" si="75"/>
-        <v>171.26916752228968</v>
-      </c>
-      <c r="FA15" s="1">
-        <f t="shared" si="75"/>
-        <v>169.55647584706679</v>
-      </c>
-      <c r="FB15" s="1">
-        <f t="shared" si="75"/>
-        <v>167.86091108859611</v>
-      </c>
-      <c r="FC15" s="1">
-        <f t="shared" si="75"/>
-        <v>166.18230197771015</v>
-      </c>
-      <c r="FD15" s="1">
-        <f t="shared" si="75"/>
-        <v>164.52047895793305</v>
-      </c>
-      <c r="FE15" s="1">
-        <f t="shared" si="75"/>
-        <v>162.87527416835371</v>
-      </c>
-      <c r="FF15" s="1">
-        <f t="shared" si="75"/>
-        <v>161.24652142667017</v>
-      </c>
-      <c r="FG15" s="1">
-        <f t="shared" si="75"/>
-        <v>159.63405621240346</v>
-      </c>
-      <c r="FH15" s="1">
-        <f t="shared" si="75"/>
-        <v>158.03771565027944</v>
-      </c>
-      <c r="FI15" s="1">
-        <f t="shared" si="75"/>
-        <v>156.45733849377663</v>
-      </c>
-      <c r="FJ15" s="1">
-        <f t="shared" si="75"/>
-        <v>154.89276510883886</v>
-      </c>
-      <c r="FK15" s="1">
-        <f t="shared" si="75"/>
-        <v>153.34383745775048</v>
+        <v>59.682985572898346</v>
       </c>
     </row>
     <row r="16" spans="2:167" x14ac:dyDescent="0.3">
@@ -3929,47 +3925,47 @@
         <v>2</v>
       </c>
       <c r="C16" s="4">
-        <f t="shared" ref="C16:L16" si="76">1211.1+23.7+234.4</f>
+        <f t="shared" ref="C16:L16" si="74">1211.1+23.7+234.4</f>
         <v>1469.2</v>
       </c>
       <c r="D16" s="4">
-        <f t="shared" si="76"/>
+        <f t="shared" si="74"/>
         <v>1469.2</v>
       </c>
       <c r="E16" s="4">
-        <f t="shared" si="76"/>
+        <f t="shared" si="74"/>
         <v>1469.2</v>
       </c>
       <c r="F16" s="4">
-        <f t="shared" si="76"/>
+        <f t="shared" si="74"/>
         <v>1469.2</v>
       </c>
       <c r="G16" s="4">
-        <f t="shared" si="76"/>
+        <f t="shared" si="74"/>
         <v>1469.2</v>
       </c>
       <c r="H16" s="4">
-        <f t="shared" si="76"/>
+        <f t="shared" si="74"/>
         <v>1469.2</v>
       </c>
       <c r="I16" s="4">
-        <f t="shared" si="76"/>
+        <f t="shared" si="74"/>
         <v>1469.2</v>
       </c>
       <c r="J16" s="4">
-        <f t="shared" si="76"/>
+        <f t="shared" si="74"/>
         <v>1469.2</v>
       </c>
       <c r="K16" s="4">
-        <f t="shared" si="76"/>
+        <f t="shared" si="74"/>
         <v>1469.2</v>
       </c>
       <c r="L16" s="4">
-        <f t="shared" si="76"/>
+        <f t="shared" si="74"/>
         <v>1469.2</v>
       </c>
       <c r="M16" s="4">
-        <f t="shared" ref="M16" si="77">1211.1+23.7+234.4</f>
+        <f t="shared" ref="M16" si="75">1211.1+23.7+234.4</f>
         <v>1469.2</v>
       </c>
       <c r="N16" s="4">
@@ -4031,16 +4027,16 @@
         <v>1696.3</v>
       </c>
       <c r="AF16" s="4">
-        <f>1442.2+22.5+231.6</f>
-        <v>1696.3</v>
+        <f>1674.9</f>
+        <v>1674.9</v>
       </c>
       <c r="AG16" s="4">
-        <f>1442.2+22.5+231.6</f>
-        <v>1696.3</v>
+        <f>1674.9</f>
+        <v>1674.9</v>
       </c>
       <c r="AH16" s="4">
-        <f>1442.2+22.5+231.6</f>
-        <v>1696.3</v>
+        <f>1674.9</f>
+        <v>1674.9</v>
       </c>
       <c r="AI16" s="4"/>
       <c r="AK16" s="4">
@@ -4065,52 +4061,52 @@
         <v>1508</v>
       </c>
       <c r="AQ16" s="4">
-        <f t="shared" ref="AQ16:BB16" si="78">1442.2+22.5+231.6</f>
+        <f t="shared" ref="AQ16" si="76">1442.2+22.5+231.6</f>
         <v>1696.3</v>
       </c>
       <c r="AR16" s="4">
-        <f t="shared" si="78"/>
-        <v>1696.3</v>
+        <f t="shared" ref="AR16:BB16" si="77">1674.9</f>
+        <v>1674.9</v>
       </c>
       <c r="AS16" s="4">
-        <f t="shared" si="78"/>
-        <v>1696.3</v>
+        <f t="shared" si="77"/>
+        <v>1674.9</v>
       </c>
       <c r="AT16" s="4">
-        <f t="shared" si="78"/>
-        <v>1696.3</v>
+        <f t="shared" si="77"/>
+        <v>1674.9</v>
       </c>
       <c r="AU16" s="4">
-        <f t="shared" si="78"/>
-        <v>1696.3</v>
+        <f t="shared" si="77"/>
+        <v>1674.9</v>
       </c>
       <c r="AV16" s="4">
-        <f t="shared" si="78"/>
-        <v>1696.3</v>
+        <f t="shared" si="77"/>
+        <v>1674.9</v>
       </c>
       <c r="AW16" s="4">
-        <f t="shared" si="78"/>
-        <v>1696.3</v>
+        <f t="shared" si="77"/>
+        <v>1674.9</v>
       </c>
       <c r="AX16" s="4">
-        <f t="shared" si="78"/>
-        <v>1696.3</v>
+        <f t="shared" si="77"/>
+        <v>1674.9</v>
       </c>
       <c r="AY16" s="4">
-        <f t="shared" si="78"/>
-        <v>1696.3</v>
+        <f t="shared" si="77"/>
+        <v>1674.9</v>
       </c>
       <c r="AZ16" s="4">
-        <f t="shared" si="78"/>
-        <v>1696.3</v>
+        <f t="shared" si="77"/>
+        <v>1674.9</v>
       </c>
       <c r="BA16" s="4">
-        <f t="shared" si="78"/>
-        <v>1696.3</v>
+        <f t="shared" si="77"/>
+        <v>1674.9</v>
       </c>
       <c r="BB16" s="4">
-        <f t="shared" si="78"/>
-        <v>1696.3</v>
+        <f t="shared" si="77"/>
+        <v>1674.9</v>
       </c>
     </row>
     <row r="17" spans="2:57" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -4118,132 +4114,132 @@
         <v>33</v>
       </c>
       <c r="C17" s="7">
-        <f t="shared" ref="C17:L17" si="79">C15/C16</f>
+        <f t="shared" ref="C17:L17" si="78">C15/C16</f>
         <v>-0.26252382248842909</v>
       </c>
       <c r="D17" s="7">
+        <f t="shared" si="78"/>
+        <v>-0.24047100462836915</v>
+      </c>
+      <c r="E17" s="7">
+        <f t="shared" si="78"/>
+        <v>-0.22134494963245302</v>
+      </c>
+      <c r="F17" s="7">
+        <f t="shared" si="78"/>
+        <v>-0.13095562210726927</v>
+      </c>
+      <c r="G17" s="7">
+        <f t="shared" si="78"/>
+        <v>-0.21099918322896818</v>
+      </c>
+      <c r="H17" s="7">
+        <f t="shared" si="78"/>
+        <v>-0.17376803702695343</v>
+      </c>
+      <c r="I17" s="7">
+        <f t="shared" si="78"/>
+        <v>-0.15498230329430981</v>
+      </c>
+      <c r="J17" s="7">
+        <f t="shared" si="78"/>
+        <v>-0.16376259188674108</v>
+      </c>
+      <c r="K17" s="7">
+        <f t="shared" si="78"/>
+        <v>-0.20820854887013335</v>
+      </c>
+      <c r="L17" s="7">
+        <f t="shared" si="78"/>
+        <v>-0.22182139940103451</v>
+      </c>
+      <c r="M17" s="7">
+        <f t="shared" ref="M17:N17" si="79">M15/M16</f>
+        <v>-0.13537979852981213</v>
+      </c>
+      <c r="N17" s="7">
         <f t="shared" si="79"/>
-        <v>-0.24047100462836915</v>
-      </c>
-      <c r="E17" s="7">
-        <f t="shared" si="79"/>
-        <v>-0.22134494963245302</v>
-      </c>
-      <c r="F17" s="7">
-        <f t="shared" si="79"/>
-        <v>-0.13095562210726927</v>
-      </c>
-      <c r="G17" s="7">
-        <f t="shared" si="79"/>
-        <v>-0.21099918322896818</v>
-      </c>
-      <c r="H17" s="7">
-        <f t="shared" si="79"/>
-        <v>-0.17376803702695343</v>
-      </c>
-      <c r="I17" s="7">
-        <f t="shared" si="79"/>
-        <v>-0.15498230329430981</v>
-      </c>
-      <c r="J17" s="7">
-        <f t="shared" si="79"/>
-        <v>-0.16376259188674108</v>
-      </c>
-      <c r="K17" s="7">
-        <f t="shared" si="79"/>
-        <v>-0.20820854887013335</v>
-      </c>
-      <c r="L17" s="7">
-        <f t="shared" si="79"/>
-        <v>-0.22182139940103451</v>
-      </c>
-      <c r="M17" s="7">
-        <f t="shared" ref="M17:N17" si="80">M15/M16</f>
-        <v>-0.13537979852981213</v>
-      </c>
-      <c r="N17" s="7">
+        <v>-7.4887931034482783E-2</v>
+      </c>
+      <c r="O17" s="7">
+        <f t="shared" ref="O17:Q17" si="80">O15/O16</f>
+        <v>-0.19018567639257292</v>
+      </c>
+      <c r="P17" s="7">
         <f t="shared" si="80"/>
-        <v>-7.4887931034482783E-2</v>
-      </c>
-      <c r="O17" s="7">
-        <f t="shared" ref="O17:Q17" si="81">O15/O16</f>
-        <v>-0.19018567639257292</v>
-      </c>
-      <c r="P17" s="7">
+        <v>-0.1005305039787798</v>
+      </c>
+      <c r="Q17" s="7">
+        <f t="shared" si="80"/>
+        <v>-4.7679045092838199E-2</v>
+      </c>
+      <c r="R17" s="7">
+        <f t="shared" ref="R17:S17" si="81">R15/R16</f>
+        <v>1.4986737400530548E-2</v>
+      </c>
+      <c r="S17" s="7">
         <f t="shared" si="81"/>
-        <v>-0.1005305039787798</v>
-      </c>
-      <c r="Q17" s="7">
-        <f t="shared" si="81"/>
-        <v>-4.7679045092838199E-2</v>
-      </c>
-      <c r="R17" s="7">
-        <f t="shared" ref="R17:S17" si="82">R15/R16</f>
-        <v>1.4986737400530548E-2</v>
-      </c>
-      <c r="S17" s="7">
+        <v>-0.23852785145888589</v>
+      </c>
+      <c r="T17" s="7">
+        <f t="shared" ref="T17:U17" si="82">T15/T16</f>
+        <v>-0.27990716180371344</v>
+      </c>
+      <c r="U17" s="7">
         <f t="shared" si="82"/>
-        <v>-0.23852785145888589</v>
-      </c>
-      <c r="T17" s="7">
-        <f t="shared" ref="T17:U17" si="83">T15/T16</f>
-        <v>-0.27990716180371344</v>
-      </c>
-      <c r="U17" s="7">
-        <f t="shared" si="83"/>
         <v>-0.33388594164456226</v>
       </c>
       <c r="V17" s="7">
-        <f t="shared" ref="V17" si="84">V15/V16</f>
+        <f t="shared" ref="V17" si="83">V15/V16</f>
         <v>-0.19124668435013256</v>
       </c>
       <c r="W17" s="7">
-        <f t="shared" ref="W17" si="85">W15/W16</f>
+        <f t="shared" ref="W17" si="84">W15/W16</f>
         <v>-0.21790450928381963</v>
       </c>
       <c r="X17" s="7">
-        <f t="shared" ref="X17:Y17" si="86">X15/X16</f>
+        <f t="shared" ref="X17:Y17" si="85">X15/X16</f>
         <v>-0.25026525198938993</v>
       </c>
       <c r="Y17" s="7">
-        <f t="shared" si="86"/>
+        <f t="shared" si="85"/>
         <v>-0.24423076923076928</v>
       </c>
       <c r="Z17" s="7">
-        <f t="shared" ref="Z17" si="87">Z15/Z16</f>
+        <f t="shared" ref="Z17" si="86">Z15/Z16</f>
         <v>-0.16458885941644566</v>
       </c>
       <c r="AA17" s="7">
-        <f t="shared" ref="AA17" si="88">AA15/AA16</f>
+        <f t="shared" ref="AA17" si="87">AA15/AA16</f>
         <v>-0.2022546419098144</v>
       </c>
       <c r="AB17" s="7">
-        <f t="shared" ref="AB17:AD17" si="89">AB15/AB16</f>
+        <f t="shared" ref="AB17:AD17" si="88">AB15/AB16</f>
         <v>-0.14975292274316021</v>
       </c>
       <c r="AC17" s="7">
+        <f t="shared" si="88"/>
+        <v>-9.1461960410207516E-2</v>
+      </c>
+      <c r="AD17" s="7">
+        <f t="shared" si="88"/>
+        <v>5.4235689441725727E-3</v>
+      </c>
+      <c r="AE17" s="7">
+        <f t="shared" ref="AE17:AH17" si="89">AE15/AE16</f>
+        <v>-8.23557153805341E-2</v>
+      </c>
+      <c r="AF17" s="7">
         <f t="shared" si="89"/>
-        <v>-9.1461960410207516E-2</v>
-      </c>
-      <c r="AD17" s="7">
+        <v>-0.15678547973013304</v>
+      </c>
+      <c r="AG17" s="7">
         <f t="shared" si="89"/>
-        <v>5.4235689441725727E-3</v>
-      </c>
-      <c r="AE17" s="7">
-        <f t="shared" ref="AE17:AH17" si="90">AE15/AE16</f>
-        <v>-8.23557153805341E-2</v>
-      </c>
-      <c r="AF17" s="7">
-        <f t="shared" si="90"/>
-        <v>-7.2874716736426245E-2</v>
-      </c>
-      <c r="AG17" s="7">
-        <f t="shared" si="90"/>
-        <v>-3.84561545717148E-2</v>
+        <v>-8.2521643083169158E-2</v>
       </c>
       <c r="AH17" s="7">
-        <f t="shared" si="90"/>
-        <v>4.1868941225019198E-2</v>
+        <f t="shared" si="89"/>
+        <v>-1.1815540629291313E-2</v>
       </c>
       <c r="AI17" s="7"/>
       <c r="AK17" s="7">
@@ -4259,64 +4255,64 @@
         <v>-0.64227538796624029</v>
       </c>
       <c r="AN17" s="7">
-        <f t="shared" ref="AN17:AW17" si="91">AN15/AN16</f>
+        <f t="shared" ref="AN17:AW17" si="90">AN15/AN16</f>
         <v>-0.32340848806366046</v>
       </c>
       <c r="AO17" s="7">
+        <f t="shared" si="90"/>
+        <v>-1.0435676392572943</v>
+      </c>
+      <c r="AP17" s="7">
+        <f t="shared" si="90"/>
+        <v>-0.87698938992042441</v>
+      </c>
+      <c r="AQ17" s="7">
+        <f t="shared" si="90"/>
+        <v>-0.4113069622118728</v>
+      </c>
+      <c r="AR17" s="7">
+        <f t="shared" si="90"/>
+        <v>-0.33453062809719952</v>
+      </c>
+      <c r="AS17" s="7">
+        <f t="shared" si="90"/>
+        <v>-0.17746567603080754</v>
+      </c>
+      <c r="AT17" s="7">
+        <f t="shared" si="90"/>
+        <v>-0.12170675809453908</v>
+      </c>
+      <c r="AU17" s="7">
+        <f t="shared" si="90"/>
+        <v>-9.0432200211905164E-2</v>
+      </c>
+      <c r="AV17" s="7">
+        <f t="shared" si="90"/>
+        <v>-5.7889337237565293E-2</v>
+      </c>
+      <c r="AW17" s="7">
+        <f t="shared" si="90"/>
+        <v>-3.6774330577614485E-2</v>
+      </c>
+      <c r="AX17" s="7">
+        <f t="shared" ref="AX17:BB17" si="91">AX15/AX16</f>
+        <v>-9.5589660989310096E-3</v>
+      </c>
+      <c r="AY17" s="7">
         <f t="shared" si="91"/>
-        <v>-1.0435676392572943</v>
-      </c>
-      <c r="AP17" s="7">
+        <v>1.8832050931734665E-2</v>
+      </c>
+      <c r="AZ17" s="7">
         <f t="shared" si="91"/>
-        <v>-0.87698938992042441</v>
-      </c>
-      <c r="AQ17" s="7">
+        <v>4.8354827674312401E-2</v>
+      </c>
+      <c r="BA17" s="7">
         <f t="shared" si="91"/>
-        <v>-0.4113069622118728</v>
-      </c>
-      <c r="AR17" s="7">
+        <v>7.9044633847845769E-2</v>
+      </c>
+      <c r="BB17" s="7">
         <f t="shared" si="91"/>
-        <v>-0.15181764546365661</v>
-      </c>
-      <c r="AS17" s="7">
-        <f t="shared" si="91"/>
-        <v>-6.6469328491421285E-3</v>
-      </c>
-      <c r="AT17" s="7">
-        <f t="shared" si="91"/>
-        <v>7.827805849255931E-2</v>
-      </c>
-      <c r="AU17" s="7">
-        <f t="shared" si="91"/>
-        <v>0.12757992977960006</v>
-      </c>
-      <c r="AV17" s="7">
-        <f t="shared" si="91"/>
-        <v>0.16573748647051742</v>
-      </c>
-      <c r="AW17" s="7">
-        <f t="shared" si="91"/>
-        <v>0.19153879148535768</v>
-      </c>
-      <c r="AX17" s="7">
-        <f t="shared" ref="AX17:BB17" si="92">AX15/AX16</f>
-        <v>0.20868222491561414</v>
-      </c>
-      <c r="AY17" s="7">
-        <f t="shared" si="92"/>
-        <v>0.22614674644861368</v>
-      </c>
-      <c r="AZ17" s="7">
-        <f t="shared" si="92"/>
-        <v>0.24408632593038351</v>
-      </c>
-      <c r="BA17" s="7">
-        <f t="shared" si="92"/>
-        <v>0.26251394656717597</v>
-      </c>
-      <c r="BB17" s="7">
-        <f t="shared" si="92"/>
-        <v>0.281440553189095</v>
+        <v>0.11093910758182224</v>
       </c>
     </row>
     <row r="19" spans="2:57" x14ac:dyDescent="0.3">
@@ -4328,112 +4324,112 @@
         <v>0.388816644993498</v>
       </c>
       <c r="H19" s="9">
-        <f t="shared" ref="H19:N19" si="93">H3/D3-1</f>
+        <f t="shared" ref="H19:N19" si="92">H3/D3-1</f>
         <v>0.47922226458253903</v>
       </c>
       <c r="I19" s="9">
-        <f t="shared" si="93"/>
+        <f t="shared" si="92"/>
         <v>0.4988243197850184</v>
       </c>
       <c r="J19" s="9">
-        <f t="shared" si="93"/>
+        <f t="shared" si="92"/>
         <v>0.4385739933316235</v>
       </c>
       <c r="K19" s="9">
-        <f t="shared" si="93"/>
+        <f t="shared" si="92"/>
         <v>0.44350811485642949</v>
       </c>
       <c r="L19" s="9">
-        <f t="shared" si="93"/>
+        <f t="shared" si="92"/>
         <v>0.17061855670103099</v>
       </c>
       <c r="M19" s="9">
-        <f t="shared" si="93"/>
+        <f t="shared" si="92"/>
         <v>0.52106678619453173</v>
       </c>
       <c r="N19" s="9">
-        <f t="shared" si="93"/>
+        <f t="shared" si="92"/>
         <v>0.62471028703868781</v>
       </c>
       <c r="O19" s="9">
-        <f t="shared" ref="O19" si="94">O3/K3-1</f>
+        <f t="shared" ref="O19" si="93">O3/K3-1</f>
         <v>0.66400000000000015</v>
       </c>
       <c r="P19" s="9">
-        <f t="shared" ref="P19" si="95">P3/L3-1</f>
+        <f t="shared" ref="P19" si="94">P3/L3-1</f>
         <v>1.1622633201232939</v>
       </c>
       <c r="Q19" s="9">
-        <f t="shared" ref="Q19" si="96">Q3/M3-1</f>
+        <f t="shared" ref="Q19" si="95">Q3/M3-1</f>
         <v>0.57285987918078662</v>
       </c>
       <c r="R19" s="9">
-        <f t="shared" ref="R19" si="97">R3/N3-1</f>
+        <f t="shared" ref="R19" si="96">R3/N3-1</f>
         <v>0.42422912323054995</v>
       </c>
       <c r="S19" s="9">
-        <f t="shared" ref="S19" si="98">S3/O3-1</f>
+        <f t="shared" ref="S19" si="97">S3/O3-1</f>
         <v>0.3808471933471933</v>
       </c>
       <c r="T19" s="9">
-        <f t="shared" ref="T19" si="99">T3/P3-1</f>
+        <f t="shared" ref="T19" si="98">T3/P3-1</f>
         <v>0.1311475409836067</v>
       </c>
       <c r="U19" s="9">
-        <f t="shared" ref="U19" si="100">U3/Q3-1</f>
+        <f t="shared" ref="U19" si="99">U3/Q3-1</f>
         <v>5.7142857142857162E-2</v>
       </c>
       <c r="V19" s="9">
-        <f t="shared" ref="V19" si="101">V3/R3-1</f>
+        <f t="shared" ref="V19" si="100">V3/R3-1</f>
         <v>1.3868556899607754E-3</v>
       </c>
       <c r="W19" s="9">
-        <f t="shared" ref="W19" si="102">W3/S3-1</f>
+        <f t="shared" ref="W19" si="101">W3/S3-1</f>
         <v>-6.9728051190364182E-2</v>
       </c>
       <c r="X19" s="9">
-        <f t="shared" ref="X19" si="103">X3/T3-1</f>
+        <f t="shared" ref="X19" si="102">X3/T3-1</f>
         <v>-3.8887388603834783E-2</v>
       </c>
       <c r="Y19" s="9">
-        <f t="shared" ref="Y19" si="104">Y3/U3-1</f>
+        <f t="shared" ref="Y19" si="103">Y3/U3-1</f>
         <v>5.325653522374818E-2</v>
       </c>
       <c r="Z19" s="9">
-        <f t="shared" ref="Z19" si="105">Z3/V3-1</f>
+        <f t="shared" ref="Z19" si="104">Z3/V3-1</f>
         <v>4.7395552819881503E-2</v>
       </c>
       <c r="AA19" s="9">
-        <f t="shared" ref="AA19" si="106">AA3/W3-1</f>
+        <f t="shared" ref="AA19" si="105">AA3/W3-1</f>
         <v>0.20857778676916849</v>
       </c>
       <c r="AB19" s="9">
-        <f t="shared" ref="AB19" si="107">AB3/X3-1</f>
+        <f t="shared" ref="AB19" si="106">AB3/X3-1</f>
         <v>0.15837782148543589</v>
       </c>
       <c r="AC19" s="9">
-        <f t="shared" ref="AC19" si="108">AC3/Y3-1</f>
+        <f t="shared" ref="AC19" si="107">AC3/Y3-1</f>
         <v>0.15471983846542159</v>
       </c>
       <c r="AD19" s="9">
-        <f t="shared" ref="AD19" si="109">AD3/Z3-1</f>
+        <f t="shared" ref="AD19" si="108">AD3/Z3-1</f>
         <v>0.14398001909939029</v>
       </c>
       <c r="AE19" s="9">
-        <f t="shared" ref="AE19" si="110">AE3/AA3-1</f>
+        <f t="shared" ref="AE19" si="109">AE3/AA3-1</f>
         <v>0.1409440910612656</v>
       </c>
       <c r="AF19" s="9">
-        <f t="shared" ref="AF19" si="111">AF3/AB3-1</f>
-        <v>0.12000000000000011</v>
+        <f t="shared" ref="AF19" si="110">AF3/AB3-1</f>
+        <v>8.7402975420439954E-2</v>
       </c>
       <c r="AG19" s="9">
-        <f t="shared" ref="AG19" si="112">AG3/AC3-1</f>
-        <v>0.10000000000000009</v>
+        <f t="shared" ref="AG19" si="111">AG3/AC3-1</f>
+        <v>8.0000000000000071E-2</v>
       </c>
       <c r="AH19" s="9">
-        <f t="shared" ref="AH19" si="113">AH3/AD3-1</f>
-        <v>0.10000000000000009</v>
+        <f t="shared" ref="AH19" si="112">AH3/AD3-1</f>
+        <v>6.0000000000000053E-2</v>
       </c>
       <c r="AI19" s="9"/>
       <c r="AK19" s="9"/>
@@ -4446,64 +4442,64 @@
         <v>0.46120664529291733</v>
       </c>
       <c r="AN19" s="9">
-        <f t="shared" ref="AN19:AX19" si="114">AN3/AM3-1</f>
+        <f t="shared" ref="AN19:AX19" si="113">AN3/AM3-1</f>
         <v>0.64243826544859806</v>
       </c>
       <c r="AO19" s="9">
-        <f t="shared" si="114"/>
+        <f t="shared" si="113"/>
         <v>0.11772849821476283</v>
       </c>
       <c r="AP19" s="9">
-        <f t="shared" si="114"/>
+        <f t="shared" si="113"/>
         <v>9.561475944195319E-4</v>
       </c>
       <c r="AQ19" s="9">
-        <f t="shared" si="114"/>
+        <f t="shared" si="113"/>
         <v>0.16395293300334335</v>
       </c>
       <c r="AR19" s="9">
-        <f t="shared" si="114"/>
-        <v>0.11373820270824786</v>
+        <f t="shared" si="113"/>
+        <v>8.9479986570672132E-2</v>
       </c>
       <c r="AS19" s="9">
-        <f t="shared" si="114"/>
-        <v>8.0000000000000071E-2</v>
+        <f t="shared" si="113"/>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="AT19" s="9">
-        <f t="shared" si="114"/>
-        <v>6.0000000000000053E-2</v>
+        <f t="shared" si="113"/>
+        <v>4.0000000000000036E-2</v>
       </c>
       <c r="AU19" s="9">
-        <f t="shared" si="114"/>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="113"/>
+        <v>4.0000000000000036E-2</v>
       </c>
       <c r="AV19" s="9">
-        <f t="shared" si="114"/>
+        <f t="shared" si="113"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AW19" s="9">
-        <f t="shared" si="114"/>
+        <f t="shared" si="113"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AX19" s="9">
-        <f t="shared" si="114"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="113"/>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AY19" s="9">
-        <f t="shared" ref="AY19" si="115">AY3/AX3-1</f>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" ref="AY19" si="114">AY3/AX3-1</f>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AZ19" s="9">
-        <f t="shared" ref="AZ19" si="116">AZ3/AY3-1</f>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" ref="AZ19" si="115">AZ3/AY3-1</f>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="BA19" s="9">
-        <f t="shared" ref="BA19" si="117">BA3/AZ3-1</f>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" ref="BA19" si="116">BA3/AZ3-1</f>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="BB19" s="9">
-        <f t="shared" ref="BB19" si="118">BB3/BA3-1</f>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" ref="BB19" si="117">BB3/BA3-1</f>
+        <v>3.0000000000000027E-2</v>
       </c>
     </row>
     <row r="20" spans="2:57" x14ac:dyDescent="0.3">
@@ -4515,200 +4511,200 @@
         <v>0.14694408322496741</v>
       </c>
       <c r="D20" s="9">
-        <f t="shared" ref="D20:N20" si="119">D5/D3</f>
+        <f t="shared" ref="D20:N20" si="118">D5/D3</f>
         <v>0.26953869614944725</v>
       </c>
       <c r="E20" s="9">
+        <f t="shared" si="118"/>
+        <v>0.33624454148471616</v>
+      </c>
+      <c r="F20" s="9">
+        <f t="shared" si="118"/>
+        <v>0.45370607848166195</v>
+      </c>
+      <c r="G20" s="9">
+        <f t="shared" si="118"/>
+        <v>0.363920099875156</v>
+      </c>
+      <c r="H20" s="9">
+        <f t="shared" si="118"/>
+        <v>0.44458762886597936</v>
+      </c>
+      <c r="I20" s="9">
+        <f t="shared" si="118"/>
+        <v>0.5</v>
+      </c>
+      <c r="J20" s="9">
+        <f t="shared" si="118"/>
+        <v>0.54822606525227313</v>
+      </c>
+      <c r="K20" s="9">
+        <f t="shared" si="118"/>
+        <v>0.45210810810810809</v>
+      </c>
+      <c r="L20" s="9">
+        <f t="shared" si="118"/>
+        <v>0.4484808454425363</v>
+      </c>
+      <c r="M20" s="9">
+        <f t="shared" si="118"/>
+        <v>0.56814498305584205</v>
+      </c>
+      <c r="N20" s="9">
+        <f t="shared" si="118"/>
+        <v>0.57697794359705912</v>
+      </c>
+      <c r="O20" s="9">
+        <f t="shared" ref="O20:R20" si="119">O5/O3</f>
+        <v>0.46387733887733884</v>
+      </c>
+      <c r="P20" s="9">
         <f t="shared" si="119"/>
-        <v>0.33624454148471616</v>
-      </c>
-      <c r="F20" s="9">
+        <v>0.54688931880663882</v>
+      </c>
+      <c r="Q20" s="9">
         <f t="shared" si="119"/>
-        <v>0.45370607848166195</v>
-      </c>
-      <c r="G20" s="9">
+        <v>0.58454332552693211</v>
+      </c>
+      <c r="R20" s="9">
         <f t="shared" si="119"/>
-        <v>0.363920099875156</v>
-      </c>
-      <c r="H20" s="9">
-        <f t="shared" si="119"/>
-        <v>0.44458762886597936</v>
-      </c>
-      <c r="I20" s="9">
-        <f t="shared" si="119"/>
-        <v>0.5</v>
-      </c>
-      <c r="J20" s="9">
-        <f t="shared" si="119"/>
-        <v>0.54822606525227313</v>
-      </c>
-      <c r="K20" s="9">
-        <f t="shared" si="119"/>
-        <v>0.45210810810810809</v>
-      </c>
-      <c r="L20" s="9">
-        <f t="shared" si="119"/>
-        <v>0.4484808454425363</v>
-      </c>
-      <c r="M20" s="9">
-        <f t="shared" si="119"/>
-        <v>0.56814498305584205</v>
-      </c>
-      <c r="N20" s="9">
-        <f t="shared" si="119"/>
-        <v>0.57697794359705912</v>
-      </c>
-      <c r="O20" s="9">
-        <f t="shared" ref="O20:R20" si="120">O5/O3</f>
-        <v>0.46387733887733884</v>
-      </c>
-      <c r="P20" s="9">
+        <v>0.65390245781647272</v>
+      </c>
+      <c r="S20" s="9">
+        <f t="shared" ref="S20:AD20" si="120">S5/S3</f>
+        <v>0.60393337724663598</v>
+      </c>
+      <c r="T20" s="9">
         <f t="shared" si="120"/>
-        <v>0.54688931880663882</v>
-      </c>
-      <c r="Q20" s="9">
+        <v>0.59816365109370784</v>
+      </c>
+      <c r="U20" s="9">
         <f t="shared" si="120"/>
-        <v>0.58454332552693211</v>
-      </c>
-      <c r="R20" s="9">
+        <v>0.58635356668143557</v>
+      </c>
+      <c r="V20" s="9">
         <f t="shared" si="120"/>
-        <v>0.65390245781647272</v>
-      </c>
-      <c r="S20" s="9">
-        <f t="shared" ref="S20:AD20" si="121">S5/S3</f>
-        <v>0.60393337724663598</v>
-      </c>
-      <c r="T20" s="9">
+        <v>0.62968377317842583</v>
+      </c>
+      <c r="W20" s="9">
+        <f t="shared" si="120"/>
+        <v>0.55492615820352009</v>
+      </c>
+      <c r="X20" s="9">
+        <f t="shared" si="120"/>
+        <v>0.53460709937248296</v>
+      </c>
+      <c r="Y20" s="9">
+        <f t="shared" si="120"/>
+        <v>0.53239104829210837</v>
+      </c>
+      <c r="Z20" s="9">
+        <f t="shared" si="120"/>
+        <v>0.54345111290678028</v>
+      </c>
+      <c r="AA20" s="9">
+        <f t="shared" si="120"/>
+        <v>0.51899899564780716</v>
+      </c>
+      <c r="AB20" s="9">
+        <f t="shared" si="120"/>
+        <v>0.5238518758085382</v>
+      </c>
+      <c r="AC20" s="9">
+        <f t="shared" si="120"/>
+        <v>0.53449908925318768</v>
+      </c>
+      <c r="AD20" s="9">
+        <f t="shared" si="120"/>
+        <v>0.56867655557696006</v>
+      </c>
+      <c r="AE20" s="9">
+        <f t="shared" ref="AE20:AH20" si="121">AE5/AE3</f>
+        <v>0.53080985915492962</v>
+      </c>
+      <c r="AF20" s="9">
         <f t="shared" si="121"/>
-        <v>0.59816365109370784</v>
-      </c>
-      <c r="U20" s="9">
+        <v>0.51423897687560416</v>
+      </c>
+      <c r="AG20" s="9">
         <f t="shared" si="121"/>
-        <v>0.58635356668143557</v>
-      </c>
-      <c r="V20" s="9">
+        <v>0.54</v>
+      </c>
+      <c r="AH20" s="9">
         <f t="shared" si="121"/>
-        <v>0.62968377317842583</v>
-      </c>
-      <c r="W20" s="9">
-        <f t="shared" si="121"/>
-        <v>0.55492615820352009</v>
-      </c>
-      <c r="X20" s="9">
-        <f t="shared" si="121"/>
-        <v>0.53460709937248296</v>
-      </c>
-      <c r="Y20" s="9">
-        <f t="shared" si="121"/>
-        <v>0.53239104829210837</v>
-      </c>
-      <c r="Z20" s="9">
-        <f t="shared" si="121"/>
-        <v>0.54345111290678028</v>
-      </c>
-      <c r="AA20" s="9">
-        <f t="shared" si="121"/>
-        <v>0.51899899564780716</v>
-      </c>
-      <c r="AB20" s="9">
-        <f t="shared" si="121"/>
-        <v>0.5238518758085382</v>
-      </c>
-      <c r="AC20" s="9">
-        <f t="shared" si="121"/>
-        <v>0.53449908925318768</v>
-      </c>
-      <c r="AD20" s="9">
-        <f t="shared" si="121"/>
-        <v>0.56867655557696006</v>
-      </c>
-      <c r="AE20" s="9">
-        <f t="shared" ref="AE20:AH20" si="122">AE5/AE3</f>
-        <v>0.53080985915492962</v>
-      </c>
-      <c r="AF20" s="9">
-        <f t="shared" si="122"/>
-        <v>0.54</v>
-      </c>
-      <c r="AG20" s="9">
-        <f t="shared" si="122"/>
-        <v>0.54</v>
-      </c>
-      <c r="AH20" s="9">
-        <f t="shared" si="122"/>
         <v>0.56999999999999995</v>
       </c>
       <c r="AI20" s="9"/>
       <c r="AK20" s="9">
-        <f t="shared" ref="AK20:AM20" si="123">AK5/AK3</f>
+        <f t="shared" ref="AK20:AM20" si="122">AK5/AK3</f>
         <v>0.32322547857021849</v>
       </c>
       <c r="AL20" s="9">
+        <f t="shared" si="122"/>
+        <v>0.47781987758670946</v>
+      </c>
+      <c r="AM20" s="9">
+        <f t="shared" si="122"/>
+        <v>0.52826425180516212</v>
+      </c>
+      <c r="AN20" s="9">
+        <f t="shared" ref="AN20:AW20" si="123">AN5/AN3</f>
+        <v>0.57487066138787013</v>
+      </c>
+      <c r="AO20" s="9">
         <f t="shared" si="123"/>
-        <v>0.47781987758670946</v>
-      </c>
-      <c r="AM20" s="9">
+        <v>0.60550219479334189</v>
+      </c>
+      <c r="AP20" s="9">
         <f t="shared" si="123"/>
-        <v>0.52826425180516212</v>
-      </c>
-      <c r="AN20" s="9">
-        <f t="shared" ref="AN20:AW20" si="124">AN5/AN3</f>
-        <v>0.57487066138787013</v>
-      </c>
-      <c r="AO20" s="9">
-        <f t="shared" si="124"/>
-        <v>0.60550219479334189</v>
-      </c>
-      <c r="AP20" s="9">
-        <f t="shared" si="124"/>
         <v>0.54100994312014239</v>
       </c>
       <c r="AQ20" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="123"/>
         <v>0.53851605923825863</v>
       </c>
       <c r="AR20" s="9">
-        <f t="shared" si="124"/>
-        <v>0.54650839463316891</v>
+        <f t="shared" si="123"/>
+        <v>0.54040200043210762</v>
       </c>
       <c r="AS20" s="9">
+        <f t="shared" si="123"/>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="AT20" s="9">
+        <f t="shared" si="123"/>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="AU20" s="9">
+        <f t="shared" si="123"/>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="AV20" s="9">
+        <f t="shared" si="123"/>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="AW20" s="9">
+        <f t="shared" si="123"/>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="AX20" s="9">
+        <f t="shared" ref="AX20:BB20" si="124">AX5/AX3</f>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="AY20" s="9">
         <f t="shared" si="124"/>
         <v>0.56000000000000005</v>
       </c>
-      <c r="AT20" s="9">
+      <c r="AZ20" s="9">
         <f t="shared" si="124"/>
         <v>0.56000000000000005</v>
       </c>
-      <c r="AU20" s="9">
+      <c r="BA20" s="9">
         <f t="shared" si="124"/>
         <v>0.56000000000000005</v>
       </c>
-      <c r="AV20" s="9">
+      <c r="BB20" s="9">
         <f t="shared" si="124"/>
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="AW20" s="9">
-        <f t="shared" si="124"/>
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="AX20" s="9">
-        <f t="shared" ref="AX20:BB20" si="125">AX5/AX3</f>
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="AY20" s="9">
-        <f t="shared" si="125"/>
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="AZ20" s="9">
-        <f t="shared" si="125"/>
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="BA20" s="9">
-        <f t="shared" si="125"/>
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="BB20" s="9">
-        <f t="shared" si="125"/>
         <v>0.56000000000000005</v>
       </c>
     </row>
@@ -4721,201 +4717,201 @@
         <v>-1.7013437364542698</v>
       </c>
       <c r="D21" s="9">
-        <f t="shared" ref="D21:N21" si="126">D9/D3</f>
+        <f t="shared" ref="D21:N21" si="125">D9/D3</f>
         <v>-1.3640869233701867</v>
       </c>
       <c r="E21" s="9">
+        <f t="shared" si="125"/>
+        <v>-1.0866644272757811</v>
+      </c>
+      <c r="F21" s="9">
+        <f t="shared" si="125"/>
+        <v>-0.49935880995126969</v>
+      </c>
+      <c r="G21" s="9">
+        <f t="shared" si="125"/>
+        <v>-0.98689138576779045</v>
+      </c>
+      <c r="H21" s="9">
+        <f t="shared" si="125"/>
+        <v>-0.78556701030927822</v>
+      </c>
+      <c r="I21" s="9">
+        <f t="shared" si="125"/>
+        <v>-0.51277454056476923</v>
+      </c>
+      <c r="J21" s="9">
+        <f t="shared" si="125"/>
+        <v>-0.45195221964699595</v>
+      </c>
+      <c r="K21" s="9">
+        <f t="shared" si="125"/>
+        <v>-0.61902702702702694</v>
+      </c>
+      <c r="L21" s="9">
+        <f t="shared" si="125"/>
+        <v>-0.68383971818582112</v>
+      </c>
+      <c r="M21" s="9">
+        <f t="shared" si="125"/>
+        <v>-0.24723736555179018</v>
+      </c>
+      <c r="N21" s="9">
+        <f t="shared" si="125"/>
+        <v>-0.10655108087347748</v>
+      </c>
+      <c r="O21" s="9">
+        <f t="shared" ref="O21:R21" si="126">O9/O3</f>
+        <v>-0.39449064449064453</v>
+      </c>
+      <c r="P21" s="9">
         <f t="shared" si="126"/>
-        <v>-1.0866644272757811</v>
-      </c>
-      <c r="F21" s="9">
+        <v>-0.19600855310049886</v>
+      </c>
+      <c r="Q21" s="9">
         <f t="shared" si="126"/>
-        <v>-0.49935880995126969</v>
-      </c>
-      <c r="G21" s="9">
+        <v>-0.16936768149882905</v>
+      </c>
+      <c r="R21" s="9">
         <f t="shared" si="126"/>
-        <v>-0.98689138576779045</v>
-      </c>
-      <c r="H21" s="9">
-        <f t="shared" si="126"/>
-        <v>-0.78556701030927822</v>
-      </c>
-      <c r="I21" s="9">
-        <f t="shared" si="126"/>
-        <v>-0.51277454056476923</v>
-      </c>
-      <c r="J21" s="9">
-        <f t="shared" si="126"/>
-        <v>-0.45195221964699595</v>
-      </c>
-      <c r="K21" s="9">
-        <f t="shared" si="126"/>
-        <v>-0.61902702702702694</v>
-      </c>
-      <c r="L21" s="9">
-        <f t="shared" si="126"/>
-        <v>-0.68383971818582112</v>
-      </c>
-      <c r="M21" s="9">
-        <f t="shared" si="126"/>
-        <v>-0.24723736555179018</v>
-      </c>
-      <c r="N21" s="9">
-        <f t="shared" si="126"/>
-        <v>-0.10655108087347748</v>
-      </c>
-      <c r="O21" s="9">
-        <f t="shared" ref="O21:R21" si="127">O9/O3</f>
-        <v>-0.39449064449064453</v>
-      </c>
-      <c r="P21" s="9">
+        <v>-1.9338932121118681E-2</v>
+      </c>
+      <c r="S21" s="9">
+        <f t="shared" ref="S21:AD21" si="127">S9/S3</f>
+        <v>-0.25557542109720521</v>
+      </c>
+      <c r="T21" s="9">
         <f t="shared" si="127"/>
-        <v>-0.19600855310049886</v>
-      </c>
-      <c r="Q21" s="9">
+        <v>-0.36096858403096577</v>
+      </c>
+      <c r="U21" s="9">
         <f t="shared" si="127"/>
-        <v>-0.16936768149882905</v>
-      </c>
-      <c r="R21" s="9">
+        <v>-0.38573327425786436</v>
+      </c>
+      <c r="V21" s="9">
         <f t="shared" si="127"/>
-        <v>-1.9338932121118681E-2</v>
-      </c>
-      <c r="S21" s="9">
-        <f t="shared" ref="S21:AD21" si="128">S9/S3</f>
-        <v>-0.25557542109720521</v>
-      </c>
-      <c r="T21" s="9">
+        <v>-0.22128183426944673</v>
+      </c>
+      <c r="W21" s="9">
+        <f t="shared" si="127"/>
+        <v>-0.36941128869107825</v>
+      </c>
+      <c r="X21" s="9">
+        <f t="shared" si="127"/>
+        <v>-0.37875807811182916</v>
+      </c>
+      <c r="Y21" s="9">
+        <f t="shared" si="127"/>
+        <v>-0.31987211845869096</v>
+      </c>
+      <c r="Z21" s="9">
+        <f t="shared" si="127"/>
+        <v>-0.18269301403070598</v>
+      </c>
+      <c r="AA21" s="9">
+        <f t="shared" si="127"/>
+        <v>-0.27887512554402422</v>
+      </c>
+      <c r="AB21" s="9">
+        <f t="shared" si="127"/>
+        <v>-0.2052878395860285</v>
+      </c>
+      <c r="AC21" s="9">
+        <f t="shared" si="127"/>
+        <v>-0.12626593806921677</v>
+      </c>
+      <c r="AD21" s="9">
+        <f t="shared" si="127"/>
+        <v>-1.7209272458742739E-2</v>
+      </c>
+      <c r="AE21" s="9">
+        <f t="shared" ref="AE21:AH21" si="128">AE9/AE3</f>
+        <v>-0.14231220657276994</v>
+      </c>
+      <c r="AF21" s="9">
         <f t="shared" si="128"/>
-        <v>-0.36096858403096577</v>
-      </c>
-      <c r="U21" s="9">
+        <v>-0.19309985872555566</v>
+      </c>
+      <c r="AG21" s="9">
         <f t="shared" si="128"/>
-        <v>-0.38573327425786436</v>
-      </c>
-      <c r="V21" s="9">
+        <v>-0.12033663900694865</v>
+      </c>
+      <c r="AH21" s="9">
         <f t="shared" si="128"/>
-        <v>-0.22128183426944673</v>
-      </c>
-      <c r="W21" s="9">
-        <f t="shared" si="128"/>
-        <v>-0.36941128869107825</v>
-      </c>
-      <c r="X21" s="9">
-        <f t="shared" si="128"/>
-        <v>-0.37875807811182916</v>
-      </c>
-      <c r="Y21" s="9">
-        <f t="shared" si="128"/>
-        <v>-0.31987211845869096</v>
-      </c>
-      <c r="Z21" s="9">
-        <f t="shared" si="128"/>
-        <v>-0.18269301403070598</v>
-      </c>
-      <c r="AA21" s="9">
-        <f t="shared" si="128"/>
-        <v>-0.27887512554402422</v>
-      </c>
-      <c r="AB21" s="9">
-        <f t="shared" si="128"/>
-        <v>-0.2052878395860285</v>
-      </c>
-      <c r="AC21" s="9">
-        <f t="shared" si="128"/>
-        <v>-0.12626593806921677</v>
-      </c>
-      <c r="AD21" s="9">
-        <f t="shared" si="128"/>
-        <v>-1.7209272458742739E-2</v>
-      </c>
-      <c r="AE21" s="9">
-        <f t="shared" ref="AE21:AH21" si="129">AE9/AE3</f>
-        <v>-0.14231220657276994</v>
-      </c>
-      <c r="AF21" s="9">
-        <f t="shared" si="129"/>
-        <v>-0.11621910229162803</v>
-      </c>
-      <c r="AG21" s="9">
-        <f t="shared" si="129"/>
-        <v>-6.7263785394932801E-2</v>
-      </c>
-      <c r="AH21" s="9">
-        <f t="shared" si="129"/>
-        <v>2.4386204561508008E-2</v>
+        <v>-3.2602036180181246E-2</v>
       </c>
       <c r="AI21" s="9"/>
       <c r="AK21" s="9">
-        <f t="shared" ref="AK21:AM21" si="130">AK9/AK3</f>
+        <f t="shared" ref="AK21:AM21" si="129">AK9/AK3</f>
         <v>-1.0744536676266305</v>
       </c>
       <c r="AL21" s="9">
+        <f t="shared" si="129"/>
+        <v>-0.64313611192072284</v>
+      </c>
+      <c r="AM21" s="9">
+        <f t="shared" si="129"/>
+        <v>-0.34379861969920622</v>
+      </c>
+      <c r="AN21" s="9">
+        <f t="shared" ref="AN21:AW21" si="130">AN9/AN3</f>
+        <v>-0.17050836754025889</v>
+      </c>
+      <c r="AO21" s="9">
         <f t="shared" si="130"/>
-        <v>-0.64313611192072284</v>
-      </c>
-      <c r="AM21" s="9">
+        <v>-0.30325090182102643</v>
+      </c>
+      <c r="AP21" s="9">
         <f t="shared" si="130"/>
-        <v>-0.34379861969920622</v>
-      </c>
-      <c r="AN21" s="9">
-        <f t="shared" ref="AN21:AW21" si="131">AN9/AN3</f>
-        <v>-0.17050836754025889</v>
-      </c>
-      <c r="AO21" s="9">
+        <v>-0.30361252225261603</v>
+      </c>
+      <c r="AQ21" s="9">
+        <f t="shared" si="130"/>
+        <v>-0.14682732122206885</v>
+      </c>
+      <c r="AR21" s="9">
+        <f t="shared" si="130"/>
+        <v>-0.11742445050947253</v>
+      </c>
+      <c r="AS21" s="9">
+        <f t="shared" si="130"/>
+        <v>-7.2797766299583816E-2</v>
+      </c>
+      <c r="AT21" s="9">
+        <f t="shared" si="130"/>
+        <v>-5.2689306069375053E-2</v>
+      </c>
+      <c r="AU21" s="9">
+        <f t="shared" si="130"/>
+        <v>-4.1236114354012823E-2</v>
+      </c>
+      <c r="AV21" s="9">
+        <f t="shared" si="130"/>
+        <v>-3.0082434829439498E-2</v>
+      </c>
+      <c r="AW21" s="9">
+        <f t="shared" si="130"/>
+        <v>-2.3290320579171658E-2</v>
+      </c>
+      <c r="AX21" s="9">
+        <f t="shared" ref="AX21:BB21" si="131">AX9/AX3</f>
+        <v>-1.5071091053362384E-2</v>
+      </c>
+      <c r="AY21" s="9">
         <f t="shared" si="131"/>
-        <v>-0.30325090182102643</v>
-      </c>
-      <c r="AP21" s="9">
+        <v>-7.0114582173748724E-3</v>
+      </c>
+      <c r="AZ21" s="9">
         <f t="shared" si="131"/>
-        <v>-0.30361252225261603</v>
-      </c>
-      <c r="AQ21" s="9">
+        <v>8.9167689364214942E-4</v>
+      </c>
+      <c r="BA21" s="9">
         <f t="shared" si="131"/>
-        <v>-0.14682732122206885</v>
-      </c>
-      <c r="AR21" s="9">
+        <v>8.6413530704647096E-3</v>
+      </c>
+      <c r="BB21" s="9">
         <f t="shared" si="131"/>
-        <v>-6.9461086187758814E-2</v>
-      </c>
-      <c r="AS21" s="9">
-        <f t="shared" si="131"/>
-        <v>-1.8774101164620537E-2</v>
-      </c>
-      <c r="AT21" s="9">
-        <f t="shared" si="131"/>
-        <v>7.6449391752707856E-3</v>
-      </c>
-      <c r="AU21" s="9">
-        <f t="shared" si="131"/>
-        <v>2.1187684544117395E-2</v>
-      </c>
-      <c r="AV21" s="9">
-        <f t="shared" si="131"/>
-        <v>3.073785097749282E-2</v>
-      </c>
-      <c r="AW21" s="9">
-        <f t="shared" si="131"/>
-        <v>3.6544247914799516E-2</v>
-      </c>
-      <c r="AX21" s="9">
-        <f t="shared" ref="AX21:BB21" si="132">AX9/AX3</f>
-        <v>4.0107539601909235E-2</v>
-      </c>
-      <c r="AY21" s="9">
-        <f t="shared" si="132"/>
-        <v>4.363589705679255E-2</v>
-      </c>
-      <c r="AZ21" s="9">
-        <f t="shared" si="132"/>
-        <v>4.7129662771922001E-2</v>
-      </c>
-      <c r="BA21" s="9">
-        <f t="shared" si="132"/>
-        <v>5.0589175882001229E-2</v>
-      </c>
-      <c r="BB21" s="9">
-        <f t="shared" si="132"/>
-        <v>5.4014772196883491E-2</v>
+        <v>1.6240550098222704E-2</v>
       </c>
       <c r="BD21" t="s">
         <v>40</v>
@@ -4933,185 +4929,185 @@
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
       <c r="G22" s="9">
-        <f t="shared" ref="G22:R22" si="133">G6/C6-1</f>
+        <f t="shared" ref="G22:R22" si="132">G6/C6-1</f>
         <v>7.5621890547263648E-2</v>
       </c>
       <c r="H22" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="132"/>
         <v>0.16240157480314954</v>
       </c>
       <c r="I22" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="132"/>
         <v>3.98034398034397E-2</v>
       </c>
       <c r="J22" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="132"/>
         <v>0.33515815085158152</v>
       </c>
       <c r="K22" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="132"/>
         <v>0.1036077705827938</v>
       </c>
       <c r="L22" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="132"/>
         <v>0.10457239627434367</v>
       </c>
       <c r="M22" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="132"/>
         <v>0.34026465028355402</v>
       </c>
       <c r="N22" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="132"/>
         <v>0.45056947608200448</v>
       </c>
       <c r="O22" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="132"/>
         <v>0.4610226320201174</v>
       </c>
       <c r="P22" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="132"/>
         <v>0.42085090072824838</v>
       </c>
       <c r="Q22" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="132"/>
         <v>0.45275035260930885</v>
       </c>
       <c r="R22" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="132"/>
         <v>0.3636934673366834</v>
       </c>
       <c r="S22" s="9">
-        <f t="shared" ref="S22" si="134">S6/O6-1</f>
+        <f t="shared" ref="S22" si="133">S6/O6-1</f>
         <v>0.30694205393000562</v>
       </c>
       <c r="T22" s="9">
-        <f t="shared" ref="T22" si="135">T6/P6-1</f>
+        <f t="shared" ref="T22" si="134">T6/P6-1</f>
         <v>0.36228756406797946</v>
       </c>
       <c r="U22" s="9">
-        <f t="shared" ref="U22" si="136">U6/Q6-1</f>
+        <f t="shared" ref="U22" si="135">U6/Q6-1</f>
         <v>0.36966019417475726</v>
       </c>
       <c r="V22" s="9">
-        <f t="shared" ref="V22" si="137">V6/R6-1</f>
+        <f t="shared" ref="V22" si="136">V6/R6-1</f>
         <v>0.34707508060801473</v>
       </c>
       <c r="W22" s="9">
-        <f t="shared" ref="W22" si="138">W6/S6-1</f>
+        <f t="shared" ref="W22" si="137">W6/S6-1</f>
         <v>-1.0974539069359412E-3</v>
       </c>
       <c r="X22" s="9">
-        <f t="shared" ref="X22" si="139">X6/T6-1</f>
+        <f t="shared" ref="X22" si="138">X6/T6-1</f>
         <v>-5.4059405940594107E-2</v>
       </c>
       <c r="Y22" s="9">
-        <f t="shared" ref="Y22" si="140">Y6/U6-1</f>
+        <f t="shared" ref="Y22" si="139">Y6/U6-1</f>
         <v>-0.12351586035796547</v>
       </c>
       <c r="Z22" s="9">
-        <f t="shared" ref="Z22" si="141">Z6/V6-1</f>
+        <f t="shared" ref="Z22" si="140">Z6/V6-1</f>
         <v>-0.17336296802872286</v>
       </c>
       <c r="AA22" s="9">
-        <f t="shared" ref="AA22" si="142">AA6/W6-1</f>
+        <f t="shared" ref="AA22" si="141">AA6/W6-1</f>
         <v>-1.1645792133597066E-2</v>
       </c>
       <c r="AB22" s="9">
-        <f t="shared" ref="AB22" si="143">AB6/X6-1</f>
+        <f t="shared" ref="AB22" si="142">AB6/X6-1</f>
         <v>-0.14967552857441913</v>
       </c>
       <c r="AC22" s="9">
-        <f t="shared" ref="AC22" si="144">AC6/Y6-1</f>
+        <f t="shared" ref="AC22" si="143">AC6/Y6-1</f>
         <v>-0.16538617064294381</v>
       </c>
       <c r="AD22" s="9">
-        <f t="shared" ref="AD22" si="145">AD6/Z6-1</f>
+        <f t="shared" ref="AD22" si="144">AD6/Z6-1</f>
         <v>-0.12533609100310239</v>
       </c>
       <c r="AE22" s="9">
-        <f t="shared" ref="AE22" si="146">AE6/AA6-1</f>
+        <f t="shared" ref="AE22" si="145">AE6/AA6-1</f>
         <v>-5.6914184081814145E-2</v>
       </c>
       <c r="AF22" s="9">
-        <f t="shared" ref="AF22" si="147">AF6/AB6-1</f>
-        <v>-2.0000000000000018E-2</v>
+        <f t="shared" ref="AF22" si="146">AF6/AB6-1</f>
+        <v>9.1334318069916431E-2</v>
       </c>
       <c r="AG22" s="9">
-        <f t="shared" ref="AG22" si="148">AG6/AC6-1</f>
-        <v>-2.0000000000000018E-2</v>
+        <f t="shared" ref="AG22" si="147">AG6/AC6-1</f>
+        <v>0.10000000000000009</v>
       </c>
       <c r="AH22" s="9">
-        <f t="shared" ref="AH22" si="149">AH6/AD6-1</f>
-        <v>-2.0000000000000018E-2</v>
+        <f t="shared" ref="AH22" si="148">AH6/AD6-1</f>
+        <v>0.10000000000000009</v>
       </c>
       <c r="AI22" s="9"/>
       <c r="AK22" s="9"/>
       <c r="AL22" s="9">
-        <f t="shared" ref="AL22:AX24" si="150">AL6/AK6-1</f>
+        <f t="shared" ref="AL22:AX24" si="149">AL6/AK6-1</f>
         <v>0.14428182877865559</v>
       </c>
       <c r="AM22" s="9">
-        <f t="shared" si="150"/>
+        <f t="shared" si="149"/>
         <v>0.24674589700056604</v>
       </c>
       <c r="AN22" s="9">
-        <f t="shared" si="150"/>
+        <f t="shared" si="149"/>
         <v>0.42124375851112128</v>
       </c>
       <c r="AO22" s="9">
-        <f t="shared" si="150"/>
+        <f t="shared" si="149"/>
         <v>0.34768444586394143</v>
       </c>
       <c r="AP22" s="9">
-        <f t="shared" si="150"/>
+        <f t="shared" si="149"/>
         <v>-9.4274338799886226E-2</v>
       </c>
       <c r="AQ22" s="9">
-        <f t="shared" si="150"/>
+        <f t="shared" si="149"/>
         <v>-0.11471034591030416</v>
       </c>
       <c r="AR22" s="9">
-        <f t="shared" si="150"/>
-        <v>-2.98149790151917E-2</v>
+        <f t="shared" si="149"/>
+        <v>5.6197907430395544E-2</v>
       </c>
       <c r="AS22" s="9">
-        <f t="shared" si="150"/>
+        <f t="shared" si="149"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AT22" s="9">
-        <f t="shared" si="150"/>
+        <f t="shared" si="149"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AU22" s="9">
-        <f t="shared" si="150"/>
+        <f t="shared" si="149"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AV22" s="9">
-        <f t="shared" si="150"/>
+        <f t="shared" si="149"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AW22" s="9">
-        <f t="shared" si="150"/>
+        <f t="shared" si="149"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AX22" s="9">
-        <f t="shared" si="150"/>
+        <f t="shared" si="149"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AY22" s="9">
-        <f t="shared" ref="AY22" si="151">AY6/AX6-1</f>
+        <f t="shared" ref="AY22" si="150">AY6/AX6-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AZ22" s="9">
-        <f t="shared" ref="AZ22" si="152">AZ6/AY6-1</f>
+        <f t="shared" ref="AZ22" si="151">AZ6/AY6-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BA22" s="9">
-        <f t="shared" ref="BA22" si="153">BA6/AZ6-1</f>
+        <f t="shared" ref="BA22" si="152">BA6/AZ6-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BB22" s="9">
-        <f t="shared" ref="BB22" si="154">BB6/BA6-1</f>
+        <f t="shared" ref="BB22" si="153">BB6/BA6-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BD22" t="s">
@@ -5130,208 +5126,208 @@
         <v>0.44256610316428263</v>
       </c>
       <c r="D23" s="9">
-        <f t="shared" ref="D23:N23" si="155">D7/D3</f>
+        <f t="shared" ref="D23:N23" si="154">D7/D3</f>
         <v>0.38772398017537169</v>
       </c>
       <c r="E23" s="9">
+        <f t="shared" si="154"/>
+        <v>0.32784682566341955</v>
+      </c>
+      <c r="F23" s="9">
+        <f t="shared" si="154"/>
+        <v>0.25519363939471662</v>
+      </c>
+      <c r="G23" s="9">
+        <f t="shared" si="154"/>
+        <v>0.30555555555555558</v>
+      </c>
+      <c r="H23" s="9">
+        <f t="shared" si="154"/>
+        <v>0.28737113402061853</v>
+      </c>
+      <c r="I23" s="9">
+        <f t="shared" si="154"/>
+        <v>0.27610936799641417</v>
+      </c>
+      <c r="J23" s="9">
+        <f t="shared" si="154"/>
+        <v>0.22463897307898023</v>
+      </c>
+      <c r="K23" s="9">
+        <f t="shared" si="154"/>
+        <v>0.26421621621621622</v>
+      </c>
+      <c r="L23" s="9">
+        <f t="shared" si="154"/>
+        <v>0.29084103918978421</v>
+      </c>
+      <c r="M23" s="9">
+        <f t="shared" si="154"/>
+        <v>0.21143362310299099</v>
+      </c>
+      <c r="N23" s="9">
+        <f t="shared" si="154"/>
+        <v>0.17293975639196751</v>
+      </c>
+      <c r="O23" s="9">
+        <f t="shared" ref="O23:R23" si="155">O7/O3</f>
+        <v>0.19529625779625781</v>
+      </c>
+      <c r="P23" s="9">
         <f t="shared" si="155"/>
-        <v>0.32784682566341955</v>
-      </c>
-      <c r="F23" s="9">
+        <v>0.18297525710212809</v>
+      </c>
+      <c r="Q23" s="9">
         <f t="shared" si="155"/>
-        <v>0.25519363939471662</v>
-      </c>
-      <c r="G23" s="9">
+        <v>0.20374707259953162</v>
+      </c>
+      <c r="R23" s="9">
         <f t="shared" si="155"/>
-        <v>0.30555555555555558</v>
-      </c>
-      <c r="H23" s="9">
-        <f t="shared" si="155"/>
-        <v>0.28737113402061853</v>
-      </c>
-      <c r="I23" s="9">
-        <f t="shared" si="155"/>
-        <v>0.27610936799641417</v>
-      </c>
-      <c r="J23" s="9">
-        <f t="shared" si="155"/>
-        <v>0.22463897307898023</v>
-      </c>
-      <c r="K23" s="9">
-        <f t="shared" si="155"/>
-        <v>0.26421621621621622</v>
-      </c>
-      <c r="L23" s="9">
-        <f t="shared" si="155"/>
-        <v>0.29084103918978421</v>
-      </c>
-      <c r="M23" s="9">
-        <f t="shared" si="155"/>
-        <v>0.21143362310299099</v>
-      </c>
-      <c r="N23" s="9">
-        <f t="shared" si="155"/>
-        <v>0.17293975639196751</v>
-      </c>
-      <c r="O23" s="9">
-        <f t="shared" ref="O23:R23" si="156">O7/O3</f>
-        <v>0.19529625779625781</v>
-      </c>
-      <c r="P23" s="9">
+        <v>0.18892056398798057</v>
+      </c>
+      <c r="S23" s="9">
+        <f t="shared" ref="S23:AD23" si="156">S7/S3</f>
+        <v>0.22762774066058153</v>
+      </c>
+      <c r="T23" s="9">
         <f t="shared" si="156"/>
-        <v>0.18297525710212809</v>
-      </c>
-      <c r="Q23" s="9">
+        <v>0.28031325951930863</v>
+      </c>
+      <c r="U23" s="9">
         <f t="shared" si="156"/>
-        <v>0.20374707259953162</v>
-      </c>
-      <c r="R23" s="9">
+        <v>0.23952148870181658</v>
+      </c>
+      <c r="V23" s="9">
         <f t="shared" si="156"/>
-        <v>0.18892056398798057</v>
-      </c>
-      <c r="S23" s="9">
-        <f t="shared" ref="S23:AD23" si="157">S7/S3</f>
-        <v>0.22762774066058153</v>
-      </c>
-      <c r="T23" s="9">
+        <v>0.22712933753943215</v>
+      </c>
+      <c r="W23" s="9">
+        <f t="shared" si="156"/>
+        <v>0.27149504349585268</v>
+      </c>
+      <c r="X23" s="9">
+        <f t="shared" si="156"/>
+        <v>0.26280790484218414</v>
+      </c>
+      <c r="Y23" s="9">
+        <f t="shared" si="156"/>
+        <v>0.25012619888944981</v>
+      </c>
+      <c r="Z23" s="9">
+        <f t="shared" si="156"/>
+        <v>0.2026004554469992</v>
+      </c>
+      <c r="AA23" s="9">
+        <f t="shared" si="156"/>
+        <v>0.23100100435219284</v>
+      </c>
+      <c r="AB23" s="9">
+        <f t="shared" si="156"/>
+        <v>0.21531371280724451</v>
+      </c>
+      <c r="AC23" s="9">
+        <f t="shared" si="156"/>
+        <v>0.19897996357012751</v>
+      </c>
+      <c r="AD23" s="9">
+        <f t="shared" si="156"/>
+        <v>0.15937841135298272</v>
+      </c>
+      <c r="AE23" s="9">
+        <f t="shared" ref="AE23:AH23" si="157">AE7/AE3</f>
+        <v>0.18926056338028169</v>
+      </c>
+      <c r="AF23" s="9">
         <f t="shared" si="157"/>
-        <v>0.28031325951930863</v>
-      </c>
-      <c r="U23" s="9">
+        <v>0.19176146925421961</v>
+      </c>
+      <c r="AG23" s="9">
         <f t="shared" si="157"/>
-        <v>0.23952148870181658</v>
-      </c>
-      <c r="V23" s="9">
+        <v>0.19</v>
+      </c>
+      <c r="AH23" s="9">
         <f t="shared" si="157"/>
-        <v>0.22712933753943215</v>
-      </c>
-      <c r="W23" s="9">
-        <f t="shared" si="157"/>
-        <v>0.27149504349585268</v>
-      </c>
-      <c r="X23" s="9">
-        <f t="shared" si="157"/>
-        <v>0.26280790484218414</v>
-      </c>
-      <c r="Y23" s="9">
-        <f t="shared" si="157"/>
-        <v>0.25012619888944981</v>
-      </c>
-      <c r="Z23" s="9">
-        <f t="shared" si="157"/>
-        <v>0.2026004554469992</v>
-      </c>
-      <c r="AA23" s="9">
-        <f t="shared" si="157"/>
-        <v>0.23100100435219284</v>
-      </c>
-      <c r="AB23" s="9">
-        <f t="shared" si="157"/>
-        <v>0.21531371280724451</v>
-      </c>
-      <c r="AC23" s="9">
-        <f t="shared" si="157"/>
-        <v>0.19897996357012751</v>
-      </c>
-      <c r="AD23" s="9">
-        <f t="shared" si="157"/>
-        <v>0.15937841135298272</v>
-      </c>
-      <c r="AE23" s="9">
-        <f t="shared" ref="AE23:AH23" si="158">AE7/AE3</f>
-        <v>0.18926056338028169</v>
-      </c>
-      <c r="AF23" s="9">
+        <v>0.16</v>
+      </c>
+      <c r="AI23" s="9"/>
+      <c r="AK23" s="9">
+        <f t="shared" ref="AK23:AW23" si="158">AK7/AK3</f>
+        <v>0.33957309842452993</v>
+      </c>
+      <c r="AL23" s="9">
         <f t="shared" si="158"/>
-        <v>0.19999999999999998</v>
-      </c>
-      <c r="AG23" s="9">
+        <v>0.26732730982220926</v>
+      </c>
+      <c r="AM23" s="9">
         <f t="shared" si="158"/>
-        <v>0.18999999999999997</v>
-      </c>
-      <c r="AH23" s="9">
+        <v>0.22156620257709339</v>
+      </c>
+      <c r="AN23" s="9">
+        <f t="shared" si="158"/>
+        <v>0.1925384372495203</v>
+      </c>
+      <c r="AO23" s="9">
+        <f t="shared" si="158"/>
+        <v>0.24312225650832281</v>
+      </c>
+      <c r="AP23" s="9">
+        <f t="shared" si="158"/>
+        <v>0.24360644348921018</v>
+      </c>
+      <c r="AQ23" s="9">
+        <f t="shared" si="158"/>
+        <v>0.19838101988286641</v>
+      </c>
+      <c r="AR23" s="9">
+        <f t="shared" si="158"/>
+        <v>0.181754836129535</v>
+      </c>
+      <c r="AS23" s="9">
+        <f t="shared" si="158"/>
+        <v>0.17</v>
+      </c>
+      <c r="AT23" s="9">
         <f t="shared" si="158"/>
         <v>0.16</v>
       </c>
-      <c r="AI23" s="9"/>
-      <c r="AK23" s="9">
-        <f t="shared" ref="AK23:AW23" si="159">AK7/AK3</f>
-        <v>0.33957309842452993</v>
-      </c>
-      <c r="AL23" s="9">
-        <f t="shared" si="159"/>
-        <v>0.26732730982220926</v>
-      </c>
-      <c r="AM23" s="9">
-        <f t="shared" si="159"/>
-        <v>0.22156620257709339</v>
-      </c>
-      <c r="AN23" s="9">
-        <f t="shared" si="159"/>
-        <v>0.1925384372495203</v>
-      </c>
-      <c r="AO23" s="9">
-        <f t="shared" si="159"/>
-        <v>0.24312225650832281</v>
-      </c>
-      <c r="AP23" s="9">
-        <f t="shared" si="159"/>
-        <v>0.24360644348921018</v>
-      </c>
-      <c r="AQ23" s="9">
-        <f t="shared" si="159"/>
-        <v>0.19838101988286641</v>
-      </c>
-      <c r="AR23" s="9">
-        <f t="shared" si="159"/>
-        <v>0.18354455288354296</v>
-      </c>
-      <c r="AS23" s="9">
-        <f t="shared" si="159"/>
-        <v>0.17</v>
-      </c>
-      <c r="AT23" s="9">
+      <c r="AU23" s="9">
+        <f t="shared" si="158"/>
+        <v>0.16</v>
+      </c>
+      <c r="AV23" s="9">
+        <f t="shared" si="158"/>
+        <v>0.16</v>
+      </c>
+      <c r="AW23" s="9">
+        <f t="shared" si="158"/>
+        <v>0.16000000000000003</v>
+      </c>
+      <c r="AX23" s="9">
+        <f t="shared" ref="AX23:BB23" si="159">AX7/AX3</f>
+        <v>0.16</v>
+      </c>
+      <c r="AY23" s="9">
         <f t="shared" si="159"/>
         <v>0.16</v>
       </c>
-      <c r="AU23" s="9">
+      <c r="AZ23" s="9">
         <f t="shared" si="159"/>
         <v>0.16</v>
       </c>
-      <c r="AV23" s="9">
+      <c r="BA23" s="9">
         <f t="shared" si="159"/>
         <v>0.16</v>
       </c>
-      <c r="AW23" s="9">
+      <c r="BB23" s="9">
         <f t="shared" si="159"/>
         <v>0.16</v>
       </c>
-      <c r="AX23" s="9">
-        <f t="shared" ref="AX23:BB23" si="160">AX7/AX3</f>
-        <v>0.16</v>
-      </c>
-      <c r="AY23" s="9">
-        <f t="shared" si="160"/>
-        <v>0.16</v>
-      </c>
-      <c r="AZ23" s="9">
-        <f t="shared" si="160"/>
-        <v>0.16</v>
-      </c>
-      <c r="BA23" s="9">
-        <f t="shared" si="160"/>
-        <v>0.16</v>
-      </c>
-      <c r="BB23" s="9">
-        <f t="shared" si="160"/>
-        <v>0.16</v>
-      </c>
       <c r="BD23" t="s">
         <v>42</v>
       </c>
       <c r="BE23" s="4">
         <f>NPV(BE22,AR15:FK15)</f>
-        <v>3696.5363909272369</v>
+        <v>-85.799747568796903</v>
       </c>
     </row>
     <row r="24" spans="2:57" x14ac:dyDescent="0.3">
@@ -5343,185 +5339,185 @@
       <c r="E24" s="9"/>
       <c r="F24" s="9"/>
       <c r="G24" s="9">
-        <f t="shared" ref="G24" si="161">G8/C8-1</f>
+        <f t="shared" ref="G24" si="160">G8/C8-1</f>
         <v>-3.7307380373073795E-2</v>
       </c>
       <c r="H24" s="9">
-        <f t="shared" ref="H24" si="162">H8/D8-1</f>
+        <f t="shared" ref="H24" si="161">H8/D8-1</f>
         <v>4.8543689320388328E-2</v>
       </c>
       <c r="I24" s="9">
-        <f t="shared" ref="I24" si="163">I8/E8-1</f>
+        <f t="shared" ref="I24" si="162">I8/E8-1</f>
         <v>-4.4081632653061309E-2</v>
       </c>
       <c r="J24" s="9">
-        <f t="shared" ref="J24" si="164">J8/F8-1</f>
+        <f t="shared" ref="J24" si="163">J8/F8-1</f>
         <v>1.0009285051067782</v>
       </c>
       <c r="K24" s="9">
-        <f t="shared" ref="K24" si="165">K8/G8-1</f>
+        <f t="shared" ref="K24" si="164">K8/G8-1</f>
         <v>0.13395113732097719</v>
       </c>
       <c r="L24" s="9">
-        <f t="shared" ref="L24" si="166">L8/H8-1</f>
+        <f t="shared" ref="L24" si="165">L8/H8-1</f>
         <v>-6.4043209876543217E-2</v>
       </c>
       <c r="M24" s="9">
-        <f t="shared" ref="M24" si="167">M8/I8-1</f>
+        <f t="shared" ref="M24" si="166">M8/I8-1</f>
         <v>7.8565328778821497E-2</v>
       </c>
       <c r="N24" s="9">
-        <f t="shared" ref="N24" si="168">N8/J8-1</f>
+        <f t="shared" ref="N24" si="167">N8/J8-1</f>
         <v>-0.31832946635730852</v>
       </c>
       <c r="O24" s="9">
-        <f t="shared" ref="O24" si="169">O8/K8-1</f>
+        <f t="shared" ref="O24" si="168">O8/K8-1</f>
         <v>0.20133729569093606</v>
       </c>
       <c r="P24" s="9">
-        <f t="shared" ref="P24" si="170">P8/L8-1</f>
+        <f t="shared" ref="P24" si="169">P8/L8-1</f>
         <v>0.47732893652102226</v>
       </c>
       <c r="Q24" s="9">
-        <f t="shared" ref="Q24" si="171">Q8/M8-1</f>
+        <f t="shared" ref="Q24" si="170">Q8/M8-1</f>
         <v>0.38796516231195577</v>
       </c>
       <c r="R24" s="9">
-        <f t="shared" ref="R24" si="172">R8/N8-1</f>
+        <f t="shared" ref="R24" si="171">R8/N8-1</f>
         <v>0.32334921715452691</v>
       </c>
       <c r="S24" s="9">
-        <f t="shared" ref="S24" si="173">S8/O8-1</f>
+        <f t="shared" ref="S24" si="172">S8/O8-1</f>
         <v>0.33518862090290669</v>
       </c>
       <c r="T24" s="9">
-        <f t="shared" ref="T24" si="174">T8/P8-1</f>
+        <f t="shared" ref="T24" si="173">T8/P8-1</f>
         <v>0.39006696428571441</v>
       </c>
       <c r="U24" s="9">
-        <f t="shared" ref="U24" si="175">U8/Q8-1</f>
+        <f t="shared" ref="U24" si="174">U8/Q8-1</f>
         <v>0.49686252139189935</v>
       </c>
       <c r="V24" s="9">
-        <f t="shared" ref="V24" si="176">V8/R8-1</f>
+        <f t="shared" ref="V24" si="175">V8/R8-1</f>
         <v>0.16203703703703698</v>
       </c>
       <c r="W24" s="9">
-        <f t="shared" ref="W24" si="177">W8/S8-1</f>
+        <f t="shared" ref="W24" si="176">W8/S8-1</f>
         <v>-0.11857341361741547</v>
       </c>
       <c r="X24" s="9">
-        <f t="shared" ref="X24" si="178">X8/T8-1</f>
+        <f t="shared" ref="X24" si="177">X8/T8-1</f>
         <v>-0.1292653552790044</v>
       </c>
       <c r="Y24" s="9">
-        <f t="shared" ref="Y24" si="179">Y8/U8-1</f>
+        <f t="shared" ref="Y24" si="178">Y8/U8-1</f>
         <v>-0.15739329268292679</v>
       </c>
       <c r="Z24" s="9">
-        <f t="shared" ref="Z24" si="180">Z8/V8-1</f>
+        <f t="shared" ref="Z24" si="179">Z8/V8-1</f>
         <v>1.4608233731739695E-2</v>
       </c>
       <c r="AA24" s="9">
-        <f t="shared" ref="AA24" si="181">AA8/W8-1</f>
+        <f t="shared" ref="AA24" si="180">AA8/W8-1</f>
         <v>0.19548081975827625</v>
       </c>
       <c r="AB24" s="9">
-        <f t="shared" ref="AB24" si="182">AB8/X8-1</f>
+        <f t="shared" ref="AB24" si="181">AB8/X8-1</f>
         <v>5.7169202397418184E-2</v>
       </c>
       <c r="AC24" s="9">
-        <f t="shared" ref="AC24" si="183">AC8/Y8-1</f>
+        <f t="shared" ref="AC24" si="182">AC8/Y8-1</f>
         <v>-4.5228403437358455E-4</v>
       </c>
       <c r="AD24" s="9">
-        <f t="shared" ref="AD24" si="184">AD8/Z8-1</f>
+        <f t="shared" ref="AD24" si="183">AD8/Z8-1</f>
         <v>5.2792321116928553E-2</v>
       </c>
       <c r="AE24" s="9">
-        <f t="shared" ref="AE24" si="185">AE8/AA8-1</f>
+        <f t="shared" ref="AE24" si="184">AE8/AA8-1</f>
         <v>3.4725274725274646E-2</v>
       </c>
       <c r="AF24" s="9">
-        <f t="shared" ref="AF24" si="186">AF8/AB8-1</f>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" ref="AF24" si="185">AF8/AB8-1</f>
+        <v>9.0710859136502231E-2</v>
       </c>
       <c r="AG24" s="9">
-        <f t="shared" ref="AG24" si="187">AG8/AC8-1</f>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" ref="AG24" si="186">AG8/AC8-1</f>
+        <v>0.10000000000000009</v>
       </c>
       <c r="AH24" s="9">
-        <f t="shared" ref="AH24" si="188">AH8/AD8-1</f>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" ref="AH24" si="187">AH8/AD8-1</f>
+        <v>9.9999999999999867E-2</v>
       </c>
       <c r="AI24" s="9"/>
       <c r="AK24" s="9"/>
       <c r="AL24" s="9">
-        <f t="shared" si="150"/>
+        <f t="shared" si="149"/>
         <v>0.2175644518968769</v>
       </c>
       <c r="AM24" s="9">
-        <f t="shared" si="150"/>
+        <f t="shared" si="149"/>
         <v>-8.9171974522292974E-2</v>
       </c>
       <c r="AN24" s="9">
-        <f t="shared" si="150"/>
+        <f t="shared" si="149"/>
         <v>0.343035343035343</v>
       </c>
       <c r="AO24" s="9">
-        <f t="shared" si="150"/>
+        <f t="shared" si="149"/>
         <v>0.34154235857022219</v>
       </c>
       <c r="AP24" s="9">
-        <f t="shared" si="150"/>
+        <f t="shared" si="149"/>
         <v>-0.10049302423161643</v>
       </c>
       <c r="AQ24" s="9">
-        <f t="shared" si="150"/>
+        <f t="shared" si="149"/>
         <v>7.1836734693877524E-2</v>
       </c>
       <c r="AR24" s="9">
-        <f t="shared" si="150"/>
-        <v>2.3644869981503946E-2</v>
+        <f t="shared" si="149"/>
+        <v>8.1525405287781627E-2</v>
       </c>
       <c r="AS24" s="9">
-        <f t="shared" si="150"/>
+        <f t="shared" si="149"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AT24" s="9">
-        <f t="shared" si="150"/>
+        <f t="shared" si="149"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AU24" s="9">
-        <f t="shared" si="150"/>
+        <f t="shared" si="149"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AV24" s="9">
-        <f t="shared" si="150"/>
+        <f t="shared" si="149"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AW24" s="9">
-        <f t="shared" si="150"/>
+        <f t="shared" si="149"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AX24" s="9">
-        <f t="shared" si="150"/>
+        <f t="shared" si="149"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AY24" s="9">
-        <f t="shared" ref="AY24" si="189">AY8/AX8-1</f>
+        <f t="shared" ref="AY24" si="188">AY8/AX8-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AZ24" s="9">
-        <f t="shared" ref="AZ24" si="190">AZ8/AY8-1</f>
+        <f t="shared" ref="AZ24" si="189">AZ8/AY8-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BA24" s="9">
-        <f t="shared" ref="BA24" si="191">BA8/AZ8-1</f>
+        <f t="shared" ref="BA24" si="190">BA8/AZ8-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BB24" s="9">
-        <f t="shared" ref="BB24" si="192">BB8/BA8-1</f>
+        <f t="shared" ref="BB24" si="191">BB8/BA8-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BD24" t="s">
@@ -5529,7 +5525,7 @@
       </c>
       <c r="BE24" s="4">
         <f>Main!D8</f>
-        <v>-406</v>
+        <v>-682.90000000000009</v>
       </c>
     </row>
     <row r="25" spans="2:57" x14ac:dyDescent="0.3">
@@ -5541,208 +5537,208 @@
         <v>-4.1655818797188236E-3</v>
       </c>
       <c r="D25" s="9">
-        <f t="shared" ref="D25:N25" si="193">D14/D13</f>
+        <f t="shared" ref="D25:N25" si="192">D14/D13</f>
         <v>-3.1232254400908582E-3</v>
       </c>
       <c r="E25" s="9">
+        <f t="shared" si="192"/>
+        <v>-6.1538461538461541E-4</v>
+      </c>
+      <c r="F25" s="9">
+        <f t="shared" si="192"/>
+        <v>-2.0833333333333333E-3</v>
+      </c>
+      <c r="G25" s="9">
+        <f t="shared" si="192"/>
+        <v>9.6680631646793396E-4</v>
+      </c>
+      <c r="H25" s="9">
+        <f t="shared" si="192"/>
+        <v>-4.3273013375295048E-3</v>
+      </c>
+      <c r="I25" s="9">
+        <f t="shared" si="192"/>
+        <v>5.6768558951965069E-3</v>
+      </c>
+      <c r="J25" s="9">
+        <f t="shared" si="192"/>
+        <v>-1.2484394506866415E-3</v>
+      </c>
+      <c r="K25" s="9">
+        <f t="shared" si="192"/>
+        <v>-2.2935779816513767E-3</v>
+      </c>
+      <c r="L25" s="9">
+        <f t="shared" si="192"/>
+        <v>3.0590394616090556E-3</v>
+      </c>
+      <c r="M25" s="9">
+        <f t="shared" si="192"/>
+        <v>0</v>
+      </c>
+      <c r="N25" s="9">
+        <f t="shared" si="192"/>
+        <v>-0.19086585610190757</v>
+      </c>
+      <c r="O25" s="9">
+        <f t="shared" ref="O25:R25" si="193">O14/O13</f>
+        <v>-4.905395935529082E-3</v>
+      </c>
+      <c r="P25" s="9">
         <f t="shared" si="193"/>
-        <v>-6.1538461538461541E-4</v>
-      </c>
-      <c r="F25" s="9">
+        <v>1.2377850162866454E-2</v>
+      </c>
+      <c r="Q25" s="9">
         <f t="shared" si="193"/>
-        <v>-2.0833333333333333E-3</v>
-      </c>
-      <c r="G25" s="9">
+        <v>-1.4104372355430182E-2</v>
+      </c>
+      <c r="R25" s="9">
         <f t="shared" si="193"/>
-        <v>9.6680631646793396E-4</v>
-      </c>
-      <c r="H25" s="9">
-        <f t="shared" si="193"/>
-        <v>-4.3273013375295048E-3</v>
-      </c>
-      <c r="I25" s="9">
-        <f t="shared" si="193"/>
-        <v>5.6768558951965069E-3</v>
-      </c>
-      <c r="J25" s="9">
-        <f t="shared" si="193"/>
-        <v>-1.2484394506866415E-3</v>
-      </c>
-      <c r="K25" s="9">
-        <f t="shared" si="193"/>
-        <v>-2.2935779816513767E-3</v>
-      </c>
-      <c r="L25" s="9">
-        <f t="shared" si="193"/>
-        <v>3.0590394616090556E-3</v>
-      </c>
-      <c r="M25" s="9">
-        <f t="shared" si="193"/>
-        <v>0</v>
-      </c>
-      <c r="N25" s="9">
-        <f t="shared" si="193"/>
-        <v>-0.19086585610190757</v>
-      </c>
-      <c r="O25" s="9">
-        <f t="shared" ref="O25:R25" si="194">O14/O13</f>
-        <v>-4.905395935529082E-3</v>
-      </c>
-      <c r="P25" s="9">
+        <v>0.36516853932584203</v>
+      </c>
+      <c r="S25" s="9">
+        <f t="shared" ref="S25:AD25" si="194">S14/S13</f>
+        <v>-2.4202733485193625E-2</v>
+      </c>
+      <c r="T25" s="9">
         <f t="shared" si="194"/>
-        <v>1.2377850162866454E-2</v>
-      </c>
-      <c r="Q25" s="9">
+        <v>-1.6863406408094441E-2</v>
+      </c>
+      <c r="U25" s="9">
         <f t="shared" si="194"/>
-        <v>-1.4104372355430182E-2</v>
-      </c>
-      <c r="R25" s="9">
+        <v>-1.8612178838761886E-2</v>
+      </c>
+      <c r="V25" s="9">
         <f t="shared" si="194"/>
-        <v>0.36516853932584203</v>
-      </c>
-      <c r="S25" s="9">
-        <f t="shared" ref="S25:AD25" si="195">S14/S13</f>
-        <v>-2.4202733485193625E-2</v>
-      </c>
-      <c r="T25" s="9">
+        <v>-1.4778325123152714E-2</v>
+      </c>
+      <c r="W25" s="9">
+        <f t="shared" si="194"/>
+        <v>-2.113113735239279E-2</v>
+      </c>
+      <c r="X25" s="9">
+        <f t="shared" si="194"/>
+        <v>-3.312346016972352E-2</v>
+      </c>
+      <c r="Y25" s="9">
+        <f t="shared" si="194"/>
+        <v>-1.5999999999999997E-2</v>
+      </c>
+      <c r="Z25" s="9">
+        <f t="shared" si="194"/>
+        <v>-1.3474887709269086E-2</v>
+      </c>
+      <c r="AA25" s="9">
+        <f t="shared" si="194"/>
+        <v>-2.3146595102314649E-2</v>
+      </c>
+      <c r="AB25" s="9">
+        <f t="shared" si="194"/>
+        <v>-2.1372790793259346E-2</v>
+      </c>
+      <c r="AC25" s="9">
+        <f t="shared" si="194"/>
+        <v>-5.7201929703652649E-2</v>
+      </c>
+      <c r="AD25" s="9">
+        <f t="shared" si="194"/>
+        <v>0.36111111111111277</v>
+      </c>
+      <c r="AE25" s="9">
+        <f t="shared" ref="AE25:AH25" si="195">AE14/AE13</f>
+        <v>-6.397562833206398E-2</v>
+      </c>
+      <c r="AF25" s="9">
         <f t="shared" si="195"/>
-        <v>-1.6863406408094441E-2</v>
-      </c>
-      <c r="U25" s="9">
+        <v>-3.0207924676343683E-2</v>
+      </c>
+      <c r="AG25" s="9">
         <f t="shared" si="195"/>
-        <v>-1.8612178838761886E-2</v>
-      </c>
-      <c r="V25" s="9">
+        <v>0.05</v>
+      </c>
+      <c r="AH25" s="9">
         <f t="shared" si="195"/>
-        <v>-1.4778325123152714E-2</v>
-      </c>
-      <c r="W25" s="9">
-        <f t="shared" si="195"/>
-        <v>-2.113113735239279E-2</v>
-      </c>
-      <c r="X25" s="9">
-        <f t="shared" si="195"/>
-        <v>-3.312346016972352E-2</v>
-      </c>
-      <c r="Y25" s="9">
-        <f t="shared" si="195"/>
-        <v>-1.5999999999999997E-2</v>
-      </c>
-      <c r="Z25" s="9">
-        <f t="shared" si="195"/>
-        <v>-1.3474887709269086E-2</v>
-      </c>
-      <c r="AA25" s="9">
-        <f t="shared" si="195"/>
-        <v>-2.3146595102314649E-2</v>
-      </c>
-      <c r="AB25" s="9">
-        <f t="shared" si="195"/>
-        <v>-2.1372790793259346E-2</v>
-      </c>
-      <c r="AC25" s="9">
-        <f t="shared" si="195"/>
-        <v>-5.7201929703652649E-2</v>
-      </c>
-      <c r="AD25" s="9">
-        <f t="shared" si="195"/>
-        <v>0.36111111111111277</v>
-      </c>
-      <c r="AE25" s="9">
-        <f t="shared" ref="AE25:AH25" si="196">AE14/AE13</f>
-        <v>-6.397562833206398E-2</v>
-      </c>
-      <c r="AF25" s="9">
-        <f t="shared" si="196"/>
-        <v>0.05</v>
-      </c>
-      <c r="AG25" s="9">
-        <f t="shared" si="196"/>
-        <v>0.05</v>
-      </c>
-      <c r="AH25" s="9">
-        <f t="shared" si="196"/>
         <v>0.05</v>
       </c>
       <c r="AI25" s="9"/>
       <c r="AK25" s="9">
-        <f t="shared" ref="AK25:AM25" si="197">AK14/AK13</f>
+        <f t="shared" ref="AK25:AM25" si="196">AK14/AK13</f>
         <v>-2.6330487512965773E-3</v>
       </c>
       <c r="AL25" s="9">
+        <f t="shared" si="196"/>
+        <v>1.9346101760495268E-4</v>
+      </c>
+      <c r="AM25" s="9">
+        <f t="shared" si="196"/>
+        <v>-1.9225971046551688E-2</v>
+      </c>
+      <c r="AN25" s="9">
+        <f t="shared" ref="AN25:AW25" si="197">AN14/AN13</f>
+        <v>-2.846900042176297E-2</v>
+      </c>
+      <c r="AO25" s="9">
         <f t="shared" si="197"/>
-        <v>1.9346101760495268E-4</v>
-      </c>
-      <c r="AM25" s="9">
+        <v>-1.8707923355774213E-2</v>
+      </c>
+      <c r="AP25" s="9">
         <f t="shared" si="197"/>
-        <v>-1.9225971046551688E-2</v>
-      </c>
-      <c r="AN25" s="9">
-        <f t="shared" ref="AN25:AW25" si="198">AN14/AN13</f>
-        <v>-2.846900042176297E-2</v>
-      </c>
-      <c r="AO25" s="9">
-        <f t="shared" si="198"/>
-        <v>-1.8707923355774213E-2</v>
-      </c>
-      <c r="AP25" s="9">
-        <f t="shared" si="198"/>
         <v>-2.1629972962533797E-2</v>
       </c>
       <c r="AQ25" s="9">
-        <f t="shared" si="198"/>
+        <f t="shared" si="197"/>
         <v>-3.8089570004463634E-2</v>
       </c>
       <c r="AR25" s="9">
-        <f t="shared" si="198"/>
-        <v>-8.6104808150840543E-3</v>
+        <f t="shared" si="197"/>
+        <v>-1.4088013094587371E-2</v>
       </c>
       <c r="AS25" s="9">
+        <f t="shared" si="197"/>
+        <v>0.2</v>
+      </c>
+      <c r="AT25" s="9">
+        <f t="shared" si="197"/>
+        <v>0.2</v>
+      </c>
+      <c r="AU25" s="9">
+        <f t="shared" si="197"/>
+        <v>0.2</v>
+      </c>
+      <c r="AV25" s="9">
+        <f t="shared" si="197"/>
+        <v>0.2</v>
+      </c>
+      <c r="AW25" s="9">
+        <f t="shared" si="197"/>
+        <v>0.2</v>
+      </c>
+      <c r="AX25" s="9">
+        <f t="shared" ref="AX25:BB25" si="198">AX14/AX13</f>
+        <v>0.2</v>
+      </c>
+      <c r="AY25" s="9">
         <f t="shared" si="198"/>
         <v>0.2</v>
       </c>
-      <c r="AT25" s="9">
+      <c r="AZ25" s="9">
         <f t="shared" si="198"/>
         <v>0.2</v>
       </c>
-      <c r="AU25" s="9">
+      <c r="BA25" s="9">
+        <f t="shared" si="198"/>
+        <v>0.20000000000000004</v>
+      </c>
+      <c r="BB25" s="9">
         <f t="shared" si="198"/>
         <v>0.2</v>
       </c>
-      <c r="AV25" s="9">
-        <f t="shared" si="198"/>
-        <v>0.2</v>
-      </c>
-      <c r="AW25" s="9">
-        <f t="shared" si="198"/>
-        <v>0.2</v>
-      </c>
-      <c r="AX25" s="9">
-        <f t="shared" ref="AX25:BB25" si="199">AX14/AX13</f>
-        <v>0.2</v>
-      </c>
-      <c r="AY25" s="9">
-        <f t="shared" si="199"/>
-        <v>0.2</v>
-      </c>
-      <c r="AZ25" s="9">
-        <f t="shared" si="199"/>
-        <v>0.2</v>
-      </c>
-      <c r="BA25" s="9">
-        <f t="shared" si="199"/>
-        <v>0.2</v>
-      </c>
-      <c r="BB25" s="9">
-        <f t="shared" si="199"/>
-        <v>0.2</v>
-      </c>
       <c r="BD25" t="s">
         <v>44</v>
       </c>
       <c r="BE25" s="4">
         <f>BE23+BE24</f>
-        <v>3290.5363909272369</v>
+        <v>-768.69974756879697</v>
       </c>
     </row>
     <row r="26" spans="2:57" x14ac:dyDescent="0.3">
@@ -5754,208 +5750,208 @@
         <v>-1.6718682271348073</v>
       </c>
       <c r="D26" s="9">
-        <f t="shared" ref="D26:R26" si="200">D15/D3</f>
+        <f t="shared" ref="D26:R26" si="199">D15/D3</f>
         <v>-1.3469309950438426</v>
       </c>
       <c r="E26" s="9">
+        <f t="shared" si="199"/>
+        <v>-1.0923748740342627</v>
+      </c>
+      <c r="F26" s="9">
+        <f t="shared" si="199"/>
+        <v>-0.49345986150294957</v>
+      </c>
+      <c r="G26" s="9">
+        <f t="shared" si="199"/>
+        <v>-0.96754057428214757</v>
+      </c>
+      <c r="H26" s="9">
+        <f t="shared" si="199"/>
+        <v>-0.65798969072164948</v>
+      </c>
+      <c r="I26" s="9">
+        <f t="shared" si="199"/>
+        <v>-0.51030927835051543</v>
+      </c>
+      <c r="J26" s="9">
+        <f t="shared" si="199"/>
+        <v>-0.42895346764129083</v>
+      </c>
+      <c r="K26" s="9">
+        <f t="shared" si="199"/>
+        <v>-0.66140540540540527</v>
+      </c>
+      <c r="L26" s="9">
+        <f t="shared" si="199"/>
+        <v>-0.71752531924262419</v>
+      </c>
+      <c r="M26" s="9">
+        <f t="shared" si="199"/>
+        <v>-0.29306026226609688</v>
+      </c>
+      <c r="N26" s="9">
+        <f t="shared" si="199"/>
+        <v>-0.12392296718972901</v>
+      </c>
+      <c r="O26" s="9">
+        <f t="shared" si="199"/>
+        <v>-0.37266112266112261</v>
+      </c>
+      <c r="P26" s="9">
+        <f t="shared" si="199"/>
+        <v>-0.15436309948070454</v>
+      </c>
+      <c r="Q26" s="9">
+        <f t="shared" si="199"/>
+        <v>-6.7353629976580801E-2</v>
+      </c>
+      <c r="R26" s="9">
+        <f t="shared" si="199"/>
+        <v>1.741274366284002E-2</v>
+      </c>
+      <c r="S26" s="9">
+        <f t="shared" ref="S26:AD26" si="200">S15/S3</f>
+        <v>-0.33847746306577575</v>
+      </c>
+      <c r="T26" s="9">
         <f t="shared" si="200"/>
-        <v>-1.0923748740342627</v>
-      </c>
-      <c r="F26" s="9">
+        <v>-0.37996219281663501</v>
+      </c>
+      <c r="U26" s="9">
         <f t="shared" si="200"/>
-        <v>-0.49345986150294957</v>
-      </c>
-      <c r="G26" s="9">
+        <v>-0.44616747895436409</v>
+      </c>
+      <c r="V26" s="9">
         <f t="shared" si="200"/>
-        <v>-0.96754057428214757</v>
-      </c>
-      <c r="H26" s="9">
+        <v>-0.22189736092944518</v>
+      </c>
+      <c r="W26" s="9">
         <f t="shared" si="200"/>
-        <v>-0.65798969072164948</v>
-      </c>
-      <c r="I26" s="9">
+        <v>-0.33238923730528019</v>
+      </c>
+      <c r="X26" s="9">
         <f t="shared" si="200"/>
-        <v>-0.51030927835051543</v>
-      </c>
-      <c r="J26" s="9">
+        <v>-0.35347007586400669</v>
+      </c>
+      <c r="Y26" s="9">
         <f t="shared" si="200"/>
-        <v>-0.42895346764129083</v>
-      </c>
-      <c r="K26" s="9">
+        <v>-0.30986033989567568</v>
+      </c>
+      <c r="Z26" s="9">
         <f t="shared" si="200"/>
-        <v>-0.66140540540540527</v>
-      </c>
-      <c r="L26" s="9">
+        <v>-0.18232571806361572</v>
+      </c>
+      <c r="AA26" s="9">
         <f t="shared" si="200"/>
-        <v>-0.71752531924262419</v>
-      </c>
-      <c r="M26" s="9">
+        <v>-0.25527284901238712</v>
+      </c>
+      <c r="AB26" s="9">
         <f t="shared" si="200"/>
-        <v>-0.29306026226609688</v>
-      </c>
-      <c r="N26" s="9">
+        <v>-0.20092173350582151</v>
+      </c>
+      <c r="AC26" s="9">
         <f t="shared" si="200"/>
-        <v>-0.12392296718972901</v>
-      </c>
-      <c r="O26" s="9">
+        <v>-0.11176684881602916</v>
+      </c>
+      <c r="AD26" s="9">
         <f t="shared" si="200"/>
-        <v>-0.37266112266112261</v>
-      </c>
-      <c r="P26" s="9">
-        <f t="shared" si="200"/>
-        <v>-0.15436309948070454</v>
-      </c>
-      <c r="Q26" s="9">
-        <f t="shared" si="200"/>
-        <v>-6.7353629976580801E-2</v>
-      </c>
-      <c r="R26" s="9">
-        <f t="shared" si="200"/>
-        <v>1.741274366284002E-2</v>
-      </c>
-      <c r="S26" s="9">
-        <f t="shared" ref="S26:AD26" si="201">S15/S3</f>
-        <v>-0.33847746306577575</v>
-      </c>
-      <c r="T26" s="9">
+        <v>5.9076606947922276E-3</v>
+      </c>
+      <c r="AE26" s="9">
+        <f t="shared" ref="AE26:AH26" si="201">AE15/AE3</f>
+        <v>-0.1024794600938967</v>
+      </c>
+      <c r="AF26" s="9">
         <f t="shared" si="201"/>
-        <v>-0.37996219281663501</v>
-      </c>
-      <c r="U26" s="9">
+        <v>-0.19525615287381951</v>
+      </c>
+      <c r="AG26" s="9">
         <f t="shared" si="201"/>
-        <v>-0.44616747895436409</v>
-      </c>
-      <c r="V26" s="9">
+        <v>-9.32439452202658E-2</v>
+      </c>
+      <c r="AH26" s="9">
         <f t="shared" si="201"/>
-        <v>-0.22189736092944518</v>
-      </c>
-      <c r="W26" s="9">
-        <f t="shared" si="201"/>
-        <v>-0.33238923730528019</v>
-      </c>
-      <c r="X26" s="9">
-        <f t="shared" si="201"/>
-        <v>-0.35347007586400669</v>
-      </c>
-      <c r="Y26" s="9">
-        <f t="shared" si="201"/>
-        <v>-0.30986033989567568</v>
-      </c>
-      <c r="Z26" s="9">
-        <f t="shared" si="201"/>
-        <v>-0.18232571806361572</v>
-      </c>
-      <c r="AA26" s="9">
-        <f t="shared" si="201"/>
-        <v>-0.25527284901238712</v>
-      </c>
-      <c r="AB26" s="9">
-        <f t="shared" si="201"/>
-        <v>-0.20092173350582151</v>
-      </c>
-      <c r="AC26" s="9">
-        <f t="shared" si="201"/>
-        <v>-0.11176684881602916</v>
-      </c>
-      <c r="AD26" s="9">
-        <f t="shared" si="201"/>
-        <v>5.9076606947922276E-3</v>
-      </c>
-      <c r="AE26" s="9">
-        <f t="shared" ref="AE26:AH26" si="202">AE15/AE3</f>
-        <v>-0.1024794600938967</v>
-      </c>
-      <c r="AF26" s="9">
-        <f t="shared" si="202"/>
-        <v>-8.9240509783311647E-2</v>
-      </c>
-      <c r="AG26" s="9">
-        <f t="shared" si="202"/>
-        <v>-4.3207931776784107E-2</v>
-      </c>
-      <c r="AH26" s="9">
-        <f t="shared" si="202"/>
-        <v>4.1460035726169457E-2</v>
+        <v>-1.1988485756067905E-2</v>
       </c>
       <c r="AI26" s="9"/>
       <c r="AK26" s="9">
-        <f t="shared" ref="AK26:AW26" si="203">AK15/AK3</f>
+        <f t="shared" ref="AK26:AW26" si="202">AK15/AK3</f>
         <v>-1.0643740470946976</v>
       </c>
       <c r="AL26" s="9">
+        <f t="shared" si="202"/>
+        <v>-0.60250655785485263</v>
+      </c>
+      <c r="AM26" s="9">
+        <f t="shared" si="202"/>
+        <v>-0.3764435313360196</v>
+      </c>
+      <c r="AN26" s="9">
+        <f t="shared" si="202"/>
+        <v>-0.11845716645211433</v>
+      </c>
+      <c r="AO26" s="9">
+        <f t="shared" si="202"/>
+        <v>-0.3419748793950193</v>
+      </c>
+      <c r="AP26" s="9">
+        <f t="shared" si="202"/>
+        <v>-0.28711302157961011</v>
+      </c>
+      <c r="AQ26" s="9">
+        <f t="shared" si="202"/>
+        <v>-0.13013392024471218</v>
+      </c>
+      <c r="AR26" s="9">
+        <f t="shared" si="202"/>
+        <v>-9.5924004705932209E-2</v>
+      </c>
+      <c r="AS26" s="9">
+        <f t="shared" si="202"/>
+        <v>-4.8463690724062834E-2</v>
+      </c>
+      <c r="AT26" s="9">
+        <f t="shared" si="202"/>
+        <v>-3.1958285460107649E-2</v>
+      </c>
+      <c r="AU26" s="9">
+        <f t="shared" si="202"/>
+        <v>-2.2832766504355468E-2</v>
+      </c>
+      <c r="AV26" s="9">
+        <f t="shared" si="202"/>
+        <v>-1.4054023527910896E-2</v>
+      </c>
+      <c r="AW26" s="9">
+        <f t="shared" si="202"/>
+        <v>-8.6678153277714338E-3</v>
+      </c>
+      <c r="AX26" s="9">
+        <f t="shared" ref="AX26:BB26" si="203">AX15/AX3</f>
+        <v>-2.1874521956350337E-3</v>
+      </c>
+      <c r="AY26" s="9">
         <f t="shared" si="203"/>
-        <v>-0.60250655785485263</v>
-      </c>
-      <c r="AM26" s="9">
+        <v>4.1839650179769693E-3</v>
+      </c>
+      <c r="AZ26" s="9">
         <f t="shared" si="203"/>
-        <v>-0.3764435313360196</v>
-      </c>
-      <c r="AN26" s="9">
+        <v>1.0430209696472787E-2</v>
+      </c>
+      <c r="BA26" s="9">
         <f t="shared" si="203"/>
-        <v>-0.11845716645211433</v>
-      </c>
-      <c r="AO26" s="9">
+        <v>1.655344412883062E-2</v>
+      </c>
+      <c r="BB26" s="9">
         <f t="shared" si="203"/>
-        <v>-0.3419748793950193</v>
-      </c>
-      <c r="AP26" s="9">
-        <f t="shared" si="203"/>
-        <v>-0.28711302157961011</v>
-      </c>
-      <c r="AQ26" s="9">
-        <f t="shared" si="203"/>
-        <v>-0.13013392024471218</v>
-      </c>
-      <c r="AR26" s="9">
-        <f t="shared" si="203"/>
-        <v>-4.3128423853445889E-2</v>
-      </c>
-      <c r="AS26" s="9">
-        <f t="shared" si="203"/>
-        <v>-1.748392243424965E-3</v>
-      </c>
-      <c r="AT26" s="9">
-        <f t="shared" si="203"/>
-        <v>1.9424585490260982E-2</v>
-      </c>
-      <c r="AU26" s="9">
-        <f t="shared" si="203"/>
-        <v>3.0151211993428798E-2</v>
-      </c>
-      <c r="AV26" s="9">
-        <f t="shared" si="203"/>
-        <v>3.7662558939622781E-2</v>
-      </c>
-      <c r="AW26" s="9">
-        <f t="shared" si="203"/>
-        <v>4.2257966487956822E-2</v>
-      </c>
-      <c r="AX26" s="9">
-        <f t="shared" ref="AX26:BB26" si="204">AX15/AX3</f>
-        <v>4.5137462237888171E-2</v>
-      </c>
-      <c r="AY26" s="9">
-        <f t="shared" si="204"/>
-        <v>4.7955878577138816E-2</v>
-      </c>
-      <c r="AZ26" s="9">
-        <f t="shared" si="204"/>
-        <v>5.0745178728090992E-2</v>
-      </c>
-      <c r="BA26" s="9">
-        <f t="shared" si="204"/>
-        <v>5.3506130630544088E-2</v>
-      </c>
-      <c r="BB26" s="9">
-        <f t="shared" si="204"/>
-        <v>5.6239010180064435E-2</v>
+        <v>2.2556069214352617E-2</v>
       </c>
       <c r="BD26" t="s">
         <v>45</v>
       </c>
       <c r="BE26" s="5">
         <f>BE25/BB16</f>
-        <v>1.9398316282068249</v>
+        <v>-0.45895262258570479</v>
       </c>
     </row>
     <row r="27" spans="2:57" x14ac:dyDescent="0.3">
@@ -5964,7 +5960,7 @@
       </c>
       <c r="BE27" s="5">
         <f>Main!D3</f>
-        <v>8.39</v>
+        <v>7.86</v>
       </c>
     </row>
     <row r="28" spans="2:57" x14ac:dyDescent="0.3">
@@ -5973,7 +5969,7 @@
       </c>
       <c r="BE28" s="10">
         <f>BE26/BE27-1</f>
-        <v>-0.76879241618512217</v>
+        <v>-1.0583909189040337</v>
       </c>
     </row>
     <row r="29" spans="2:57" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -5988,6 +5984,10 @@
         <f>AA15</f>
         <v>-305.00000000000011</v>
       </c>
+      <c r="AB29" s="8">
+        <f>AB15</f>
+        <v>-248.50000000000003</v>
+      </c>
       <c r="AD29" s="8">
         <f>AD15</f>
         <v>9.1999999999999353</v>
@@ -5996,6 +5996,10 @@
         <f>AE15</f>
         <v>-139.69999999999999</v>
       </c>
+      <c r="AF29" s="8">
+        <f>AF15</f>
+        <v>-262.59999999999985</v>
+      </c>
       <c r="AO29" s="8">
         <f>AO15</f>
         <v>-1573.6999999999998</v>
@@ -6009,48 +6013,48 @@
         <v>-697.69999999999982</v>
       </c>
       <c r="AR29" s="8">
-        <f t="shared" ref="AR29:BB29" si="205">AR15</f>
-        <v>-257.5282720000007</v>
+        <f t="shared" ref="AR29:BB29" si="204">AR15</f>
+        <v>-560.30534899999952</v>
       </c>
       <c r="AS29" s="8">
-        <f t="shared" si="205"/>
-        <v>-11.275192191999793</v>
+        <f t="shared" si="204"/>
+        <v>-297.23726078399955</v>
       </c>
       <c r="AT29" s="8">
-        <f t="shared" si="205"/>
-        <v>132.78307062092836</v>
+        <f t="shared" si="204"/>
+        <v>-203.84664913254352</v>
       </c>
       <c r="AU29" s="8">
-        <f t="shared" si="205"/>
-        <v>216.41383488513557</v>
+        <f t="shared" si="204"/>
+        <v>-151.46489213491998</v>
       </c>
       <c r="AV29" s="8">
-        <f t="shared" si="205"/>
-        <v>281.14049829993871</v>
+        <f t="shared" si="204"/>
+        <v>-96.958850939198115</v>
       </c>
       <c r="AW29" s="8">
-        <f t="shared" si="205"/>
-        <v>324.90725199661222</v>
+        <f t="shared" si="204"/>
+        <v>-61.593326284446505</v>
       </c>
       <c r="AX29" s="8">
-        <f t="shared" si="205"/>
-        <v>353.98765812435624</v>
+        <f t="shared" si="204"/>
+        <v>-16.010312319099548</v>
       </c>
       <c r="AY29" s="8">
-        <f t="shared" si="205"/>
-        <v>383.61272600078337</v>
+        <f t="shared" si="204"/>
+        <v>31.54180210556239</v>
       </c>
       <c r="AZ29" s="8">
-        <f t="shared" si="205"/>
-        <v>414.04363467570954</v>
+        <f t="shared" si="204"/>
+        <v>80.989500871705843</v>
       </c>
       <c r="BA29" s="8">
-        <f t="shared" si="205"/>
-        <v>445.30240756190062</v>
+        <f t="shared" si="204"/>
+        <v>132.39185723175689</v>
       </c>
       <c r="BB29" s="8">
-        <f t="shared" si="205"/>
-        <v>477.40761037466183</v>
+        <f t="shared" si="204"/>
+        <v>185.81191128879408</v>
       </c>
       <c r="BD29" t="s">
         <v>48</v>
@@ -6069,11 +6073,17 @@
       <c r="AA30" s="4">
         <v>41.7</v>
       </c>
+      <c r="AB30" s="4">
+        <v>40</v>
+      </c>
       <c r="AD30" s="4">
         <v>39.6</v>
       </c>
       <c r="AE30" s="4">
         <v>37.700000000000003</v>
+      </c>
+      <c r="AF30" s="4">
+        <v>40</v>
       </c>
       <c r="AO30" s="4">
         <v>202.2</v>
@@ -6089,43 +6099,43 @@
         <v>159.68099999999998</v>
       </c>
       <c r="AS30" s="4">
-        <f t="shared" ref="AS30:BB30" si="206">AR30*1.01</f>
+        <f t="shared" ref="AS30:BB30" si="205">AR30*1.01</f>
         <v>161.27780999999999</v>
       </c>
       <c r="AT30" s="4">
-        <f t="shared" si="206"/>
+        <f t="shared" si="205"/>
         <v>162.8905881</v>
       </c>
       <c r="AU30" s="4">
-        <f t="shared" si="206"/>
+        <f t="shared" si="205"/>
         <v>164.51949398100001</v>
       </c>
       <c r="AV30" s="4">
-        <f t="shared" si="206"/>
+        <f t="shared" si="205"/>
         <v>166.16468892081002</v>
       </c>
       <c r="AW30" s="4">
-        <f t="shared" si="206"/>
+        <f t="shared" si="205"/>
         <v>167.82633581001812</v>
       </c>
       <c r="AX30" s="4">
-        <f t="shared" si="206"/>
+        <f t="shared" si="205"/>
         <v>169.50459916811832</v>
       </c>
       <c r="AY30" s="4">
-        <f t="shared" si="206"/>
+        <f t="shared" si="205"/>
         <v>171.1996451597995</v>
       </c>
       <c r="AZ30" s="4">
-        <f t="shared" si="206"/>
+        <f t="shared" si="205"/>
         <v>172.9116416113975</v>
       </c>
       <c r="BA30" s="4">
-        <f t="shared" si="206"/>
+        <f t="shared" si="205"/>
         <v>174.64075802751148</v>
       </c>
       <c r="BB30" s="4">
-        <f t="shared" si="206"/>
+        <f t="shared" si="205"/>
         <v>176.38716560778659</v>
       </c>
     </row>
@@ -6139,12 +6149,18 @@
       <c r="AA31" s="4">
         <v>263.8</v>
       </c>
+      <c r="AB31" s="4">
+        <v>251.9</v>
+      </c>
       <c r="AD31" s="4">
         <v>257.7</v>
       </c>
       <c r="AE31" s="4">
         <v>247.3</v>
       </c>
+      <c r="AF31" s="4">
+        <v>251.9</v>
+      </c>
       <c r="AO31" s="4">
         <v>1387.8</v>
       </c>
@@ -6155,48 +6171,48 @@
         <v>1041</v>
       </c>
       <c r="AR31" s="4">
-        <f>AQ31*0.85</f>
-        <v>884.85</v>
+        <f>AQ31*1.01</f>
+        <v>1051.4100000000001</v>
       </c>
       <c r="AS31" s="4">
-        <f t="shared" ref="AS31:AU31" si="207">AR31*0.85</f>
-        <v>752.12249999999995</v>
+        <f>AR31*0.95</f>
+        <v>998.83950000000004</v>
       </c>
       <c r="AT31" s="4">
-        <f t="shared" si="207"/>
-        <v>639.30412499999989</v>
+        <f t="shared" ref="AT31:BB31" si="206">AS31*0.95</f>
+        <v>948.89752499999997</v>
       </c>
       <c r="AU31" s="4">
-        <f t="shared" si="207"/>
-        <v>543.40850624999985</v>
+        <f t="shared" si="206"/>
+        <v>901.45264874999998</v>
       </c>
       <c r="AV31" s="4">
-        <f>AU31*0.95</f>
-        <v>516.23808093749983</v>
+        <f t="shared" si="206"/>
+        <v>856.38001631249995</v>
       </c>
       <c r="AW31" s="4">
-        <f t="shared" ref="AW31:BB31" si="208">AV31*0.95</f>
-        <v>490.42617689062479</v>
+        <f t="shared" si="206"/>
+        <v>813.56101549687492</v>
       </c>
       <c r="AX31" s="4">
-        <f t="shared" si="208"/>
-        <v>465.90486804609355</v>
+        <f t="shared" si="206"/>
+        <v>772.88296472203115</v>
       </c>
       <c r="AY31" s="4">
-        <f t="shared" si="208"/>
-        <v>442.60962464378883</v>
+        <f t="shared" si="206"/>
+        <v>734.23881648592953</v>
       </c>
       <c r="AZ31" s="4">
-        <f t="shared" si="208"/>
-        <v>420.47914341159935</v>
+        <f t="shared" si="206"/>
+        <v>697.52687566163297</v>
       </c>
       <c r="BA31" s="4">
-        <f t="shared" si="208"/>
-        <v>399.45518624101936</v>
+        <f t="shared" si="206"/>
+        <v>662.65053187855131</v>
       </c>
       <c r="BB31" s="4">
-        <f t="shared" si="208"/>
-        <v>379.48242692896838</v>
+        <f t="shared" si="206"/>
+        <v>629.51800528462365</v>
       </c>
     </row>
     <row r="32" spans="2:57" x14ac:dyDescent="0.3">
@@ -6209,11 +6225,17 @@
       <c r="AA32" s="4">
         <v>1.7</v>
       </c>
+      <c r="AB32" s="4">
+        <v>-0.6</v>
+      </c>
       <c r="AD32" s="4">
         <v>2.7</v>
       </c>
       <c r="AE32" s="4">
         <v>7.6</v>
+      </c>
+      <c r="AF32" s="4">
+        <v>-0.6</v>
       </c>
       <c r="AO32" s="4">
         <v>6.9</v>
@@ -6229,43 +6251,43 @@
         <v>9.4939999999999998</v>
       </c>
       <c r="AS32" s="4">
-        <f t="shared" ref="AS32:BB32" si="209">AR32*1.01</f>
+        <f t="shared" ref="AS32:BB32" si="207">AR32*1.01</f>
         <v>9.5889399999999991</v>
       </c>
       <c r="AT32" s="4">
-        <f t="shared" si="209"/>
+        <f t="shared" si="207"/>
         <v>9.6848293999999999</v>
       </c>
       <c r="AU32" s="4">
-        <f t="shared" si="209"/>
+        <f t="shared" si="207"/>
         <v>9.7816776940000008</v>
       </c>
       <c r="AV32" s="4">
-        <f t="shared" si="209"/>
+        <f t="shared" si="207"/>
         <v>9.879494470940001</v>
       </c>
       <c r="AW32" s="4">
-        <f t="shared" si="209"/>
+        <f t="shared" si="207"/>
         <v>9.9782894156494013</v>
       </c>
       <c r="AX32" s="4">
-        <f t="shared" si="209"/>
+        <f t="shared" si="207"/>
         <v>10.078072309805895</v>
       </c>
       <c r="AY32" s="4">
-        <f t="shared" si="209"/>
+        <f t="shared" si="207"/>
         <v>10.178853032903953</v>
       </c>
       <c r="AZ32" s="4">
-        <f t="shared" si="209"/>
+        <f t="shared" si="207"/>
         <v>10.280641563232994</v>
       </c>
       <c r="BA32" s="4">
-        <f t="shared" si="209"/>
+        <f t="shared" si="207"/>
         <v>10.383447978865323</v>
       </c>
       <c r="BB32" s="4">
-        <f t="shared" si="209"/>
+        <f t="shared" si="207"/>
         <v>10.487282458653977</v>
       </c>
     </row>
@@ -6279,11 +6301,17 @@
       <c r="AA33" s="4">
         <v>9</v>
       </c>
+      <c r="AB33" s="4">
+        <v>-1.2</v>
+      </c>
       <c r="AD33" s="4">
         <v>-3.7</v>
       </c>
       <c r="AE33" s="4">
         <v>15.8</v>
+      </c>
+      <c r="AF33" s="4">
+        <v>-1.2</v>
       </c>
       <c r="AO33" s="4">
         <v>36.799999999999997</v>
@@ -6336,9 +6364,15 @@
       <c r="AA34" s="4">
         <v>-8.9</v>
       </c>
+      <c r="AB34" s="4">
+        <v>0</v>
+      </c>
       <c r="AD34" s="4"/>
       <c r="AE34" s="4">
         <v>-66.900000000000006</v>
+      </c>
+      <c r="AF34" s="4">
+        <v>0</v>
       </c>
       <c r="AO34" s="4"/>
       <c r="AP34" s="4"/>
@@ -6365,11 +6399,17 @@
       <c r="AA35" s="4">
         <v>-7.8</v>
       </c>
+      <c r="AB35" s="4">
+        <v>12.4</v>
+      </c>
       <c r="AD35" s="4">
         <v>-10.3</v>
       </c>
       <c r="AE35" s="4">
         <v>-0.8</v>
+      </c>
+      <c r="AF35" s="4">
+        <v>12.4</v>
       </c>
       <c r="AO35" s="4">
         <v>15.6</v>
@@ -6424,11 +6464,17 @@
       <c r="AA36" s="4">
         <v>162.19999999999999</v>
       </c>
+      <c r="AB36" s="4">
+        <v>-3.1</v>
+      </c>
       <c r="AD36" s="4">
         <v>-167.4</v>
       </c>
       <c r="AE36" s="4">
         <v>194.2</v>
+      </c>
+      <c r="AF36" s="4">
+        <v>-3.1</v>
       </c>
       <c r="AO36" s="4">
         <v>-119.8</v>
@@ -6483,11 +6529,17 @@
       <c r="AA37" s="4">
         <v>-13.6</v>
       </c>
+      <c r="AB37" s="4">
+        <v>-7.1</v>
+      </c>
       <c r="AD37" s="4">
         <v>-0.3</v>
       </c>
       <c r="AE37" s="4">
         <v>-22.8</v>
+      </c>
+      <c r="AF37" s="4">
+        <v>-7.1</v>
       </c>
       <c r="AO37" s="4">
         <v>-40.9</v>
@@ -6542,11 +6594,17 @@
       <c r="AA38" s="4">
         <v>13.6</v>
       </c>
+      <c r="AB38" s="4">
+        <v>13.8</v>
+      </c>
       <c r="AD38" s="4">
         <v>12.9</v>
       </c>
       <c r="AE38" s="4">
         <v>14.1</v>
+      </c>
+      <c r="AF38" s="4">
+        <v>13.8</v>
       </c>
       <c r="AO38" s="4">
         <v>71.400000000000006</v>
@@ -6601,11 +6659,17 @@
       <c r="AA39" s="4">
         <v>-5.0999999999999996</v>
       </c>
+      <c r="AB39" s="4">
+        <v>-2.1</v>
+      </c>
       <c r="AD39" s="4">
         <v>-6.9</v>
       </c>
       <c r="AE39" s="4">
         <v>9</v>
+      </c>
+      <c r="AF39" s="4">
+        <v>-2.1</v>
       </c>
       <c r="AO39" s="4">
         <v>-0.5</v>
@@ -6660,11 +6724,17 @@
       <c r="AA40" s="4">
         <v>-34.1</v>
       </c>
+      <c r="AB40" s="4">
+        <v>-94.2</v>
+      </c>
       <c r="AD40" s="4">
         <v>11.6</v>
       </c>
       <c r="AE40" s="4">
         <v>34.299999999999997</v>
+      </c>
+      <c r="AF40" s="4">
+        <v>-94.2</v>
       </c>
       <c r="AO40" s="4">
         <v>46.5</v>
@@ -6719,11 +6789,17 @@
       <c r="AA41" s="4">
         <v>-18.399999999999999</v>
       </c>
+      <c r="AB41" s="4">
+        <v>147.69999999999999</v>
+      </c>
       <c r="AD41" s="4">
         <v>103.6</v>
       </c>
       <c r="AE41" s="4">
         <v>-162.6</v>
+      </c>
+      <c r="AF41" s="4">
+        <v>147.69999999999999</v>
       </c>
       <c r="AO41" s="4">
         <v>71.7</v>
@@ -6778,11 +6854,17 @@
       <c r="AA42" s="4">
         <v>-13.9</v>
       </c>
+      <c r="AB42" s="4">
+        <v>-8.5</v>
+      </c>
       <c r="AD42" s="4">
         <v>-18.399999999999999</v>
       </c>
       <c r="AE42" s="4">
         <v>-17</v>
+      </c>
+      <c r="AF42" s="4">
+        <v>-8.5</v>
       </c>
       <c r="AO42" s="4">
         <v>-68.900000000000006</v>
@@ -6837,11 +6919,17 @@
       <c r="AA43" s="4">
         <v>3.3</v>
       </c>
+      <c r="AB43" s="4">
+        <v>2</v>
+      </c>
       <c r="AD43" s="4">
         <v>0.5</v>
       </c>
       <c r="AE43" s="4">
         <v>1.2</v>
+      </c>
+      <c r="AF43" s="4">
+        <v>2</v>
       </c>
       <c r="AO43" s="4">
         <v>5.5</v>
@@ -6898,6 +6986,10 @@
         <f>AA29+SUM(AA30:AA43)</f>
         <v>88.499999999999886</v>
       </c>
+      <c r="AB44" s="8">
+        <f>AB29+SUM(AB30:AB43)</f>
+        <v>102.49999999999986</v>
+      </c>
       <c r="AD44" s="8">
         <f>AD29+SUM(AD30:AD43)</f>
         <v>230.7999999999999</v>
@@ -6906,6 +6998,10 @@
         <f>AE29+SUM(AE30:AE43)</f>
         <v>151.39999999999998</v>
       </c>
+      <c r="AF44" s="8">
+        <f>AF29+SUM(AF30:AF43)</f>
+        <v>88.400000000000034</v>
+      </c>
       <c r="AO44" s="8">
         <f>AO29+SUM(AO30:AO43)</f>
         <v>40.600000000000136</v>
@@ -6920,47 +7016,47 @@
       </c>
       <c r="AR44" s="8">
         <f>AR29+SUM(AR30:AR43)</f>
-        <v>796.49672799999917</v>
+        <v>660.27965100000051</v>
       </c>
       <c r="AS44" s="8">
-        <f t="shared" ref="AS44:BB44" si="210">AS29+SUM(AS30:AS43)</f>
-        <v>911.71405780800023</v>
+        <f t="shared" ref="AS44:BB44" si="208">AS29+SUM(AS30:AS43)</f>
+        <v>872.46898921600064</v>
       </c>
       <c r="AT44" s="8">
-        <f t="shared" si="210"/>
-        <v>944.66261312092831</v>
+        <f t="shared" si="208"/>
+        <v>917.62629336745636</v>
       </c>
       <c r="AU44" s="8">
-        <f t="shared" si="210"/>
-        <v>934.12351281013537</v>
+        <f t="shared" si="208"/>
+        <v>924.28892829008021</v>
       </c>
       <c r="AV44" s="8">
-        <f t="shared" si="210"/>
-        <v>973.42276262918858</v>
+        <f t="shared" si="208"/>
+        <v>935.46534876505189</v>
       </c>
       <c r="AW44" s="8">
-        <f t="shared" si="210"/>
-        <v>993.13805411290457</v>
+        <f t="shared" si="208"/>
+        <v>929.77231443809592</v>
       </c>
       <c r="AX44" s="8">
-        <f t="shared" si="210"/>
-        <v>999.47519764837398</v>
+        <f t="shared" si="208"/>
+        <v>936.45532388085587</v>
       </c>
       <c r="AY44" s="8">
-        <f t="shared" si="210"/>
-        <v>1007.6008488372756</v>
+        <f t="shared" si="208"/>
+        <v>947.15911678419536</v>
       </c>
       <c r="AZ44" s="8">
-        <f t="shared" si="210"/>
-        <v>1017.7150612619394</v>
+        <f t="shared" si="208"/>
+        <v>961.70865970796922</v>
       </c>
       <c r="BA44" s="8">
-        <f t="shared" si="210"/>
-        <v>1029.7817998092969</v>
+        <f t="shared" si="208"/>
+        <v>980.06659511668499</v>
       </c>
       <c r="BB44" s="8">
-        <f t="shared" si="210"/>
-        <v>1043.7644853700708</v>
+        <f t="shared" si="208"/>
+        <v>1002.2043646398583</v>
       </c>
     </row>
     <row r="45" spans="2:147" x14ac:dyDescent="0.3">
@@ -6973,11 +7069,17 @@
       <c r="AA45" s="4">
         <v>50.4</v>
       </c>
+      <c r="AB45" s="4">
+        <v>64.7</v>
+      </c>
       <c r="AD45" s="4">
         <v>48.3</v>
       </c>
       <c r="AE45" s="4">
         <v>37.200000000000003</v>
+      </c>
+      <c r="AF45" s="4">
+        <v>64.7</v>
       </c>
       <c r="AO45" s="4">
         <v>129.30000000000001</v>
@@ -6993,43 +7095,43 @@
         <v>196.74800000000002</v>
       </c>
       <c r="AS45" s="4">
-        <f t="shared" ref="AS45:BB45" si="211">AR45*1.01</f>
+        <f t="shared" ref="AS45:BB45" si="209">AR45*1.01</f>
         <v>198.71548000000001</v>
       </c>
       <c r="AT45" s="4">
-        <f t="shared" si="211"/>
+        <f t="shared" si="209"/>
         <v>200.70263480000003</v>
       </c>
       <c r="AU45" s="4">
-        <f t="shared" si="211"/>
+        <f t="shared" si="209"/>
         <v>202.70966114800004</v>
       </c>
       <c r="AV45" s="4">
-        <f t="shared" si="211"/>
+        <f t="shared" si="209"/>
         <v>204.73675775948004</v>
       </c>
       <c r="AW45" s="4">
-        <f t="shared" si="211"/>
+        <f t="shared" si="209"/>
         <v>206.78412533707484</v>
       </c>
       <c r="AX45" s="4">
-        <f t="shared" si="211"/>
+        <f t="shared" si="209"/>
         <v>208.85196659044558</v>
       </c>
       <c r="AY45" s="4">
-        <f t="shared" si="211"/>
+        <f t="shared" si="209"/>
         <v>210.94048625635006</v>
       </c>
       <c r="AZ45" s="4">
-        <f t="shared" si="211"/>
+        <f t="shared" si="209"/>
         <v>213.04989111891356</v>
       </c>
       <c r="BA45" s="4">
-        <f t="shared" si="211"/>
+        <f t="shared" si="209"/>
         <v>215.1803900301027</v>
       </c>
       <c r="BB45" s="4">
-        <f t="shared" si="211"/>
+        <f t="shared" si="209"/>
         <v>217.33219393040372</v>
       </c>
     </row>
@@ -7045,6 +7147,10 @@
         <f>AA44-AA45</f>
         <v>38.099999999999888</v>
       </c>
+      <c r="AB46" s="8">
+        <f>AB44-AB45</f>
+        <v>37.799999999999855</v>
+      </c>
       <c r="AD46" s="8">
         <f>AD44-AD45</f>
         <v>182.49999999999989</v>
@@ -7053,6 +7159,10 @@
         <f>AE44-AE45</f>
         <v>114.19999999999997</v>
       </c>
+      <c r="AF46" s="8">
+        <f>AF44-AF45</f>
+        <v>23.700000000000031</v>
+      </c>
       <c r="AO46" s="8">
         <f>AO44-AO45</f>
         <v>-88.699999999999875</v>
@@ -7067,455 +7177,455 @@
       </c>
       <c r="AR46" s="8">
         <f>AR44-AR45</f>
-        <v>599.74872799999912</v>
+        <v>463.53165100000047</v>
       </c>
       <c r="AS46" s="8">
-        <f t="shared" ref="AS46:BB46" si="212">AS44-AS45</f>
-        <v>712.99857780800016</v>
+        <f t="shared" ref="AS46:BB46" si="210">AS44-AS45</f>
+        <v>673.75350921600057</v>
       </c>
       <c r="AT46" s="8">
-        <f t="shared" si="212"/>
-        <v>743.95997832092826</v>
+        <f t="shared" si="210"/>
+        <v>716.9236585674563</v>
       </c>
       <c r="AU46" s="8">
-        <f t="shared" si="212"/>
-        <v>731.41385166213536</v>
+        <f t="shared" si="210"/>
+        <v>721.5792671420802</v>
       </c>
       <c r="AV46" s="8">
-        <f t="shared" si="212"/>
-        <v>768.68600486970854</v>
+        <f t="shared" si="210"/>
+        <v>730.72859100557184</v>
       </c>
       <c r="AW46" s="8">
-        <f t="shared" si="212"/>
-        <v>786.35392877582967</v>
+        <f t="shared" si="210"/>
+        <v>722.98818910102113</v>
       </c>
       <c r="AX46" s="8">
-        <f t="shared" si="212"/>
-        <v>790.62323105792836</v>
+        <f t="shared" si="210"/>
+        <v>727.60335729041026</v>
       </c>
       <c r="AY46" s="8">
-        <f t="shared" si="212"/>
-        <v>796.66036258092561</v>
+        <f t="shared" si="210"/>
+        <v>736.21863052784533</v>
       </c>
       <c r="AZ46" s="8">
-        <f t="shared" si="212"/>
-        <v>804.66517014302576</v>
+        <f t="shared" si="210"/>
+        <v>748.65876858905563</v>
       </c>
       <c r="BA46" s="8">
-        <f t="shared" si="212"/>
-        <v>814.60140977919423</v>
+        <f t="shared" si="210"/>
+        <v>764.88620508658232</v>
       </c>
       <c r="BB46" s="8">
-        <f t="shared" si="212"/>
-        <v>826.4322914396671</v>
+        <f t="shared" si="210"/>
+        <v>784.87217070945462</v>
       </c>
       <c r="BC46" s="1">
         <f>BB46*(1+$BE$21)</f>
-        <v>818.16796852527045</v>
+        <v>777.02344900236005</v>
       </c>
       <c r="BD46" s="1">
-        <f t="shared" ref="BD46:DO46" si="213">BC46*(1+$BE$21)</f>
-        <v>809.98628884001778</v>
+        <f t="shared" ref="BD46:DO46" si="211">BC46*(1+$BE$21)</f>
+        <v>769.2532145123364</v>
       </c>
       <c r="BE46" s="1">
-        <f t="shared" si="213"/>
-        <v>801.88642595161764</v>
+        <f t="shared" si="211"/>
+        <v>761.56068236721308</v>
       </c>
       <c r="BF46" s="1">
-        <f t="shared" si="213"/>
-        <v>793.8675616921015</v>
+        <f t="shared" si="211"/>
+        <v>753.94507554354095</v>
       </c>
       <c r="BG46" s="1">
-        <f t="shared" si="213"/>
-        <v>785.92888607518046</v>
+        <f t="shared" si="211"/>
+        <v>746.40562478810557</v>
       </c>
       <c r="BH46" s="1">
-        <f t="shared" si="213"/>
-        <v>778.06959721442865</v>
+        <f t="shared" si="211"/>
+        <v>738.94156854022447</v>
       </c>
       <c r="BI46" s="1">
-        <f t="shared" si="213"/>
-        <v>770.2889012422844</v>
+        <f t="shared" si="211"/>
+        <v>731.55215285482222</v>
       </c>
       <c r="BJ46" s="1">
-        <f t="shared" si="213"/>
-        <v>762.58601222986158</v>
+        <f t="shared" si="211"/>
+        <v>724.23663132627405</v>
       </c>
       <c r="BK46" s="1">
-        <f t="shared" si="213"/>
-        <v>754.96015210756298</v>
+        <f t="shared" si="211"/>
+        <v>716.99426501301127</v>
       </c>
       <c r="BL46" s="1">
-        <f t="shared" si="213"/>
-        <v>747.41055058648737</v>
+        <f t="shared" si="211"/>
+        <v>709.82432236288116</v>
       </c>
       <c r="BM46" s="1">
-        <f t="shared" si="213"/>
-        <v>739.93644508062255</v>
+        <f t="shared" si="211"/>
+        <v>702.72607913925231</v>
       </c>
       <c r="BN46" s="1">
-        <f t="shared" si="213"/>
-        <v>732.53708062981627</v>
+        <f t="shared" si="211"/>
+        <v>695.69881834785974</v>
       </c>
       <c r="BO46" s="1">
-        <f t="shared" si="213"/>
-        <v>725.21170982351805</v>
+        <f t="shared" si="211"/>
+        <v>688.7418301643811</v>
       </c>
       <c r="BP46" s="1">
-        <f t="shared" si="213"/>
-        <v>717.95959272528285</v>
+        <f t="shared" si="211"/>
+        <v>681.85441186273727</v>
       </c>
       <c r="BQ46" s="1">
-        <f t="shared" si="213"/>
-        <v>710.77999679802997</v>
+        <f t="shared" si="211"/>
+        <v>675.03586774410985</v>
       </c>
       <c r="BR46" s="1">
-        <f t="shared" si="213"/>
-        <v>703.67219683004964</v>
+        <f t="shared" si="211"/>
+        <v>668.28550906666874</v>
       </c>
       <c r="BS46" s="1">
-        <f t="shared" si="213"/>
-        <v>696.63547486174912</v>
+        <f t="shared" si="211"/>
+        <v>661.60265397600199</v>
       </c>
       <c r="BT46" s="1">
-        <f t="shared" si="213"/>
-        <v>689.66912011313161</v>
+        <f t="shared" si="211"/>
+        <v>654.98662743624197</v>
       </c>
       <c r="BU46" s="1">
-        <f t="shared" si="213"/>
-        <v>682.77242891200024</v>
+        <f t="shared" si="211"/>
+        <v>648.43676116187953</v>
       </c>
       <c r="BV46" s="1">
-        <f t="shared" si="213"/>
-        <v>675.94470462288018</v>
+        <f t="shared" si="211"/>
+        <v>641.95239355026069</v>
       </c>
       <c r="BW46" s="1">
-        <f t="shared" si="213"/>
-        <v>669.18525757665134</v>
+        <f t="shared" si="211"/>
+        <v>635.53286961475806</v>
       </c>
       <c r="BX46" s="1">
-        <f t="shared" si="213"/>
-        <v>662.49340500088476</v>
+        <f t="shared" si="211"/>
+        <v>629.17754091861048</v>
       </c>
       <c r="BY46" s="1">
-        <f t="shared" si="213"/>
-        <v>655.86847095087592</v>
+        <f t="shared" si="211"/>
+        <v>622.88576550942435</v>
       </c>
       <c r="BZ46" s="1">
-        <f t="shared" si="213"/>
-        <v>649.30978624136719</v>
+        <f t="shared" si="211"/>
+        <v>616.65690785433014</v>
       </c>
       <c r="CA46" s="1">
-        <f t="shared" si="213"/>
-        <v>642.81668837895347</v>
+        <f t="shared" si="211"/>
+        <v>610.49033877578688</v>
       </c>
       <c r="CB46" s="1">
-        <f t="shared" si="213"/>
-        <v>636.3885214951639</v>
+        <f t="shared" si="211"/>
+        <v>604.38543538802901</v>
       </c>
       <c r="CC46" s="1">
-        <f t="shared" si="213"/>
-        <v>630.02463628021223</v>
+        <f t="shared" si="211"/>
+        <v>598.3415810341487</v>
       </c>
       <c r="CD46" s="1">
-        <f t="shared" si="213"/>
-        <v>623.72438991741012</v>
+        <f t="shared" si="211"/>
+        <v>592.35816522380719</v>
       </c>
       <c r="CE46" s="1">
-        <f t="shared" si="213"/>
-        <v>617.48714601823599</v>
+        <f t="shared" si="211"/>
+        <v>586.43458357156908</v>
       </c>
       <c r="CF46" s="1">
-        <f t="shared" si="213"/>
-        <v>611.31227455805367</v>
+        <f t="shared" si="211"/>
+        <v>580.57023773585342</v>
       </c>
       <c r="CG46" s="1">
-        <f t="shared" si="213"/>
-        <v>605.19915181247313</v>
+        <f t="shared" si="211"/>
+        <v>574.76453535849487</v>
       </c>
       <c r="CH46" s="1">
-        <f t="shared" si="213"/>
-        <v>599.1471602943484</v>
+        <f t="shared" si="211"/>
+        <v>569.0168900049099</v>
       </c>
       <c r="CI46" s="1">
-        <f t="shared" si="213"/>
-        <v>593.15568869140486</v>
+        <f t="shared" si="211"/>
+        <v>563.32672110486078</v>
       </c>
       <c r="CJ46" s="1">
-        <f t="shared" si="213"/>
-        <v>587.22413180449075</v>
+        <f t="shared" si="211"/>
+        <v>557.69345389381215</v>
       </c>
       <c r="CK46" s="1">
-        <f t="shared" si="213"/>
-        <v>581.35189048644588</v>
+        <f t="shared" si="211"/>
+        <v>552.11651935487407</v>
       </c>
       <c r="CL46" s="1">
-        <f t="shared" si="213"/>
-        <v>575.53837158158137</v>
+        <f t="shared" si="211"/>
+        <v>546.5953541613253</v>
       </c>
       <c r="CM46" s="1">
-        <f t="shared" si="213"/>
-        <v>569.78298786576556</v>
+        <f t="shared" si="211"/>
+        <v>541.1294006197121</v>
       </c>
       <c r="CN46" s="1">
-        <f t="shared" si="213"/>
-        <v>564.08515798710789</v>
+        <f t="shared" si="211"/>
+        <v>535.71810661351492</v>
       </c>
       <c r="CO46" s="1">
-        <f t="shared" si="213"/>
-        <v>558.44430640723681</v>
+        <f t="shared" si="211"/>
+        <v>530.36092554737979</v>
       </c>
       <c r="CP46" s="1">
-        <f t="shared" si="213"/>
-        <v>552.85986334316442</v>
+        <f t="shared" si="211"/>
+        <v>525.05731629190598</v>
       </c>
       <c r="CQ46" s="1">
-        <f t="shared" si="213"/>
-        <v>547.33126470973275</v>
+        <f t="shared" si="211"/>
+        <v>519.80674312898691</v>
       </c>
       <c r="CR46" s="1">
-        <f t="shared" si="213"/>
-        <v>541.85795206263538</v>
+        <f t="shared" si="211"/>
+        <v>514.60867569769698</v>
       </c>
       <c r="CS46" s="1">
-        <f t="shared" si="213"/>
-        <v>536.43937254200898</v>
+        <f t="shared" si="211"/>
+        <v>509.46258894072002</v>
       </c>
       <c r="CT46" s="1">
-        <f t="shared" si="213"/>
-        <v>531.0749788165889</v>
+        <f t="shared" si="211"/>
+        <v>504.36796305131281</v>
       </c>
       <c r="CU46" s="1">
-        <f t="shared" si="213"/>
-        <v>525.76422902842296</v>
+        <f t="shared" si="211"/>
+        <v>499.3242834207997</v>
       </c>
       <c r="CV46" s="1">
-        <f t="shared" si="213"/>
-        <v>520.50658673813871</v>
+        <f t="shared" si="211"/>
+        <v>494.33104058659171</v>
       </c>
       <c r="CW46" s="1">
-        <f t="shared" si="213"/>
-        <v>515.30152087075737</v>
+        <f t="shared" si="211"/>
+        <v>489.38773018072578</v>
       </c>
       <c r="CX46" s="1">
-        <f t="shared" si="213"/>
-        <v>510.14850566204979</v>
+        <f t="shared" si="211"/>
+        <v>484.49385287891852</v>
       </c>
       <c r="CY46" s="1">
-        <f t="shared" si="213"/>
-        <v>505.04702060542928</v>
+        <f t="shared" si="211"/>
+        <v>479.6489143501293</v>
       </c>
       <c r="CZ46" s="1">
-        <f t="shared" si="213"/>
-        <v>499.996550399375</v>
+        <f t="shared" si="211"/>
+        <v>474.85242520662803</v>
       </c>
       <c r="DA46" s="1">
-        <f t="shared" si="213"/>
-        <v>494.99658489538126</v>
+        <f t="shared" si="211"/>
+        <v>470.10390095456177</v>
       </c>
       <c r="DB46" s="1">
-        <f t="shared" si="213"/>
-        <v>490.04661904642745</v>
+        <f t="shared" si="211"/>
+        <v>465.40286194501613</v>
       </c>
       <c r="DC46" s="1">
-        <f t="shared" si="213"/>
-        <v>485.14615285596318</v>
+        <f t="shared" si="211"/>
+        <v>460.74883332556595</v>
       </c>
       <c r="DD46" s="1">
-        <f t="shared" si="213"/>
-        <v>480.29469132740354</v>
+        <f t="shared" si="211"/>
+        <v>456.14134499231028</v>
       </c>
       <c r="DE46" s="1">
-        <f t="shared" si="213"/>
-        <v>475.49174441412953</v>
+        <f t="shared" si="211"/>
+        <v>451.57993154238716</v>
       </c>
       <c r="DF46" s="1">
-        <f t="shared" si="213"/>
-        <v>470.73682696998821</v>
+        <f t="shared" si="211"/>
+        <v>447.0641322269633</v>
       </c>
       <c r="DG46" s="1">
-        <f t="shared" si="213"/>
-        <v>466.02945870028833</v>
+        <f t="shared" si="211"/>
+        <v>442.59349090469368</v>
       </c>
       <c r="DH46" s="1">
-        <f t="shared" si="213"/>
-        <v>461.36916411328542</v>
+        <f t="shared" si="211"/>
+        <v>438.16755599564675</v>
       </c>
       <c r="DI46" s="1">
-        <f t="shared" si="213"/>
-        <v>456.75547247215258</v>
+        <f t="shared" si="211"/>
+        <v>433.78588043569027</v>
       </c>
       <c r="DJ46" s="1">
-        <f t="shared" si="213"/>
-        <v>452.18791774743107</v>
+        <f t="shared" si="211"/>
+        <v>429.44802163133335</v>
       </c>
       <c r="DK46" s="1">
-        <f t="shared" si="213"/>
-        <v>447.66603856995675</v>
+        <f t="shared" si="211"/>
+        <v>425.15354141502002</v>
       </c>
       <c r="DL46" s="1">
-        <f t="shared" si="213"/>
-        <v>443.18937818425718</v>
+        <f t="shared" si="211"/>
+        <v>420.90200600086979</v>
       </c>
       <c r="DM46" s="1">
-        <f t="shared" si="213"/>
-        <v>438.7574844024146</v>
+        <f t="shared" si="211"/>
+        <v>416.69298594086109</v>
       </c>
       <c r="DN46" s="1">
-        <f t="shared" si="213"/>
-        <v>434.36990955839048</v>
+        <f t="shared" si="211"/>
+        <v>412.52605608145245</v>
       </c>
       <c r="DO46" s="1">
-        <f t="shared" si="213"/>
-        <v>430.02621046280655</v>
+        <f t="shared" si="211"/>
+        <v>408.40079552063793</v>
       </c>
       <c r="DP46" s="1">
-        <f t="shared" ref="DP46:EQ46" si="214">DO46*(1+$BE$21)</f>
-        <v>425.72594835817847</v>
+        <f t="shared" ref="DP46:EQ46" si="212">DO46*(1+$BE$21)</f>
+        <v>404.31678756543153</v>
       </c>
       <c r="DQ46" s="1">
-        <f t="shared" si="214"/>
-        <v>421.46868887459669</v>
+        <f t="shared" si="212"/>
+        <v>400.27361968977721</v>
       </c>
       <c r="DR46" s="1">
-        <f t="shared" si="214"/>
-        <v>417.25400198585072</v>
+        <f t="shared" si="212"/>
+        <v>396.27088349287942</v>
       </c>
       <c r="DS46" s="1">
-        <f t="shared" si="214"/>
-        <v>413.08146196599222</v>
+        <f t="shared" si="212"/>
+        <v>392.30817465795064</v>
       </c>
       <c r="DT46" s="1">
-        <f t="shared" si="214"/>
-        <v>408.95064734633229</v>
+        <f t="shared" si="212"/>
+        <v>388.38509291137115</v>
       </c>
       <c r="DU46" s="1">
-        <f t="shared" si="214"/>
-        <v>404.86114087286899</v>
+        <f t="shared" si="212"/>
+        <v>384.50124198225745</v>
       </c>
       <c r="DV46" s="1">
-        <f t="shared" si="214"/>
-        <v>400.81252946414031</v>
+        <f t="shared" si="212"/>
+        <v>380.65622956243487</v>
       </c>
       <c r="DW46" s="1">
-        <f t="shared" si="214"/>
-        <v>396.80440416949892</v>
+        <f t="shared" si="212"/>
+        <v>376.84966726681051</v>
       </c>
       <c r="DX46" s="1">
-        <f t="shared" si="214"/>
-        <v>392.83636012780391</v>
+        <f t="shared" si="212"/>
+        <v>373.08117059414241</v>
       </c>
       <c r="DY46" s="1">
-        <f t="shared" si="214"/>
-        <v>388.90799652652589</v>
+        <f t="shared" si="212"/>
+        <v>369.35035888820096</v>
       </c>
       <c r="DZ46" s="1">
-        <f t="shared" si="214"/>
-        <v>385.01891656126065</v>
+        <f t="shared" si="212"/>
+        <v>365.65685529931892</v>
       </c>
       <c r="EA46" s="1">
-        <f t="shared" si="214"/>
-        <v>381.16872739564803</v>
+        <f t="shared" si="212"/>
+        <v>362.00028674632574</v>
       </c>
       <c r="EB46" s="1">
-        <f t="shared" si="214"/>
-        <v>377.35704012169157</v>
+        <f t="shared" si="212"/>
+        <v>358.38028387886249</v>
       </c>
       <c r="EC46" s="1">
-        <f t="shared" si="214"/>
-        <v>373.58346972047462</v>
+        <f t="shared" si="212"/>
+        <v>354.79648104007384</v>
       </c>
       <c r="ED46" s="1">
-        <f t="shared" si="214"/>
-        <v>369.8476350232699</v>
+        <f t="shared" si="212"/>
+        <v>351.2485162296731</v>
       </c>
       <c r="EE46" s="1">
-        <f t="shared" si="214"/>
-        <v>366.14915867303722</v>
+        <f t="shared" si="212"/>
+        <v>347.73603106737636</v>
       </c>
       <c r="EF46" s="1">
-        <f t="shared" si="214"/>
-        <v>362.48766708630683</v>
+        <f t="shared" si="212"/>
+        <v>344.2586707567026</v>
       </c>
       <c r="EG46" s="1">
-        <f t="shared" si="214"/>
-        <v>358.86279041544378</v>
+        <f t="shared" si="212"/>
+        <v>340.81608404913555</v>
       </c>
       <c r="EH46" s="1">
-        <f t="shared" si="214"/>
-        <v>355.27416251128932</v>
+        <f t="shared" si="212"/>
+        <v>337.40792320864421</v>
       </c>
       <c r="EI46" s="1">
-        <f t="shared" si="214"/>
-        <v>351.72142088617642</v>
+        <f t="shared" si="212"/>
+        <v>334.03384397655776</v>
       </c>
       <c r="EJ46" s="1">
-        <f t="shared" si="214"/>
-        <v>348.20420667731463</v>
+        <f t="shared" si="212"/>
+        <v>330.6935055367922</v>
       </c>
       <c r="EK46" s="1">
-        <f t="shared" si="214"/>
-        <v>344.72216461054148</v>
+        <f t="shared" si="212"/>
+        <v>327.38657048142426</v>
       </c>
       <c r="EL46" s="1">
-        <f t="shared" si="214"/>
-        <v>341.27494296443609</v>
+        <f t="shared" si="212"/>
+        <v>324.11270477661003</v>
       </c>
       <c r="EM46" s="1">
-        <f t="shared" si="214"/>
-        <v>337.86219353479174</v>
+        <f t="shared" si="212"/>
+        <v>320.87157772884393</v>
       </c>
       <c r="EN46" s="1">
-        <f t="shared" si="214"/>
-        <v>334.48357159944385</v>
+        <f t="shared" si="212"/>
+        <v>317.6628619515555</v>
       </c>
       <c r="EO46" s="1">
-        <f t="shared" si="214"/>
-        <v>331.13873588344939</v>
+        <f t="shared" si="212"/>
+        <v>314.48623333203994</v>
       </c>
       <c r="EP46" s="1">
-        <f t="shared" si="214"/>
-        <v>327.82734852461488</v>
+        <f t="shared" si="212"/>
+        <v>311.34137099871953</v>
       </c>
       <c r="EQ46" s="1">
-        <f t="shared" si="214"/>
-        <v>324.54907503936874</v>
+        <f t="shared" si="212"/>
+        <v>308.22795728873234</v>
       </c>
     </row>
     <row r="49" spans="57:57" x14ac:dyDescent="0.3">
       <c r="BE49" s="4">
         <f>NPV(BE22,AR46:EQ46)</f>
-        <v>9237.1875193448286</v>
+        <v>8648.6546435549772</v>
       </c>
     </row>
     <row r="50" spans="57:57" x14ac:dyDescent="0.3">
       <c r="BE50" s="4">
         <f>Main!D8</f>
-        <v>-406</v>
+        <v>-682.90000000000009</v>
       </c>
     </row>
     <row r="51" spans="57:57" x14ac:dyDescent="0.3">
       <c r="BE51" s="4">
         <f>BE49+BE50</f>
-        <v>8831.1875193448286</v>
+        <v>7965.7546435549775</v>
       </c>
     </row>
     <row r="52" spans="57:57" x14ac:dyDescent="0.3">
       <c r="BE52" s="5">
         <f>BE51/BB16</f>
-        <v>5.2061472141394969</v>
+        <v>4.7559583518747255</v>
       </c>
     </row>
     <row r="53" spans="57:57" x14ac:dyDescent="0.3">
       <c r="BE53" s="5">
         <f>Main!D3</f>
-        <v>8.39</v>
+        <v>7.86</v>
       </c>
     </row>
     <row r="54" spans="57:57" x14ac:dyDescent="0.3">
       <c r="BE54" s="10">
         <f>BE52/BE53-1</f>
-        <v>-0.37948185767109699</v>
+        <v>-0.39491624021950056</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/SNAP.xlsx
+++ b/Financial Analysis/SNAP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EB81D1D-BA17-41E2-BCC5-163A9D437D69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA26759E-6B0F-4EA5-BF70-C99FC6D48B53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{48C45758-2500-4F87-8506-866CB0FEFDEC}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="90">
   <si>
     <t>SNAP</t>
   </si>
@@ -292,7 +292,10 @@
     <t>FCF</t>
   </si>
   <si>
-    <t>Q225 8K</t>
+    <t>Q325 8K</t>
+  </si>
+  <si>
+    <t>Overvalued</t>
   </si>
 </sst>
 </file>
@@ -392,14 +395,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>32</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>32</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
       <xdr:row>50</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
@@ -416,7 +419,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="19972020" y="0"/>
+          <a:off x="20574000" y="0"/>
           <a:ext cx="0" cy="9304020"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -815,17 +818,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="5">
-        <v>7.86</v>
+        <v>8.58</v>
       </c>
       <c r="E3" s="3">
-        <v>45875</v>
+        <v>45967</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45909</v>
+        <v>45967</v>
       </c>
       <c r="G3" s="3">
-        <v>45958</v>
+        <v>46063</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -833,8 +836,8 @@
         <v>2</v>
       </c>
       <c r="D4" s="4">
-        <f>1674.9</f>
-        <v>1674.9</v>
+        <f>1696.5</f>
+        <v>1696.5</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>88</v>
@@ -846,7 +849,7 @@
       </c>
       <c r="D5" s="4">
         <f>D3*D4</f>
-        <v>13164.714000000002</v>
+        <v>14555.97</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -888,7 +891,7 @@
       </c>
       <c r="D9" s="4">
         <f>D5-D8</f>
-        <v>13847.614000000001</v>
+        <v>15238.869999999999</v>
       </c>
     </row>
   </sheetData>
@@ -899,7 +902,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59D9429E-4E4D-4756-99DE-9A816F2CA7A1}">
-  <dimension ref="B2:FK54"/>
+  <dimension ref="B2:FK55"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="15.21875" bestFit="1" customWidth="1"/>
@@ -1157,12 +1160,11 @@
         <v>1344.9</v>
       </c>
       <c r="AG3" s="8">
-        <f>AC3*1.08</f>
-        <v>1482.3000000000002</v>
+        <v>1506.8</v>
       </c>
       <c r="AH3" s="8">
-        <f>AD3*1.06</f>
-        <v>1650.7380000000001</v>
+        <f>AD3*1.08</f>
+        <v>1681.884</v>
       </c>
       <c r="AI3" s="8"/>
       <c r="AK3" s="8">
@@ -1195,47 +1197,47 @@
       </c>
       <c r="AR3" s="8">
         <f>SUM(AE3:AH3)</f>
-        <v>5841.1380000000008</v>
+        <v>5896.7840000000006</v>
       </c>
       <c r="AS3" s="8">
-        <f>AR3*1.05</f>
-        <v>6133.1949000000013</v>
+        <f>AR3*1.07</f>
+        <v>6309.5588800000014</v>
       </c>
       <c r="AT3" s="8">
-        <f>AS3*1.04</f>
-        <v>6378.5226960000018</v>
+        <f>AS3*1.06</f>
+        <v>6688.1324128000015</v>
       </c>
       <c r="AU3" s="8">
-        <f>AT3*1.04</f>
-        <v>6633.663603840002</v>
+        <f>AT3*1.05</f>
+        <v>7022.5390334400017</v>
       </c>
       <c r="AV3" s="8">
         <f>AU3*1.04</f>
-        <v>6899.010147993602</v>
+        <v>7303.4405947776022</v>
       </c>
       <c r="AW3" s="8">
         <f>AV3*1.03</f>
-        <v>7105.9804524334104</v>
+        <v>7522.5438126209301</v>
       </c>
       <c r="AX3" s="8">
         <f t="shared" ref="AX3:BB3" si="0">AW3*1.03</f>
-        <v>7319.1598660064128</v>
+        <v>7748.2201269995585</v>
       </c>
       <c r="AY3" s="8">
         <f t="shared" si="0"/>
-        <v>7538.7346619866057</v>
+        <v>7980.6667308095457</v>
       </c>
       <c r="AZ3" s="8">
         <f t="shared" si="0"/>
-        <v>7764.8967018462045</v>
+        <v>8220.0867327338328</v>
       </c>
       <c r="BA3" s="8">
         <f t="shared" si="0"/>
-        <v>7997.8436029015911</v>
+        <v>8466.6893347158475</v>
       </c>
       <c r="BB3" s="8">
         <f t="shared" si="0"/>
-        <v>8237.7789109886398</v>
+        <v>8720.6900147573233</v>
       </c>
     </row>
     <row r="4" spans="2:167" x14ac:dyDescent="0.3">
@@ -1333,12 +1335,11 @@
         <v>653.29999999999995</v>
       </c>
       <c r="AG4" s="4">
-        <f t="shared" ref="AG4" si="1">AG3-AG5</f>
-        <v>681.85800000000006</v>
+        <v>674.2</v>
       </c>
       <c r="AH4" s="4">
         <f>AH3-AH5</f>
-        <v>709.81734000000006</v>
+        <v>723.21012000000007</v>
       </c>
       <c r="AI4" s="4"/>
       <c r="AK4" s="4">
@@ -1371,47 +1372,47 @@
       </c>
       <c r="AR4" s="4">
         <f>SUM(AE4:AH4)</f>
-        <v>2684.5753400000003</v>
+        <v>2690.3101200000001</v>
       </c>
       <c r="AS4" s="4">
-        <f t="shared" ref="AS4:AW4" si="2">AS3-AS5</f>
-        <v>2698.6057560000004</v>
+        <f t="shared" ref="AS4:AW4" si="1">AS3-AS5</f>
+        <v>2776.2059072000002</v>
       </c>
       <c r="AT4" s="4">
+        <f t="shared" si="1"/>
+        <v>2942.7782616320001</v>
+      </c>
+      <c r="AU4" s="4">
+        <f t="shared" si="1"/>
+        <v>3089.9171747136002</v>
+      </c>
+      <c r="AV4" s="4">
+        <f t="shared" si="1"/>
+        <v>3213.5138617021444</v>
+      </c>
+      <c r="AW4" s="4">
+        <f t="shared" si="1"/>
+        <v>3309.9192775532092</v>
+      </c>
+      <c r="AX4" s="4">
+        <f t="shared" ref="AX4:BB4" si="2">AX3-AX5</f>
+        <v>3409.2168558798057</v>
+      </c>
+      <c r="AY4" s="4">
         <f t="shared" si="2"/>
-        <v>2806.5499862400006</v>
-      </c>
-      <c r="AU4" s="4">
+        <v>3511.4933615561995</v>
+      </c>
+      <c r="AZ4" s="4">
         <f t="shared" si="2"/>
-        <v>2918.8119856896005</v>
-      </c>
-      <c r="AV4" s="4">
+        <v>3616.8381624028862</v>
+      </c>
+      <c r="BA4" s="4">
         <f t="shared" si="2"/>
-        <v>3035.5644651171847</v>
-      </c>
-      <c r="AW4" s="4">
+        <v>3725.3433072749722</v>
+      </c>
+      <c r="BB4" s="4">
         <f t="shared" si="2"/>
-        <v>3126.6313990707004</v>
-      </c>
-      <c r="AX4" s="4">
-        <f t="shared" ref="AX4:BB4" si="3">AX3-AX5</f>
-        <v>3220.4303410428211</v>
-      </c>
-      <c r="AY4" s="4">
-        <f t="shared" si="3"/>
-        <v>3317.0432512741063</v>
-      </c>
-      <c r="AZ4" s="4">
-        <f t="shared" si="3"/>
-        <v>3416.5545488123298</v>
-      </c>
-      <c r="BA4" s="4">
-        <f t="shared" si="3"/>
-        <v>3519.0511852766995</v>
-      </c>
-      <c r="BB4" s="4">
-        <f t="shared" si="3"/>
-        <v>3624.622720835001</v>
+        <v>3837.1036064932214</v>
       </c>
     </row>
     <row r="5" spans="2:167" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1419,132 +1420,132 @@
         <v>24</v>
       </c>
       <c r="C5" s="8">
-        <f t="shared" ref="C5:Q5" si="4">C3-C4</f>
+        <f t="shared" ref="C5:Q5" si="3">C3-C4</f>
         <v>33.899999999999977</v>
       </c>
       <c r="D5" s="8">
+        <f t="shared" si="3"/>
+        <v>70.700000000000017</v>
+      </c>
+      <c r="E5" s="8">
+        <f t="shared" si="3"/>
+        <v>100.1</v>
+      </c>
+      <c r="F5" s="8">
+        <f t="shared" si="3"/>
+        <v>176.89999999999998</v>
+      </c>
+      <c r="G5" s="8">
+        <f t="shared" si="3"/>
+        <v>116.59999999999997</v>
+      </c>
+      <c r="H5" s="8">
+        <f t="shared" si="3"/>
+        <v>172.5</v>
+      </c>
+      <c r="I5" s="8">
+        <f t="shared" si="3"/>
+        <v>223.1</v>
+      </c>
+      <c r="J5" s="8">
+        <f t="shared" si="3"/>
+        <v>307.5</v>
+      </c>
+      <c r="K5" s="8">
+        <f t="shared" si="3"/>
+        <v>209.1</v>
+      </c>
+      <c r="L5" s="8">
+        <f t="shared" si="3"/>
+        <v>203.7</v>
+      </c>
+      <c r="M5" s="8">
+        <f t="shared" si="3"/>
+        <v>385.6</v>
+      </c>
+      <c r="N5" s="8">
+        <f t="shared" si="3"/>
+        <v>525.79999999999995</v>
+      </c>
+      <c r="O5" s="8">
+        <f t="shared" si="3"/>
+        <v>357</v>
+      </c>
+      <c r="P5" s="8">
+        <f t="shared" si="3"/>
+        <v>537.1</v>
+      </c>
+      <c r="Q5" s="8">
+        <f t="shared" si="3"/>
+        <v>624</v>
+      </c>
+      <c r="R5" s="8">
+        <f t="shared" ref="R5:S5" si="4">R3-R4</f>
+        <v>848.7</v>
+      </c>
+      <c r="S5" s="8">
         <f t="shared" si="4"/>
-        <v>70.700000000000017</v>
-      </c>
-      <c r="E5" s="8">
-        <f t="shared" si="4"/>
-        <v>100.1</v>
-      </c>
-      <c r="F5" s="8">
-        <f t="shared" si="4"/>
-        <v>176.89999999999998</v>
-      </c>
-      <c r="G5" s="8">
-        <f t="shared" si="4"/>
-        <v>116.59999999999997</v>
-      </c>
-      <c r="H5" s="8">
-        <f t="shared" si="4"/>
-        <v>172.5</v>
-      </c>
-      <c r="I5" s="8">
-        <f t="shared" si="4"/>
-        <v>223.1</v>
-      </c>
-      <c r="J5" s="8">
-        <f t="shared" si="4"/>
-        <v>307.5</v>
-      </c>
-      <c r="K5" s="8">
-        <f t="shared" si="4"/>
-        <v>209.1</v>
-      </c>
-      <c r="L5" s="8">
-        <f t="shared" si="4"/>
-        <v>203.7</v>
-      </c>
-      <c r="M5" s="8">
-        <f t="shared" si="4"/>
-        <v>385.6</v>
-      </c>
-      <c r="N5" s="8">
-        <f t="shared" si="4"/>
-        <v>525.79999999999995</v>
-      </c>
-      <c r="O5" s="8">
-        <f t="shared" si="4"/>
-        <v>357</v>
-      </c>
-      <c r="P5" s="8">
-        <f t="shared" si="4"/>
-        <v>537.1</v>
-      </c>
-      <c r="Q5" s="8">
-        <f t="shared" si="4"/>
-        <v>624</v>
-      </c>
-      <c r="R5" s="8">
-        <f t="shared" ref="R5:S5" si="5">R3-R4</f>
-        <v>848.7</v>
-      </c>
-      <c r="S5" s="8">
+        <v>641.80000000000007</v>
+      </c>
+      <c r="T5" s="8">
+        <f t="shared" ref="T5:U5" si="5">T3-T4</f>
+        <v>664.50000000000011</v>
+      </c>
+      <c r="U5" s="8">
         <f t="shared" si="5"/>
-        <v>641.80000000000007</v>
-      </c>
-      <c r="T5" s="8">
-        <f t="shared" ref="T5:U5" si="6">T3-T4</f>
-        <v>664.50000000000011</v>
-      </c>
-      <c r="U5" s="8">
-        <f t="shared" si="6"/>
         <v>661.7</v>
       </c>
       <c r="V5" s="8">
-        <f t="shared" ref="V5" si="7">V3-V4</f>
+        <f t="shared" ref="V5" si="6">V3-V4</f>
         <v>818.40000000000009</v>
       </c>
       <c r="W5" s="8">
-        <f t="shared" ref="W5" si="8">W3-W4</f>
+        <f t="shared" ref="W5" si="7">W3-W4</f>
         <v>548.6</v>
       </c>
       <c r="X5" s="8">
-        <f t="shared" ref="X5:Y5" si="9">X3-X4</f>
+        <f t="shared" ref="X5:Y5" si="8">X3-X4</f>
         <v>570.80000000000007</v>
       </c>
       <c r="Y5" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>632.79999999999995</v>
       </c>
       <c r="Z5" s="8">
-        <f t="shared" ref="Z5" si="10">Z3-Z4</f>
+        <f t="shared" ref="Z5" si="9">Z3-Z4</f>
         <v>739.8</v>
       </c>
       <c r="AA5" s="8">
-        <f t="shared" ref="AA5" si="11">AA3-AA4</f>
+        <f t="shared" ref="AA5" si="10">AA3-AA4</f>
         <v>620.09999999999991</v>
       </c>
       <c r="AB5" s="8">
-        <f t="shared" ref="AB5:AF5" si="12">AB3-AB4</f>
+        <f t="shared" ref="AB5:AG5" si="11">AB3-AB4</f>
         <v>647.9</v>
       </c>
       <c r="AC5" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>733.6</v>
       </c>
       <c r="AD5" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>885.59999999999991</v>
       </c>
       <c r="AE5" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>723.6</v>
       </c>
       <c r="AF5" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>691.60000000000014</v>
       </c>
       <c r="AG5" s="8">
-        <f t="shared" ref="AG5" si="13">AG3*0.54</f>
-        <v>800.44200000000012</v>
+        <f t="shared" si="11"/>
+        <v>832.59999999999991</v>
       </c>
       <c r="AH5" s="8">
         <f>AH3*0.57</f>
-        <v>940.92066</v>
+        <v>958.67387999999994</v>
       </c>
       <c r="AI5" s="8"/>
       <c r="AJ5" s="8"/>
@@ -1561,64 +1562,64 @@
         <v>1324.1999999999998</v>
       </c>
       <c r="AN5" s="8">
-        <f t="shared" ref="AN5:AR5" si="14">AN3-AN4</f>
+        <f t="shared" ref="AN5:AR5" si="12">AN3-AN4</f>
         <v>2366.8000000000002</v>
       </c>
       <c r="AO5" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>2786.4000000000005</v>
       </c>
       <c r="AP5" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>2492</v>
       </c>
       <c r="AQ5" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>2887.2</v>
       </c>
       <c r="AR5" s="8">
-        <f t="shared" si="14"/>
-        <v>3156.5626600000005</v>
+        <f t="shared" si="12"/>
+        <v>3206.4738800000005</v>
       </c>
       <c r="AS5" s="8">
         <f>AS3*0.56</f>
-        <v>3434.5891440000009</v>
+        <v>3533.3529728000012</v>
       </c>
       <c r="AT5" s="8">
-        <f t="shared" ref="AT5:BB5" si="15">AT3*0.56</f>
-        <v>3571.9727097600012</v>
+        <f t="shared" ref="AT5:BB5" si="13">AT3*0.56</f>
+        <v>3745.3541511680014</v>
       </c>
       <c r="AU5" s="8">
-        <f t="shared" si="15"/>
-        <v>3714.8516181504015</v>
+        <f t="shared" si="13"/>
+        <v>3932.6218587264016</v>
       </c>
       <c r="AV5" s="8">
-        <f t="shared" si="15"/>
-        <v>3863.4456828764173</v>
+        <f t="shared" si="13"/>
+        <v>4089.9267330754578</v>
       </c>
       <c r="AW5" s="8">
-        <f t="shared" si="15"/>
-        <v>3979.34905336271</v>
+        <f t="shared" si="13"/>
+        <v>4212.6245350677209</v>
       </c>
       <c r="AX5" s="8">
-        <f t="shared" si="15"/>
-        <v>4098.7295249635918</v>
+        <f t="shared" si="13"/>
+        <v>4339.0032711197528</v>
       </c>
       <c r="AY5" s="8">
-        <f t="shared" si="15"/>
-        <v>4221.6914107124994</v>
+        <f t="shared" si="13"/>
+        <v>4469.1733692533462</v>
       </c>
       <c r="AZ5" s="8">
-        <f t="shared" si="15"/>
-        <v>4348.3421530338746</v>
+        <f t="shared" si="13"/>
+        <v>4603.2485703309467</v>
       </c>
       <c r="BA5" s="8">
-        <f t="shared" si="15"/>
-        <v>4478.7924176248916</v>
+        <f t="shared" si="13"/>
+        <v>4741.3460274408753</v>
       </c>
       <c r="BB5" s="8">
-        <f t="shared" si="15"/>
-        <v>4613.1561901536388</v>
+        <f t="shared" si="13"/>
+        <v>4883.5864082641019</v>
       </c>
     </row>
     <row r="6" spans="2:167" x14ac:dyDescent="0.3">
@@ -1716,8 +1717,7 @@
         <v>443.3</v>
       </c>
       <c r="AG6" s="4">
-        <f>AC6*1.1</f>
-        <v>454.08000000000004</v>
+        <v>453.4</v>
       </c>
       <c r="AH6" s="4">
         <f>AD6*1.1</f>
@@ -1734,7 +1734,7 @@
         <v>883.5</v>
       </c>
       <c r="AM6" s="4">
-        <f t="shared" ref="AM6:AM8" si="16">SUM(K6:N6)</f>
+        <f t="shared" ref="AM6:AM8" si="14">SUM(K6:N6)</f>
         <v>1101.5</v>
       </c>
       <c r="AN6" s="4">
@@ -1755,47 +1755,47 @@
       </c>
       <c r="AR6" s="4">
         <f>SUM(AE6:AH6)</f>
-        <v>1786.77</v>
+        <v>1786.0900000000001</v>
       </c>
       <c r="AS6" s="4">
         <f>AR6*1.01</f>
-        <v>1804.6377</v>
+        <v>1803.9509000000003</v>
       </c>
       <c r="AT6" s="4">
-        <f t="shared" ref="AT6:BB6" si="17">AS6*1.01</f>
-        <v>1822.6840770000001</v>
+        <f t="shared" ref="AT6:BB6" si="15">AS6*1.01</f>
+        <v>1821.9904090000002</v>
       </c>
       <c r="AU6" s="4">
-        <f t="shared" si="17"/>
-        <v>1840.9109177700002</v>
+        <f t="shared" si="15"/>
+        <v>1840.2103130900002</v>
       </c>
       <c r="AV6" s="4">
-        <f t="shared" si="17"/>
-        <v>1859.3200269477002</v>
+        <f t="shared" si="15"/>
+        <v>1858.6124162209003</v>
       </c>
       <c r="AW6" s="4">
-        <f t="shared" si="17"/>
-        <v>1877.9132272171771</v>
+        <f t="shared" si="15"/>
+        <v>1877.1985403831093</v>
       </c>
       <c r="AX6" s="4">
-        <f t="shared" si="17"/>
-        <v>1896.692359489349</v>
+        <f t="shared" si="15"/>
+        <v>1895.9705257869405</v>
       </c>
       <c r="AY6" s="4">
-        <f t="shared" si="17"/>
-        <v>1915.6592830842426</v>
+        <f t="shared" si="15"/>
+        <v>1914.9302310448099</v>
       </c>
       <c r="AZ6" s="4">
-        <f t="shared" si="17"/>
-        <v>1934.8158759150851</v>
+        <f t="shared" si="15"/>
+        <v>1934.079533355258</v>
       </c>
       <c r="BA6" s="4">
-        <f t="shared" si="17"/>
-        <v>1954.1640346742361</v>
+        <f t="shared" si="15"/>
+        <v>1953.4203286888107</v>
       </c>
       <c r="BB6" s="4">
-        <f t="shared" si="17"/>
-        <v>1973.7056750209783</v>
+        <f t="shared" si="15"/>
+        <v>1972.954531975699</v>
       </c>
     </row>
     <row r="7" spans="2:167" x14ac:dyDescent="0.3">
@@ -1893,12 +1893,11 @@
         <v>257.89999999999998</v>
       </c>
       <c r="AG7" s="4">
-        <f>AG3*0.19</f>
-        <v>281.63700000000006</v>
+        <v>256.2</v>
       </c>
       <c r="AH7" s="4">
         <f>AH3*0.16</f>
-        <v>264.11808000000002</v>
+        <v>269.10144000000003</v>
       </c>
       <c r="AI7" s="4"/>
       <c r="AK7" s="4">
@@ -1910,7 +1909,7 @@
         <v>458.6</v>
       </c>
       <c r="AM7" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>555.4</v>
       </c>
       <c r="AN7" s="4">
@@ -1931,47 +1930,47 @@
       </c>
       <c r="AR7" s="4">
         <f>SUM(AE7:AH7)</f>
-        <v>1061.65508</v>
+        <v>1041.2014399999998</v>
       </c>
       <c r="AS7" s="4">
         <f>AS3*0.17</f>
-        <v>1042.6431330000003</v>
+        <v>1072.6250096000003</v>
       </c>
       <c r="AT7" s="4">
         <f>AT3*0.16</f>
-        <v>1020.5636313600003</v>
+        <v>1070.1011860480003</v>
       </c>
       <c r="AU7" s="4">
         <f>AU3*0.16</f>
-        <v>1061.3861766144003</v>
+        <v>1123.6062453504003</v>
       </c>
       <c r="AV7" s="4">
-        <f t="shared" ref="AV7:BB7" si="18">AV3*0.16</f>
-        <v>1103.8416236789762</v>
+        <f t="shared" ref="AV7:BB7" si="16">AV3*0.16</f>
+        <v>1168.5504951644164</v>
       </c>
       <c r="AW7" s="4">
-        <f t="shared" si="18"/>
-        <v>1136.9568723893458</v>
+        <f t="shared" si="16"/>
+        <v>1203.6070100193488</v>
       </c>
       <c r="AX7" s="4">
-        <f t="shared" si="18"/>
-        <v>1171.0655785610261</v>
+        <f t="shared" si="16"/>
+        <v>1239.7152203199294</v>
       </c>
       <c r="AY7" s="4">
-        <f t="shared" si="18"/>
-        <v>1206.197545917857</v>
+        <f t="shared" si="16"/>
+        <v>1276.9066769295273</v>
       </c>
       <c r="AZ7" s="4">
-        <f t="shared" si="18"/>
-        <v>1242.3834722953927</v>
+        <f t="shared" si="16"/>
+        <v>1315.2138772374133</v>
       </c>
       <c r="BA7" s="4">
-        <f t="shared" si="18"/>
-        <v>1279.6549764642546</v>
+        <f t="shared" si="16"/>
+        <v>1354.6702935545356</v>
       </c>
       <c r="BB7" s="4">
-        <f t="shared" si="18"/>
-        <v>1318.0446257581823</v>
+        <f t="shared" si="16"/>
+        <v>1395.3104023611718</v>
       </c>
     </row>
     <row r="8" spans="2:167" x14ac:dyDescent="0.3">
@@ -2069,8 +2068,7 @@
         <v>250.1</v>
       </c>
       <c r="AG8" s="4">
-        <f>AC8*1.1</f>
-        <v>243.10000000000002</v>
+        <v>251.3</v>
       </c>
       <c r="AH8" s="4">
         <f>AD8*1.1</f>
@@ -2086,7 +2084,7 @@
         <v>580.9</v>
       </c>
       <c r="AM8" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>529.1</v>
       </c>
       <c r="AN8" s="4">
@@ -2107,47 +2105,47 @@
       </c>
       <c r="AR8" s="4">
         <f>SUM(AE8:AH8)</f>
-        <v>994.03</v>
+        <v>1002.23</v>
       </c>
       <c r="AS8" s="4">
         <f>AR8*1.04</f>
-        <v>1033.7912000000001</v>
+        <v>1042.3192000000001</v>
       </c>
       <c r="AT8" s="4">
         <f>AS8*1.03</f>
-        <v>1064.8049360000002</v>
+        <v>1073.5887760000003</v>
       </c>
       <c r="AU8" s="4">
-        <f t="shared" ref="AU8:AW8" si="19">AT8*1.02</f>
-        <v>1086.1010347200001</v>
+        <f t="shared" ref="AU8:AW8" si="17">AT8*1.02</f>
+        <v>1095.0605515200002</v>
       </c>
       <c r="AV8" s="4">
-        <f t="shared" si="19"/>
-        <v>1107.8230554144002</v>
+        <f t="shared" si="17"/>
+        <v>1116.9617625504002</v>
       </c>
       <c r="AW8" s="4">
-        <f t="shared" si="19"/>
-        <v>1129.9795165226883</v>
+        <f t="shared" si="17"/>
+        <v>1139.3009978014081</v>
       </c>
       <c r="AX8" s="4">
         <f>AW8*1.01</f>
-        <v>1141.2793116879152</v>
+        <v>1150.6940077794222</v>
       </c>
       <c r="AY8" s="4">
-        <f t="shared" ref="AY8:BB8" si="20">AX8*1.01</f>
-        <v>1152.6921048047943</v>
+        <f t="shared" ref="AY8:BB8" si="18">AX8*1.01</f>
+        <v>1162.2009478572165</v>
       </c>
       <c r="AZ8" s="4">
-        <f t="shared" si="20"/>
-        <v>1164.2190258528424</v>
+        <f t="shared" si="18"/>
+        <v>1173.8229573357887</v>
       </c>
       <c r="BA8" s="4">
-        <f t="shared" si="20"/>
-        <v>1175.8612161113708</v>
+        <f t="shared" si="18"/>
+        <v>1185.5611869091465</v>
       </c>
       <c r="BB8" s="4">
-        <f t="shared" si="20"/>
-        <v>1187.6198282724845</v>
+        <f t="shared" si="18"/>
+        <v>1197.416798778238</v>
       </c>
     </row>
     <row r="9" spans="2:167" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2155,132 +2153,132 @@
         <v>28</v>
       </c>
       <c r="C9" s="8">
-        <f t="shared" ref="C9:Q9" si="21">C5-C6-C7-C8</f>
+        <f t="shared" ref="C9:Q9" si="19">C5-C6-C7-C8</f>
         <v>-392.50000000000006</v>
       </c>
       <c r="D9" s="8">
+        <f t="shared" si="19"/>
+        <v>-357.79999999999995</v>
+      </c>
+      <c r="E9" s="8">
+        <f t="shared" si="19"/>
+        <v>-323.5</v>
+      </c>
+      <c r="F9" s="8">
+        <f t="shared" si="19"/>
+        <v>-194.70000000000005</v>
+      </c>
+      <c r="G9" s="8">
+        <f t="shared" si="19"/>
+        <v>-316.20000000000005</v>
+      </c>
+      <c r="H9" s="8">
+        <f t="shared" si="19"/>
+        <v>-304.79999999999995</v>
+      </c>
+      <c r="I9" s="8">
+        <f t="shared" si="19"/>
+        <v>-228.8</v>
+      </c>
+      <c r="J9" s="8">
+        <f t="shared" si="19"/>
+        <v>-253.5</v>
+      </c>
+      <c r="K9" s="8">
+        <f t="shared" si="19"/>
+        <v>-286.29999999999995</v>
+      </c>
+      <c r="L9" s="8">
+        <f t="shared" si="19"/>
+        <v>-310.59999999999997</v>
+      </c>
+      <c r="M9" s="8">
+        <f t="shared" si="19"/>
+        <v>-167.8</v>
+      </c>
+      <c r="N9" s="8">
+        <f t="shared" si="19"/>
+        <v>-97.100000000000023</v>
+      </c>
+      <c r="O9" s="8">
+        <f t="shared" si="19"/>
+        <v>-303.60000000000002</v>
+      </c>
+      <c r="P9" s="8">
+        <f t="shared" si="19"/>
+        <v>-192.49999999999994</v>
+      </c>
+      <c r="Q9" s="8">
+        <f t="shared" si="19"/>
+        <v>-180.8</v>
+      </c>
+      <c r="R9" s="8">
+        <f t="shared" ref="R9:S9" si="20">R5-R6-R7-R8</f>
+        <v>-25.099999999999937</v>
+      </c>
+      <c r="S9" s="8">
+        <f t="shared" si="20"/>
+        <v>-271.59999999999997</v>
+      </c>
+      <c r="T9" s="8">
+        <f t="shared" ref="T9:U9" si="21">T5-T6-T7-T8</f>
+        <v>-400.99999999999989</v>
+      </c>
+      <c r="U9" s="8">
         <f t="shared" si="21"/>
-        <v>-357.79999999999995</v>
-      </c>
-      <c r="E9" s="8">
-        <f t="shared" si="21"/>
-        <v>-323.5</v>
-      </c>
-      <c r="F9" s="8">
-        <f t="shared" si="21"/>
-        <v>-194.70000000000005</v>
-      </c>
-      <c r="G9" s="8">
-        <f t="shared" si="21"/>
-        <v>-316.20000000000005</v>
-      </c>
-      <c r="H9" s="8">
-        <f t="shared" si="21"/>
-        <v>-304.79999999999995</v>
-      </c>
-      <c r="I9" s="8">
-        <f t="shared" si="21"/>
-        <v>-228.8</v>
-      </c>
-      <c r="J9" s="8">
-        <f t="shared" si="21"/>
-        <v>-253.5</v>
-      </c>
-      <c r="K9" s="8">
-        <f t="shared" si="21"/>
-        <v>-286.29999999999995</v>
-      </c>
-      <c r="L9" s="8">
-        <f t="shared" si="21"/>
-        <v>-310.59999999999997</v>
-      </c>
-      <c r="M9" s="8">
-        <f t="shared" si="21"/>
-        <v>-167.8</v>
-      </c>
-      <c r="N9" s="8">
-        <f t="shared" si="21"/>
-        <v>-97.100000000000023</v>
-      </c>
-      <c r="O9" s="8">
-        <f t="shared" si="21"/>
-        <v>-303.60000000000002</v>
-      </c>
-      <c r="P9" s="8">
-        <f t="shared" si="21"/>
-        <v>-192.49999999999994</v>
-      </c>
-      <c r="Q9" s="8">
-        <f t="shared" si="21"/>
-        <v>-180.8</v>
-      </c>
-      <c r="R9" s="8">
-        <f t="shared" ref="R9:S9" si="22">R5-R6-R7-R8</f>
-        <v>-25.099999999999937</v>
-      </c>
-      <c r="S9" s="8">
-        <f t="shared" si="22"/>
-        <v>-271.59999999999997</v>
-      </c>
-      <c r="T9" s="8">
-        <f t="shared" ref="T9:U9" si="23">T5-T6-T7-T8</f>
-        <v>-400.99999999999989</v>
-      </c>
-      <c r="U9" s="8">
-        <f t="shared" si="23"/>
         <v>-435.2999999999999</v>
       </c>
       <c r="V9" s="8">
-        <f t="shared" ref="V9" si="24">V5-V6-V7-V8</f>
+        <f t="shared" ref="V9" si="22">V5-V6-V7-V8</f>
         <v>-287.59999999999991</v>
       </c>
       <c r="W9" s="8">
-        <f t="shared" ref="W9" si="25">W5-W6-W7-W8</f>
+        <f t="shared" ref="W9" si="23">W5-W6-W7-W8</f>
         <v>-365.2</v>
       </c>
       <c r="X9" s="8">
-        <f t="shared" ref="X9:Y9" si="26">X5-X6-X7-X8</f>
+        <f t="shared" ref="X9:Y9" si="24">X5-X6-X7-X8</f>
         <v>-404.4</v>
       </c>
       <c r="Y9" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="24"/>
         <v>-380.20000000000005</v>
       </c>
       <c r="Z9" s="8">
-        <f t="shared" ref="Z9" si="27">Z5-Z6-Z7-Z8</f>
+        <f t="shared" ref="Z9" si="25">Z5-Z6-Z7-Z8</f>
         <v>-248.70000000000005</v>
       </c>
       <c r="AA9" s="8">
-        <f t="shared" ref="AA9" si="28">AA5-AA6-AA7-AA8</f>
+        <f t="shared" ref="AA9" si="26">AA5-AA6-AA7-AA8</f>
         <v>-333.2000000000001</v>
       </c>
       <c r="AB9" s="8">
-        <f t="shared" ref="AB9:AH9" si="29">AB5-AB6-AB7-AB8</f>
+        <f t="shared" ref="AB9:AH9" si="27">AB5-AB6-AB7-AB8</f>
         <v>-253.90000000000003</v>
       </c>
       <c r="AC9" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>-173.3</v>
       </c>
       <c r="AD9" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>-26.800000000000068</v>
       </c>
       <c r="AE9" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>-193.99999999999997</v>
       </c>
       <c r="AF9" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>-259.69999999999982</v>
       </c>
       <c r="AG9" s="8">
-        <f t="shared" si="29"/>
-        <v>-178.375</v>
+        <f t="shared" si="27"/>
+        <v>-128.30000000000007</v>
       </c>
       <c r="AH9" s="8">
-        <f t="shared" si="29"/>
-        <v>-53.817420000000027</v>
+        <f t="shared" si="27"/>
+        <v>-41.04756000000009</v>
       </c>
       <c r="AI9" s="8"/>
       <c r="AK9" s="8">
@@ -2296,64 +2294,64 @@
         <v>-861.80000000000018</v>
       </c>
       <c r="AN9" s="8">
-        <f t="shared" ref="AN9:AW9" si="30">AN5-AN6-AN7-AN8</f>
+        <f t="shared" ref="AN9:AW9" si="28">AN5-AN6-AN7-AN8</f>
         <v>-701.99999999999989</v>
       </c>
       <c r="AO9" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>-1395.4999999999995</v>
       </c>
       <c r="AP9" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>-1398.5</v>
       </c>
       <c r="AQ9" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>-787.19999999999982</v>
       </c>
       <c r="AR9" s="8">
-        <f t="shared" si="30"/>
-        <v>-685.89241999999945</v>
+        <f t="shared" si="28"/>
+        <v>-623.04755999999952</v>
       </c>
       <c r="AS9" s="8">
-        <f t="shared" si="30"/>
-        <v>-446.48288899999943</v>
+        <f t="shared" si="28"/>
+        <v>-385.54213679999953</v>
       </c>
       <c r="AT9" s="8">
-        <f t="shared" si="30"/>
-        <v>-336.07993459999943</v>
+        <f t="shared" si="28"/>
+        <v>-220.32621987999937</v>
       </c>
       <c r="AU9" s="8">
-        <f t="shared" si="30"/>
-        <v>-273.54651095399913</v>
+        <f t="shared" si="28"/>
+        <v>-126.25525123399893</v>
       </c>
       <c r="AV9" s="8">
-        <f t="shared" si="30"/>
-        <v>-207.53902316465928</v>
+        <f t="shared" si="28"/>
+        <v>-54.197940860258996</v>
       </c>
       <c r="AW9" s="8">
-        <f t="shared" si="30"/>
-        <v>-165.50056276650139</v>
+        <f t="shared" si="28"/>
+        <v>-7.4820131361454969</v>
       </c>
       <c r="AX9" s="8">
-        <f t="shared" ref="AX9:BB9" si="31">AX5-AX6-AX7-AX8</f>
-        <v>-110.30772477469827</v>
+        <f t="shared" ref="AX9:BB9" si="29">AX5-AX6-AX7-AX8</f>
+        <v>52.623517233460689</v>
       </c>
       <c r="AY9" s="8">
-        <f t="shared" si="31"/>
-        <v>-52.857523094394764</v>
+        <f t="shared" si="29"/>
+        <v>115.13551342179221</v>
       </c>
       <c r="AZ9" s="8">
-        <f t="shared" si="31"/>
-        <v>6.9237789705543946</v>
+        <f t="shared" si="29"/>
+        <v>180.13220240248688</v>
       </c>
       <c r="BA9" s="8">
-        <f t="shared" si="31"/>
-        <v>69.112190375030195</v>
+        <f t="shared" si="29"/>
+        <v>247.69421828838267</v>
       </c>
       <c r="BB9" s="8">
-        <f t="shared" si="31"/>
-        <v>133.78606110199348</v>
+        <f t="shared" si="29"/>
+        <v>317.90467514899319</v>
       </c>
     </row>
     <row r="10" spans="2:167" x14ac:dyDescent="0.3">
@@ -2451,11 +2449,10 @@
         <v>-33.200000000000003</v>
       </c>
       <c r="AG10" s="4">
-        <f t="shared" ref="AG10:AH10" si="32">AC10*1.01</f>
-        <v>-38.884999999999998</v>
+        <v>-32.299999999999997</v>
       </c>
       <c r="AH10" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" ref="AG10:AH10" si="30">AD10*1.01</f>
         <v>-38.986000000000004</v>
       </c>
       <c r="AI10" s="4"/>
@@ -2468,7 +2465,7 @@
         <v>-35.700000000000003</v>
       </c>
       <c r="AM10" s="4">
-        <f t="shared" ref="AM10:AM12" si="33">SUM(K10:N10)</f>
+        <f t="shared" ref="AM10:AM12" si="31">SUM(K10:N10)</f>
         <v>-18.169</v>
       </c>
       <c r="AN10" s="4">
@@ -2489,47 +2486,47 @@
       </c>
       <c r="AR10" s="4">
         <f>SUM(AE10:AH10)</f>
-        <v>-148.07100000000003</v>
+        <v>-141.48599999999999</v>
       </c>
       <c r="AS10" s="4">
-        <f t="shared" ref="AS10:BB10" si="34">AR10*1.02</f>
-        <v>-151.03242000000003</v>
+        <f t="shared" ref="AS10:BB10" si="32">AR10*1.02</f>
+        <v>-144.31572</v>
       </c>
       <c r="AT10" s="4">
-        <f t="shared" si="34"/>
-        <v>-154.05306840000003</v>
+        <f t="shared" si="32"/>
+        <v>-147.2020344</v>
       </c>
       <c r="AU10" s="4">
-        <f t="shared" si="34"/>
-        <v>-157.13412976800004</v>
+        <f t="shared" si="32"/>
+        <v>-150.146075088</v>
       </c>
       <c r="AV10" s="4">
-        <f t="shared" si="34"/>
-        <v>-160.27681236336005</v>
+        <f t="shared" si="32"/>
+        <v>-153.14899658976</v>
       </c>
       <c r="AW10" s="4">
-        <f t="shared" si="34"/>
-        <v>-163.48234861062724</v>
+        <f t="shared" si="32"/>
+        <v>-156.21197652155521</v>
       </c>
       <c r="AX10" s="4">
-        <f t="shared" si="34"/>
-        <v>-166.75199558283978</v>
+        <f t="shared" si="32"/>
+        <v>-159.33621605198633</v>
       </c>
       <c r="AY10" s="4">
-        <f t="shared" si="34"/>
-        <v>-170.08703549449658</v>
+        <f t="shared" si="32"/>
+        <v>-162.52294037302605</v>
       </c>
       <c r="AZ10" s="4">
-        <f t="shared" si="34"/>
-        <v>-173.48877620438651</v>
+        <f t="shared" si="32"/>
+        <v>-165.77339918048656</v>
       </c>
       <c r="BA10" s="4">
-        <f t="shared" si="34"/>
-        <v>-176.95855172847425</v>
+        <f t="shared" si="32"/>
+        <v>-169.08886716409629</v>
       </c>
       <c r="BB10" s="4">
-        <f t="shared" si="34"/>
-        <v>-180.49772276304373</v>
+        <f t="shared" si="32"/>
+        <v>-172.47064450737821</v>
       </c>
     </row>
     <row r="11" spans="2:167" x14ac:dyDescent="0.3">
@@ -2627,7 +2624,7 @@
         <v>27.6</v>
       </c>
       <c r="AG11" s="4">
-        <v>6</v>
+        <v>34.5</v>
       </c>
       <c r="AH11" s="4">
         <v>6</v>
@@ -2642,7 +2639,7 @@
         <v>25.1</v>
       </c>
       <c r="AM11" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>97.2</v>
       </c>
       <c r="AN11" s="4">
@@ -2663,47 +2660,47 @@
       </c>
       <c r="AR11" s="4">
         <f>SUM(AE11:AH11)</f>
-        <v>63</v>
+        <v>91.5</v>
       </c>
       <c r="AS11" s="4">
         <f>AR11*1.03</f>
-        <v>64.89</v>
+        <v>94.245000000000005</v>
       </c>
       <c r="AT11" s="4">
-        <f t="shared" ref="AT11:BB11" si="35">AS11*1.03</f>
-        <v>66.836700000000008</v>
+        <f t="shared" ref="AT11:BB11" si="33">AS11*1.03</f>
+        <v>97.07235</v>
       </c>
       <c r="AU11" s="4">
-        <f t="shared" si="35"/>
-        <v>68.841801000000004</v>
+        <f t="shared" si="33"/>
+        <v>99.984520500000002</v>
       </c>
       <c r="AV11" s="4">
-        <f t="shared" si="35"/>
-        <v>70.907055030000009</v>
+        <f t="shared" si="33"/>
+        <v>102.984056115</v>
       </c>
       <c r="AW11" s="4">
-        <f t="shared" si="35"/>
-        <v>73.034266680900018</v>
+        <f t="shared" si="33"/>
+        <v>106.07357779845</v>
       </c>
       <c r="AX11" s="4">
-        <f t="shared" si="35"/>
-        <v>75.225294681327014</v>
+        <f t="shared" si="33"/>
+        <v>109.2557851324035</v>
       </c>
       <c r="AY11" s="4">
-        <f t="shared" si="35"/>
-        <v>77.482053521766829</v>
+        <f t="shared" si="33"/>
+        <v>112.53345868637561</v>
       </c>
       <c r="AZ11" s="4">
-        <f t="shared" si="35"/>
-        <v>79.806515127419843</v>
+        <f t="shared" si="33"/>
+        <v>115.90946244696688</v>
       </c>
       <c r="BA11" s="4">
-        <f t="shared" si="35"/>
-        <v>82.200710581242447</v>
+        <f t="shared" si="33"/>
+        <v>119.38674632037589</v>
       </c>
       <c r="BB11" s="4">
-        <f t="shared" si="35"/>
-        <v>84.666731898679728</v>
+        <f t="shared" si="33"/>
+        <v>122.96834870998717</v>
       </c>
     </row>
     <row r="12" spans="2:167" x14ac:dyDescent="0.3">
@@ -2801,7 +2798,7 @@
         <v>0.8</v>
       </c>
       <c r="AG12" s="4">
-        <v>0</v>
+        <v>-27.6</v>
       </c>
       <c r="AH12" s="4">
         <v>0</v>
@@ -2816,7 +2813,7 @@
         <v>-58.9</v>
       </c>
       <c r="AM12" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>-15</v>
       </c>
       <c r="AN12" s="4">
@@ -2837,47 +2834,47 @@
       </c>
       <c r="AR12" s="4">
         <f>SUM(AE12:AH12)</f>
-        <v>-48.300000000000004</v>
+        <v>-75.900000000000006</v>
       </c>
       <c r="AS12" s="4">
-        <f t="shared" ref="AS12:AX12" si="36">-AR15*0.02</f>
-        <v>11.206106979999991</v>
+        <f t="shared" ref="AS12:AX12" si="34">-AR15*0.02</f>
+        <v>10.26716963999999</v>
       </c>
       <c r="AT12" s="4">
-        <f t="shared" si="36"/>
-        <v>5.9447452156799914</v>
+        <f t="shared" si="34"/>
+        <v>5.5318173830399919</v>
       </c>
       <c r="AU12" s="4">
-        <f t="shared" si="36"/>
-        <v>4.0769329826508702</v>
+        <f t="shared" si="34"/>
+        <v>2.8116536458086294</v>
       </c>
       <c r="AV12" s="4">
-        <f t="shared" si="36"/>
-        <v>3.0292978426983996</v>
+        <f t="shared" si="34"/>
+        <v>1.262485604668921</v>
       </c>
       <c r="AW12" s="4">
-        <f t="shared" si="36"/>
-        <v>1.9391770187839623</v>
+        <f t="shared" si="34"/>
+        <v>8.4727775842686648E-2</v>
       </c>
       <c r="AX12" s="4">
-        <f t="shared" si="36"/>
-        <v>1.2318665256889301</v>
+        <f t="shared" si="34"/>
+        <v>-0.68114652497787254</v>
       </c>
       <c r="AY12" s="4">
-        <f t="shared" ref="AY12" si="37">-AX15*0.02</f>
-        <v>0.32020624638199097</v>
+        <f t="shared" ref="AY12" si="35">-AX15*0.02</f>
+        <v>-1.6541615148483422</v>
       </c>
       <c r="AZ12" s="4">
-        <f t="shared" ref="AZ12" si="38">-AY15*0.02</f>
-        <v>-0.63083604211124777</v>
+        <f t="shared" ref="AZ12" si="36">-AY15*0.02</f>
+        <v>-2.6684665059726553</v>
       </c>
       <c r="BA12" s="4">
-        <f t="shared" ref="BA12" si="39">-AZ15*0.02</f>
-        <v>-1.6197900174341169</v>
+        <f t="shared" ref="BA12" si="37">-AZ15*0.02</f>
+        <v>-3.7226336902716675</v>
       </c>
       <c r="BB12" s="4">
-        <f t="shared" ref="BB12" si="40">-BA15*0.02</f>
-        <v>-2.6478371446351376</v>
+        <f t="shared" ref="BB12" si="38">-BA15*0.02</f>
+        <v>-4.8179035651579962</v>
       </c>
     </row>
     <row r="13" spans="2:167" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2885,132 +2882,132 @@
         <v>30</v>
       </c>
       <c r="C13" s="8">
-        <f t="shared" ref="C13:L13" si="41">C9-C10-C11-C12</f>
+        <f t="shared" ref="C13:L13" si="39">C9-C10-C11-C12</f>
         <v>-384.1</v>
       </c>
       <c r="D13" s="8">
+        <f t="shared" si="39"/>
+        <v>-352.19999999999993</v>
+      </c>
+      <c r="E13" s="8">
+        <f t="shared" si="39"/>
+        <v>-325</v>
+      </c>
+      <c r="F13" s="8">
+        <f t="shared" si="39"/>
+        <v>-192.00000000000003</v>
+      </c>
+      <c r="G13" s="8">
+        <f t="shared" si="39"/>
+        <v>-310.30000000000007</v>
+      </c>
+      <c r="H13" s="8">
+        <f t="shared" si="39"/>
+        <v>-254.2</v>
+      </c>
+      <c r="I13" s="8">
+        <f t="shared" si="39"/>
+        <v>-229</v>
+      </c>
+      <c r="J13" s="8">
+        <f t="shared" si="39"/>
+        <v>-240.3</v>
+      </c>
+      <c r="K13" s="8">
+        <f t="shared" si="39"/>
+        <v>-305.19999999999993</v>
+      </c>
+      <c r="L13" s="8">
+        <f t="shared" si="39"/>
+        <v>-326.89999999999992</v>
+      </c>
+      <c r="M13" s="8">
+        <f t="shared" ref="M13:Q13" si="40">M9-M10-M11-M12</f>
+        <v>-198.89999999999998</v>
+      </c>
+      <c r="N13" s="8">
+        <f t="shared" si="40"/>
+        <v>-94.831000000000031</v>
+      </c>
+      <c r="O13" s="8">
+        <f t="shared" si="40"/>
+        <v>-285.39999999999998</v>
+      </c>
+      <c r="P13" s="8">
+        <f t="shared" si="40"/>
+        <v>-153.49999999999994</v>
+      </c>
+      <c r="Q13" s="8">
+        <f t="shared" si="40"/>
+        <v>-70.900000000000006</v>
+      </c>
+      <c r="R13" s="8">
+        <f t="shared" ref="R13:S13" si="41">R9-R10-R11-R12</f>
+        <v>35.600000000000065</v>
+      </c>
+      <c r="S13" s="8">
         <f t="shared" si="41"/>
-        <v>-352.19999999999993</v>
-      </c>
-      <c r="E13" s="8">
-        <f t="shared" si="41"/>
-        <v>-325</v>
-      </c>
-      <c r="F13" s="8">
-        <f t="shared" si="41"/>
-        <v>-192.00000000000003</v>
-      </c>
-      <c r="G13" s="8">
-        <f t="shared" si="41"/>
-        <v>-310.30000000000007</v>
-      </c>
-      <c r="H13" s="8">
-        <f t="shared" si="41"/>
-        <v>-254.2</v>
-      </c>
-      <c r="I13" s="8">
-        <f t="shared" si="41"/>
-        <v>-229</v>
-      </c>
-      <c r="J13" s="8">
-        <f t="shared" si="41"/>
-        <v>-240.3</v>
-      </c>
-      <c r="K13" s="8">
-        <f t="shared" si="41"/>
-        <v>-305.19999999999993</v>
-      </c>
-      <c r="L13" s="8">
-        <f t="shared" si="41"/>
-        <v>-326.89999999999992</v>
-      </c>
-      <c r="M13" s="8">
-        <f t="shared" ref="M13:Q13" si="42">M9-M10-M11-M12</f>
-        <v>-198.89999999999998</v>
-      </c>
-      <c r="N13" s="8">
+        <v>-351.19999999999993</v>
+      </c>
+      <c r="T13" s="8">
+        <f t="shared" ref="T13:U13" si="42">T9-T10-T11-T12</f>
+        <v>-415.09999999999985</v>
+      </c>
+      <c r="U13" s="8">
         <f t="shared" si="42"/>
-        <v>-94.831000000000031</v>
-      </c>
-      <c r="O13" s="8">
-        <f t="shared" si="42"/>
-        <v>-285.39999999999998</v>
-      </c>
-      <c r="P13" s="8">
-        <f t="shared" si="42"/>
-        <v>-153.49999999999994</v>
-      </c>
-      <c r="Q13" s="8">
-        <f t="shared" si="42"/>
-        <v>-70.900000000000006</v>
-      </c>
-      <c r="R13" s="8">
-        <f t="shared" ref="R13:S13" si="43">R9-R10-R11-R12</f>
-        <v>35.600000000000065</v>
-      </c>
-      <c r="S13" s="8">
-        <f t="shared" si="43"/>
-        <v>-351.19999999999993</v>
-      </c>
-      <c r="T13" s="8">
-        <f t="shared" ref="T13:U13" si="44">T9-T10-T11-T12</f>
-        <v>-415.09999999999985</v>
-      </c>
-      <c r="U13" s="8">
-        <f t="shared" si="44"/>
         <v>-494.2999999999999</v>
       </c>
       <c r="V13" s="8">
-        <f t="shared" ref="V13" si="45">V9-V10-V11-V12</f>
+        <f t="shared" ref="V13" si="43">V9-V10-V11-V12</f>
         <v>-284.19999999999993</v>
       </c>
       <c r="W13" s="8">
-        <f t="shared" ref="W13" si="46">W9-W10-W11-W12</f>
+        <f t="shared" ref="W13" si="44">W9-W10-W11-W12</f>
         <v>-321.8</v>
       </c>
       <c r="X13" s="8">
-        <f t="shared" ref="X13:Y13" si="47">X9-X10-X11-X12</f>
+        <f t="shared" ref="X13:Y13" si="45">X9-X10-X11-X12</f>
         <v>-365.29999999999995</v>
       </c>
       <c r="Y13" s="8">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>-362.50000000000006</v>
       </c>
       <c r="Z13" s="8">
-        <f t="shared" ref="Z13" si="48">Z9-Z10-Z11-Z12</f>
+        <f t="shared" ref="Z13" si="46">Z9-Z10-Z11-Z12</f>
         <v>-244.90000000000006</v>
       </c>
       <c r="AA13" s="8">
-        <f t="shared" ref="AA13" si="49">AA9-AA10-AA11-AA12</f>
+        <f t="shared" ref="AA13" si="47">AA9-AA10-AA11-AA12</f>
         <v>-298.10000000000014</v>
       </c>
       <c r="AB13" s="8">
-        <f t="shared" ref="AB13:AH13" si="50">AB9-AB10-AB11-AB12</f>
+        <f t="shared" ref="AB13:AH13" si="48">AB9-AB10-AB11-AB12</f>
         <v>-243.30000000000004</v>
       </c>
       <c r="AC13" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>-145.10000000000002</v>
       </c>
       <c r="AD13" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>14.399999999999935</v>
       </c>
       <c r="AE13" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>-131.29999999999998</v>
       </c>
       <c r="AF13" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>-254.89999999999984</v>
       </c>
       <c r="AG13" s="8">
-        <f t="shared" si="50"/>
-        <v>-145.49</v>
+        <f t="shared" si="48"/>
+        <v>-102.90000000000006</v>
       </c>
       <c r="AH13" s="8">
-        <f t="shared" si="50"/>
-        <v>-20.831420000000023</v>
+        <f t="shared" si="48"/>
+        <v>-8.0615600000000853</v>
       </c>
       <c r="AI13" s="8"/>
       <c r="AK13" s="8">
@@ -3026,64 +3023,64 @@
         <v>-925.83100000000024</v>
       </c>
       <c r="AN13" s="8">
-        <f t="shared" ref="AN13:AW13" si="51">AN9-AN10-AN11-AN12</f>
+        <f t="shared" ref="AN13:AW13" si="49">AN9-AN10-AN11-AN12</f>
         <v>-474.2</v>
       </c>
       <c r="AO13" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>-1544.7999999999997</v>
       </c>
       <c r="AP13" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>-1294.5</v>
       </c>
       <c r="AQ13" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>-672.0999999999998</v>
       </c>
       <c r="AR13" s="8">
-        <f t="shared" si="51"/>
-        <v>-552.52141999999947</v>
+        <f t="shared" si="49"/>
+        <v>-497.16155999999955</v>
       </c>
       <c r="AS13" s="8">
-        <f t="shared" si="51"/>
-        <v>-371.54657597999943</v>
+        <f t="shared" si="49"/>
+        <v>-345.73858643999949</v>
       </c>
       <c r="AT13" s="8">
-        <f t="shared" si="51"/>
-        <v>-254.80831141567941</v>
+        <f t="shared" si="49"/>
+        <v>-175.72835286303936</v>
       </c>
       <c r="AU13" s="8">
-        <f t="shared" si="51"/>
-        <v>-189.33111516864997</v>
+        <f t="shared" si="49"/>
+        <v>-78.905350291807565</v>
       </c>
       <c r="AV13" s="8">
-        <f t="shared" si="51"/>
-        <v>-121.19856367399764</v>
+        <f t="shared" si="49"/>
+        <v>-5.295485990167915</v>
       </c>
       <c r="AW13" s="8">
-        <f t="shared" si="51"/>
-        <v>-76.991657855558131</v>
+        <f t="shared" si="49"/>
+        <v>42.571657811117028</v>
       </c>
       <c r="AX13" s="8">
-        <f t="shared" ref="AX13:BB13" si="52">AX9-AX10-AX11-AX12</f>
-        <v>-20.012890398874433</v>
+        <f t="shared" ref="AX13:BB13" si="50">AX9-AX10-AX11-AX12</f>
+        <v>103.38509467802139</v>
       </c>
       <c r="AY13" s="8">
-        <f t="shared" si="52"/>
-        <v>39.427252631952989</v>
+        <f t="shared" si="50"/>
+        <v>166.77915662329096</v>
       </c>
       <c r="AZ13" s="8">
-        <f t="shared" si="52"/>
-        <v>101.2368760896323</v>
+        <f t="shared" si="50"/>
+        <v>232.66460564197919</v>
       </c>
       <c r="BA13" s="8">
-        <f t="shared" si="52"/>
-        <v>165.48982153969612</v>
+        <f t="shared" si="50"/>
+        <v>301.11897282237476</v>
       </c>
       <c r="BB13" s="8">
-        <f t="shared" si="52"/>
-        <v>232.26488911099261</v>
+        <f t="shared" si="50"/>
+        <v>372.22487451154228</v>
       </c>
     </row>
     <row r="14" spans="2:167" x14ac:dyDescent="0.3">
@@ -3181,12 +3178,11 @@
         <v>7.7</v>
       </c>
       <c r="AG14" s="4">
-        <f t="shared" ref="AG14:AH14" si="53">AG13*0.05</f>
-        <v>-7.2745000000000006</v>
+        <v>0.5</v>
       </c>
       <c r="AH14" s="4">
-        <f t="shared" si="53"/>
-        <v>-1.0415710000000011</v>
+        <f t="shared" ref="AG14:AH14" si="51">AH13*0.05</f>
+        <v>-0.40307800000000427</v>
       </c>
       <c r="AI14" s="4"/>
       <c r="AK14" s="4">
@@ -3219,47 +3215,47 @@
       </c>
       <c r="AR14" s="4">
         <f>SUM(AE14:AH14)</f>
-        <v>7.7839290000000005</v>
+        <v>16.196921999999997</v>
       </c>
       <c r="AS14" s="4">
         <f>AS13*0.2</f>
-        <v>-74.309315195999886</v>
+        <v>-69.147717287999896</v>
       </c>
       <c r="AT14" s="4">
-        <f t="shared" ref="AT14:AW14" si="54">AT13*0.2</f>
-        <v>-50.961662283135887</v>
+        <f t="shared" ref="AT14:AW14" si="52">AT13*0.2</f>
+        <v>-35.145670572607877</v>
       </c>
       <c r="AU14" s="4">
-        <f t="shared" si="54"/>
-        <v>-37.866223033729995</v>
+        <f t="shared" si="52"/>
+        <v>-15.781070058361514</v>
       </c>
       <c r="AV14" s="4">
-        <f t="shared" si="54"/>
-        <v>-24.239712734799529</v>
+        <f t="shared" si="52"/>
+        <v>-1.059097198033583</v>
       </c>
       <c r="AW14" s="4">
-        <f t="shared" si="54"/>
-        <v>-15.398331571111626</v>
+        <f t="shared" si="52"/>
+        <v>8.5143315622234059</v>
       </c>
       <c r="AX14" s="4">
-        <f t="shared" ref="AX14:BB14" si="55">AX13*0.2</f>
-        <v>-4.0025780797748869</v>
+        <f t="shared" ref="AX14:BB14" si="53">AX13*0.2</f>
+        <v>20.677018935604281</v>
       </c>
       <c r="AY14" s="4">
-        <f t="shared" si="55"/>
-        <v>7.8854505263905983</v>
+        <f t="shared" si="53"/>
+        <v>33.35583132465819</v>
       </c>
       <c r="AZ14" s="4">
-        <f t="shared" si="55"/>
-        <v>20.247375217926461</v>
+        <f t="shared" si="53"/>
+        <v>46.532921128395841</v>
       </c>
       <c r="BA14" s="4">
-        <f t="shared" si="55"/>
-        <v>33.097964307939229</v>
+        <f t="shared" si="53"/>
+        <v>60.223794564474957</v>
       </c>
       <c r="BB14" s="4">
-        <f t="shared" si="55"/>
-        <v>46.452977822198527</v>
+        <f t="shared" si="53"/>
+        <v>74.444974902308459</v>
       </c>
     </row>
     <row r="15" spans="2:167" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3267,132 +3263,132 @@
         <v>32</v>
       </c>
       <c r="C15" s="8">
-        <f t="shared" ref="C15:L15" si="56">C13-C14</f>
+        <f t="shared" ref="C15:L15" si="54">C13-C14</f>
         <v>-385.70000000000005</v>
       </c>
       <c r="D15" s="8">
+        <f t="shared" si="54"/>
+        <v>-353.29999999999995</v>
+      </c>
+      <c r="E15" s="8">
+        <f t="shared" si="54"/>
+        <v>-325.2</v>
+      </c>
+      <c r="F15" s="8">
+        <f t="shared" si="54"/>
+        <v>-192.40000000000003</v>
+      </c>
+      <c r="G15" s="8">
+        <f t="shared" si="54"/>
+        <v>-310.00000000000006</v>
+      </c>
+      <c r="H15" s="8">
+        <f t="shared" si="54"/>
+        <v>-255.29999999999998</v>
+      </c>
+      <c r="I15" s="8">
+        <f t="shared" si="54"/>
+        <v>-227.7</v>
+      </c>
+      <c r="J15" s="8">
+        <f t="shared" si="54"/>
+        <v>-240.60000000000002</v>
+      </c>
+      <c r="K15" s="8">
+        <f t="shared" si="54"/>
+        <v>-305.89999999999992</v>
+      </c>
+      <c r="L15" s="8">
+        <f t="shared" si="54"/>
+        <v>-325.89999999999992</v>
+      </c>
+      <c r="M15" s="8">
+        <f t="shared" ref="M15:N15" si="55">M13-M14</f>
+        <v>-198.89999999999998</v>
+      </c>
+      <c r="N15" s="8">
+        <f t="shared" si="55"/>
+        <v>-112.93100000000004</v>
+      </c>
+      <c r="O15" s="8">
+        <f t="shared" ref="O15:Q15" si="56">O13-O14</f>
+        <v>-286.79999999999995</v>
+      </c>
+      <c r="P15" s="8">
         <f t="shared" si="56"/>
-        <v>-353.29999999999995</v>
-      </c>
-      <c r="E15" s="8">
+        <v>-151.59999999999994</v>
+      </c>
+      <c r="Q15" s="8">
         <f t="shared" si="56"/>
-        <v>-325.2</v>
-      </c>
-      <c r="F15" s="8">
-        <f t="shared" si="56"/>
-        <v>-192.40000000000003</v>
-      </c>
-      <c r="G15" s="8">
-        <f t="shared" si="56"/>
-        <v>-310.00000000000006</v>
-      </c>
-      <c r="H15" s="8">
-        <f t="shared" si="56"/>
-        <v>-255.29999999999998</v>
-      </c>
-      <c r="I15" s="8">
-        <f t="shared" si="56"/>
-        <v>-227.7</v>
-      </c>
-      <c r="J15" s="8">
-        <f t="shared" si="56"/>
-        <v>-240.60000000000002</v>
-      </c>
-      <c r="K15" s="8">
-        <f t="shared" si="56"/>
-        <v>-305.89999999999992</v>
-      </c>
-      <c r="L15" s="8">
-        <f t="shared" si="56"/>
-        <v>-325.89999999999992</v>
-      </c>
-      <c r="M15" s="8">
-        <f t="shared" ref="M15:N15" si="57">M13-M14</f>
-        <v>-198.89999999999998</v>
-      </c>
-      <c r="N15" s="8">
+        <v>-71.900000000000006</v>
+      </c>
+      <c r="R15" s="8">
+        <f t="shared" ref="R15:S15" si="57">R13-R14</f>
+        <v>22.600000000000065</v>
+      </c>
+      <c r="S15" s="8">
         <f t="shared" si="57"/>
-        <v>-112.93100000000004</v>
-      </c>
-      <c r="O15" s="8">
-        <f t="shared" ref="O15:Q15" si="58">O13-O14</f>
-        <v>-286.79999999999995</v>
-      </c>
-      <c r="P15" s="8">
+        <v>-359.69999999999993</v>
+      </c>
+      <c r="T15" s="8">
+        <f t="shared" ref="T15:U15" si="58">T13-T14</f>
+        <v>-422.09999999999985</v>
+      </c>
+      <c r="U15" s="8">
         <f t="shared" si="58"/>
-        <v>-151.59999999999994</v>
-      </c>
-      <c r="Q15" s="8">
-        <f t="shared" si="58"/>
-        <v>-71.900000000000006</v>
-      </c>
-      <c r="R15" s="8">
-        <f t="shared" ref="R15:S15" si="59">R13-R14</f>
-        <v>22.600000000000065</v>
-      </c>
-      <c r="S15" s="8">
-        <f t="shared" si="59"/>
-        <v>-359.69999999999993</v>
-      </c>
-      <c r="T15" s="8">
-        <f t="shared" ref="T15:U15" si="60">T13-T14</f>
-        <v>-422.09999999999985</v>
-      </c>
-      <c r="U15" s="8">
-        <f t="shared" si="60"/>
         <v>-503.49999999999989</v>
       </c>
       <c r="V15" s="8">
-        <f t="shared" ref="V15" si="61">V13-V14</f>
+        <f t="shared" ref="V15" si="59">V13-V14</f>
         <v>-288.39999999999992</v>
       </c>
       <c r="W15" s="8">
-        <f t="shared" ref="W15" si="62">W13-W14</f>
+        <f t="shared" ref="W15" si="60">W13-W14</f>
         <v>-328.6</v>
       </c>
       <c r="X15" s="8">
-        <f t="shared" ref="X15:Y15" si="63">X13-X14</f>
+        <f t="shared" ref="X15:Y15" si="61">X13-X14</f>
         <v>-377.4</v>
       </c>
       <c r="Y15" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="61"/>
         <v>-368.30000000000007</v>
       </c>
       <c r="Z15" s="8">
-        <f t="shared" ref="Z15" si="64">Z13-Z14</f>
+        <f t="shared" ref="Z15" si="62">Z13-Z14</f>
         <v>-248.20000000000007</v>
       </c>
       <c r="AA15" s="8">
-        <f t="shared" ref="AA15" si="65">AA13-AA14</f>
+        <f t="shared" ref="AA15" si="63">AA13-AA14</f>
         <v>-305.00000000000011</v>
       </c>
       <c r="AB15" s="8">
-        <f t="shared" ref="AB15:AD15" si="66">AB13-AB14</f>
+        <f t="shared" ref="AB15:AD15" si="64">AB13-AB14</f>
         <v>-248.50000000000003</v>
       </c>
       <c r="AC15" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="64"/>
         <v>-153.40000000000003</v>
       </c>
       <c r="AD15" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="64"/>
         <v>9.1999999999999353</v>
       </c>
       <c r="AE15" s="8">
-        <f t="shared" ref="AE15:AH15" si="67">AE13-AE14</f>
+        <f t="shared" ref="AE15:AH15" si="65">AE13-AE14</f>
         <v>-139.69999999999999</v>
       </c>
       <c r="AF15" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="65"/>
         <v>-262.59999999999985</v>
       </c>
       <c r="AG15" s="8">
-        <f t="shared" si="67"/>
-        <v>-138.21550000000002</v>
+        <f t="shared" si="65"/>
+        <v>-103.40000000000006</v>
       </c>
       <c r="AH15" s="8">
-        <f t="shared" si="67"/>
-        <v>-19.789849000000022</v>
+        <f t="shared" si="65"/>
+        <v>-7.6584820000000811</v>
       </c>
       <c r="AI15" s="8"/>
       <c r="AK15" s="8">
@@ -3408,516 +3404,516 @@
         <v>-943.6310000000002</v>
       </c>
       <c r="AN15" s="8">
-        <f t="shared" ref="AN15:AW15" si="68">AN13-AN14</f>
+        <f t="shared" ref="AN15:AW15" si="66">AN13-AN14</f>
         <v>-487.7</v>
       </c>
       <c r="AO15" s="8">
+        <f t="shared" si="66"/>
+        <v>-1573.6999999999998</v>
+      </c>
+      <c r="AP15" s="8">
+        <f t="shared" si="66"/>
+        <v>-1322.5</v>
+      </c>
+      <c r="AQ15" s="8">
+        <f t="shared" si="66"/>
+        <v>-697.69999999999982</v>
+      </c>
+      <c r="AR15" s="8">
+        <f t="shared" si="66"/>
+        <v>-513.35848199999953</v>
+      </c>
+      <c r="AS15" s="8">
+        <f t="shared" si="66"/>
+        <v>-276.59086915199958</v>
+      </c>
+      <c r="AT15" s="8">
+        <f t="shared" si="66"/>
+        <v>-140.58268229043148</v>
+      </c>
+      <c r="AU15" s="8">
+        <f t="shared" si="66"/>
+        <v>-63.124280233446051</v>
+      </c>
+      <c r="AV15" s="8">
+        <f t="shared" si="66"/>
+        <v>-4.2363887921343322</v>
+      </c>
+      <c r="AW15" s="8">
+        <f t="shared" si="66"/>
+        <v>34.057326248893624</v>
+      </c>
+      <c r="AX15" s="8">
+        <f t="shared" ref="AX15:BB15" si="67">AX13-AX14</f>
+        <v>82.708075742417108</v>
+      </c>
+      <c r="AY15" s="8">
+        <f t="shared" si="67"/>
+        <v>133.42332529863276</v>
+      </c>
+      <c r="AZ15" s="8">
+        <f t="shared" si="67"/>
+        <v>186.13168451358337</v>
+      </c>
+      <c r="BA15" s="8">
+        <f t="shared" si="67"/>
+        <v>240.8951782578998</v>
+      </c>
+      <c r="BB15" s="8">
+        <f t="shared" si="67"/>
+        <v>297.77989960923384</v>
+      </c>
+      <c r="BC15" s="1">
+        <f t="shared" ref="BC15:CH15" si="68">BB15*(1+$BE$21)</f>
+        <v>294.80210061314148</v>
+      </c>
+      <c r="BD15" s="1">
         <f t="shared" si="68"/>
-        <v>-1573.6999999999998</v>
-      </c>
-      <c r="AP15" s="8">
+        <v>291.85407960701008</v>
+      </c>
+      <c r="BE15" s="1">
         <f t="shared" si="68"/>
-        <v>-1322.5</v>
-      </c>
-      <c r="AQ15" s="8">
+        <v>288.93553881093999</v>
+      </c>
+      <c r="BF15" s="1">
         <f t="shared" si="68"/>
-        <v>-697.69999999999982</v>
-      </c>
-      <c r="AR15" s="8">
+        <v>286.04618342283061</v>
+      </c>
+      <c r="BG15" s="1">
         <f t="shared" si="68"/>
-        <v>-560.30534899999952</v>
-      </c>
-      <c r="AS15" s="8">
+        <v>283.18572158860229</v>
+      </c>
+      <c r="BH15" s="1">
         <f t="shared" si="68"/>
-        <v>-297.23726078399955</v>
-      </c>
-      <c r="AT15" s="8">
+        <v>280.35386437271626</v>
+      </c>
+      <c r="BI15" s="1">
         <f t="shared" si="68"/>
-        <v>-203.84664913254352</v>
-      </c>
-      <c r="AU15" s="8">
+        <v>277.55032572898909</v>
+      </c>
+      <c r="BJ15" s="1">
         <f t="shared" si="68"/>
-        <v>-151.46489213491998</v>
-      </c>
-      <c r="AV15" s="8">
+        <v>274.77482247169922</v>
+      </c>
+      <c r="BK15" s="1">
         <f t="shared" si="68"/>
-        <v>-96.958850939198115</v>
-      </c>
-      <c r="AW15" s="8">
+        <v>272.02707424698224</v>
+      </c>
+      <c r="BL15" s="1">
         <f t="shared" si="68"/>
-        <v>-61.593326284446505</v>
-      </c>
-      <c r="AX15" s="8">
-        <f t="shared" ref="AX15:BB15" si="69">AX13-AX14</f>
-        <v>-16.010312319099548</v>
-      </c>
-      <c r="AY15" s="8">
+        <v>269.3068035045124</v>
+      </c>
+      <c r="BM15" s="1">
+        <f t="shared" si="68"/>
+        <v>266.61373546946726</v>
+      </c>
+      <c r="BN15" s="1">
+        <f t="shared" si="68"/>
+        <v>263.94759811477257</v>
+      </c>
+      <c r="BO15" s="1">
+        <f t="shared" si="68"/>
+        <v>261.30812213362486</v>
+      </c>
+      <c r="BP15" s="1">
+        <f t="shared" si="68"/>
+        <v>258.69504091228862</v>
+      </c>
+      <c r="BQ15" s="1">
+        <f t="shared" si="68"/>
+        <v>256.10809050316573</v>
+      </c>
+      <c r="BR15" s="1">
+        <f t="shared" si="68"/>
+        <v>253.54700959813405</v>
+      </c>
+      <c r="BS15" s="1">
+        <f t="shared" si="68"/>
+        <v>251.01153950215271</v>
+      </c>
+      <c r="BT15" s="1">
+        <f t="shared" si="68"/>
+        <v>248.50142410713119</v>
+      </c>
+      <c r="BU15" s="1">
+        <f t="shared" si="68"/>
+        <v>246.01640986605986</v>
+      </c>
+      <c r="BV15" s="1">
+        <f t="shared" si="68"/>
+        <v>243.55624576739925</v>
+      </c>
+      <c r="BW15" s="1">
+        <f t="shared" si="68"/>
+        <v>241.12068330972525</v>
+      </c>
+      <c r="BX15" s="1">
+        <f t="shared" si="68"/>
+        <v>238.709476476628</v>
+      </c>
+      <c r="BY15" s="1">
+        <f t="shared" si="68"/>
+        <v>236.32238171186171</v>
+      </c>
+      <c r="BZ15" s="1">
+        <f t="shared" si="68"/>
+        <v>233.9591578947431</v>
+      </c>
+      <c r="CA15" s="1">
+        <f t="shared" si="68"/>
+        <v>231.61956631579568</v>
+      </c>
+      <c r="CB15" s="1">
+        <f t="shared" si="68"/>
+        <v>229.30337065263771</v>
+      </c>
+      <c r="CC15" s="1">
+        <f t="shared" si="68"/>
+        <v>227.01033694611132</v>
+      </c>
+      <c r="CD15" s="1">
+        <f t="shared" si="68"/>
+        <v>224.74023357665021</v>
+      </c>
+      <c r="CE15" s="1">
+        <f t="shared" si="68"/>
+        <v>222.4928312408837</v>
+      </c>
+      <c r="CF15" s="1">
+        <f t="shared" si="68"/>
+        <v>220.26790292847485</v>
+      </c>
+      <c r="CG15" s="1">
+        <f t="shared" si="68"/>
+        <v>218.0652238991901</v>
+      </c>
+      <c r="CH15" s="1">
+        <f t="shared" si="68"/>
+        <v>215.88457166019819</v>
+      </c>
+      <c r="CI15" s="1">
+        <f t="shared" ref="CI15:DN15" si="69">CH15*(1+$BE$21)</f>
+        <v>213.72572594359622</v>
+      </c>
+      <c r="CJ15" s="1">
         <f t="shared" si="69"/>
-        <v>31.54180210556239</v>
-      </c>
-      <c r="AZ15" s="8">
+        <v>211.58846868416026</v>
+      </c>
+      <c r="CK15" s="1">
         <f t="shared" si="69"/>
-        <v>80.989500871705843</v>
-      </c>
-      <c r="BA15" s="8">
+        <v>209.47258399731865</v>
+      </c>
+      <c r="CL15" s="1">
         <f t="shared" si="69"/>
-        <v>132.39185723175689</v>
-      </c>
-      <c r="BB15" s="8">
+        <v>207.37785815734546</v>
+      </c>
+      <c r="CM15" s="1">
         <f t="shared" si="69"/>
-        <v>185.81191128879408</v>
-      </c>
-      <c r="BC15" s="1">
-        <f t="shared" ref="BC15:CH15" si="70">BB15*(1+$BE$21)</f>
-        <v>183.95379217590613</v>
-      </c>
-      <c r="BD15" s="1">
+        <v>205.30407957577199</v>
+      </c>
+      <c r="CN15" s="1">
+        <f t="shared" si="69"/>
+        <v>203.25103878001428</v>
+      </c>
+      <c r="CO15" s="1">
+        <f t="shared" si="69"/>
+        <v>201.21852839221413</v>
+      </c>
+      <c r="CP15" s="1">
+        <f t="shared" si="69"/>
+        <v>199.20634310829197</v>
+      </c>
+      <c r="CQ15" s="1">
+        <f t="shared" si="69"/>
+        <v>197.21427967720905</v>
+      </c>
+      <c r="CR15" s="1">
+        <f t="shared" si="69"/>
+        <v>195.24213688043696</v>
+      </c>
+      <c r="CS15" s="1">
+        <f t="shared" si="69"/>
+        <v>193.28971551163258</v>
+      </c>
+      <c r="CT15" s="1">
+        <f t="shared" si="69"/>
+        <v>191.35681835651624</v>
+      </c>
+      <c r="CU15" s="1">
+        <f t="shared" si="69"/>
+        <v>189.44325017295108</v>
+      </c>
+      <c r="CV15" s="1">
+        <f t="shared" si="69"/>
+        <v>187.54881767122157</v>
+      </c>
+      <c r="CW15" s="1">
+        <f t="shared" si="69"/>
+        <v>185.67332949450935</v>
+      </c>
+      <c r="CX15" s="1">
+        <f t="shared" si="69"/>
+        <v>183.81659619956426</v>
+      </c>
+      <c r="CY15" s="1">
+        <f t="shared" si="69"/>
+        <v>181.9784302375686</v>
+      </c>
+      <c r="CZ15" s="1">
+        <f t="shared" si="69"/>
+        <v>180.15864593519291</v>
+      </c>
+      <c r="DA15" s="1">
+        <f t="shared" si="69"/>
+        <v>178.35705947584097</v>
+      </c>
+      <c r="DB15" s="1">
+        <f t="shared" si="69"/>
+        <v>176.57348888108257</v>
+      </c>
+      <c r="DC15" s="1">
+        <f t="shared" si="69"/>
+        <v>174.80775399227173</v>
+      </c>
+      <c r="DD15" s="1">
+        <f t="shared" si="69"/>
+        <v>173.05967645234901</v>
+      </c>
+      <c r="DE15" s="1">
+        <f t="shared" si="69"/>
+        <v>171.32907968782553</v>
+      </c>
+      <c r="DF15" s="1">
+        <f t="shared" si="69"/>
+        <v>169.61578889094727</v>
+      </c>
+      <c r="DG15" s="1">
+        <f t="shared" si="69"/>
+        <v>167.91963100203779</v>
+      </c>
+      <c r="DH15" s="1">
+        <f t="shared" si="69"/>
+        <v>166.2404346920174</v>
+      </c>
+      <c r="DI15" s="1">
+        <f t="shared" si="69"/>
+        <v>164.57803034509723</v>
+      </c>
+      <c r="DJ15" s="1">
+        <f t="shared" si="69"/>
+        <v>162.93225004164626</v>
+      </c>
+      <c r="DK15" s="1">
+        <f t="shared" si="69"/>
+        <v>161.30292754122979</v>
+      </c>
+      <c r="DL15" s="1">
+        <f t="shared" si="69"/>
+        <v>159.6898982658175</v>
+      </c>
+      <c r="DM15" s="1">
+        <f t="shared" si="69"/>
+        <v>158.09299928315932</v>
+      </c>
+      <c r="DN15" s="1">
+        <f t="shared" si="69"/>
+        <v>156.51206929032773</v>
+      </c>
+      <c r="DO15" s="1">
+        <f t="shared" ref="DO15:ET15" si="70">DN15*(1+$BE$21)</f>
+        <v>154.94694859742444</v>
+      </c>
+      <c r="DP15" s="1">
         <f t="shared" si="70"/>
-        <v>182.11425425414706</v>
-      </c>
-      <c r="BE15" s="1">
+        <v>153.3974791114502</v>
+      </c>
+      <c r="DQ15" s="1">
         <f t="shared" si="70"/>
-        <v>180.29311171160558</v>
-      </c>
-      <c r="BF15" s="1">
+        <v>151.86350432033569</v>
+      </c>
+      <c r="DR15" s="1">
         <f t="shared" si="70"/>
-        <v>178.49018059448952</v>
-      </c>
-      <c r="BG15" s="1">
+        <v>150.34486927713235</v>
+      </c>
+      <c r="DS15" s="1">
         <f t="shared" si="70"/>
-        <v>176.70527878854463</v>
-      </c>
-      <c r="BH15" s="1">
+        <v>148.84142058436103</v>
+      </c>
+      <c r="DT15" s="1">
         <f t="shared" si="70"/>
-        <v>174.93822600065917</v>
-      </c>
-      <c r="BI15" s="1">
+        <v>147.35300637851742</v>
+      </c>
+      <c r="DU15" s="1">
         <f t="shared" si="70"/>
-        <v>173.18884374065257</v>
-      </c>
-      <c r="BJ15" s="1">
+        <v>145.87947631473224</v>
+      </c>
+      <c r="DV15" s="1">
         <f t="shared" si="70"/>
-        <v>171.45695530324605</v>
-      </c>
-      <c r="BK15" s="1">
+        <v>144.42068155158492</v>
+      </c>
+      <c r="DW15" s="1">
         <f t="shared" si="70"/>
-        <v>169.74238575021357</v>
-      </c>
-      <c r="BL15" s="1">
+        <v>142.97647473606906</v>
+      </c>
+      <c r="DX15" s="1">
         <f t="shared" si="70"/>
-        <v>168.04496189271143</v>
-      </c>
-      <c r="BM15" s="1">
+        <v>141.54670998870839</v>
+      </c>
+      <c r="DY15" s="1">
         <f t="shared" si="70"/>
-        <v>166.3645122737843</v>
-      </c>
-      <c r="BN15" s="1">
+        <v>140.1312428888213</v>
+      </c>
+      <c r="DZ15" s="1">
         <f t="shared" si="70"/>
-        <v>164.70086715104645</v>
-      </c>
-      <c r="BO15" s="1">
+        <v>138.72993045993309</v>
+      </c>
+      <c r="EA15" s="1">
         <f t="shared" si="70"/>
-        <v>163.05385847953599</v>
-      </c>
-      <c r="BP15" s="1">
+        <v>137.34263115533375</v>
+      </c>
+      <c r="EB15" s="1">
         <f t="shared" si="70"/>
-        <v>161.42331989474062</v>
-      </c>
-      <c r="BQ15" s="1">
+        <v>135.9692048437804</v>
+      </c>
+      <c r="EC15" s="1">
         <f t="shared" si="70"/>
-        <v>159.80908669579321</v>
-      </c>
-      <c r="BR15" s="1">
+        <v>134.6095127953426</v>
+      </c>
+      <c r="ED15" s="1">
         <f t="shared" si="70"/>
-        <v>158.21099582883528</v>
-      </c>
-      <c r="BS15" s="1">
+        <v>133.26341766738918</v>
+      </c>
+      <c r="EE15" s="1">
         <f t="shared" si="70"/>
-        <v>156.62888587054692</v>
-      </c>
-      <c r="BT15" s="1">
+        <v>131.93078349071527</v>
+      </c>
+      <c r="EF15" s="1">
         <f t="shared" si="70"/>
-        <v>155.06259701184146</v>
-      </c>
-      <c r="BU15" s="1">
+        <v>130.61147565580811</v>
+      </c>
+      <c r="EG15" s="1">
         <f t="shared" si="70"/>
-        <v>153.51197104172306</v>
-      </c>
-      <c r="BV15" s="1">
+        <v>129.30536089925002</v>
+      </c>
+      <c r="EH15" s="1">
         <f t="shared" si="70"/>
-        <v>151.97685133130582</v>
-      </c>
-      <c r="BW15" s="1">
+        <v>128.01230729025752</v>
+      </c>
+      <c r="EI15" s="1">
         <f t="shared" si="70"/>
-        <v>150.45708281799276</v>
-      </c>
-      <c r="BX15" s="1">
+        <v>126.73218421735494</v>
+      </c>
+      <c r="EJ15" s="1">
         <f t="shared" si="70"/>
-        <v>148.95251198981282</v>
-      </c>
-      <c r="BY15" s="1">
+        <v>125.4648623751814</v>
+      </c>
+      <c r="EK15" s="1">
         <f t="shared" si="70"/>
-        <v>147.46298686991469</v>
-      </c>
-      <c r="BZ15" s="1">
+        <v>124.21021375142958</v>
+      </c>
+      <c r="EL15" s="1">
         <f t="shared" si="70"/>
-        <v>145.98835700121555</v>
-      </c>
-      <c r="CA15" s="1">
+        <v>122.96811161391528</v>
+      </c>
+      <c r="EM15" s="1">
         <f t="shared" si="70"/>
-        <v>144.52847343120339</v>
-      </c>
-      <c r="CB15" s="1">
+        <v>121.73843049777614</v>
+      </c>
+      <c r="EN15" s="1">
         <f t="shared" si="70"/>
-        <v>143.08318869689137</v>
-      </c>
-      <c r="CC15" s="1">
+        <v>120.52104619279838</v>
+      </c>
+      <c r="EO15" s="1">
         <f t="shared" si="70"/>
-        <v>141.65235680992245</v>
-      </c>
-      <c r="CD15" s="1">
+        <v>119.31583573087039</v>
+      </c>
+      <c r="EP15" s="1">
         <f t="shared" si="70"/>
-        <v>140.23583324182323</v>
-      </c>
-      <c r="CE15" s="1">
+        <v>118.12267737356169</v>
+      </c>
+      <c r="EQ15" s="1">
         <f t="shared" si="70"/>
-        <v>138.833474909405</v>
-      </c>
-      <c r="CF15" s="1">
+        <v>116.94145059982607</v>
+      </c>
+      <c r="ER15" s="1">
         <f t="shared" si="70"/>
-        <v>137.44514016031096</v>
-      </c>
-      <c r="CG15" s="1">
+        <v>115.77203609382781</v>
+      </c>
+      <c r="ES15" s="1">
         <f t="shared" si="70"/>
-        <v>136.07068875870783</v>
-      </c>
-      <c r="CH15" s="1">
+        <v>114.61431573288952</v>
+      </c>
+      <c r="ET15" s="1">
         <f t="shared" si="70"/>
-        <v>134.70998187112076</v>
-      </c>
-      <c r="CI15" s="1">
-        <f t="shared" ref="CI15:DN15" si="71">CH15*(1+$BE$21)</f>
-        <v>133.36288205240956</v>
-      </c>
-      <c r="CJ15" s="1">
+        <v>113.46817257556063</v>
+      </c>
+      <c r="EU15" s="1">
+        <f t="shared" ref="EU15:FK15" si="71">ET15*(1+$BE$21)</f>
+        <v>112.33349084980502</v>
+      </c>
+      <c r="EV15" s="1">
         <f t="shared" si="71"/>
-        <v>132.02925323188546</v>
-      </c>
-      <c r="CK15" s="1">
+        <v>111.21015594130697</v>
+      </c>
+      <c r="EW15" s="1">
         <f t="shared" si="71"/>
-        <v>130.7089606995666</v>
-      </c>
-      <c r="CL15" s="1">
+        <v>110.09805438189389</v>
+      </c>
+      <c r="EX15" s="1">
         <f t="shared" si="71"/>
-        <v>129.40187109257093</v>
-      </c>
-      <c r="CM15" s="1">
+        <v>108.99707383807495</v>
+      </c>
+      <c r="EY15" s="1">
         <f t="shared" si="71"/>
-        <v>128.10785238164522</v>
-      </c>
-      <c r="CN15" s="1">
+        <v>107.9071030996942</v>
+      </c>
+      <c r="EZ15" s="1">
         <f t="shared" si="71"/>
-        <v>126.82677385782877</v>
-      </c>
-      <c r="CO15" s="1">
+        <v>106.82803206869725</v>
+      </c>
+      <c r="FA15" s="1">
         <f t="shared" si="71"/>
-        <v>125.55850611925048</v>
-      </c>
-      <c r="CP15" s="1">
+        <v>105.75975174801029</v>
+      </c>
+      <c r="FB15" s="1">
         <f t="shared" si="71"/>
-        <v>124.30292105805798</v>
-      </c>
-      <c r="CQ15" s="1">
+        <v>104.70215423053018</v>
+      </c>
+      <c r="FC15" s="1">
         <f t="shared" si="71"/>
-        <v>123.05989184747739</v>
-      </c>
-      <c r="CR15" s="1">
+        <v>103.65513268822488</v>
+      </c>
+      <c r="FD15" s="1">
         <f t="shared" si="71"/>
-        <v>121.82929292900262</v>
-      </c>
-      <c r="CS15" s="1">
+        <v>102.61858136134263</v>
+      </c>
+      <c r="FE15" s="1">
         <f t="shared" si="71"/>
-        <v>120.61099999971259</v>
-      </c>
-      <c r="CT15" s="1">
+        <v>101.59239554772921</v>
+      </c>
+      <c r="FF15" s="1">
         <f t="shared" si="71"/>
-        <v>119.40488999971546</v>
-      </c>
-      <c r="CU15" s="1">
+        <v>100.57647159225192</v>
+      </c>
+      <c r="FG15" s="1">
         <f t="shared" si="71"/>
-        <v>118.21084109971831</v>
-      </c>
-      <c r="CV15" s="1">
+        <v>99.570706876329396</v>
+      </c>
+      <c r="FH15" s="1">
         <f t="shared" si="71"/>
-        <v>117.02873268872112</v>
-      </c>
-      <c r="CW15" s="1">
+        <v>98.574999807566101</v>
+      </c>
+      <c r="FI15" s="1">
         <f t="shared" si="71"/>
-        <v>115.85844536183392</v>
-      </c>
-      <c r="CX15" s="1">
+        <v>97.58924980949044</v>
+      </c>
+      <c r="FJ15" s="1">
         <f t="shared" si="71"/>
-        <v>114.69986090821557</v>
-      </c>
-      <c r="CY15" s="1">
+        <v>96.613357311395532</v>
+      </c>
+      <c r="FK15" s="1">
         <f t="shared" si="71"/>
-        <v>113.55286229913341</v>
-      </c>
-      <c r="CZ15" s="1">
-        <f t="shared" si="71"/>
-        <v>112.41733367614208</v>
-      </c>
-      <c r="DA15" s="1">
-        <f t="shared" si="71"/>
-        <v>111.29316033938066</v>
-      </c>
-      <c r="DB15" s="1">
-        <f t="shared" si="71"/>
-        <v>110.18022873598686</v>
-      </c>
-      <c r="DC15" s="1">
-        <f t="shared" si="71"/>
-        <v>109.07842644862698</v>
-      </c>
-      <c r="DD15" s="1">
-        <f t="shared" si="71"/>
-        <v>107.98764218414071</v>
-      </c>
-      <c r="DE15" s="1">
-        <f t="shared" si="71"/>
-        <v>106.90776576229931</v>
-      </c>
-      <c r="DF15" s="1">
-        <f t="shared" si="71"/>
-        <v>105.83868810467631</v>
-      </c>
-      <c r="DG15" s="1">
-        <f t="shared" si="71"/>
-        <v>104.78030122362955</v>
-      </c>
-      <c r="DH15" s="1">
-        <f t="shared" si="71"/>
-        <v>103.73249821139325</v>
-      </c>
-      <c r="DI15" s="1">
-        <f t="shared" si="71"/>
-        <v>102.69517322927932</v>
-      </c>
-      <c r="DJ15" s="1">
-        <f t="shared" si="71"/>
-        <v>101.66822149698652</v>
-      </c>
-      <c r="DK15" s="1">
-        <f t="shared" si="71"/>
-        <v>100.65153928201666</v>
-      </c>
-      <c r="DL15" s="1">
-        <f t="shared" si="71"/>
-        <v>99.645023889196494</v>
-      </c>
-      <c r="DM15" s="1">
-        <f t="shared" si="71"/>
-        <v>98.648573650304527</v>
-      </c>
-      <c r="DN15" s="1">
-        <f t="shared" si="71"/>
-        <v>97.662087913801486</v>
-      </c>
-      <c r="DO15" s="1">
-        <f t="shared" ref="DO15:ET15" si="72">DN15*(1+$BE$21)</f>
-        <v>96.685467034663475</v>
-      </c>
-      <c r="DP15" s="1">
-        <f t="shared" si="72"/>
-        <v>95.71861236431684</v>
-      </c>
-      <c r="DQ15" s="1">
-        <f t="shared" si="72"/>
-        <v>94.761426240673671</v>
-      </c>
-      <c r="DR15" s="1">
-        <f t="shared" si="72"/>
-        <v>93.813811978266941</v>
-      </c>
-      <c r="DS15" s="1">
-        <f t="shared" si="72"/>
-        <v>92.875673858484276</v>
-      </c>
-      <c r="DT15" s="1">
-        <f t="shared" si="72"/>
-        <v>91.946917119899439</v>
-      </c>
-      <c r="DU15" s="1">
-        <f t="shared" si="72"/>
-        <v>91.027447948700441</v>
-      </c>
-      <c r="DV15" s="1">
-        <f t="shared" si="72"/>
-        <v>90.117173469213441</v>
-      </c>
-      <c r="DW15" s="1">
-        <f t="shared" si="72"/>
-        <v>89.216001734521299</v>
-      </c>
-      <c r="DX15" s="1">
-        <f t="shared" si="72"/>
-        <v>88.32384171717608</v>
-      </c>
-      <c r="DY15" s="1">
-        <f t="shared" si="72"/>
-        <v>87.440603300004312</v>
-      </c>
-      <c r="DZ15" s="1">
-        <f t="shared" si="72"/>
-        <v>86.56619726700427</v>
-      </c>
-      <c r="EA15" s="1">
-        <f t="shared" si="72"/>
-        <v>85.70053529433423</v>
-      </c>
-      <c r="EB15" s="1">
-        <f t="shared" si="72"/>
-        <v>84.843529941390884</v>
-      </c>
-      <c r="EC15" s="1">
-        <f t="shared" si="72"/>
-        <v>83.995094641976976</v>
-      </c>
-      <c r="ED15" s="1">
-        <f t="shared" si="72"/>
-        <v>83.1551436955572</v>
-      </c>
-      <c r="EE15" s="1">
-        <f t="shared" si="72"/>
-        <v>82.323592258601622</v>
-      </c>
-      <c r="EF15" s="1">
-        <f t="shared" si="72"/>
-        <v>81.500356336015599</v>
-      </c>
-      <c r="EG15" s="1">
-        <f t="shared" si="72"/>
-        <v>80.685352772655449</v>
-      </c>
-      <c r="EH15" s="1">
-        <f t="shared" si="72"/>
-        <v>79.878499244928889</v>
-      </c>
-      <c r="EI15" s="1">
-        <f t="shared" si="72"/>
-        <v>79.079714252479604</v>
-      </c>
-      <c r="EJ15" s="1">
-        <f t="shared" si="72"/>
-        <v>78.288917109954809</v>
-      </c>
-      <c r="EK15" s="1">
-        <f t="shared" si="72"/>
-        <v>77.506027938855254</v>
-      </c>
-      <c r="EL15" s="1">
-        <f t="shared" si="72"/>
-        <v>76.7309676594667</v>
-      </c>
-      <c r="EM15" s="1">
-        <f t="shared" si="72"/>
-        <v>75.963657982872036</v>
-      </c>
-      <c r="EN15" s="1">
-        <f t="shared" si="72"/>
-        <v>75.204021403043313</v>
-      </c>
-      <c r="EO15" s="1">
-        <f t="shared" si="72"/>
-        <v>74.451981189012884</v>
-      </c>
-      <c r="EP15" s="1">
-        <f t="shared" si="72"/>
-        <v>73.707461377122755</v>
-      </c>
-      <c r="EQ15" s="1">
-        <f t="shared" si="72"/>
-        <v>72.970386763351527</v>
-      </c>
-      <c r="ER15" s="1">
-        <f t="shared" si="72"/>
-        <v>72.24068289571801</v>
-      </c>
-      <c r="ES15" s="1">
-        <f t="shared" si="72"/>
-        <v>71.518276066760833</v>
-      </c>
-      <c r="ET15" s="1">
-        <f t="shared" si="72"/>
-        <v>70.803093306093231</v>
-      </c>
-      <c r="EU15" s="1">
-        <f t="shared" ref="EU15:FK15" si="73">ET15*(1+$BE$21)</f>
-        <v>70.095062373032292</v>
-      </c>
-      <c r="EV15" s="1">
-        <f t="shared" si="73"/>
-        <v>69.39411174930197</v>
-      </c>
-      <c r="EW15" s="1">
-        <f t="shared" si="73"/>
-        <v>68.700170631808945</v>
-      </c>
-      <c r="EX15" s="1">
-        <f t="shared" si="73"/>
-        <v>68.013168925490859</v>
-      </c>
-      <c r="EY15" s="1">
-        <f t="shared" si="73"/>
-        <v>67.333037236235953</v>
-      </c>
-      <c r="EZ15" s="1">
-        <f t="shared" si="73"/>
-        <v>66.659706863873595</v>
-      </c>
-      <c r="FA15" s="1">
-        <f t="shared" si="73"/>
-        <v>65.993109795234858</v>
-      </c>
-      <c r="FB15" s="1">
-        <f t="shared" si="73"/>
-        <v>65.333178697282506</v>
-      </c>
-      <c r="FC15" s="1">
-        <f t="shared" si="73"/>
-        <v>64.679846910309678</v>
-      </c>
-      <c r="FD15" s="1">
-        <f t="shared" si="73"/>
-        <v>64.033048441206574</v>
-      </c>
-      <c r="FE15" s="1">
-        <f t="shared" si="73"/>
-        <v>63.392717956794506</v>
-      </c>
-      <c r="FF15" s="1">
-        <f t="shared" si="73"/>
-        <v>62.758790777226558</v>
-      </c>
-      <c r="FG15" s="1">
-        <f t="shared" si="73"/>
-        <v>62.131202869454292</v>
-      </c>
-      <c r="FH15" s="1">
-        <f t="shared" si="73"/>
-        <v>61.509890840759745</v>
-      </c>
-      <c r="FI15" s="1">
-        <f t="shared" si="73"/>
-        <v>60.894791932352149</v>
-      </c>
-      <c r="FJ15" s="1">
-        <f t="shared" si="73"/>
-        <v>60.28584401302863</v>
-      </c>
-      <c r="FK15" s="1">
-        <f t="shared" si="73"/>
-        <v>59.682985572898346</v>
+        <v>95.647223738281582</v>
       </c>
     </row>
     <row r="16" spans="2:167" x14ac:dyDescent="0.3">
@@ -3925,47 +3921,47 @@
         <v>2</v>
       </c>
       <c r="C16" s="4">
-        <f t="shared" ref="C16:L16" si="74">1211.1+23.7+234.4</f>
+        <f t="shared" ref="C16:L16" si="72">1211.1+23.7+234.4</f>
         <v>1469.2</v>
       </c>
       <c r="D16" s="4">
-        <f t="shared" si="74"/>
+        <f t="shared" si="72"/>
         <v>1469.2</v>
       </c>
       <c r="E16" s="4">
-        <f t="shared" si="74"/>
+        <f t="shared" si="72"/>
         <v>1469.2</v>
       </c>
       <c r="F16" s="4">
-        <f t="shared" si="74"/>
+        <f t="shared" si="72"/>
         <v>1469.2</v>
       </c>
       <c r="G16" s="4">
-        <f t="shared" si="74"/>
+        <f t="shared" si="72"/>
         <v>1469.2</v>
       </c>
       <c r="H16" s="4">
-        <f t="shared" si="74"/>
+        <f t="shared" si="72"/>
         <v>1469.2</v>
       </c>
       <c r="I16" s="4">
-        <f t="shared" si="74"/>
+        <f t="shared" si="72"/>
         <v>1469.2</v>
       </c>
       <c r="J16" s="4">
-        <f t="shared" si="74"/>
+        <f t="shared" si="72"/>
         <v>1469.2</v>
       </c>
       <c r="K16" s="4">
-        <f t="shared" si="74"/>
+        <f t="shared" si="72"/>
         <v>1469.2</v>
       </c>
       <c r="L16" s="4">
-        <f t="shared" si="74"/>
+        <f t="shared" si="72"/>
         <v>1469.2</v>
       </c>
       <c r="M16" s="4">
-        <f t="shared" ref="M16" si="75">1211.1+23.7+234.4</f>
+        <f t="shared" ref="M16" si="73">1211.1+23.7+234.4</f>
         <v>1469.2</v>
       </c>
       <c r="N16" s="4">
@@ -4031,12 +4027,12 @@
         <v>1674.9</v>
       </c>
       <c r="AG16" s="4">
-        <f>1674.9</f>
-        <v>1674.9</v>
+        <f>1696.5</f>
+        <v>1696.5</v>
       </c>
       <c r="AH16" s="4">
-        <f>1674.9</f>
-        <v>1674.9</v>
+        <f>1696.5</f>
+        <v>1696.5</v>
       </c>
       <c r="AI16" s="4"/>
       <c r="AK16" s="4">
@@ -4061,52 +4057,52 @@
         <v>1508</v>
       </c>
       <c r="AQ16" s="4">
-        <f t="shared" ref="AQ16" si="76">1442.2+22.5+231.6</f>
+        <f t="shared" ref="AQ16" si="74">1442.2+22.5+231.6</f>
         <v>1696.3</v>
       </c>
       <c r="AR16" s="4">
-        <f t="shared" ref="AR16:BB16" si="77">1674.9</f>
-        <v>1674.9</v>
+        <f>1696.5</f>
+        <v>1696.5</v>
       </c>
       <c r="AS16" s="4">
-        <f t="shared" si="77"/>
-        <v>1674.9</v>
+        <f>1696.5</f>
+        <v>1696.5</v>
       </c>
       <c r="AT16" s="4">
-        <f t="shared" si="77"/>
-        <v>1674.9</v>
+        <f>1696.5</f>
+        <v>1696.5</v>
       </c>
       <c r="AU16" s="4">
-        <f t="shared" si="77"/>
-        <v>1674.9</v>
+        <f>1696.5</f>
+        <v>1696.5</v>
       </c>
       <c r="AV16" s="4">
-        <f t="shared" si="77"/>
-        <v>1674.9</v>
+        <f>1696.5</f>
+        <v>1696.5</v>
       </c>
       <c r="AW16" s="4">
-        <f t="shared" si="77"/>
-        <v>1674.9</v>
+        <f>1696.5</f>
+        <v>1696.5</v>
       </c>
       <c r="AX16" s="4">
-        <f t="shared" si="77"/>
-        <v>1674.9</v>
+        <f>1696.5</f>
+        <v>1696.5</v>
       </c>
       <c r="AY16" s="4">
-        <f t="shared" si="77"/>
-        <v>1674.9</v>
+        <f>1696.5</f>
+        <v>1696.5</v>
       </c>
       <c r="AZ16" s="4">
-        <f t="shared" si="77"/>
-        <v>1674.9</v>
+        <f>1696.5</f>
+        <v>1696.5</v>
       </c>
       <c r="BA16" s="4">
-        <f t="shared" si="77"/>
-        <v>1674.9</v>
+        <f>1696.5</f>
+        <v>1696.5</v>
       </c>
       <c r="BB16" s="4">
-        <f t="shared" si="77"/>
-        <v>1674.9</v>
+        <f>1696.5</f>
+        <v>1696.5</v>
       </c>
     </row>
     <row r="17" spans="2:57" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -4114,132 +4110,132 @@
         <v>33</v>
       </c>
       <c r="C17" s="7">
-        <f t="shared" ref="C17:L17" si="78">C15/C16</f>
+        <f t="shared" ref="C17:L17" si="75">C15/C16</f>
         <v>-0.26252382248842909</v>
       </c>
       <c r="D17" s="7">
+        <f t="shared" si="75"/>
+        <v>-0.24047100462836915</v>
+      </c>
+      <c r="E17" s="7">
+        <f t="shared" si="75"/>
+        <v>-0.22134494963245302</v>
+      </c>
+      <c r="F17" s="7">
+        <f t="shared" si="75"/>
+        <v>-0.13095562210726927</v>
+      </c>
+      <c r="G17" s="7">
+        <f t="shared" si="75"/>
+        <v>-0.21099918322896818</v>
+      </c>
+      <c r="H17" s="7">
+        <f t="shared" si="75"/>
+        <v>-0.17376803702695343</v>
+      </c>
+      <c r="I17" s="7">
+        <f t="shared" si="75"/>
+        <v>-0.15498230329430981</v>
+      </c>
+      <c r="J17" s="7">
+        <f t="shared" si="75"/>
+        <v>-0.16376259188674108</v>
+      </c>
+      <c r="K17" s="7">
+        <f t="shared" si="75"/>
+        <v>-0.20820854887013335</v>
+      </c>
+      <c r="L17" s="7">
+        <f t="shared" si="75"/>
+        <v>-0.22182139940103451</v>
+      </c>
+      <c r="M17" s="7">
+        <f t="shared" ref="M17:N17" si="76">M15/M16</f>
+        <v>-0.13537979852981213</v>
+      </c>
+      <c r="N17" s="7">
+        <f t="shared" si="76"/>
+        <v>-7.4887931034482783E-2</v>
+      </c>
+      <c r="O17" s="7">
+        <f t="shared" ref="O17:Q17" si="77">O15/O16</f>
+        <v>-0.19018567639257292</v>
+      </c>
+      <c r="P17" s="7">
+        <f t="shared" si="77"/>
+        <v>-0.1005305039787798</v>
+      </c>
+      <c r="Q17" s="7">
+        <f t="shared" si="77"/>
+        <v>-4.7679045092838199E-2</v>
+      </c>
+      <c r="R17" s="7">
+        <f t="shared" ref="R17:S17" si="78">R15/R16</f>
+        <v>1.4986737400530548E-2</v>
+      </c>
+      <c r="S17" s="7">
         <f t="shared" si="78"/>
-        <v>-0.24047100462836915</v>
-      </c>
-      <c r="E17" s="7">
-        <f t="shared" si="78"/>
-        <v>-0.22134494963245302</v>
-      </c>
-      <c r="F17" s="7">
-        <f t="shared" si="78"/>
-        <v>-0.13095562210726927</v>
-      </c>
-      <c r="G17" s="7">
-        <f t="shared" si="78"/>
-        <v>-0.21099918322896818</v>
-      </c>
-      <c r="H17" s="7">
-        <f t="shared" si="78"/>
-        <v>-0.17376803702695343</v>
-      </c>
-      <c r="I17" s="7">
-        <f t="shared" si="78"/>
-        <v>-0.15498230329430981</v>
-      </c>
-      <c r="J17" s="7">
-        <f t="shared" si="78"/>
-        <v>-0.16376259188674108</v>
-      </c>
-      <c r="K17" s="7">
-        <f t="shared" si="78"/>
-        <v>-0.20820854887013335</v>
-      </c>
-      <c r="L17" s="7">
-        <f t="shared" si="78"/>
-        <v>-0.22182139940103451</v>
-      </c>
-      <c r="M17" s="7">
-        <f t="shared" ref="M17:N17" si="79">M15/M16</f>
-        <v>-0.13537979852981213</v>
-      </c>
-      <c r="N17" s="7">
+        <v>-0.23852785145888589</v>
+      </c>
+      <c r="T17" s="7">
+        <f t="shared" ref="T17:U17" si="79">T15/T16</f>
+        <v>-0.27990716180371344</v>
+      </c>
+      <c r="U17" s="7">
         <f t="shared" si="79"/>
-        <v>-7.4887931034482783E-2</v>
-      </c>
-      <c r="O17" s="7">
-        <f t="shared" ref="O17:Q17" si="80">O15/O16</f>
-        <v>-0.19018567639257292</v>
-      </c>
-      <c r="P17" s="7">
-        <f t="shared" si="80"/>
-        <v>-0.1005305039787798</v>
-      </c>
-      <c r="Q17" s="7">
-        <f t="shared" si="80"/>
-        <v>-4.7679045092838199E-2</v>
-      </c>
-      <c r="R17" s="7">
-        <f t="shared" ref="R17:S17" si="81">R15/R16</f>
-        <v>1.4986737400530548E-2</v>
-      </c>
-      <c r="S17" s="7">
-        <f t="shared" si="81"/>
-        <v>-0.23852785145888589</v>
-      </c>
-      <c r="T17" s="7">
-        <f t="shared" ref="T17:U17" si="82">T15/T16</f>
-        <v>-0.27990716180371344</v>
-      </c>
-      <c r="U17" s="7">
+        <v>-0.33388594164456226</v>
+      </c>
+      <c r="V17" s="7">
+        <f t="shared" ref="V17" si="80">V15/V16</f>
+        <v>-0.19124668435013256</v>
+      </c>
+      <c r="W17" s="7">
+        <f t="shared" ref="W17" si="81">W15/W16</f>
+        <v>-0.21790450928381963</v>
+      </c>
+      <c r="X17" s="7">
+        <f t="shared" ref="X17:Y17" si="82">X15/X16</f>
+        <v>-0.25026525198938993</v>
+      </c>
+      <c r="Y17" s="7">
         <f t="shared" si="82"/>
-        <v>-0.33388594164456226</v>
-      </c>
-      <c r="V17" s="7">
-        <f t="shared" ref="V17" si="83">V15/V16</f>
-        <v>-0.19124668435013256</v>
-      </c>
-      <c r="W17" s="7">
-        <f t="shared" ref="W17" si="84">W15/W16</f>
-        <v>-0.21790450928381963</v>
-      </c>
-      <c r="X17" s="7">
-        <f t="shared" ref="X17:Y17" si="85">X15/X16</f>
-        <v>-0.25026525198938993</v>
-      </c>
-      <c r="Y17" s="7">
+        <v>-0.24423076923076928</v>
+      </c>
+      <c r="Z17" s="7">
+        <f t="shared" ref="Z17" si="83">Z15/Z16</f>
+        <v>-0.16458885941644566</v>
+      </c>
+      <c r="AA17" s="7">
+        <f t="shared" ref="AA17" si="84">AA15/AA16</f>
+        <v>-0.2022546419098144</v>
+      </c>
+      <c r="AB17" s="7">
+        <f t="shared" ref="AB17:AD17" si="85">AB15/AB16</f>
+        <v>-0.14975292274316021</v>
+      </c>
+      <c r="AC17" s="7">
         <f t="shared" si="85"/>
-        <v>-0.24423076923076928</v>
-      </c>
-      <c r="Z17" s="7">
-        <f t="shared" ref="Z17" si="86">Z15/Z16</f>
-        <v>-0.16458885941644566</v>
-      </c>
-      <c r="AA17" s="7">
-        <f t="shared" ref="AA17" si="87">AA15/AA16</f>
-        <v>-0.2022546419098144</v>
-      </c>
-      <c r="AB17" s="7">
-        <f t="shared" ref="AB17:AD17" si="88">AB15/AB16</f>
-        <v>-0.14975292274316021</v>
-      </c>
-      <c r="AC17" s="7">
-        <f t="shared" si="88"/>
         <v>-9.1461960410207516E-2</v>
       </c>
       <c r="AD17" s="7">
-        <f t="shared" si="88"/>
+        <f t="shared" si="85"/>
         <v>5.4235689441725727E-3</v>
       </c>
       <c r="AE17" s="7">
-        <f t="shared" ref="AE17:AH17" si="89">AE15/AE16</f>
+        <f t="shared" ref="AE17:AH17" si="86">AE15/AE16</f>
         <v>-8.23557153805341E-2</v>
       </c>
       <c r="AF17" s="7">
-        <f t="shared" si="89"/>
+        <f t="shared" si="86"/>
         <v>-0.15678547973013304</v>
       </c>
       <c r="AG17" s="7">
-        <f t="shared" si="89"/>
-        <v>-8.2521643083169158E-2</v>
+        <f t="shared" si="86"/>
+        <v>-6.0949012673150643E-2</v>
       </c>
       <c r="AH17" s="7">
-        <f t="shared" si="89"/>
-        <v>-1.1815540629291313E-2</v>
+        <f t="shared" si="86"/>
+        <v>-4.5142835249042624E-3</v>
       </c>
       <c r="AI17" s="7"/>
       <c r="AK17" s="7">
@@ -4255,64 +4251,64 @@
         <v>-0.64227538796624029</v>
       </c>
       <c r="AN17" s="7">
-        <f t="shared" ref="AN17:AW17" si="90">AN15/AN16</f>
+        <f t="shared" ref="AN17:AW17" si="87">AN15/AN16</f>
         <v>-0.32340848806366046</v>
       </c>
       <c r="AO17" s="7">
-        <f t="shared" si="90"/>
+        <f t="shared" si="87"/>
         <v>-1.0435676392572943</v>
       </c>
       <c r="AP17" s="7">
-        <f t="shared" si="90"/>
+        <f t="shared" si="87"/>
         <v>-0.87698938992042441</v>
       </c>
       <c r="AQ17" s="7">
-        <f t="shared" si="90"/>
+        <f t="shared" si="87"/>
         <v>-0.4113069622118728</v>
       </c>
       <c r="AR17" s="7">
-        <f t="shared" si="90"/>
-        <v>-0.33453062809719952</v>
+        <f t="shared" si="87"/>
+        <v>-0.3025985747126434</v>
       </c>
       <c r="AS17" s="7">
-        <f t="shared" si="90"/>
-        <v>-0.17746567603080754</v>
+        <f t="shared" si="87"/>
+        <v>-0.16303617397701126</v>
       </c>
       <c r="AT17" s="7">
-        <f t="shared" si="90"/>
-        <v>-0.12170675809453908</v>
+        <f t="shared" si="87"/>
+        <v>-8.2866302558462404E-2</v>
       </c>
       <c r="AU17" s="7">
-        <f t="shared" si="90"/>
-        <v>-9.0432200211905164E-2</v>
+        <f t="shared" si="87"/>
+        <v>-3.7208535357174215E-2</v>
       </c>
       <c r="AV17" s="7">
-        <f t="shared" si="90"/>
-        <v>-5.7889337237565293E-2</v>
+        <f t="shared" si="87"/>
+        <v>-2.4971345665395417E-3</v>
       </c>
       <c r="AW17" s="7">
-        <f t="shared" si="90"/>
-        <v>-3.6774330577614485E-2</v>
+        <f t="shared" si="87"/>
+        <v>2.0075052312934643E-2</v>
       </c>
       <c r="AX17" s="7">
-        <f t="shared" ref="AX17:BB17" si="91">AX15/AX16</f>
-        <v>-9.5589660989310096E-3</v>
+        <f t="shared" ref="AX17:BB17" si="88">AX15/AX16</f>
+        <v>4.8752181398418575E-2</v>
       </c>
       <c r="AY17" s="7">
-        <f t="shared" si="91"/>
-        <v>1.8832050931734665E-2</v>
+        <f t="shared" si="88"/>
+        <v>7.8646227703290758E-2</v>
       </c>
       <c r="AZ17" s="7">
-        <f t="shared" si="91"/>
-        <v>4.8354827674312401E-2</v>
+        <f t="shared" si="88"/>
+        <v>0.10971511023494451</v>
       </c>
       <c r="BA17" s="7">
-        <f t="shared" si="91"/>
-        <v>7.9044633847845769E-2</v>
+        <f t="shared" si="88"/>
+        <v>0.14199538948299428</v>
       </c>
       <c r="BB17" s="7">
-        <f t="shared" si="91"/>
-        <v>0.11093910758182224</v>
+        <f t="shared" si="88"/>
+        <v>0.17552602393706682</v>
       </c>
     </row>
     <row r="19" spans="2:57" x14ac:dyDescent="0.3">
@@ -4324,112 +4320,112 @@
         <v>0.388816644993498</v>
       </c>
       <c r="H19" s="9">
-        <f t="shared" ref="H19:N19" si="92">H3/D3-1</f>
+        <f t="shared" ref="H19:N19" si="89">H3/D3-1</f>
         <v>0.47922226458253903</v>
       </c>
       <c r="I19" s="9">
-        <f t="shared" si="92"/>
+        <f t="shared" si="89"/>
         <v>0.4988243197850184</v>
       </c>
       <c r="J19" s="9">
-        <f t="shared" si="92"/>
+        <f t="shared" si="89"/>
         <v>0.4385739933316235</v>
       </c>
       <c r="K19" s="9">
-        <f t="shared" si="92"/>
+        <f t="shared" si="89"/>
         <v>0.44350811485642949</v>
       </c>
       <c r="L19" s="9">
-        <f t="shared" si="92"/>
+        <f t="shared" si="89"/>
         <v>0.17061855670103099</v>
       </c>
       <c r="M19" s="9">
-        <f t="shared" si="92"/>
+        <f t="shared" si="89"/>
         <v>0.52106678619453173</v>
       </c>
       <c r="N19" s="9">
-        <f t="shared" si="92"/>
+        <f t="shared" si="89"/>
         <v>0.62471028703868781</v>
       </c>
       <c r="O19" s="9">
-        <f t="shared" ref="O19" si="93">O3/K3-1</f>
+        <f t="shared" ref="O19" si="90">O3/K3-1</f>
         <v>0.66400000000000015</v>
       </c>
       <c r="P19" s="9">
-        <f t="shared" ref="P19" si="94">P3/L3-1</f>
+        <f t="shared" ref="P19" si="91">P3/L3-1</f>
         <v>1.1622633201232939</v>
       </c>
       <c r="Q19" s="9">
-        <f t="shared" ref="Q19" si="95">Q3/M3-1</f>
+        <f t="shared" ref="Q19" si="92">Q3/M3-1</f>
         <v>0.57285987918078662</v>
       </c>
       <c r="R19" s="9">
-        <f t="shared" ref="R19" si="96">R3/N3-1</f>
+        <f t="shared" ref="R19" si="93">R3/N3-1</f>
         <v>0.42422912323054995</v>
       </c>
       <c r="S19" s="9">
-        <f t="shared" ref="S19" si="97">S3/O3-1</f>
+        <f t="shared" ref="S19" si="94">S3/O3-1</f>
         <v>0.3808471933471933</v>
       </c>
       <c r="T19" s="9">
-        <f t="shared" ref="T19" si="98">T3/P3-1</f>
+        <f t="shared" ref="T19" si="95">T3/P3-1</f>
         <v>0.1311475409836067</v>
       </c>
       <c r="U19" s="9">
-        <f t="shared" ref="U19" si="99">U3/Q3-1</f>
+        <f t="shared" ref="U19" si="96">U3/Q3-1</f>
         <v>5.7142857142857162E-2</v>
       </c>
       <c r="V19" s="9">
-        <f t="shared" ref="V19" si="100">V3/R3-1</f>
+        <f t="shared" ref="V19" si="97">V3/R3-1</f>
         <v>1.3868556899607754E-3</v>
       </c>
       <c r="W19" s="9">
-        <f t="shared" ref="W19" si="101">W3/S3-1</f>
+        <f t="shared" ref="W19" si="98">W3/S3-1</f>
         <v>-6.9728051190364182E-2</v>
       </c>
       <c r="X19" s="9">
-        <f t="shared" ref="X19" si="102">X3/T3-1</f>
+        <f t="shared" ref="X19" si="99">X3/T3-1</f>
         <v>-3.8887388603834783E-2</v>
       </c>
       <c r="Y19" s="9">
-        <f t="shared" ref="Y19" si="103">Y3/U3-1</f>
+        <f t="shared" ref="Y19" si="100">Y3/U3-1</f>
         <v>5.325653522374818E-2</v>
       </c>
       <c r="Z19" s="9">
-        <f t="shared" ref="Z19" si="104">Z3/V3-1</f>
+        <f t="shared" ref="Z19" si="101">Z3/V3-1</f>
         <v>4.7395552819881503E-2</v>
       </c>
       <c r="AA19" s="9">
-        <f t="shared" ref="AA19" si="105">AA3/W3-1</f>
+        <f t="shared" ref="AA19" si="102">AA3/W3-1</f>
         <v>0.20857778676916849</v>
       </c>
       <c r="AB19" s="9">
-        <f t="shared" ref="AB19" si="106">AB3/X3-1</f>
+        <f t="shared" ref="AB19" si="103">AB3/X3-1</f>
         <v>0.15837782148543589</v>
       </c>
       <c r="AC19" s="9">
-        <f t="shared" ref="AC19" si="107">AC3/Y3-1</f>
+        <f t="shared" ref="AC19" si="104">AC3/Y3-1</f>
         <v>0.15471983846542159</v>
       </c>
       <c r="AD19" s="9">
-        <f t="shared" ref="AD19" si="108">AD3/Z3-1</f>
+        <f t="shared" ref="AD19" si="105">AD3/Z3-1</f>
         <v>0.14398001909939029</v>
       </c>
       <c r="AE19" s="9">
-        <f t="shared" ref="AE19" si="109">AE3/AA3-1</f>
+        <f t="shared" ref="AE19" si="106">AE3/AA3-1</f>
         <v>0.1409440910612656</v>
       </c>
       <c r="AF19" s="9">
-        <f t="shared" ref="AF19" si="110">AF3/AB3-1</f>
+        <f t="shared" ref="AF19" si="107">AF3/AB3-1</f>
         <v>8.7402975420439954E-2</v>
       </c>
       <c r="AG19" s="9">
-        <f t="shared" ref="AG19" si="111">AG3/AC3-1</f>
+        <f t="shared" ref="AG19" si="108">AG3/AC3-1</f>
+        <v>9.7850637522768569E-2</v>
+      </c>
+      <c r="AH19" s="9">
+        <f t="shared" ref="AH19" si="109">AH3/AD3-1</f>
         <v>8.0000000000000071E-2</v>
-      </c>
-      <c r="AH19" s="9">
-        <f t="shared" ref="AH19" si="112">AH3/AD3-1</f>
-        <v>6.0000000000000053E-2</v>
       </c>
       <c r="AI19" s="9"/>
       <c r="AK19" s="9"/>
@@ -4442,63 +4438,63 @@
         <v>0.46120664529291733</v>
       </c>
       <c r="AN19" s="9">
-        <f t="shared" ref="AN19:AX19" si="113">AN3/AM3-1</f>
+        <f t="shared" ref="AN19:AX19" si="110">AN3/AM3-1</f>
         <v>0.64243826544859806</v>
       </c>
       <c r="AO19" s="9">
-        <f t="shared" si="113"/>
+        <f t="shared" si="110"/>
         <v>0.11772849821476283</v>
       </c>
       <c r="AP19" s="9">
-        <f t="shared" si="113"/>
+        <f t="shared" si="110"/>
         <v>9.561475944195319E-4</v>
       </c>
       <c r="AQ19" s="9">
-        <f t="shared" si="113"/>
+        <f t="shared" si="110"/>
         <v>0.16395293300334335</v>
       </c>
       <c r="AR19" s="9">
-        <f t="shared" si="113"/>
-        <v>8.9479986570672132E-2</v>
+        <f t="shared" si="110"/>
+        <v>9.9858992054314255E-2</v>
       </c>
       <c r="AS19" s="9">
-        <f t="shared" si="113"/>
+        <f t="shared" si="110"/>
+        <v>7.0000000000000062E-2</v>
+      </c>
+      <c r="AT19" s="9">
+        <f t="shared" si="110"/>
+        <v>6.0000000000000053E-2</v>
+      </c>
+      <c r="AU19" s="9">
+        <f t="shared" si="110"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AT19" s="9">
-        <f t="shared" si="113"/>
+      <c r="AV19" s="9">
+        <f t="shared" si="110"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AU19" s="9">
-        <f t="shared" si="113"/>
-        <v>4.0000000000000036E-2</v>
-      </c>
-      <c r="AV19" s="9">
-        <f t="shared" si="113"/>
-        <v>4.0000000000000036E-2</v>
-      </c>
       <c r="AW19" s="9">
-        <f t="shared" si="113"/>
+        <f t="shared" si="110"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AX19" s="9">
-        <f t="shared" si="113"/>
+        <f t="shared" si="110"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AY19" s="9">
-        <f t="shared" ref="AY19" si="114">AY3/AX3-1</f>
+        <f t="shared" ref="AY19" si="111">AY3/AX3-1</f>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AZ19" s="9">
-        <f t="shared" ref="AZ19" si="115">AZ3/AY3-1</f>
+        <f t="shared" ref="AZ19" si="112">AZ3/AY3-1</f>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="BA19" s="9">
-        <f t="shared" ref="BA19" si="116">BA3/AZ3-1</f>
+        <f t="shared" ref="BA19" si="113">BA3/AZ3-1</f>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="BB19" s="9">
-        <f t="shared" ref="BB19" si="117">BB3/BA3-1</f>
+        <f t="shared" ref="BB19" si="114">BB3/BA3-1</f>
         <v>3.0000000000000027E-2</v>
       </c>
     </row>
@@ -4511,200 +4507,200 @@
         <v>0.14694408322496741</v>
       </c>
       <c r="D20" s="9">
-        <f t="shared" ref="D20:N20" si="118">D5/D3</f>
+        <f t="shared" ref="D20:N20" si="115">D5/D3</f>
         <v>0.26953869614944725</v>
       </c>
       <c r="E20" s="9">
+        <f t="shared" si="115"/>
+        <v>0.33624454148471616</v>
+      </c>
+      <c r="F20" s="9">
+        <f t="shared" si="115"/>
+        <v>0.45370607848166195</v>
+      </c>
+      <c r="G20" s="9">
+        <f t="shared" si="115"/>
+        <v>0.363920099875156</v>
+      </c>
+      <c r="H20" s="9">
+        <f t="shared" si="115"/>
+        <v>0.44458762886597936</v>
+      </c>
+      <c r="I20" s="9">
+        <f t="shared" si="115"/>
+        <v>0.5</v>
+      </c>
+      <c r="J20" s="9">
+        <f t="shared" si="115"/>
+        <v>0.54822606525227313</v>
+      </c>
+      <c r="K20" s="9">
+        <f t="shared" si="115"/>
+        <v>0.45210810810810809</v>
+      </c>
+      <c r="L20" s="9">
+        <f t="shared" si="115"/>
+        <v>0.4484808454425363</v>
+      </c>
+      <c r="M20" s="9">
+        <f t="shared" si="115"/>
+        <v>0.56814498305584205</v>
+      </c>
+      <c r="N20" s="9">
+        <f t="shared" si="115"/>
+        <v>0.57697794359705912</v>
+      </c>
+      <c r="O20" s="9">
+        <f t="shared" ref="O20:R20" si="116">O5/O3</f>
+        <v>0.46387733887733884</v>
+      </c>
+      <c r="P20" s="9">
+        <f t="shared" si="116"/>
+        <v>0.54688931880663882</v>
+      </c>
+      <c r="Q20" s="9">
+        <f t="shared" si="116"/>
+        <v>0.58454332552693211</v>
+      </c>
+      <c r="R20" s="9">
+        <f t="shared" si="116"/>
+        <v>0.65390245781647272</v>
+      </c>
+      <c r="S20" s="9">
+        <f t="shared" ref="S20:AD20" si="117">S5/S3</f>
+        <v>0.60393337724663598</v>
+      </c>
+      <c r="T20" s="9">
+        <f t="shared" si="117"/>
+        <v>0.59816365109370784</v>
+      </c>
+      <c r="U20" s="9">
+        <f t="shared" si="117"/>
+        <v>0.58635356668143557</v>
+      </c>
+      <c r="V20" s="9">
+        <f t="shared" si="117"/>
+        <v>0.62968377317842583</v>
+      </c>
+      <c r="W20" s="9">
+        <f t="shared" si="117"/>
+        <v>0.55492615820352009</v>
+      </c>
+      <c r="X20" s="9">
+        <f t="shared" si="117"/>
+        <v>0.53460709937248296</v>
+      </c>
+      <c r="Y20" s="9">
+        <f t="shared" si="117"/>
+        <v>0.53239104829210837</v>
+      </c>
+      <c r="Z20" s="9">
+        <f t="shared" si="117"/>
+        <v>0.54345111290678028</v>
+      </c>
+      <c r="AA20" s="9">
+        <f t="shared" si="117"/>
+        <v>0.51899899564780716</v>
+      </c>
+      <c r="AB20" s="9">
+        <f t="shared" si="117"/>
+        <v>0.5238518758085382</v>
+      </c>
+      <c r="AC20" s="9">
+        <f t="shared" si="117"/>
+        <v>0.53449908925318768</v>
+      </c>
+      <c r="AD20" s="9">
+        <f t="shared" si="117"/>
+        <v>0.56867655557696006</v>
+      </c>
+      <c r="AE20" s="9">
+        <f t="shared" ref="AE20:AH20" si="118">AE5/AE3</f>
+        <v>0.53080985915492962</v>
+      </c>
+      <c r="AF20" s="9">
         <f t="shared" si="118"/>
-        <v>0.33624454148471616</v>
-      </c>
-      <c r="F20" s="9">
+        <v>0.51423897687560416</v>
+      </c>
+      <c r="AG20" s="9">
         <f t="shared" si="118"/>
-        <v>0.45370607848166195</v>
-      </c>
-      <c r="G20" s="9">
+        <v>0.55256172020175198</v>
+      </c>
+      <c r="AH20" s="9">
         <f t="shared" si="118"/>
-        <v>0.363920099875156</v>
-      </c>
-      <c r="H20" s="9">
-        <f t="shared" si="118"/>
-        <v>0.44458762886597936</v>
-      </c>
-      <c r="I20" s="9">
-        <f t="shared" si="118"/>
-        <v>0.5</v>
-      </c>
-      <c r="J20" s="9">
-        <f t="shared" si="118"/>
-        <v>0.54822606525227313</v>
-      </c>
-      <c r="K20" s="9">
-        <f t="shared" si="118"/>
-        <v>0.45210810810810809</v>
-      </c>
-      <c r="L20" s="9">
-        <f t="shared" si="118"/>
-        <v>0.4484808454425363</v>
-      </c>
-      <c r="M20" s="9">
-        <f t="shared" si="118"/>
-        <v>0.56814498305584205</v>
-      </c>
-      <c r="N20" s="9">
-        <f t="shared" si="118"/>
-        <v>0.57697794359705912</v>
-      </c>
-      <c r="O20" s="9">
-        <f t="shared" ref="O20:R20" si="119">O5/O3</f>
-        <v>0.46387733887733884</v>
-      </c>
-      <c r="P20" s="9">
-        <f t="shared" si="119"/>
-        <v>0.54688931880663882</v>
-      </c>
-      <c r="Q20" s="9">
-        <f t="shared" si="119"/>
-        <v>0.58454332552693211</v>
-      </c>
-      <c r="R20" s="9">
-        <f t="shared" si="119"/>
-        <v>0.65390245781647272</v>
-      </c>
-      <c r="S20" s="9">
-        <f t="shared" ref="S20:AD20" si="120">S5/S3</f>
-        <v>0.60393337724663598</v>
-      </c>
-      <c r="T20" s="9">
-        <f t="shared" si="120"/>
-        <v>0.59816365109370784</v>
-      </c>
-      <c r="U20" s="9">
-        <f t="shared" si="120"/>
-        <v>0.58635356668143557</v>
-      </c>
-      <c r="V20" s="9">
-        <f t="shared" si="120"/>
-        <v>0.62968377317842583</v>
-      </c>
-      <c r="W20" s="9">
-        <f t="shared" si="120"/>
-        <v>0.55492615820352009</v>
-      </c>
-      <c r="X20" s="9">
-        <f t="shared" si="120"/>
-        <v>0.53460709937248296</v>
-      </c>
-      <c r="Y20" s="9">
-        <f t="shared" si="120"/>
-        <v>0.53239104829210837</v>
-      </c>
-      <c r="Z20" s="9">
-        <f t="shared" si="120"/>
-        <v>0.54345111290678028</v>
-      </c>
-      <c r="AA20" s="9">
-        <f t="shared" si="120"/>
-        <v>0.51899899564780716</v>
-      </c>
-      <c r="AB20" s="9">
-        <f t="shared" si="120"/>
-        <v>0.5238518758085382</v>
-      </c>
-      <c r="AC20" s="9">
-        <f t="shared" si="120"/>
-        <v>0.53449908925318768</v>
-      </c>
-      <c r="AD20" s="9">
-        <f t="shared" si="120"/>
-        <v>0.56867655557696006</v>
-      </c>
-      <c r="AE20" s="9">
-        <f t="shared" ref="AE20:AH20" si="121">AE5/AE3</f>
-        <v>0.53080985915492962</v>
-      </c>
-      <c r="AF20" s="9">
-        <f t="shared" si="121"/>
-        <v>0.51423897687560416</v>
-      </c>
-      <c r="AG20" s="9">
-        <f t="shared" si="121"/>
-        <v>0.54</v>
-      </c>
-      <c r="AH20" s="9">
-        <f t="shared" si="121"/>
         <v>0.56999999999999995</v>
       </c>
       <c r="AI20" s="9"/>
       <c r="AK20" s="9">
-        <f t="shared" ref="AK20:AM20" si="122">AK5/AK3</f>
+        <f t="shared" ref="AK20:AM20" si="119">AK5/AK3</f>
         <v>0.32322547857021849</v>
       </c>
       <c r="AL20" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="119"/>
         <v>0.47781987758670946</v>
       </c>
       <c r="AM20" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="119"/>
         <v>0.52826425180516212</v>
       </c>
       <c r="AN20" s="9">
-        <f t="shared" ref="AN20:AW20" si="123">AN5/AN3</f>
+        <f t="shared" ref="AN20:AW20" si="120">AN5/AN3</f>
         <v>0.57487066138787013</v>
       </c>
       <c r="AO20" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="120"/>
         <v>0.60550219479334189</v>
       </c>
       <c r="AP20" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="120"/>
         <v>0.54100994312014239</v>
       </c>
       <c r="AQ20" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="120"/>
         <v>0.53851605923825863</v>
       </c>
       <c r="AR20" s="9">
-        <f t="shared" si="123"/>
-        <v>0.54040200043210762</v>
+        <f t="shared" si="120"/>
+        <v>0.54376654800311497</v>
       </c>
       <c r="AS20" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="120"/>
         <v>0.56000000000000005</v>
       </c>
       <c r="AT20" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="120"/>
         <v>0.56000000000000005</v>
       </c>
       <c r="AU20" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="120"/>
         <v>0.56000000000000005</v>
       </c>
       <c r="AV20" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="120"/>
         <v>0.56000000000000005</v>
       </c>
       <c r="AW20" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="120"/>
         <v>0.56000000000000005</v>
       </c>
       <c r="AX20" s="9">
-        <f t="shared" ref="AX20:BB20" si="124">AX5/AX3</f>
+        <f t="shared" ref="AX20:BB20" si="121">AX5/AX3</f>
         <v>0.56000000000000005</v>
       </c>
       <c r="AY20" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="121"/>
         <v>0.56000000000000005</v>
       </c>
       <c r="AZ20" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="121"/>
         <v>0.56000000000000005</v>
       </c>
       <c r="BA20" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="121"/>
         <v>0.56000000000000005</v>
       </c>
       <c r="BB20" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="121"/>
         <v>0.56000000000000005</v>
       </c>
     </row>
@@ -4717,201 +4713,201 @@
         <v>-1.7013437364542698</v>
       </c>
       <c r="D21" s="9">
-        <f t="shared" ref="D21:N21" si="125">D9/D3</f>
+        <f t="shared" ref="D21:N21" si="122">D9/D3</f>
         <v>-1.3640869233701867</v>
       </c>
       <c r="E21" s="9">
+        <f t="shared" si="122"/>
+        <v>-1.0866644272757811</v>
+      </c>
+      <c r="F21" s="9">
+        <f t="shared" si="122"/>
+        <v>-0.49935880995126969</v>
+      </c>
+      <c r="G21" s="9">
+        <f t="shared" si="122"/>
+        <v>-0.98689138576779045</v>
+      </c>
+      <c r="H21" s="9">
+        <f t="shared" si="122"/>
+        <v>-0.78556701030927822</v>
+      </c>
+      <c r="I21" s="9">
+        <f t="shared" si="122"/>
+        <v>-0.51277454056476923</v>
+      </c>
+      <c r="J21" s="9">
+        <f t="shared" si="122"/>
+        <v>-0.45195221964699595</v>
+      </c>
+      <c r="K21" s="9">
+        <f t="shared" si="122"/>
+        <v>-0.61902702702702694</v>
+      </c>
+      <c r="L21" s="9">
+        <f t="shared" si="122"/>
+        <v>-0.68383971818582112</v>
+      </c>
+      <c r="M21" s="9">
+        <f t="shared" si="122"/>
+        <v>-0.24723736555179018</v>
+      </c>
+      <c r="N21" s="9">
+        <f t="shared" si="122"/>
+        <v>-0.10655108087347748</v>
+      </c>
+      <c r="O21" s="9">
+        <f t="shared" ref="O21:R21" si="123">O9/O3</f>
+        <v>-0.39449064449064453</v>
+      </c>
+      <c r="P21" s="9">
+        <f t="shared" si="123"/>
+        <v>-0.19600855310049886</v>
+      </c>
+      <c r="Q21" s="9">
+        <f t="shared" si="123"/>
+        <v>-0.16936768149882905</v>
+      </c>
+      <c r="R21" s="9">
+        <f t="shared" si="123"/>
+        <v>-1.9338932121118681E-2</v>
+      </c>
+      <c r="S21" s="9">
+        <f t="shared" ref="S21:AD21" si="124">S9/S3</f>
+        <v>-0.25557542109720521</v>
+      </c>
+      <c r="T21" s="9">
+        <f t="shared" si="124"/>
+        <v>-0.36096858403096577</v>
+      </c>
+      <c r="U21" s="9">
+        <f t="shared" si="124"/>
+        <v>-0.38573327425786436</v>
+      </c>
+      <c r="V21" s="9">
+        <f t="shared" si="124"/>
+        <v>-0.22128183426944673</v>
+      </c>
+      <c r="W21" s="9">
+        <f t="shared" si="124"/>
+        <v>-0.36941128869107825</v>
+      </c>
+      <c r="X21" s="9">
+        <f t="shared" si="124"/>
+        <v>-0.37875807811182916</v>
+      </c>
+      <c r="Y21" s="9">
+        <f t="shared" si="124"/>
+        <v>-0.31987211845869096</v>
+      </c>
+      <c r="Z21" s="9">
+        <f t="shared" si="124"/>
+        <v>-0.18269301403070598</v>
+      </c>
+      <c r="AA21" s="9">
+        <f t="shared" si="124"/>
+        <v>-0.27887512554402422</v>
+      </c>
+      <c r="AB21" s="9">
+        <f t="shared" si="124"/>
+        <v>-0.2052878395860285</v>
+      </c>
+      <c r="AC21" s="9">
+        <f t="shared" si="124"/>
+        <v>-0.12626593806921677</v>
+      </c>
+      <c r="AD21" s="9">
+        <f t="shared" si="124"/>
+        <v>-1.7209272458742739E-2</v>
+      </c>
+      <c r="AE21" s="9">
+        <f t="shared" ref="AE21:AH21" si="125">AE9/AE3</f>
+        <v>-0.14231220657276994</v>
+      </c>
+      <c r="AF21" s="9">
         <f t="shared" si="125"/>
-        <v>-1.0866644272757811</v>
-      </c>
-      <c r="F21" s="9">
+        <v>-0.19309985872555566</v>
+      </c>
+      <c r="AG21" s="9">
         <f t="shared" si="125"/>
-        <v>-0.49935880995126969</v>
-      </c>
-      <c r="G21" s="9">
+        <v>-8.5147332094504966E-2</v>
+      </c>
+      <c r="AH21" s="9">
         <f t="shared" si="125"/>
-        <v>-0.98689138576779045</v>
-      </c>
-      <c r="H21" s="9">
-        <f t="shared" si="125"/>
-        <v>-0.78556701030927822</v>
-      </c>
-      <c r="I21" s="9">
-        <f t="shared" si="125"/>
-        <v>-0.51277454056476923</v>
-      </c>
-      <c r="J21" s="9">
-        <f t="shared" si="125"/>
-        <v>-0.45195221964699595</v>
-      </c>
-      <c r="K21" s="9">
-        <f t="shared" si="125"/>
-        <v>-0.61902702702702694</v>
-      </c>
-      <c r="L21" s="9">
-        <f t="shared" si="125"/>
-        <v>-0.68383971818582112</v>
-      </c>
-      <c r="M21" s="9">
-        <f t="shared" si="125"/>
-        <v>-0.24723736555179018</v>
-      </c>
-      <c r="N21" s="9">
-        <f t="shared" si="125"/>
-        <v>-0.10655108087347748</v>
-      </c>
-      <c r="O21" s="9">
-        <f t="shared" ref="O21:R21" si="126">O9/O3</f>
-        <v>-0.39449064449064453</v>
-      </c>
-      <c r="P21" s="9">
-        <f t="shared" si="126"/>
-        <v>-0.19600855310049886</v>
-      </c>
-      <c r="Q21" s="9">
-        <f t="shared" si="126"/>
-        <v>-0.16936768149882905</v>
-      </c>
-      <c r="R21" s="9">
-        <f t="shared" si="126"/>
-        <v>-1.9338932121118681E-2</v>
-      </c>
-      <c r="S21" s="9">
-        <f t="shared" ref="S21:AD21" si="127">S9/S3</f>
-        <v>-0.25557542109720521</v>
-      </c>
-      <c r="T21" s="9">
-        <f t="shared" si="127"/>
-        <v>-0.36096858403096577</v>
-      </c>
-      <c r="U21" s="9">
-        <f t="shared" si="127"/>
-        <v>-0.38573327425786436</v>
-      </c>
-      <c r="V21" s="9">
-        <f t="shared" si="127"/>
-        <v>-0.22128183426944673</v>
-      </c>
-      <c r="W21" s="9">
-        <f t="shared" si="127"/>
-        <v>-0.36941128869107825</v>
-      </c>
-      <c r="X21" s="9">
-        <f t="shared" si="127"/>
-        <v>-0.37875807811182916</v>
-      </c>
-      <c r="Y21" s="9">
-        <f t="shared" si="127"/>
-        <v>-0.31987211845869096</v>
-      </c>
-      <c r="Z21" s="9">
-        <f t="shared" si="127"/>
-        <v>-0.18269301403070598</v>
-      </c>
-      <c r="AA21" s="9">
-        <f t="shared" si="127"/>
-        <v>-0.27887512554402422</v>
-      </c>
-      <c r="AB21" s="9">
-        <f t="shared" si="127"/>
-        <v>-0.2052878395860285</v>
-      </c>
-      <c r="AC21" s="9">
-        <f t="shared" si="127"/>
-        <v>-0.12626593806921677</v>
-      </c>
-      <c r="AD21" s="9">
-        <f t="shared" si="127"/>
-        <v>-1.7209272458742739E-2</v>
-      </c>
-      <c r="AE21" s="9">
-        <f t="shared" ref="AE21:AH21" si="128">AE9/AE3</f>
-        <v>-0.14231220657276994</v>
-      </c>
-      <c r="AF21" s="9">
-        <f t="shared" si="128"/>
-        <v>-0.19309985872555566</v>
-      </c>
-      <c r="AG21" s="9">
-        <f t="shared" si="128"/>
-        <v>-0.12033663900694865</v>
-      </c>
-      <c r="AH21" s="9">
-        <f t="shared" si="128"/>
-        <v>-3.2602036180181246E-2</v>
+        <v>-2.4405702176844592E-2</v>
       </c>
       <c r="AI21" s="9"/>
       <c r="AK21" s="9">
-        <f t="shared" ref="AK21:AM21" si="129">AK9/AK3</f>
+        <f t="shared" ref="AK21:AM21" si="126">AK9/AK3</f>
         <v>-1.0744536676266305</v>
       </c>
       <c r="AL21" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="126"/>
         <v>-0.64313611192072284</v>
       </c>
       <c r="AM21" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="126"/>
         <v>-0.34379861969920622</v>
       </c>
       <c r="AN21" s="9">
-        <f t="shared" ref="AN21:AW21" si="130">AN9/AN3</f>
+        <f t="shared" ref="AN21:AW21" si="127">AN9/AN3</f>
         <v>-0.17050836754025889</v>
       </c>
       <c r="AO21" s="9">
-        <f t="shared" si="130"/>
+        <f t="shared" si="127"/>
         <v>-0.30325090182102643</v>
       </c>
       <c r="AP21" s="9">
-        <f t="shared" si="130"/>
+        <f t="shared" si="127"/>
         <v>-0.30361252225261603</v>
       </c>
       <c r="AQ21" s="9">
-        <f t="shared" si="130"/>
+        <f t="shared" si="127"/>
         <v>-0.14682732122206885</v>
       </c>
       <c r="AR21" s="9">
-        <f t="shared" si="130"/>
-        <v>-0.11742445050947253</v>
+        <f t="shared" si="127"/>
+        <v>-0.10565887439662017</v>
       </c>
       <c r="AS21" s="9">
-        <f t="shared" si="130"/>
-        <v>-7.2797766299583816E-2</v>
+        <f t="shared" si="127"/>
+        <v>-6.110445185353424E-2</v>
       </c>
       <c r="AT21" s="9">
-        <f t="shared" si="130"/>
-        <v>-5.2689306069375053E-2</v>
+        <f t="shared" si="127"/>
+        <v>-3.2942861516666554E-2</v>
       </c>
       <c r="AU21" s="9">
-        <f t="shared" si="130"/>
-        <v>-4.1236114354012823E-2</v>
+        <f t="shared" si="127"/>
+        <v>-1.7978575929987049E-2</v>
       </c>
       <c r="AV21" s="9">
-        <f t="shared" si="130"/>
-        <v>-3.0082434829439498E-2</v>
+        <f t="shared" si="127"/>
+        <v>-7.4208778940454134E-3</v>
       </c>
       <c r="AW21" s="9">
-        <f t="shared" si="130"/>
-        <v>-2.3290320579171658E-2</v>
+        <f t="shared" si="127"/>
+        <v>-9.9461210496276111E-4</v>
       </c>
       <c r="AX21" s="9">
-        <f t="shared" ref="AX21:BB21" si="131">AX9/AX3</f>
-        <v>-1.5071091053362384E-2</v>
+        <f t="shared" ref="AX21:BB21" si="128">AX9/AX3</f>
+        <v>6.7916910427064442E-3</v>
       </c>
       <c r="AY21" s="9">
-        <f t="shared" si="131"/>
-        <v>-7.0114582173748724E-3</v>
+        <f t="shared" si="128"/>
+        <v>1.4426803837993753E-2</v>
       </c>
       <c r="AZ21" s="9">
-        <f t="shared" si="131"/>
-        <v>8.9167689364214942E-4</v>
+        <f t="shared" si="128"/>
+        <v>2.1913662015896833E-2</v>
       </c>
       <c r="BA21" s="9">
-        <f t="shared" si="131"/>
-        <v>8.6413530704647096E-3</v>
+        <f t="shared" si="128"/>
+        <v>2.9255144306850323E-2</v>
       </c>
       <c r="BB21" s="9">
-        <f t="shared" si="131"/>
-        <v>1.6240550098222704E-2</v>
+        <f t="shared" si="128"/>
+        <v>3.64540735436105E-2</v>
       </c>
       <c r="BD21" t="s">
         <v>40</v>
@@ -4929,185 +4925,185 @@
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
       <c r="G22" s="9">
-        <f t="shared" ref="G22:R22" si="132">G6/C6-1</f>
+        <f t="shared" ref="G22:R22" si="129">G6/C6-1</f>
         <v>7.5621890547263648E-2</v>
       </c>
       <c r="H22" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="129"/>
         <v>0.16240157480314954</v>
       </c>
       <c r="I22" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="129"/>
         <v>3.98034398034397E-2</v>
       </c>
       <c r="J22" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="129"/>
         <v>0.33515815085158152</v>
       </c>
       <c r="K22" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="129"/>
         <v>0.1036077705827938</v>
       </c>
       <c r="L22" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="129"/>
         <v>0.10457239627434367</v>
       </c>
       <c r="M22" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="129"/>
         <v>0.34026465028355402</v>
       </c>
       <c r="N22" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="129"/>
         <v>0.45056947608200448</v>
       </c>
       <c r="O22" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="129"/>
         <v>0.4610226320201174</v>
       </c>
       <c r="P22" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="129"/>
         <v>0.42085090072824838</v>
       </c>
       <c r="Q22" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="129"/>
         <v>0.45275035260930885</v>
       </c>
       <c r="R22" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="129"/>
         <v>0.3636934673366834</v>
       </c>
       <c r="S22" s="9">
-        <f t="shared" ref="S22" si="133">S6/O6-1</f>
+        <f t="shared" ref="S22" si="130">S6/O6-1</f>
         <v>0.30694205393000562</v>
       </c>
       <c r="T22" s="9">
-        <f t="shared" ref="T22" si="134">T6/P6-1</f>
+        <f t="shared" ref="T22" si="131">T6/P6-1</f>
         <v>0.36228756406797946</v>
       </c>
       <c r="U22" s="9">
-        <f t="shared" ref="U22" si="135">U6/Q6-1</f>
+        <f t="shared" ref="U22" si="132">U6/Q6-1</f>
         <v>0.36966019417475726</v>
       </c>
       <c r="V22" s="9">
-        <f t="shared" ref="V22" si="136">V6/R6-1</f>
+        <f t="shared" ref="V22" si="133">V6/R6-1</f>
         <v>0.34707508060801473</v>
       </c>
       <c r="W22" s="9">
-        <f t="shared" ref="W22" si="137">W6/S6-1</f>
+        <f t="shared" ref="W22" si="134">W6/S6-1</f>
         <v>-1.0974539069359412E-3</v>
       </c>
       <c r="X22" s="9">
-        <f t="shared" ref="X22" si="138">X6/T6-1</f>
+        <f t="shared" ref="X22" si="135">X6/T6-1</f>
         <v>-5.4059405940594107E-2</v>
       </c>
       <c r="Y22" s="9">
-        <f t="shared" ref="Y22" si="139">Y6/U6-1</f>
+        <f t="shared" ref="Y22" si="136">Y6/U6-1</f>
         <v>-0.12351586035796547</v>
       </c>
       <c r="Z22" s="9">
-        <f t="shared" ref="Z22" si="140">Z6/V6-1</f>
+        <f t="shared" ref="Z22" si="137">Z6/V6-1</f>
         <v>-0.17336296802872286</v>
       </c>
       <c r="AA22" s="9">
-        <f t="shared" ref="AA22" si="141">AA6/W6-1</f>
+        <f t="shared" ref="AA22" si="138">AA6/W6-1</f>
         <v>-1.1645792133597066E-2</v>
       </c>
       <c r="AB22" s="9">
-        <f t="shared" ref="AB22" si="142">AB6/X6-1</f>
+        <f t="shared" ref="AB22" si="139">AB6/X6-1</f>
         <v>-0.14967552857441913</v>
       </c>
       <c r="AC22" s="9">
-        <f t="shared" ref="AC22" si="143">AC6/Y6-1</f>
+        <f t="shared" ref="AC22" si="140">AC6/Y6-1</f>
         <v>-0.16538617064294381</v>
       </c>
       <c r="AD22" s="9">
-        <f t="shared" ref="AD22" si="144">AD6/Z6-1</f>
+        <f t="shared" ref="AD22" si="141">AD6/Z6-1</f>
         <v>-0.12533609100310239</v>
       </c>
       <c r="AE22" s="9">
-        <f t="shared" ref="AE22" si="145">AE6/AA6-1</f>
+        <f t="shared" ref="AE22" si="142">AE6/AA6-1</f>
         <v>-5.6914184081814145E-2</v>
       </c>
       <c r="AF22" s="9">
-        <f t="shared" ref="AF22" si="146">AF6/AB6-1</f>
+        <f t="shared" ref="AF22" si="143">AF6/AB6-1</f>
         <v>9.1334318069916431E-2</v>
       </c>
       <c r="AG22" s="9">
-        <f t="shared" ref="AG22" si="147">AG6/AC6-1</f>
-        <v>0.10000000000000009</v>
+        <f t="shared" ref="AG22" si="144">AG6/AC6-1</f>
+        <v>9.8352713178294415E-2</v>
       </c>
       <c r="AH22" s="9">
-        <f t="shared" ref="AH22" si="148">AH6/AD6-1</f>
+        <f t="shared" ref="AH22" si="145">AH6/AD6-1</f>
         <v>0.10000000000000009</v>
       </c>
       <c r="AI22" s="9"/>
       <c r="AK22" s="9"/>
       <c r="AL22" s="9">
-        <f t="shared" ref="AL22:AX24" si="149">AL6/AK6-1</f>
+        <f t="shared" ref="AL22:AX24" si="146">AL6/AK6-1</f>
         <v>0.14428182877865559</v>
       </c>
       <c r="AM22" s="9">
-        <f t="shared" si="149"/>
+        <f t="shared" si="146"/>
         <v>0.24674589700056604</v>
       </c>
       <c r="AN22" s="9">
-        <f t="shared" si="149"/>
+        <f t="shared" si="146"/>
         <v>0.42124375851112128</v>
       </c>
       <c r="AO22" s="9">
-        <f t="shared" si="149"/>
+        <f t="shared" si="146"/>
         <v>0.34768444586394143</v>
       </c>
       <c r="AP22" s="9">
-        <f t="shared" si="149"/>
+        <f t="shared" si="146"/>
         <v>-9.4274338799886226E-2</v>
       </c>
       <c r="AQ22" s="9">
-        <f t="shared" si="149"/>
+        <f t="shared" si="146"/>
         <v>-0.11471034591030416</v>
       </c>
       <c r="AR22" s="9">
-        <f t="shared" si="149"/>
-        <v>5.6197907430395544E-2</v>
+        <f t="shared" si="146"/>
+        <v>5.5795944907489625E-2</v>
       </c>
       <c r="AS22" s="9">
-        <f t="shared" si="149"/>
+        <f t="shared" si="146"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AT22" s="9">
-        <f t="shared" si="149"/>
+        <f t="shared" si="146"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AU22" s="9">
-        <f t="shared" si="149"/>
+        <f t="shared" si="146"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AV22" s="9">
-        <f t="shared" si="149"/>
+        <f t="shared" si="146"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AW22" s="9">
-        <f t="shared" si="149"/>
+        <f t="shared" si="146"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AX22" s="9">
-        <f t="shared" si="149"/>
+        <f t="shared" si="146"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AY22" s="9">
-        <f t="shared" ref="AY22" si="150">AY6/AX6-1</f>
+        <f t="shared" ref="AY22" si="147">AY6/AX6-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AZ22" s="9">
-        <f t="shared" ref="AZ22" si="151">AZ6/AY6-1</f>
+        <f t="shared" ref="AZ22" si="148">AZ6/AY6-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BA22" s="9">
-        <f t="shared" ref="BA22" si="152">BA6/AZ6-1</f>
+        <f t="shared" ref="BA22" si="149">BA6/AZ6-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BB22" s="9">
-        <f t="shared" ref="BB22" si="153">BB6/BA6-1</f>
+        <f t="shared" ref="BB22" si="150">BB6/BA6-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BD22" t="s">
@@ -5126,200 +5122,200 @@
         <v>0.44256610316428263</v>
       </c>
       <c r="D23" s="9">
-        <f t="shared" ref="D23:N23" si="154">D7/D3</f>
+        <f t="shared" ref="D23:N23" si="151">D7/D3</f>
         <v>0.38772398017537169</v>
       </c>
       <c r="E23" s="9">
+        <f t="shared" si="151"/>
+        <v>0.32784682566341955</v>
+      </c>
+      <c r="F23" s="9">
+        <f t="shared" si="151"/>
+        <v>0.25519363939471662</v>
+      </c>
+      <c r="G23" s="9">
+        <f t="shared" si="151"/>
+        <v>0.30555555555555558</v>
+      </c>
+      <c r="H23" s="9">
+        <f t="shared" si="151"/>
+        <v>0.28737113402061853</v>
+      </c>
+      <c r="I23" s="9">
+        <f t="shared" si="151"/>
+        <v>0.27610936799641417</v>
+      </c>
+      <c r="J23" s="9">
+        <f t="shared" si="151"/>
+        <v>0.22463897307898023</v>
+      </c>
+      <c r="K23" s="9">
+        <f t="shared" si="151"/>
+        <v>0.26421621621621622</v>
+      </c>
+      <c r="L23" s="9">
+        <f t="shared" si="151"/>
+        <v>0.29084103918978421</v>
+      </c>
+      <c r="M23" s="9">
+        <f t="shared" si="151"/>
+        <v>0.21143362310299099</v>
+      </c>
+      <c r="N23" s="9">
+        <f t="shared" si="151"/>
+        <v>0.17293975639196751</v>
+      </c>
+      <c r="O23" s="9">
+        <f t="shared" ref="O23:R23" si="152">O7/O3</f>
+        <v>0.19529625779625781</v>
+      </c>
+      <c r="P23" s="9">
+        <f t="shared" si="152"/>
+        <v>0.18297525710212809</v>
+      </c>
+      <c r="Q23" s="9">
+        <f t="shared" si="152"/>
+        <v>0.20374707259953162</v>
+      </c>
+      <c r="R23" s="9">
+        <f t="shared" si="152"/>
+        <v>0.18892056398798057</v>
+      </c>
+      <c r="S23" s="9">
+        <f t="shared" ref="S23:AD23" si="153">S7/S3</f>
+        <v>0.22762774066058153</v>
+      </c>
+      <c r="T23" s="9">
+        <f t="shared" si="153"/>
+        <v>0.28031325951930863</v>
+      </c>
+      <c r="U23" s="9">
+        <f t="shared" si="153"/>
+        <v>0.23952148870181658</v>
+      </c>
+      <c r="V23" s="9">
+        <f t="shared" si="153"/>
+        <v>0.22712933753943215</v>
+      </c>
+      <c r="W23" s="9">
+        <f t="shared" si="153"/>
+        <v>0.27149504349585268</v>
+      </c>
+      <c r="X23" s="9">
+        <f t="shared" si="153"/>
+        <v>0.26280790484218414</v>
+      </c>
+      <c r="Y23" s="9">
+        <f t="shared" si="153"/>
+        <v>0.25012619888944981</v>
+      </c>
+      <c r="Z23" s="9">
+        <f t="shared" si="153"/>
+        <v>0.2026004554469992</v>
+      </c>
+      <c r="AA23" s="9">
+        <f t="shared" si="153"/>
+        <v>0.23100100435219284</v>
+      </c>
+      <c r="AB23" s="9">
+        <f t="shared" si="153"/>
+        <v>0.21531371280724451</v>
+      </c>
+      <c r="AC23" s="9">
+        <f t="shared" si="153"/>
+        <v>0.19897996357012751</v>
+      </c>
+      <c r="AD23" s="9">
+        <f t="shared" si="153"/>
+        <v>0.15937841135298272</v>
+      </c>
+      <c r="AE23" s="9">
+        <f t="shared" ref="AE23:AH23" si="154">AE7/AE3</f>
+        <v>0.18926056338028169</v>
+      </c>
+      <c r="AF23" s="9">
         <f t="shared" si="154"/>
-        <v>0.32784682566341955</v>
-      </c>
-      <c r="F23" s="9">
+        <v>0.19176146925421961</v>
+      </c>
+      <c r="AG23" s="9">
         <f t="shared" si="154"/>
-        <v>0.25519363939471662</v>
-      </c>
-      <c r="G23" s="9">
+        <v>0.17002920095566765</v>
+      </c>
+      <c r="AH23" s="9">
         <f t="shared" si="154"/>
-        <v>0.30555555555555558</v>
-      </c>
-      <c r="H23" s="9">
-        <f t="shared" si="154"/>
-        <v>0.28737113402061853</v>
-      </c>
-      <c r="I23" s="9">
-        <f t="shared" si="154"/>
-        <v>0.27610936799641417</v>
-      </c>
-      <c r="J23" s="9">
-        <f t="shared" si="154"/>
-        <v>0.22463897307898023</v>
-      </c>
-      <c r="K23" s="9">
-        <f t="shared" si="154"/>
-        <v>0.26421621621621622</v>
-      </c>
-      <c r="L23" s="9">
-        <f t="shared" si="154"/>
-        <v>0.29084103918978421</v>
-      </c>
-      <c r="M23" s="9">
-        <f t="shared" si="154"/>
-        <v>0.21143362310299099</v>
-      </c>
-      <c r="N23" s="9">
-        <f t="shared" si="154"/>
-        <v>0.17293975639196751</v>
-      </c>
-      <c r="O23" s="9">
-        <f t="shared" ref="O23:R23" si="155">O7/O3</f>
-        <v>0.19529625779625781</v>
-      </c>
-      <c r="P23" s="9">
-        <f t="shared" si="155"/>
-        <v>0.18297525710212809</v>
-      </c>
-      <c r="Q23" s="9">
-        <f t="shared" si="155"/>
-        <v>0.20374707259953162</v>
-      </c>
-      <c r="R23" s="9">
-        <f t="shared" si="155"/>
-        <v>0.18892056398798057</v>
-      </c>
-      <c r="S23" s="9">
-        <f t="shared" ref="S23:AD23" si="156">S7/S3</f>
-        <v>0.22762774066058153</v>
-      </c>
-      <c r="T23" s="9">
-        <f t="shared" si="156"/>
-        <v>0.28031325951930863</v>
-      </c>
-      <c r="U23" s="9">
-        <f t="shared" si="156"/>
-        <v>0.23952148870181658</v>
-      </c>
-      <c r="V23" s="9">
-        <f t="shared" si="156"/>
-        <v>0.22712933753943215</v>
-      </c>
-      <c r="W23" s="9">
-        <f t="shared" si="156"/>
-        <v>0.27149504349585268</v>
-      </c>
-      <c r="X23" s="9">
-        <f t="shared" si="156"/>
-        <v>0.26280790484218414</v>
-      </c>
-      <c r="Y23" s="9">
-        <f t="shared" si="156"/>
-        <v>0.25012619888944981</v>
-      </c>
-      <c r="Z23" s="9">
-        <f t="shared" si="156"/>
-        <v>0.2026004554469992</v>
-      </c>
-      <c r="AA23" s="9">
-        <f t="shared" si="156"/>
-        <v>0.23100100435219284</v>
-      </c>
-      <c r="AB23" s="9">
-        <f t="shared" si="156"/>
-        <v>0.21531371280724451</v>
-      </c>
-      <c r="AC23" s="9">
-        <f t="shared" si="156"/>
-        <v>0.19897996357012751</v>
-      </c>
-      <c r="AD23" s="9">
-        <f t="shared" si="156"/>
-        <v>0.15937841135298272</v>
-      </c>
-      <c r="AE23" s="9">
-        <f t="shared" ref="AE23:AH23" si="157">AE7/AE3</f>
-        <v>0.18926056338028169</v>
-      </c>
-      <c r="AF23" s="9">
-        <f t="shared" si="157"/>
-        <v>0.19176146925421961</v>
-      </c>
-      <c r="AG23" s="9">
-        <f t="shared" si="157"/>
-        <v>0.19</v>
-      </c>
-      <c r="AH23" s="9">
-        <f t="shared" si="157"/>
         <v>0.16</v>
       </c>
       <c r="AI23" s="9"/>
       <c r="AK23" s="9">
-        <f t="shared" ref="AK23:AW23" si="158">AK7/AK3</f>
+        <f t="shared" ref="AK23:AW23" si="155">AK7/AK3</f>
         <v>0.33957309842452993</v>
       </c>
       <c r="AL23" s="9">
-        <f t="shared" si="158"/>
+        <f t="shared" si="155"/>
         <v>0.26732730982220926</v>
       </c>
       <c r="AM23" s="9">
-        <f t="shared" si="158"/>
+        <f t="shared" si="155"/>
         <v>0.22156620257709339</v>
       </c>
       <c r="AN23" s="9">
-        <f t="shared" si="158"/>
+        <f t="shared" si="155"/>
         <v>0.1925384372495203</v>
       </c>
       <c r="AO23" s="9">
-        <f t="shared" si="158"/>
+        <f t="shared" si="155"/>
         <v>0.24312225650832281</v>
       </c>
       <c r="AP23" s="9">
-        <f t="shared" si="158"/>
+        <f t="shared" si="155"/>
         <v>0.24360644348921018</v>
       </c>
       <c r="AQ23" s="9">
-        <f t="shared" si="158"/>
+        <f t="shared" si="155"/>
         <v>0.19838101988286641</v>
       </c>
       <c r="AR23" s="9">
-        <f t="shared" si="158"/>
-        <v>0.181754836129535</v>
+        <f t="shared" si="155"/>
+        <v>0.17657106653389368</v>
       </c>
       <c r="AS23" s="9">
-        <f t="shared" si="158"/>
+        <f t="shared" si="155"/>
         <v>0.17</v>
       </c>
       <c r="AT23" s="9">
-        <f t="shared" si="158"/>
+        <f t="shared" si="155"/>
         <v>0.16</v>
       </c>
       <c r="AU23" s="9">
-        <f t="shared" si="158"/>
+        <f t="shared" si="155"/>
         <v>0.16</v>
       </c>
       <c r="AV23" s="9">
-        <f t="shared" si="158"/>
+        <f t="shared" si="155"/>
         <v>0.16</v>
       </c>
       <c r="AW23" s="9">
-        <f t="shared" si="158"/>
-        <v>0.16000000000000003</v>
+        <f t="shared" si="155"/>
+        <v>0.16</v>
       </c>
       <c r="AX23" s="9">
-        <f t="shared" ref="AX23:BB23" si="159">AX7/AX3</f>
+        <f t="shared" ref="AX23:BB23" si="156">AX7/AX3</f>
         <v>0.16</v>
       </c>
       <c r="AY23" s="9">
-        <f t="shared" si="159"/>
+        <f t="shared" si="156"/>
         <v>0.16</v>
       </c>
       <c r="AZ23" s="9">
-        <f t="shared" si="159"/>
+        <f t="shared" si="156"/>
         <v>0.16</v>
       </c>
       <c r="BA23" s="9">
-        <f t="shared" si="159"/>
+        <f t="shared" si="156"/>
         <v>0.16</v>
       </c>
       <c r="BB23" s="9">
-        <f t="shared" si="159"/>
+        <f t="shared" si="156"/>
         <v>0.16</v>
       </c>
       <c r="BD23" t="s">
@@ -5327,7 +5323,7 @@
       </c>
       <c r="BE23" s="4">
         <f>NPV(BE22,AR15:FK15)</f>
-        <v>-85.799747568796903</v>
+        <v>1005.6313757734623</v>
       </c>
     </row>
     <row r="24" spans="2:57" x14ac:dyDescent="0.3">
@@ -5339,185 +5335,185 @@
       <c r="E24" s="9"/>
       <c r="F24" s="9"/>
       <c r="G24" s="9">
-        <f t="shared" ref="G24" si="160">G8/C8-1</f>
+        <f t="shared" ref="G24" si="157">G8/C8-1</f>
         <v>-3.7307380373073795E-2</v>
       </c>
       <c r="H24" s="9">
-        <f t="shared" ref="H24" si="161">H8/D8-1</f>
+        <f t="shared" ref="H24" si="158">H8/D8-1</f>
         <v>4.8543689320388328E-2</v>
       </c>
       <c r="I24" s="9">
-        <f t="shared" ref="I24" si="162">I8/E8-1</f>
+        <f t="shared" ref="I24" si="159">I8/E8-1</f>
         <v>-4.4081632653061309E-2</v>
       </c>
       <c r="J24" s="9">
-        <f t="shared" ref="J24" si="163">J8/F8-1</f>
+        <f t="shared" ref="J24" si="160">J8/F8-1</f>
         <v>1.0009285051067782</v>
       </c>
       <c r="K24" s="9">
-        <f t="shared" ref="K24" si="164">K8/G8-1</f>
+        <f t="shared" ref="K24" si="161">K8/G8-1</f>
         <v>0.13395113732097719</v>
       </c>
       <c r="L24" s="9">
-        <f t="shared" ref="L24" si="165">L8/H8-1</f>
+        <f t="shared" ref="L24" si="162">L8/H8-1</f>
         <v>-6.4043209876543217E-2</v>
       </c>
       <c r="M24" s="9">
-        <f t="shared" ref="M24" si="166">M8/I8-1</f>
+        <f t="shared" ref="M24" si="163">M8/I8-1</f>
         <v>7.8565328778821497E-2</v>
       </c>
       <c r="N24" s="9">
-        <f t="shared" ref="N24" si="167">N8/J8-1</f>
+        <f t="shared" ref="N24" si="164">N8/J8-1</f>
         <v>-0.31832946635730852</v>
       </c>
       <c r="O24" s="9">
-        <f t="shared" ref="O24" si="168">O8/K8-1</f>
+        <f t="shared" ref="O24" si="165">O8/K8-1</f>
         <v>0.20133729569093606</v>
       </c>
       <c r="P24" s="9">
-        <f t="shared" ref="P24" si="169">P8/L8-1</f>
+        <f t="shared" ref="P24" si="166">P8/L8-1</f>
         <v>0.47732893652102226</v>
       </c>
       <c r="Q24" s="9">
-        <f t="shared" ref="Q24" si="170">Q8/M8-1</f>
+        <f t="shared" ref="Q24" si="167">Q8/M8-1</f>
         <v>0.38796516231195577</v>
       </c>
       <c r="R24" s="9">
-        <f t="shared" ref="R24" si="171">R8/N8-1</f>
+        <f t="shared" ref="R24" si="168">R8/N8-1</f>
         <v>0.32334921715452691</v>
       </c>
       <c r="S24" s="9">
-        <f t="shared" ref="S24" si="172">S8/O8-1</f>
+        <f t="shared" ref="S24" si="169">S8/O8-1</f>
         <v>0.33518862090290669</v>
       </c>
       <c r="T24" s="9">
-        <f t="shared" ref="T24" si="173">T8/P8-1</f>
+        <f t="shared" ref="T24" si="170">T8/P8-1</f>
         <v>0.39006696428571441</v>
       </c>
       <c r="U24" s="9">
-        <f t="shared" ref="U24" si="174">U8/Q8-1</f>
+        <f t="shared" ref="U24" si="171">U8/Q8-1</f>
         <v>0.49686252139189935</v>
       </c>
       <c r="V24" s="9">
-        <f t="shared" ref="V24" si="175">V8/R8-1</f>
+        <f t="shared" ref="V24" si="172">V8/R8-1</f>
         <v>0.16203703703703698</v>
       </c>
       <c r="W24" s="9">
-        <f t="shared" ref="W24" si="176">W8/S8-1</f>
+        <f t="shared" ref="W24" si="173">W8/S8-1</f>
         <v>-0.11857341361741547</v>
       </c>
       <c r="X24" s="9">
-        <f t="shared" ref="X24" si="177">X8/T8-1</f>
+        <f t="shared" ref="X24" si="174">X8/T8-1</f>
         <v>-0.1292653552790044</v>
       </c>
       <c r="Y24" s="9">
-        <f t="shared" ref="Y24" si="178">Y8/U8-1</f>
+        <f t="shared" ref="Y24" si="175">Y8/U8-1</f>
         <v>-0.15739329268292679</v>
       </c>
       <c r="Z24" s="9">
-        <f t="shared" ref="Z24" si="179">Z8/V8-1</f>
+        <f t="shared" ref="Z24" si="176">Z8/V8-1</f>
         <v>1.4608233731739695E-2</v>
       </c>
       <c r="AA24" s="9">
-        <f t="shared" ref="AA24" si="180">AA8/W8-1</f>
+        <f t="shared" ref="AA24" si="177">AA8/W8-1</f>
         <v>0.19548081975827625</v>
       </c>
       <c r="AB24" s="9">
-        <f t="shared" ref="AB24" si="181">AB8/X8-1</f>
+        <f t="shared" ref="AB24" si="178">AB8/X8-1</f>
         <v>5.7169202397418184E-2</v>
       </c>
       <c r="AC24" s="9">
-        <f t="shared" ref="AC24" si="182">AC8/Y8-1</f>
+        <f t="shared" ref="AC24" si="179">AC8/Y8-1</f>
         <v>-4.5228403437358455E-4</v>
       </c>
       <c r="AD24" s="9">
-        <f t="shared" ref="AD24" si="183">AD8/Z8-1</f>
+        <f t="shared" ref="AD24" si="180">AD8/Z8-1</f>
         <v>5.2792321116928553E-2</v>
       </c>
       <c r="AE24" s="9">
-        <f t="shared" ref="AE24" si="184">AE8/AA8-1</f>
+        <f t="shared" ref="AE24" si="181">AE8/AA8-1</f>
         <v>3.4725274725274646E-2</v>
       </c>
       <c r="AF24" s="9">
-        <f t="shared" ref="AF24" si="185">AF8/AB8-1</f>
+        <f t="shared" ref="AF24" si="182">AF8/AB8-1</f>
         <v>9.0710859136502231E-2</v>
       </c>
       <c r="AG24" s="9">
-        <f t="shared" ref="AG24" si="186">AG8/AC8-1</f>
-        <v>0.10000000000000009</v>
+        <f t="shared" ref="AG24" si="183">AG8/AC8-1</f>
+        <v>0.13710407239819</v>
       </c>
       <c r="AH24" s="9">
-        <f t="shared" ref="AH24" si="187">AH8/AD8-1</f>
+        <f t="shared" ref="AH24" si="184">AH8/AD8-1</f>
         <v>9.9999999999999867E-2</v>
       </c>
       <c r="AI24" s="9"/>
       <c r="AK24" s="9"/>
       <c r="AL24" s="9">
-        <f t="shared" si="149"/>
+        <f t="shared" si="146"/>
         <v>0.2175644518968769</v>
       </c>
       <c r="AM24" s="9">
-        <f t="shared" si="149"/>
+        <f t="shared" si="146"/>
         <v>-8.9171974522292974E-2</v>
       </c>
       <c r="AN24" s="9">
-        <f t="shared" si="149"/>
+        <f t="shared" si="146"/>
         <v>0.343035343035343</v>
       </c>
       <c r="AO24" s="9">
-        <f t="shared" si="149"/>
+        <f t="shared" si="146"/>
         <v>0.34154235857022219</v>
       </c>
       <c r="AP24" s="9">
-        <f t="shared" si="149"/>
+        <f t="shared" si="146"/>
         <v>-0.10049302423161643</v>
       </c>
       <c r="AQ24" s="9">
-        <f t="shared" si="149"/>
+        <f t="shared" si="146"/>
         <v>7.1836734693877524E-2</v>
       </c>
       <c r="AR24" s="9">
-        <f t="shared" si="149"/>
-        <v>8.1525405287781627E-2</v>
+        <f t="shared" si="146"/>
+        <v>9.0447176585790601E-2</v>
       </c>
       <c r="AS24" s="9">
-        <f t="shared" si="149"/>
+        <f t="shared" si="146"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AT24" s="9">
-        <f t="shared" si="149"/>
+        <f t="shared" si="146"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AU24" s="9">
-        <f t="shared" si="149"/>
+        <f t="shared" si="146"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AV24" s="9">
-        <f t="shared" si="149"/>
+        <f t="shared" si="146"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AW24" s="9">
-        <f t="shared" si="149"/>
+        <f t="shared" si="146"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AX24" s="9">
-        <f t="shared" si="149"/>
+        <f t="shared" si="146"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AY24" s="9">
-        <f t="shared" ref="AY24" si="188">AY8/AX8-1</f>
+        <f t="shared" ref="AY24" si="185">AY8/AX8-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AZ24" s="9">
-        <f t="shared" ref="AZ24" si="189">AZ8/AY8-1</f>
+        <f t="shared" ref="AZ24" si="186">AZ8/AY8-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BA24" s="9">
-        <f t="shared" ref="BA24" si="190">BA8/AZ8-1</f>
+        <f t="shared" ref="BA24" si="187">BA8/AZ8-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BB24" s="9">
-        <f t="shared" ref="BB24" si="191">BB8/BA8-1</f>
+        <f t="shared" ref="BB24" si="188">BB8/BA8-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BD24" t="s">
@@ -5537,200 +5533,200 @@
         <v>-4.1655818797188236E-3</v>
       </c>
       <c r="D25" s="9">
-        <f t="shared" ref="D25:N25" si="192">D14/D13</f>
+        <f t="shared" ref="D25:N25" si="189">D14/D13</f>
         <v>-3.1232254400908582E-3</v>
       </c>
       <c r="E25" s="9">
+        <f t="shared" si="189"/>
+        <v>-6.1538461538461541E-4</v>
+      </c>
+      <c r="F25" s="9">
+        <f t="shared" si="189"/>
+        <v>-2.0833333333333333E-3</v>
+      </c>
+      <c r="G25" s="9">
+        <f t="shared" si="189"/>
+        <v>9.6680631646793396E-4</v>
+      </c>
+      <c r="H25" s="9">
+        <f t="shared" si="189"/>
+        <v>-4.3273013375295048E-3</v>
+      </c>
+      <c r="I25" s="9">
+        <f t="shared" si="189"/>
+        <v>5.6768558951965069E-3</v>
+      </c>
+      <c r="J25" s="9">
+        <f t="shared" si="189"/>
+        <v>-1.2484394506866415E-3</v>
+      </c>
+      <c r="K25" s="9">
+        <f t="shared" si="189"/>
+        <v>-2.2935779816513767E-3</v>
+      </c>
+      <c r="L25" s="9">
+        <f t="shared" si="189"/>
+        <v>3.0590394616090556E-3</v>
+      </c>
+      <c r="M25" s="9">
+        <f t="shared" si="189"/>
+        <v>0</v>
+      </c>
+      <c r="N25" s="9">
+        <f t="shared" si="189"/>
+        <v>-0.19086585610190757</v>
+      </c>
+      <c r="O25" s="9">
+        <f t="shared" ref="O25:R25" si="190">O14/O13</f>
+        <v>-4.905395935529082E-3</v>
+      </c>
+      <c r="P25" s="9">
+        <f t="shared" si="190"/>
+        <v>1.2377850162866454E-2</v>
+      </c>
+      <c r="Q25" s="9">
+        <f t="shared" si="190"/>
+        <v>-1.4104372355430182E-2</v>
+      </c>
+      <c r="R25" s="9">
+        <f t="shared" si="190"/>
+        <v>0.36516853932584203</v>
+      </c>
+      <c r="S25" s="9">
+        <f t="shared" ref="S25:AD25" si="191">S14/S13</f>
+        <v>-2.4202733485193625E-2</v>
+      </c>
+      <c r="T25" s="9">
+        <f t="shared" si="191"/>
+        <v>-1.6863406408094441E-2</v>
+      </c>
+      <c r="U25" s="9">
+        <f t="shared" si="191"/>
+        <v>-1.8612178838761886E-2</v>
+      </c>
+      <c r="V25" s="9">
+        <f t="shared" si="191"/>
+        <v>-1.4778325123152714E-2</v>
+      </c>
+      <c r="W25" s="9">
+        <f t="shared" si="191"/>
+        <v>-2.113113735239279E-2</v>
+      </c>
+      <c r="X25" s="9">
+        <f t="shared" si="191"/>
+        <v>-3.312346016972352E-2</v>
+      </c>
+      <c r="Y25" s="9">
+        <f t="shared" si="191"/>
+        <v>-1.5999999999999997E-2</v>
+      </c>
+      <c r="Z25" s="9">
+        <f t="shared" si="191"/>
+        <v>-1.3474887709269086E-2</v>
+      </c>
+      <c r="AA25" s="9">
+        <f t="shared" si="191"/>
+        <v>-2.3146595102314649E-2</v>
+      </c>
+      <c r="AB25" s="9">
+        <f t="shared" si="191"/>
+        <v>-2.1372790793259346E-2</v>
+      </c>
+      <c r="AC25" s="9">
+        <f t="shared" si="191"/>
+        <v>-5.7201929703652649E-2</v>
+      </c>
+      <c r="AD25" s="9">
+        <f t="shared" si="191"/>
+        <v>0.36111111111111277</v>
+      </c>
+      <c r="AE25" s="9">
+        <f t="shared" ref="AE25:AH25" si="192">AE14/AE13</f>
+        <v>-6.397562833206398E-2</v>
+      </c>
+      <c r="AF25" s="9">
         <f t="shared" si="192"/>
-        <v>-6.1538461538461541E-4</v>
-      </c>
-      <c r="F25" s="9">
+        <v>-3.0207924676343683E-2</v>
+      </c>
+      <c r="AG25" s="9">
         <f t="shared" si="192"/>
-        <v>-2.0833333333333333E-3</v>
-      </c>
-      <c r="G25" s="9">
+        <v>-4.8590864917395504E-3</v>
+      </c>
+      <c r="AH25" s="9">
         <f t="shared" si="192"/>
-        <v>9.6680631646793396E-4</v>
-      </c>
-      <c r="H25" s="9">
-        <f t="shared" si="192"/>
-        <v>-4.3273013375295048E-3</v>
-      </c>
-      <c r="I25" s="9">
-        <f t="shared" si="192"/>
-        <v>5.6768558951965069E-3</v>
-      </c>
-      <c r="J25" s="9">
-        <f t="shared" si="192"/>
-        <v>-1.2484394506866415E-3</v>
-      </c>
-      <c r="K25" s="9">
-        <f t="shared" si="192"/>
-        <v>-2.2935779816513767E-3</v>
-      </c>
-      <c r="L25" s="9">
-        <f t="shared" si="192"/>
-        <v>3.0590394616090556E-3</v>
-      </c>
-      <c r="M25" s="9">
-        <f t="shared" si="192"/>
-        <v>0</v>
-      </c>
-      <c r="N25" s="9">
-        <f t="shared" si="192"/>
-        <v>-0.19086585610190757</v>
-      </c>
-      <c r="O25" s="9">
-        <f t="shared" ref="O25:R25" si="193">O14/O13</f>
-        <v>-4.905395935529082E-3</v>
-      </c>
-      <c r="P25" s="9">
-        <f t="shared" si="193"/>
-        <v>1.2377850162866454E-2</v>
-      </c>
-      <c r="Q25" s="9">
-        <f t="shared" si="193"/>
-        <v>-1.4104372355430182E-2</v>
-      </c>
-      <c r="R25" s="9">
-        <f t="shared" si="193"/>
-        <v>0.36516853932584203</v>
-      </c>
-      <c r="S25" s="9">
-        <f t="shared" ref="S25:AD25" si="194">S14/S13</f>
-        <v>-2.4202733485193625E-2</v>
-      </c>
-      <c r="T25" s="9">
-        <f t="shared" si="194"/>
-        <v>-1.6863406408094441E-2</v>
-      </c>
-      <c r="U25" s="9">
-        <f t="shared" si="194"/>
-        <v>-1.8612178838761886E-2</v>
-      </c>
-      <c r="V25" s="9">
-        <f t="shared" si="194"/>
-        <v>-1.4778325123152714E-2</v>
-      </c>
-      <c r="W25" s="9">
-        <f t="shared" si="194"/>
-        <v>-2.113113735239279E-2</v>
-      </c>
-      <c r="X25" s="9">
-        <f t="shared" si="194"/>
-        <v>-3.312346016972352E-2</v>
-      </c>
-      <c r="Y25" s="9">
-        <f t="shared" si="194"/>
-        <v>-1.5999999999999997E-2</v>
-      </c>
-      <c r="Z25" s="9">
-        <f t="shared" si="194"/>
-        <v>-1.3474887709269086E-2</v>
-      </c>
-      <c r="AA25" s="9">
-        <f t="shared" si="194"/>
-        <v>-2.3146595102314649E-2</v>
-      </c>
-      <c r="AB25" s="9">
-        <f t="shared" si="194"/>
-        <v>-2.1372790793259346E-2</v>
-      </c>
-      <c r="AC25" s="9">
-        <f t="shared" si="194"/>
-        <v>-5.7201929703652649E-2</v>
-      </c>
-      <c r="AD25" s="9">
-        <f t="shared" si="194"/>
-        <v>0.36111111111111277</v>
-      </c>
-      <c r="AE25" s="9">
-        <f t="shared" ref="AE25:AH25" si="195">AE14/AE13</f>
-        <v>-6.397562833206398E-2</v>
-      </c>
-      <c r="AF25" s="9">
-        <f t="shared" si="195"/>
-        <v>-3.0207924676343683E-2</v>
-      </c>
-      <c r="AG25" s="9">
-        <f t="shared" si="195"/>
-        <v>0.05</v>
-      </c>
-      <c r="AH25" s="9">
-        <f t="shared" si="195"/>
         <v>0.05</v>
       </c>
       <c r="AI25" s="9"/>
       <c r="AK25" s="9">
-        <f t="shared" ref="AK25:AM25" si="196">AK14/AK13</f>
+        <f t="shared" ref="AK25:AM25" si="193">AK14/AK13</f>
         <v>-2.6330487512965773E-3</v>
       </c>
       <c r="AL25" s="9">
-        <f t="shared" si="196"/>
+        <f t="shared" si="193"/>
         <v>1.9346101760495268E-4</v>
       </c>
       <c r="AM25" s="9">
-        <f t="shared" si="196"/>
+        <f t="shared" si="193"/>
         <v>-1.9225971046551688E-2</v>
       </c>
       <c r="AN25" s="9">
-        <f t="shared" ref="AN25:AW25" si="197">AN14/AN13</f>
+        <f t="shared" ref="AN25:AW25" si="194">AN14/AN13</f>
         <v>-2.846900042176297E-2</v>
       </c>
       <c r="AO25" s="9">
-        <f t="shared" si="197"/>
+        <f t="shared" si="194"/>
         <v>-1.8707923355774213E-2</v>
       </c>
       <c r="AP25" s="9">
-        <f t="shared" si="197"/>
+        <f t="shared" si="194"/>
         <v>-2.1629972962533797E-2</v>
       </c>
       <c r="AQ25" s="9">
-        <f t="shared" si="197"/>
+        <f t="shared" si="194"/>
         <v>-3.8089570004463634E-2</v>
       </c>
       <c r="AR25" s="9">
-        <f t="shared" si="197"/>
-        <v>-1.4088013094587371E-2</v>
+        <f t="shared" si="194"/>
+        <v>-3.2578789880697963E-2</v>
       </c>
       <c r="AS25" s="9">
-        <f t="shared" si="197"/>
+        <f t="shared" si="194"/>
+        <v>0.19999999999999998</v>
+      </c>
+      <c r="AT25" s="9">
+        <f t="shared" si="194"/>
         <v>0.2</v>
       </c>
-      <c r="AT25" s="9">
-        <f t="shared" si="197"/>
+      <c r="AU25" s="9">
+        <f t="shared" si="194"/>
         <v>0.2</v>
       </c>
-      <c r="AU25" s="9">
-        <f t="shared" si="197"/>
+      <c r="AV25" s="9">
+        <f t="shared" si="194"/>
         <v>0.2</v>
       </c>
-      <c r="AV25" s="9">
-        <f t="shared" si="197"/>
+      <c r="AW25" s="9">
+        <f t="shared" si="194"/>
         <v>0.2</v>
       </c>
-      <c r="AW25" s="9">
-        <f t="shared" si="197"/>
+      <c r="AX25" s="9">
+        <f t="shared" ref="AX25:BB25" si="195">AX14/AX13</f>
+        <v>0.20000000000000004</v>
+      </c>
+      <c r="AY25" s="9">
+        <f t="shared" si="195"/>
+        <v>0.19999999999999998</v>
+      </c>
+      <c r="AZ25" s="9">
+        <f t="shared" si="195"/>
         <v>0.2</v>
       </c>
-      <c r="AX25" s="9">
-        <f t="shared" ref="AX25:BB25" si="198">AX14/AX13</f>
+      <c r="BA25" s="9">
+        <f t="shared" si="195"/>
         <v>0.2</v>
       </c>
-      <c r="AY25" s="9">
-        <f t="shared" si="198"/>
-        <v>0.2</v>
-      </c>
-      <c r="AZ25" s="9">
-        <f t="shared" si="198"/>
-        <v>0.2</v>
-      </c>
-      <c r="BA25" s="9">
-        <f t="shared" si="198"/>
-        <v>0.20000000000000004</v>
-      </c>
       <c r="BB25" s="9">
-        <f t="shared" si="198"/>
+        <f t="shared" si="195"/>
         <v>0.2</v>
       </c>
       <c r="BD25" t="s">
@@ -5738,7 +5734,7 @@
       </c>
       <c r="BE25" s="4">
         <f>BE23+BE24</f>
-        <v>-768.69974756879697</v>
+        <v>322.73137577346222</v>
       </c>
     </row>
     <row r="26" spans="2:57" x14ac:dyDescent="0.3">
@@ -5750,208 +5746,208 @@
         <v>-1.6718682271348073</v>
       </c>
       <c r="D26" s="9">
-        <f t="shared" ref="D26:R26" si="199">D15/D3</f>
+        <f t="shared" ref="D26:R26" si="196">D15/D3</f>
         <v>-1.3469309950438426</v>
       </c>
       <c r="E26" s="9">
-        <f t="shared" si="199"/>
+        <f t="shared" si="196"/>
         <v>-1.0923748740342627</v>
       </c>
       <c r="F26" s="9">
-        <f t="shared" si="199"/>
+        <f t="shared" si="196"/>
         <v>-0.49345986150294957</v>
       </c>
       <c r="G26" s="9">
-        <f t="shared" si="199"/>
+        <f t="shared" si="196"/>
         <v>-0.96754057428214757</v>
       </c>
       <c r="H26" s="9">
-        <f t="shared" si="199"/>
+        <f t="shared" si="196"/>
         <v>-0.65798969072164948</v>
       </c>
       <c r="I26" s="9">
-        <f t="shared" si="199"/>
+        <f t="shared" si="196"/>
         <v>-0.51030927835051543</v>
       </c>
       <c r="J26" s="9">
-        <f t="shared" si="199"/>
+        <f t="shared" si="196"/>
         <v>-0.42895346764129083</v>
       </c>
       <c r="K26" s="9">
-        <f t="shared" si="199"/>
+        <f t="shared" si="196"/>
         <v>-0.66140540540540527</v>
       </c>
       <c r="L26" s="9">
-        <f t="shared" si="199"/>
+        <f t="shared" si="196"/>
         <v>-0.71752531924262419</v>
       </c>
       <c r="M26" s="9">
-        <f t="shared" si="199"/>
+        <f t="shared" si="196"/>
         <v>-0.29306026226609688</v>
       </c>
       <c r="N26" s="9">
-        <f t="shared" si="199"/>
+        <f t="shared" si="196"/>
         <v>-0.12392296718972901</v>
       </c>
       <c r="O26" s="9">
-        <f t="shared" si="199"/>
+        <f t="shared" si="196"/>
         <v>-0.37266112266112261</v>
       </c>
       <c r="P26" s="9">
-        <f t="shared" si="199"/>
+        <f t="shared" si="196"/>
         <v>-0.15436309948070454</v>
       </c>
       <c r="Q26" s="9">
-        <f t="shared" si="199"/>
+        <f t="shared" si="196"/>
         <v>-6.7353629976580801E-2</v>
       </c>
       <c r="R26" s="9">
-        <f t="shared" si="199"/>
+        <f t="shared" si="196"/>
         <v>1.741274366284002E-2</v>
       </c>
       <c r="S26" s="9">
-        <f t="shared" ref="S26:AD26" si="200">S15/S3</f>
+        <f t="shared" ref="S26:AD26" si="197">S15/S3</f>
         <v>-0.33847746306577575</v>
       </c>
       <c r="T26" s="9">
-        <f t="shared" si="200"/>
+        <f t="shared" si="197"/>
         <v>-0.37996219281663501</v>
       </c>
       <c r="U26" s="9">
-        <f t="shared" si="200"/>
+        <f t="shared" si="197"/>
         <v>-0.44616747895436409</v>
       </c>
       <c r="V26" s="9">
-        <f t="shared" si="200"/>
+        <f t="shared" si="197"/>
         <v>-0.22189736092944518</v>
       </c>
       <c r="W26" s="9">
-        <f t="shared" si="200"/>
+        <f t="shared" si="197"/>
         <v>-0.33238923730528019</v>
       </c>
       <c r="X26" s="9">
-        <f t="shared" si="200"/>
+        <f t="shared" si="197"/>
         <v>-0.35347007586400669</v>
       </c>
       <c r="Y26" s="9">
-        <f t="shared" si="200"/>
+        <f t="shared" si="197"/>
         <v>-0.30986033989567568</v>
       </c>
       <c r="Z26" s="9">
-        <f t="shared" si="200"/>
+        <f t="shared" si="197"/>
         <v>-0.18232571806361572</v>
       </c>
       <c r="AA26" s="9">
-        <f t="shared" si="200"/>
+        <f t="shared" si="197"/>
         <v>-0.25527284901238712</v>
       </c>
       <c r="AB26" s="9">
-        <f t="shared" si="200"/>
+        <f t="shared" si="197"/>
         <v>-0.20092173350582151</v>
       </c>
       <c r="AC26" s="9">
-        <f t="shared" si="200"/>
+        <f t="shared" si="197"/>
         <v>-0.11176684881602916</v>
       </c>
       <c r="AD26" s="9">
-        <f t="shared" si="200"/>
+        <f t="shared" si="197"/>
         <v>5.9076606947922276E-3</v>
       </c>
       <c r="AE26" s="9">
-        <f t="shared" ref="AE26:AH26" si="201">AE15/AE3</f>
+        <f t="shared" ref="AE26:AH26" si="198">AE15/AE3</f>
         <v>-0.1024794600938967</v>
       </c>
       <c r="AF26" s="9">
-        <f t="shared" si="201"/>
+        <f t="shared" si="198"/>
         <v>-0.19525615287381951</v>
       </c>
       <c r="AG26" s="9">
-        <f t="shared" si="201"/>
-        <v>-9.32439452202658E-2</v>
+        <f t="shared" si="198"/>
+        <v>-6.8622245818954125E-2</v>
       </c>
       <c r="AH26" s="9">
-        <f t="shared" si="201"/>
-        <v>-1.1988485756067905E-2</v>
+        <f t="shared" si="198"/>
+        <v>-4.5535137976222386E-3</v>
       </c>
       <c r="AI26" s="9"/>
       <c r="AK26" s="9">
-        <f t="shared" ref="AK26:AW26" si="202">AK15/AK3</f>
+        <f t="shared" ref="AK26:AW26" si="199">AK15/AK3</f>
         <v>-1.0643740470946976</v>
       </c>
       <c r="AL26" s="9">
-        <f t="shared" si="202"/>
+        <f t="shared" si="199"/>
         <v>-0.60250655785485263</v>
       </c>
       <c r="AM26" s="9">
-        <f t="shared" si="202"/>
+        <f t="shared" si="199"/>
         <v>-0.3764435313360196</v>
       </c>
       <c r="AN26" s="9">
-        <f t="shared" si="202"/>
+        <f t="shared" si="199"/>
         <v>-0.11845716645211433</v>
       </c>
       <c r="AO26" s="9">
-        <f t="shared" si="202"/>
+        <f t="shared" si="199"/>
         <v>-0.3419748793950193</v>
       </c>
       <c r="AP26" s="9">
-        <f t="shared" si="202"/>
+        <f t="shared" si="199"/>
         <v>-0.28711302157961011</v>
       </c>
       <c r="AQ26" s="9">
-        <f t="shared" si="202"/>
+        <f t="shared" si="199"/>
         <v>-0.13013392024471218</v>
       </c>
       <c r="AR26" s="9">
-        <f t="shared" si="202"/>
-        <v>-9.5924004705932209E-2</v>
+        <f t="shared" si="199"/>
+        <v>-8.7057365845518417E-2</v>
       </c>
       <c r="AS26" s="9">
-        <f t="shared" si="202"/>
-        <v>-4.8463690724062834E-2</v>
+        <f t="shared" si="199"/>
+        <v>-4.3836799752948741E-2</v>
       </c>
       <c r="AT26" s="9">
-        <f t="shared" si="202"/>
-        <v>-3.1958285460107649E-2</v>
+        <f t="shared" si="199"/>
+        <v>-2.1019721741958788E-2</v>
       </c>
       <c r="AU26" s="9">
-        <f t="shared" si="202"/>
-        <v>-2.2832766504355468E-2</v>
+        <f t="shared" si="199"/>
+        <v>-8.9888115869289128E-3</v>
       </c>
       <c r="AV26" s="9">
-        <f t="shared" si="202"/>
-        <v>-1.4054023527910896E-2</v>
+        <f t="shared" si="199"/>
+        <v>-5.8005384409693208E-4</v>
       </c>
       <c r="AW26" s="9">
-        <f t="shared" si="202"/>
-        <v>-8.6678153277714338E-3</v>
+        <f t="shared" si="199"/>
+        <v>4.5273682808937617E-3</v>
       </c>
       <c r="AX26" s="9">
-        <f t="shared" ref="AX26:BB26" si="203">AX15/AX3</f>
-        <v>-2.1874521956350337E-3</v>
+        <f t="shared" ref="AX26:BB26" si="200">AX15/AX3</f>
+        <v>1.0674461281012316E-2</v>
       </c>
       <c r="AY26" s="9">
-        <f t="shared" si="203"/>
-        <v>4.1839650179769693E-3</v>
+        <f t="shared" si="200"/>
+        <v>1.6718318130432508E-2</v>
       </c>
       <c r="AZ26" s="9">
-        <f t="shared" si="203"/>
-        <v>1.0430209696472787E-2</v>
+        <f t="shared" si="200"/>
+        <v>2.2643518318654014E-2</v>
       </c>
       <c r="BA26" s="9">
-        <f t="shared" si="203"/>
-        <v>1.655344412883062E-2</v>
+        <f t="shared" si="200"/>
+        <v>2.8452110232763672E-2</v>
       </c>
       <c r="BB26" s="9">
-        <f t="shared" si="203"/>
-        <v>2.2556069214352617E-2</v>
+        <f t="shared" si="200"/>
+        <v>3.4146369049389995E-2</v>
       </c>
       <c r="BD26" t="s">
         <v>45</v>
       </c>
       <c r="BE26" s="5">
         <f>BE25/BB16</f>
-        <v>-0.45895262258570479</v>
+        <v>0.19023364324990405</v>
       </c>
     </row>
     <row r="27" spans="2:57" x14ac:dyDescent="0.3">
@@ -5960,7 +5956,7 @@
       </c>
       <c r="BE27" s="5">
         <f>Main!D3</f>
-        <v>7.86</v>
+        <v>8.58</v>
       </c>
     </row>
     <row r="28" spans="2:57" x14ac:dyDescent="0.3">
@@ -5969,7 +5965,7 @@
       </c>
       <c r="BE28" s="10">
         <f>BE26/BE27-1</f>
-        <v>-1.0583909189040337</v>
+        <v>-0.97782824670747037</v>
       </c>
     </row>
     <row r="29" spans="2:57" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -5988,6 +5984,10 @@
         <f>AB15</f>
         <v>-248.50000000000003</v>
       </c>
+      <c r="AC29" s="8">
+        <f>AC15</f>
+        <v>-153.40000000000003</v>
+      </c>
       <c r="AD29" s="8">
         <f>AD15</f>
         <v>9.1999999999999353</v>
@@ -6000,6 +6000,14 @@
         <f>AF15</f>
         <v>-262.59999999999985</v>
       </c>
+      <c r="AG29" s="8">
+        <f>AG15</f>
+        <v>-103.40000000000006</v>
+      </c>
+      <c r="AH29" s="8">
+        <f>AH15</f>
+        <v>-7.6584820000000811</v>
+      </c>
       <c r="AO29" s="8">
         <f>AO15</f>
         <v>-1573.6999999999998</v>
@@ -6013,48 +6021,48 @@
         <v>-697.69999999999982</v>
       </c>
       <c r="AR29" s="8">
-        <f t="shared" ref="AR29:BB29" si="204">AR15</f>
-        <v>-560.30534899999952</v>
+        <f t="shared" ref="AR29:BB29" si="201">AR15</f>
+        <v>-513.35848199999953</v>
       </c>
       <c r="AS29" s="8">
-        <f t="shared" si="204"/>
-        <v>-297.23726078399955</v>
+        <f t="shared" si="201"/>
+        <v>-276.59086915199958</v>
       </c>
       <c r="AT29" s="8">
-        <f t="shared" si="204"/>
-        <v>-203.84664913254352</v>
+        <f t="shared" si="201"/>
+        <v>-140.58268229043148</v>
       </c>
       <c r="AU29" s="8">
-        <f t="shared" si="204"/>
-        <v>-151.46489213491998</v>
+        <f t="shared" si="201"/>
+        <v>-63.124280233446051</v>
       </c>
       <c r="AV29" s="8">
-        <f t="shared" si="204"/>
-        <v>-96.958850939198115</v>
+        <f t="shared" si="201"/>
+        <v>-4.2363887921343322</v>
       </c>
       <c r="AW29" s="8">
-        <f t="shared" si="204"/>
-        <v>-61.593326284446505</v>
+        <f t="shared" si="201"/>
+        <v>34.057326248893624</v>
       </c>
       <c r="AX29" s="8">
-        <f t="shared" si="204"/>
-        <v>-16.010312319099548</v>
+        <f t="shared" si="201"/>
+        <v>82.708075742417108</v>
       </c>
       <c r="AY29" s="8">
-        <f t="shared" si="204"/>
-        <v>31.54180210556239</v>
+        <f t="shared" si="201"/>
+        <v>133.42332529863276</v>
       </c>
       <c r="AZ29" s="8">
-        <f t="shared" si="204"/>
-        <v>80.989500871705843</v>
+        <f t="shared" si="201"/>
+        <v>186.13168451358337</v>
       </c>
       <c r="BA29" s="8">
-        <f t="shared" si="204"/>
-        <v>132.39185723175689</v>
+        <f t="shared" si="201"/>
+        <v>240.8951782578998</v>
       </c>
       <c r="BB29" s="8">
-        <f t="shared" si="204"/>
-        <v>185.81191128879408</v>
+        <f t="shared" si="201"/>
+        <v>297.77989960923384</v>
       </c>
       <c r="BD29" t="s">
         <v>48</v>
@@ -6076,6 +6084,9 @@
       <c r="AB30" s="4">
         <v>40</v>
       </c>
+      <c r="AC30" s="4">
+        <v>38.9</v>
+      </c>
       <c r="AD30" s="4">
         <v>39.6</v>
       </c>
@@ -6085,6 +6096,12 @@
       <c r="AF30" s="4">
         <v>40</v>
       </c>
+      <c r="AG30" s="4">
+        <v>42.5</v>
+      </c>
+      <c r="AH30" s="4">
+        <v>44</v>
+      </c>
       <c r="AO30" s="4">
         <v>202.2</v>
       </c>
@@ -6095,48 +6112,48 @@
         <v>158.1</v>
       </c>
       <c r="AR30" s="4">
-        <f>AQ30*1.01</f>
-        <v>159.68099999999998</v>
+        <f>SUM(AE30:AH30)</f>
+        <v>164.2</v>
       </c>
       <c r="AS30" s="4">
-        <f t="shared" ref="AS30:BB30" si="205">AR30*1.01</f>
-        <v>161.27780999999999</v>
+        <f t="shared" ref="AS30:BB30" si="202">AR30*1.01</f>
+        <v>165.84199999999998</v>
       </c>
       <c r="AT30" s="4">
-        <f t="shared" si="205"/>
-        <v>162.8905881</v>
+        <f t="shared" si="202"/>
+        <v>167.50041999999999</v>
       </c>
       <c r="AU30" s="4">
-        <f t="shared" si="205"/>
-        <v>164.51949398100001</v>
+        <f t="shared" si="202"/>
+        <v>169.17542419999998</v>
       </c>
       <c r="AV30" s="4">
-        <f t="shared" si="205"/>
-        <v>166.16468892081002</v>
+        <f t="shared" si="202"/>
+        <v>170.86717844199998</v>
       </c>
       <c r="AW30" s="4">
-        <f t="shared" si="205"/>
-        <v>167.82633581001812</v>
+        <f t="shared" si="202"/>
+        <v>172.57585022641999</v>
       </c>
       <c r="AX30" s="4">
-        <f t="shared" si="205"/>
-        <v>169.50459916811832</v>
+        <f t="shared" si="202"/>
+        <v>174.30160872868419</v>
       </c>
       <c r="AY30" s="4">
-        <f t="shared" si="205"/>
-        <v>171.1996451597995</v>
+        <f t="shared" si="202"/>
+        <v>176.04462481597102</v>
       </c>
       <c r="AZ30" s="4">
-        <f t="shared" si="205"/>
-        <v>172.9116416113975</v>
+        <f t="shared" si="202"/>
+        <v>177.80507106413074</v>
       </c>
       <c r="BA30" s="4">
-        <f t="shared" si="205"/>
-        <v>174.64075802751148</v>
+        <f t="shared" si="202"/>
+        <v>179.58312177477205</v>
       </c>
       <c r="BB30" s="4">
-        <f t="shared" si="205"/>
-        <v>176.38716560778659</v>
+        <f t="shared" si="202"/>
+        <v>181.37895299251977</v>
       </c>
     </row>
     <row r="31" spans="2:57" x14ac:dyDescent="0.3">
@@ -6152,6 +6169,9 @@
       <c r="AB31" s="4">
         <v>251.9</v>
       </c>
+      <c r="AC31" s="4">
+        <v>260.2</v>
+      </c>
       <c r="AD31" s="4">
         <v>257.7</v>
       </c>
@@ -6161,6 +6181,12 @@
       <c r="AF31" s="4">
         <v>251.9</v>
       </c>
+      <c r="AG31" s="4">
+        <v>260.39999999999998</v>
+      </c>
+      <c r="AH31" s="4">
+        <v>260.39999999999998</v>
+      </c>
       <c r="AO31" s="4">
         <v>1387.8</v>
       </c>
@@ -6171,48 +6197,48 @@
         <v>1041</v>
       </c>
       <c r="AR31" s="4">
-        <f>AQ31*1.01</f>
-        <v>1051.4100000000001</v>
+        <f t="shared" ref="AR31:AR43" si="203">SUM(AE31:AH31)</f>
+        <v>1020</v>
       </c>
       <c r="AS31" s="4">
-        <f>AR31*0.95</f>
-        <v>998.83950000000004</v>
+        <f>AR31*0.97</f>
+        <v>989.4</v>
       </c>
       <c r="AT31" s="4">
-        <f t="shared" ref="AT31:BB31" si="206">AS31*0.95</f>
-        <v>948.89752499999997</v>
+        <f t="shared" ref="AT31:BB31" si="204">AS31*0.97</f>
+        <v>959.71799999999996</v>
       </c>
       <c r="AU31" s="4">
-        <f t="shared" si="206"/>
-        <v>901.45264874999998</v>
+        <f t="shared" si="204"/>
+        <v>930.92645999999991</v>
       </c>
       <c r="AV31" s="4">
-        <f t="shared" si="206"/>
-        <v>856.38001631249995</v>
+        <f t="shared" si="204"/>
+        <v>902.99866619999989</v>
       </c>
       <c r="AW31" s="4">
-        <f t="shared" si="206"/>
-        <v>813.56101549687492</v>
+        <f t="shared" si="204"/>
+        <v>875.90870621399984</v>
       </c>
       <c r="AX31" s="4">
-        <f t="shared" si="206"/>
-        <v>772.88296472203115</v>
+        <f t="shared" si="204"/>
+        <v>849.63144502757984</v>
       </c>
       <c r="AY31" s="4">
-        <f t="shared" si="206"/>
-        <v>734.23881648592953</v>
+        <f t="shared" si="204"/>
+        <v>824.14250167675243</v>
       </c>
       <c r="AZ31" s="4">
-        <f t="shared" si="206"/>
-        <v>697.52687566163297</v>
+        <f t="shared" si="204"/>
+        <v>799.41822662644984</v>
       </c>
       <c r="BA31" s="4">
-        <f t="shared" si="206"/>
-        <v>662.65053187855131</v>
+        <f t="shared" si="204"/>
+        <v>775.43567982765637</v>
       </c>
       <c r="BB31" s="4">
-        <f t="shared" si="206"/>
-        <v>629.51800528462365</v>
+        <f t="shared" si="204"/>
+        <v>752.17260943282668</v>
       </c>
     </row>
     <row r="32" spans="2:57" x14ac:dyDescent="0.3">
@@ -6228,6 +6254,9 @@
       <c r="AB32" s="4">
         <v>-0.6</v>
       </c>
+      <c r="AC32" s="4">
+        <v>2.7</v>
+      </c>
       <c r="AD32" s="4">
         <v>2.7</v>
       </c>
@@ -6237,6 +6266,12 @@
       <c r="AF32" s="4">
         <v>-0.6</v>
       </c>
+      <c r="AG32" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="AH32" s="4">
+        <v>0.7</v>
+      </c>
       <c r="AO32" s="4">
         <v>6.9</v>
       </c>
@@ -6247,48 +6282,48 @@
         <v>9.4</v>
       </c>
       <c r="AR32" s="4">
-        <f>AQ32*1.01</f>
-        <v>9.4939999999999998</v>
+        <f t="shared" si="203"/>
+        <v>8.4</v>
       </c>
       <c r="AS32" s="4">
-        <f t="shared" ref="AS32:BB32" si="207">AR32*1.01</f>
-        <v>9.5889399999999991</v>
+        <f t="shared" ref="AS32:BB32" si="205">AR32*1.01</f>
+        <v>8.484</v>
       </c>
       <c r="AT32" s="4">
-        <f t="shared" si="207"/>
-        <v>9.6848293999999999</v>
+        <f t="shared" si="205"/>
+        <v>8.5688399999999998</v>
       </c>
       <c r="AU32" s="4">
-        <f t="shared" si="207"/>
-        <v>9.7816776940000008</v>
+        <f t="shared" si="205"/>
+        <v>8.6545284000000002</v>
       </c>
       <c r="AV32" s="4">
-        <f t="shared" si="207"/>
-        <v>9.879494470940001</v>
+        <f t="shared" si="205"/>
+        <v>8.7410736839999998</v>
       </c>
       <c r="AW32" s="4">
-        <f t="shared" si="207"/>
-        <v>9.9782894156494013</v>
+        <f t="shared" si="205"/>
+        <v>8.8284844208400006</v>
       </c>
       <c r="AX32" s="4">
-        <f t="shared" si="207"/>
-        <v>10.078072309805895</v>
+        <f t="shared" si="205"/>
+        <v>8.9167692650484014</v>
       </c>
       <c r="AY32" s="4">
-        <f t="shared" si="207"/>
-        <v>10.178853032903953</v>
+        <f t="shared" si="205"/>
+        <v>9.0059369576988857</v>
       </c>
       <c r="AZ32" s="4">
-        <f t="shared" si="207"/>
-        <v>10.280641563232994</v>
+        <f t="shared" si="205"/>
+        <v>9.0959963272758753</v>
       </c>
       <c r="BA32" s="4">
-        <f t="shared" si="207"/>
-        <v>10.383447978865323</v>
+        <f t="shared" si="205"/>
+        <v>9.1869562905486344</v>
       </c>
       <c r="BB32" s="4">
-        <f t="shared" si="207"/>
-        <v>10.487282458653977</v>
+        <f t="shared" si="205"/>
+        <v>9.278825853454121</v>
       </c>
     </row>
     <row r="33" spans="2:147" x14ac:dyDescent="0.3">
@@ -6304,6 +6339,9 @@
       <c r="AB33" s="4">
         <v>-1.2</v>
       </c>
+      <c r="AC33" s="4">
+        <v>0.5</v>
+      </c>
       <c r="AD33" s="4">
         <v>-3.7</v>
       </c>
@@ -6313,6 +6351,12 @@
       <c r="AF33" s="4">
         <v>-1.2</v>
       </c>
+      <c r="AG33" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="AH33" s="4">
+        <v>1.2</v>
+      </c>
       <c r="AO33" s="4">
         <v>36.799999999999997</v>
       </c>
@@ -6323,7 +6367,8 @@
         <v>8.5</v>
       </c>
       <c r="AR33" s="4">
-        <v>0</v>
+        <f t="shared" si="203"/>
+        <v>17</v>
       </c>
       <c r="AS33" s="4">
         <v>0</v>
@@ -6367,6 +6412,9 @@
       <c r="AB34" s="4">
         <v>0</v>
       </c>
+      <c r="AC34" s="4">
+        <v>0</v>
+      </c>
       <c r="AD34" s="4"/>
       <c r="AE34" s="4">
         <v>-66.900000000000006</v>
@@ -6374,10 +6422,19 @@
       <c r="AF34" s="4">
         <v>0</v>
       </c>
+      <c r="AG34" s="4">
+        <v>-29.8</v>
+      </c>
+      <c r="AH34" s="4">
+        <v>0</v>
+      </c>
       <c r="AO34" s="4"/>
       <c r="AP34" s="4"/>
       <c r="AQ34" s="4"/>
-      <c r="AR34" s="4"/>
+      <c r="AR34" s="4">
+        <f t="shared" si="203"/>
+        <v>-96.7</v>
+      </c>
       <c r="AS34" s="4"/>
       <c r="AT34" s="4"/>
       <c r="AU34" s="4"/>
@@ -6402,6 +6459,9 @@
       <c r="AB35" s="4">
         <v>12.4</v>
       </c>
+      <c r="AC35" s="4">
+        <v>2.2000000000000002</v>
+      </c>
       <c r="AD35" s="4">
         <v>-10.3</v>
       </c>
@@ -6411,6 +6471,12 @@
       <c r="AF35" s="4">
         <v>12.4</v>
       </c>
+      <c r="AG35" s="4">
+        <v>3</v>
+      </c>
+      <c r="AH35" s="4">
+        <v>0</v>
+      </c>
       <c r="AO35" s="4">
         <v>15.6</v>
       </c>
@@ -6421,7 +6487,8 @@
         <v>-14.2</v>
       </c>
       <c r="AR35" s="4">
-        <v>0</v>
+        <f t="shared" si="203"/>
+        <v>14.6</v>
       </c>
       <c r="AS35" s="4">
         <v>0</v>
@@ -6467,6 +6534,9 @@
       <c r="AB36" s="4">
         <v>-3.1</v>
       </c>
+      <c r="AC36" s="4">
+        <v>-51.9</v>
+      </c>
       <c r="AD36" s="4">
         <v>-167.4</v>
       </c>
@@ -6476,6 +6546,12 @@
       <c r="AF36" s="4">
         <v>-3.1</v>
       </c>
+      <c r="AG36" s="4">
+        <v>-89.1</v>
+      </c>
+      <c r="AH36" s="4">
+        <v>0</v>
+      </c>
       <c r="AO36" s="4">
         <v>-119.8</v>
       </c>
@@ -6486,7 +6562,8 @@
         <v>-94</v>
       </c>
       <c r="AR36" s="4">
-        <v>0</v>
+        <f t="shared" si="203"/>
+        <v>102</v>
       </c>
       <c r="AS36" s="4">
         <v>0</v>
@@ -6532,6 +6609,9 @@
       <c r="AB37" s="4">
         <v>-7.1</v>
       </c>
+      <c r="AC37" s="4">
+        <v>11.9</v>
+      </c>
       <c r="AD37" s="4">
         <v>-0.3</v>
       </c>
@@ -6541,6 +6621,12 @@
       <c r="AF37" s="4">
         <v>-7.1</v>
       </c>
+      <c r="AG37" s="4">
+        <v>-16.3</v>
+      </c>
+      <c r="AH37" s="4">
+        <v>0</v>
+      </c>
       <c r="AO37" s="4">
         <v>-40.9</v>
       </c>
@@ -6551,7 +6637,8 @@
         <v>-36.5</v>
       </c>
       <c r="AR37" s="4">
-        <v>0</v>
+        <f t="shared" si="203"/>
+        <v>-46.2</v>
       </c>
       <c r="AS37" s="4">
         <v>0</v>
@@ -6597,6 +6684,9 @@
       <c r="AB38" s="4">
         <v>13.8</v>
       </c>
+      <c r="AC38" s="4">
+        <v>12.7</v>
+      </c>
       <c r="AD38" s="4">
         <v>12.9</v>
       </c>
@@ -6606,6 +6696,12 @@
       <c r="AF38" s="4">
         <v>13.8</v>
       </c>
+      <c r="AG38" s="4">
+        <v>14.9</v>
+      </c>
+      <c r="AH38" s="4">
+        <v>0</v>
+      </c>
       <c r="AO38" s="4">
         <v>71.400000000000006</v>
       </c>
@@ -6616,7 +6712,8 @@
         <v>54.1</v>
       </c>
       <c r="AR38" s="4">
-        <v>0</v>
+        <f t="shared" si="203"/>
+        <v>42.8</v>
       </c>
       <c r="AS38" s="4">
         <v>0</v>
@@ -6662,6 +6759,9 @@
       <c r="AB39" s="4">
         <v>-2.1</v>
       </c>
+      <c r="AC39" s="4">
+        <v>3.1</v>
+      </c>
       <c r="AD39" s="4">
         <v>-6.9</v>
       </c>
@@ -6671,6 +6771,12 @@
       <c r="AF39" s="4">
         <v>-2.1</v>
       </c>
+      <c r="AG39" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="AH39" s="4">
+        <v>0</v>
+      </c>
       <c r="AO39" s="4">
         <v>-0.5</v>
       </c>
@@ -6681,7 +6787,8 @@
         <v>-10</v>
       </c>
       <c r="AR39" s="4">
-        <v>0</v>
+        <f t="shared" si="203"/>
+        <v>7.1000000000000005</v>
       </c>
       <c r="AS39" s="4">
         <v>0</v>
@@ -6727,6 +6834,9 @@
       <c r="AB40" s="4">
         <v>-94.2</v>
       </c>
+      <c r="AC40" s="4">
+        <v>-16.600000000000001</v>
+      </c>
       <c r="AD40" s="4">
         <v>11.6</v>
       </c>
@@ -6736,6 +6846,12 @@
       <c r="AF40" s="4">
         <v>-94.2</v>
       </c>
+      <c r="AG40" s="4">
+        <v>38.1</v>
+      </c>
+      <c r="AH40" s="4">
+        <v>0</v>
+      </c>
       <c r="AO40" s="4">
         <v>46.5</v>
       </c>
@@ -6746,7 +6862,8 @@
         <v>-100.7</v>
       </c>
       <c r="AR40" s="4">
-        <v>0</v>
+        <f t="shared" si="203"/>
+        <v>-21.800000000000004</v>
       </c>
       <c r="AS40" s="4">
         <v>0</v>
@@ -6792,6 +6909,9 @@
       <c r="AB41" s="4">
         <v>147.69999999999999</v>
       </c>
+      <c r="AC41" s="4">
+        <v>19.3</v>
+      </c>
       <c r="AD41" s="4">
         <v>103.6</v>
       </c>
@@ -6801,6 +6921,12 @@
       <c r="AF41" s="4">
         <v>147.69999999999999</v>
       </c>
+      <c r="AG41" s="4">
+        <v>23.9</v>
+      </c>
+      <c r="AH41" s="4">
+        <v>0</v>
+      </c>
       <c r="AO41" s="4">
         <v>71.7</v>
       </c>
@@ -6811,7 +6937,8 @@
         <v>150.4</v>
       </c>
       <c r="AR41" s="4">
-        <v>0</v>
+        <f t="shared" si="203"/>
+        <v>8.9999999999999929</v>
       </c>
       <c r="AS41" s="4">
         <v>0</v>
@@ -6857,6 +6984,9 @@
       <c r="AB42" s="4">
         <v>-8.5</v>
       </c>
+      <c r="AC42" s="4">
+        <v>-16.399999999999999</v>
+      </c>
       <c r="AD42" s="4">
         <v>-18.399999999999999</v>
       </c>
@@ -6866,6 +6996,12 @@
       <c r="AF42" s="4">
         <v>-8.5</v>
       </c>
+      <c r="AG42" s="4">
+        <v>1.3</v>
+      </c>
+      <c r="AH42" s="4">
+        <v>0</v>
+      </c>
       <c r="AO42" s="4">
         <v>-68.900000000000006</v>
       </c>
@@ -6876,7 +7012,8 @@
         <v>-62.7</v>
       </c>
       <c r="AR42" s="4">
-        <v>0</v>
+        <f t="shared" si="203"/>
+        <v>-24.2</v>
       </c>
       <c r="AS42" s="4">
         <v>0</v>
@@ -6922,6 +7059,9 @@
       <c r="AB43" s="4">
         <v>2</v>
       </c>
+      <c r="AC43" s="4">
+        <v>2.5</v>
+      </c>
       <c r="AD43" s="4">
         <v>0.5</v>
       </c>
@@ -6931,6 +7071,12 @@
       <c r="AF43" s="4">
         <v>2</v>
       </c>
+      <c r="AG43" s="4">
+        <v>-0.9</v>
+      </c>
+      <c r="AH43" s="4">
+        <v>0</v>
+      </c>
       <c r="AO43" s="4">
         <v>5.5</v>
       </c>
@@ -6941,7 +7087,8 @@
         <v>7.9</v>
       </c>
       <c r="AR43" s="4">
-        <v>0</v>
+        <f t="shared" si="203"/>
+        <v>2.3000000000000003</v>
       </c>
       <c r="AS43" s="4">
         <v>0</v>
@@ -6990,6 +7137,10 @@
         <f>AB29+SUM(AB30:AB43)</f>
         <v>102.49999999999986</v>
       </c>
+      <c r="AC44" s="8">
+        <f>AC29+SUM(AC30:AC43)</f>
+        <v>115.69999999999993</v>
+      </c>
       <c r="AD44" s="8">
         <f>AD29+SUM(AD30:AD43)</f>
         <v>230.7999999999999</v>
@@ -7002,6 +7153,14 @@
         <f>AF29+SUM(AF30:AF43)</f>
         <v>88.400000000000034</v>
       </c>
+      <c r="AG44" s="8">
+        <f>AG29+SUM(AG30:AG43)</f>
+        <v>146.69999999999987</v>
+      </c>
+      <c r="AH44" s="8">
+        <f>AH29+SUM(AH30:AH43)</f>
+        <v>298.64151799999985</v>
+      </c>
       <c r="AO44" s="8">
         <f>AO29+SUM(AO30:AO43)</f>
         <v>40.600000000000136</v>
@@ -7016,47 +7175,47 @@
       </c>
       <c r="AR44" s="8">
         <f>AR29+SUM(AR30:AR43)</f>
-        <v>660.27965100000051</v>
+        <v>685.14151800000025</v>
       </c>
       <c r="AS44" s="8">
-        <f t="shared" ref="AS44:BB44" si="208">AS29+SUM(AS30:AS43)</f>
-        <v>872.46898921600064</v>
+        <f t="shared" ref="AS44:BB44" si="206">AS29+SUM(AS30:AS43)</f>
+        <v>887.13513084800024</v>
       </c>
       <c r="AT44" s="8">
-        <f t="shared" si="208"/>
-        <v>917.62629336745636</v>
+        <f t="shared" si="206"/>
+        <v>995.20457770956841</v>
       </c>
       <c r="AU44" s="8">
-        <f t="shared" si="208"/>
-        <v>924.28892829008021</v>
+        <f t="shared" si="206"/>
+        <v>1045.6321323665536</v>
       </c>
       <c r="AV44" s="8">
-        <f t="shared" si="208"/>
-        <v>935.46534876505189</v>
+        <f t="shared" si="206"/>
+        <v>1078.3705295338657</v>
       </c>
       <c r="AW44" s="8">
-        <f t="shared" si="208"/>
-        <v>929.77231443809592</v>
+        <f t="shared" si="206"/>
+        <v>1091.3703671101532</v>
       </c>
       <c r="AX44" s="8">
-        <f t="shared" si="208"/>
-        <v>936.45532388085587</v>
+        <f t="shared" si="206"/>
+        <v>1115.5578987637296</v>
       </c>
       <c r="AY44" s="8">
-        <f t="shared" si="208"/>
-        <v>947.15911678419536</v>
+        <f t="shared" si="206"/>
+        <v>1142.616388749055</v>
       </c>
       <c r="AZ44" s="8">
-        <f t="shared" si="208"/>
-        <v>961.70865970796922</v>
+        <f t="shared" si="206"/>
+        <v>1172.4509785314399</v>
       </c>
       <c r="BA44" s="8">
-        <f t="shared" si="208"/>
-        <v>980.06659511668499</v>
+        <f t="shared" si="206"/>
+        <v>1205.1009361508768</v>
       </c>
       <c r="BB44" s="8">
-        <f t="shared" si="208"/>
-        <v>1002.2043646398583</v>
+        <f t="shared" si="206"/>
+        <v>1240.6102878880345</v>
       </c>
     </row>
     <row r="45" spans="2:147" x14ac:dyDescent="0.3">
@@ -7072,6 +7231,9 @@
       <c r="AB45" s="4">
         <v>64.7</v>
       </c>
+      <c r="AC45" s="4">
+        <v>44</v>
+      </c>
       <c r="AD45" s="4">
         <v>48.3</v>
       </c>
@@ -7081,6 +7243,12 @@
       <c r="AF45" s="4">
         <v>64.7</v>
       </c>
+      <c r="AG45" s="4">
+        <v>53</v>
+      </c>
+      <c r="AH45" s="4">
+        <v>53</v>
+      </c>
       <c r="AO45" s="4">
         <v>129.30000000000001</v>
       </c>
@@ -7091,48 +7259,48 @@
         <v>194.8</v>
       </c>
       <c r="AR45" s="4">
-        <f>AQ45*1.01</f>
-        <v>196.74800000000002</v>
+        <f>SUM(AE45:AH45)</f>
+        <v>207.9</v>
       </c>
       <c r="AS45" s="4">
-        <f t="shared" ref="AS45:BB45" si="209">AR45*1.01</f>
-        <v>198.71548000000001</v>
+        <f>AR45*1.05</f>
+        <v>218.29500000000002</v>
       </c>
       <c r="AT45" s="4">
-        <f t="shared" si="209"/>
-        <v>200.70263480000003</v>
+        <f>AS45*1.04</f>
+        <v>227.02680000000004</v>
       </c>
       <c r="AU45" s="4">
-        <f t="shared" si="209"/>
-        <v>202.70966114800004</v>
+        <f>AT45*1.03</f>
+        <v>233.83760400000006</v>
       </c>
       <c r="AV45" s="4">
-        <f t="shared" si="209"/>
-        <v>204.73675775948004</v>
+        <f>AU45*1.02</f>
+        <v>238.51435608000006</v>
       </c>
       <c r="AW45" s="4">
-        <f t="shared" si="209"/>
-        <v>206.78412533707484</v>
+        <f t="shared" ref="AW45:BB45" si="207">AV45*1.02</f>
+        <v>243.28464320160006</v>
       </c>
       <c r="AX45" s="4">
-        <f t="shared" si="209"/>
-        <v>208.85196659044558</v>
+        <f t="shared" si="207"/>
+        <v>248.15033606563208</v>
       </c>
       <c r="AY45" s="4">
-        <f t="shared" si="209"/>
-        <v>210.94048625635006</v>
+        <f t="shared" si="207"/>
+        <v>253.11334278694471</v>
       </c>
       <c r="AZ45" s="4">
-        <f t="shared" si="209"/>
-        <v>213.04989111891356</v>
+        <f t="shared" si="207"/>
+        <v>258.17560964268364</v>
       </c>
       <c r="BA45" s="4">
-        <f t="shared" si="209"/>
-        <v>215.1803900301027</v>
+        <f t="shared" si="207"/>
+        <v>263.3391218355373</v>
       </c>
       <c r="BB45" s="4">
-        <f t="shared" si="209"/>
-        <v>217.33219393040372</v>
+        <f t="shared" si="207"/>
+        <v>268.60590427224804</v>
       </c>
     </row>
     <row r="46" spans="2:147" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -7151,6 +7319,10 @@
         <f>AB44-AB45</f>
         <v>37.799999999999855</v>
       </c>
+      <c r="AC46" s="8">
+        <f>AC44-AC45</f>
+        <v>71.699999999999932</v>
+      </c>
       <c r="AD46" s="8">
         <f>AD44-AD45</f>
         <v>182.49999999999989</v>
@@ -7163,6 +7335,14 @@
         <f>AF44-AF45</f>
         <v>23.700000000000031</v>
       </c>
+      <c r="AG46" s="8">
+        <f>AG44-AG45</f>
+        <v>93.699999999999875</v>
+      </c>
+      <c r="AH46" s="8">
+        <f>AH44-AH45</f>
+        <v>245.64151799999985</v>
+      </c>
       <c r="AO46" s="8">
         <f>AO44-AO45</f>
         <v>-88.699999999999875</v>
@@ -7177,425 +7357,425 @@
       </c>
       <c r="AR46" s="8">
         <f>AR44-AR45</f>
-        <v>463.53165100000047</v>
+        <v>477.24151800000027</v>
       </c>
       <c r="AS46" s="8">
-        <f t="shared" ref="AS46:BB46" si="210">AS44-AS45</f>
-        <v>673.75350921600057</v>
+        <f t="shared" ref="AS46:BB46" si="208">AS44-AS45</f>
+        <v>668.84013084800017</v>
       </c>
       <c r="AT46" s="8">
-        <f t="shared" si="210"/>
-        <v>716.9236585674563</v>
+        <f t="shared" si="208"/>
+        <v>768.17777770956832</v>
       </c>
       <c r="AU46" s="8">
-        <f t="shared" si="210"/>
-        <v>721.5792671420802</v>
+        <f t="shared" si="208"/>
+        <v>811.79452836655355</v>
       </c>
       <c r="AV46" s="8">
-        <f t="shared" si="210"/>
-        <v>730.72859100557184</v>
+        <f t="shared" si="208"/>
+        <v>839.85617345386561</v>
       </c>
       <c r="AW46" s="8">
-        <f t="shared" si="210"/>
-        <v>722.98818910102113</v>
+        <f t="shared" si="208"/>
+        <v>848.08572390855318</v>
       </c>
       <c r="AX46" s="8">
-        <f t="shared" si="210"/>
-        <v>727.60335729041026</v>
+        <f t="shared" si="208"/>
+        <v>867.40756269809754</v>
       </c>
       <c r="AY46" s="8">
-        <f t="shared" si="210"/>
-        <v>736.21863052784533</v>
+        <f t="shared" si="208"/>
+        <v>889.50304596211026</v>
       </c>
       <c r="AZ46" s="8">
-        <f t="shared" si="210"/>
-        <v>748.65876858905563</v>
+        <f t="shared" si="208"/>
+        <v>914.27536888875625</v>
       </c>
       <c r="BA46" s="8">
-        <f t="shared" si="210"/>
-        <v>764.88620508658232</v>
+        <f t="shared" si="208"/>
+        <v>941.76181431533951</v>
       </c>
       <c r="BB46" s="8">
-        <f t="shared" si="210"/>
-        <v>784.87217070945462</v>
+        <f t="shared" si="208"/>
+        <v>972.00438361578642</v>
       </c>
       <c r="BC46" s="1">
         <f>BB46*(1+$BE$21)</f>
-        <v>777.02344900236005</v>
+        <v>962.28433977962857</v>
       </c>
       <c r="BD46" s="1">
-        <f t="shared" ref="BD46:DO46" si="211">BC46*(1+$BE$21)</f>
-        <v>769.2532145123364</v>
+        <f t="shared" ref="BD46:DO46" si="209">BC46*(1+$BE$21)</f>
+        <v>952.66149638183231</v>
       </c>
       <c r="BE46" s="1">
-        <f t="shared" si="211"/>
-        <v>761.56068236721308</v>
+        <f t="shared" si="209"/>
+        <v>943.13488141801395</v>
       </c>
       <c r="BF46" s="1">
-        <f t="shared" si="211"/>
-        <v>753.94507554354095</v>
+        <f t="shared" si="209"/>
+        <v>933.70353260383376</v>
       </c>
       <c r="BG46" s="1">
-        <f t="shared" si="211"/>
-        <v>746.40562478810557</v>
+        <f t="shared" si="209"/>
+        <v>924.36649727779547</v>
       </c>
       <c r="BH46" s="1">
-        <f t="shared" si="211"/>
-        <v>738.94156854022447</v>
+        <f t="shared" si="209"/>
+        <v>915.12283230501748</v>
       </c>
       <c r="BI46" s="1">
-        <f t="shared" si="211"/>
-        <v>731.55215285482222</v>
+        <f t="shared" si="209"/>
+        <v>905.97160398196729</v>
       </c>
       <c r="BJ46" s="1">
-        <f t="shared" si="211"/>
-        <v>724.23663132627405</v>
+        <f t="shared" si="209"/>
+        <v>896.91188794214759</v>
       </c>
       <c r="BK46" s="1">
-        <f t="shared" si="211"/>
-        <v>716.99426501301127</v>
+        <f t="shared" si="209"/>
+        <v>887.94276906272614</v>
       </c>
       <c r="BL46" s="1">
-        <f t="shared" si="211"/>
-        <v>709.82432236288116</v>
+        <f t="shared" si="209"/>
+        <v>879.06334137209888</v>
       </c>
       <c r="BM46" s="1">
-        <f t="shared" si="211"/>
-        <v>702.72607913925231</v>
+        <f t="shared" si="209"/>
+        <v>870.27270795837785</v>
       </c>
       <c r="BN46" s="1">
-        <f t="shared" si="211"/>
-        <v>695.69881834785974</v>
+        <f t="shared" si="209"/>
+        <v>861.56998087879401</v>
       </c>
       <c r="BO46" s="1">
-        <f t="shared" si="211"/>
-        <v>688.7418301643811</v>
+        <f t="shared" si="209"/>
+        <v>852.95428107000612</v>
       </c>
       <c r="BP46" s="1">
-        <f t="shared" si="211"/>
-        <v>681.85441186273727</v>
+        <f t="shared" si="209"/>
+        <v>844.42473825930608</v>
       </c>
       <c r="BQ46" s="1">
-        <f t="shared" si="211"/>
-        <v>675.03586774410985</v>
+        <f t="shared" si="209"/>
+        <v>835.98049087671302</v>
       </c>
       <c r="BR46" s="1">
-        <f t="shared" si="211"/>
-        <v>668.28550906666874</v>
+        <f t="shared" si="209"/>
+        <v>827.62068596794586</v>
       </c>
       <c r="BS46" s="1">
-        <f t="shared" si="211"/>
-        <v>661.60265397600199</v>
+        <f t="shared" si="209"/>
+        <v>819.34447910826634</v>
       </c>
       <c r="BT46" s="1">
-        <f t="shared" si="211"/>
-        <v>654.98662743624197</v>
+        <f t="shared" si="209"/>
+        <v>811.15103431718364</v>
       </c>
       <c r="BU46" s="1">
-        <f t="shared" si="211"/>
-        <v>648.43676116187953</v>
+        <f t="shared" si="209"/>
+        <v>803.03952397401179</v>
       </c>
       <c r="BV46" s="1">
-        <f t="shared" si="211"/>
-        <v>641.95239355026069</v>
+        <f t="shared" si="209"/>
+        <v>795.00912873427171</v>
       </c>
       <c r="BW46" s="1">
-        <f t="shared" si="211"/>
-        <v>635.53286961475806</v>
+        <f t="shared" si="209"/>
+        <v>787.05903744692898</v>
       </c>
       <c r="BX46" s="1">
-        <f t="shared" si="211"/>
-        <v>629.17754091861048</v>
+        <f t="shared" si="209"/>
+        <v>779.18844707245967</v>
       </c>
       <c r="BY46" s="1">
-        <f t="shared" si="211"/>
-        <v>622.88576550942435</v>
+        <f t="shared" si="209"/>
+        <v>771.39656260173501</v>
       </c>
       <c r="BZ46" s="1">
-        <f t="shared" si="211"/>
-        <v>616.65690785433014</v>
+        <f t="shared" si="209"/>
+        <v>763.68259697571762</v>
       </c>
       <c r="CA46" s="1">
-        <f t="shared" si="211"/>
-        <v>610.49033877578688</v>
+        <f t="shared" si="209"/>
+        <v>756.04577100596043</v>
       </c>
       <c r="CB46" s="1">
-        <f t="shared" si="211"/>
-        <v>604.38543538802901</v>
+        <f t="shared" si="209"/>
+        <v>748.48531329590082</v>
       </c>
       <c r="CC46" s="1">
-        <f t="shared" si="211"/>
-        <v>598.3415810341487</v>
+        <f t="shared" si="209"/>
+        <v>741.00046016294186</v>
       </c>
       <c r="CD46" s="1">
-        <f t="shared" si="211"/>
-        <v>592.35816522380719</v>
+        <f t="shared" si="209"/>
+        <v>733.59045556131241</v>
       </c>
       <c r="CE46" s="1">
-        <f t="shared" si="211"/>
-        <v>586.43458357156908</v>
+        <f t="shared" si="209"/>
+        <v>726.25455100569923</v>
       </c>
       <c r="CF46" s="1">
-        <f t="shared" si="211"/>
-        <v>580.57023773585342</v>
+        <f t="shared" si="209"/>
+        <v>718.99200549564227</v>
       </c>
       <c r="CG46" s="1">
-        <f t="shared" si="211"/>
-        <v>574.76453535849487</v>
+        <f t="shared" si="209"/>
+        <v>711.8020854406858</v>
       </c>
       <c r="CH46" s="1">
-        <f t="shared" si="211"/>
-        <v>569.0168900049099</v>
+        <f t="shared" si="209"/>
+        <v>704.68406458627896</v>
       </c>
       <c r="CI46" s="1">
-        <f t="shared" si="211"/>
-        <v>563.32672110486078</v>
+        <f t="shared" si="209"/>
+        <v>697.63722394041622</v>
       </c>
       <c r="CJ46" s="1">
-        <f t="shared" si="211"/>
-        <v>557.69345389381215</v>
+        <f t="shared" si="209"/>
+        <v>690.66085170101201</v>
       </c>
       <c r="CK46" s="1">
-        <f t="shared" si="211"/>
-        <v>552.11651935487407</v>
+        <f t="shared" si="209"/>
+        <v>683.75424318400189</v>
       </c>
       <c r="CL46" s="1">
-        <f t="shared" si="211"/>
-        <v>546.5953541613253</v>
+        <f t="shared" si="209"/>
+        <v>676.91670075216189</v>
       </c>
       <c r="CM46" s="1">
-        <f t="shared" si="211"/>
-        <v>541.1294006197121</v>
+        <f t="shared" si="209"/>
+        <v>670.14753374464021</v>
       </c>
       <c r="CN46" s="1">
-        <f t="shared" si="211"/>
-        <v>535.71810661351492</v>
+        <f t="shared" si="209"/>
+        <v>663.44605840719385</v>
       </c>
       <c r="CO46" s="1">
-        <f t="shared" si="211"/>
-        <v>530.36092554737979</v>
+        <f t="shared" si="209"/>
+        <v>656.81159782312193</v>
       </c>
       <c r="CP46" s="1">
-        <f t="shared" si="211"/>
-        <v>525.05731629190598</v>
+        <f t="shared" si="209"/>
+        <v>650.24348184489065</v>
       </c>
       <c r="CQ46" s="1">
-        <f t="shared" si="211"/>
-        <v>519.80674312898691</v>
+        <f t="shared" si="209"/>
+        <v>643.74104702644172</v>
       </c>
       <c r="CR46" s="1">
-        <f t="shared" si="211"/>
-        <v>514.60867569769698</v>
+        <f t="shared" si="209"/>
+        <v>637.30363655617725</v>
       </c>
       <c r="CS46" s="1">
-        <f t="shared" si="211"/>
-        <v>509.46258894072002</v>
+        <f t="shared" si="209"/>
+        <v>630.93060019061545</v>
       </c>
       <c r="CT46" s="1">
-        <f t="shared" si="211"/>
-        <v>504.36796305131281</v>
+        <f t="shared" si="209"/>
+        <v>624.62129418870927</v>
       </c>
       <c r="CU46" s="1">
-        <f t="shared" si="211"/>
-        <v>499.3242834207997</v>
+        <f t="shared" si="209"/>
+        <v>618.37508124682222</v>
       </c>
       <c r="CV46" s="1">
-        <f t="shared" si="211"/>
-        <v>494.33104058659171</v>
+        <f t="shared" si="209"/>
+        <v>612.19133043435397</v>
       </c>
       <c r="CW46" s="1">
-        <f t="shared" si="211"/>
-        <v>489.38773018072578</v>
+        <f t="shared" si="209"/>
+        <v>606.06941713001038</v>
       </c>
       <c r="CX46" s="1">
-        <f t="shared" si="211"/>
-        <v>484.49385287891852</v>
+        <f t="shared" si="209"/>
+        <v>600.00872295871022</v>
       </c>
       <c r="CY46" s="1">
-        <f t="shared" si="211"/>
-        <v>479.6489143501293</v>
+        <f t="shared" si="209"/>
+        <v>594.00863572912317</v>
       </c>
       <c r="CZ46" s="1">
-        <f t="shared" si="211"/>
-        <v>474.85242520662803</v>
+        <f t="shared" si="209"/>
+        <v>588.06854937183198</v>
       </c>
       <c r="DA46" s="1">
-        <f t="shared" si="211"/>
-        <v>470.10390095456177</v>
+        <f t="shared" si="209"/>
+        <v>582.1878638781136</v>
       </c>
       <c r="DB46" s="1">
-        <f t="shared" si="211"/>
-        <v>465.40286194501613</v>
+        <f t="shared" si="209"/>
+        <v>576.36598523933242</v>
       </c>
       <c r="DC46" s="1">
-        <f t="shared" si="211"/>
-        <v>460.74883332556595</v>
+        <f t="shared" si="209"/>
+        <v>570.60232538693913</v>
       </c>
       <c r="DD46" s="1">
-        <f t="shared" si="211"/>
-        <v>456.14134499231028</v>
+        <f t="shared" si="209"/>
+        <v>564.89630213306975</v>
       </c>
       <c r="DE46" s="1">
-        <f t="shared" si="211"/>
-        <v>451.57993154238716</v>
+        <f t="shared" si="209"/>
+        <v>559.24733911173905</v>
       </c>
       <c r="DF46" s="1">
-        <f t="shared" si="211"/>
-        <v>447.0641322269633</v>
+        <f t="shared" si="209"/>
+        <v>553.65486572062161</v>
       </c>
       <c r="DG46" s="1">
-        <f t="shared" si="211"/>
-        <v>442.59349090469368</v>
+        <f t="shared" si="209"/>
+        <v>548.11831706341536</v>
       </c>
       <c r="DH46" s="1">
-        <f t="shared" si="211"/>
-        <v>438.16755599564675</v>
+        <f t="shared" si="209"/>
+        <v>542.63713389278121</v>
       </c>
       <c r="DI46" s="1">
-        <f t="shared" si="211"/>
-        <v>433.78588043569027</v>
+        <f t="shared" si="209"/>
+        <v>537.21076255385344</v>
       </c>
       <c r="DJ46" s="1">
-        <f t="shared" si="211"/>
-        <v>429.44802163133335</v>
+        <f t="shared" si="209"/>
+        <v>531.8386549283149</v>
       </c>
       <c r="DK46" s="1">
-        <f t="shared" si="211"/>
-        <v>425.15354141502002</v>
+        <f t="shared" si="209"/>
+        <v>526.52026837903179</v>
       </c>
       <c r="DL46" s="1">
-        <f t="shared" si="211"/>
-        <v>420.90200600086979</v>
+        <f t="shared" si="209"/>
+        <v>521.25506569524146</v>
       </c>
       <c r="DM46" s="1">
-        <f t="shared" si="211"/>
-        <v>416.69298594086109</v>
+        <f t="shared" si="209"/>
+        <v>516.04251503828903</v>
       </c>
       <c r="DN46" s="1">
-        <f t="shared" si="211"/>
-        <v>412.52605608145245</v>
+        <f t="shared" si="209"/>
+        <v>510.88208988790615</v>
       </c>
       <c r="DO46" s="1">
-        <f t="shared" si="211"/>
-        <v>408.40079552063793</v>
+        <f t="shared" si="209"/>
+        <v>505.77326898902709</v>
       </c>
       <c r="DP46" s="1">
-        <f t="shared" ref="DP46:EQ46" si="212">DO46*(1+$BE$21)</f>
-        <v>404.31678756543153</v>
+        <f t="shared" ref="DP46:EQ46" si="210">DO46*(1+$BE$21)</f>
+        <v>500.71553629913683</v>
       </c>
       <c r="DQ46" s="1">
-        <f t="shared" si="212"/>
-        <v>400.27361968977721</v>
+        <f t="shared" si="210"/>
+        <v>495.70838093614543</v>
       </c>
       <c r="DR46" s="1">
-        <f t="shared" si="212"/>
-        <v>396.27088349287942</v>
+        <f t="shared" si="210"/>
+        <v>490.75129712678398</v>
       </c>
       <c r="DS46" s="1">
-        <f t="shared" si="212"/>
-        <v>392.30817465795064</v>
+        <f t="shared" si="210"/>
+        <v>485.84378415551612</v>
       </c>
       <c r="DT46" s="1">
-        <f t="shared" si="212"/>
-        <v>388.38509291137115</v>
+        <f t="shared" si="210"/>
+        <v>480.98534631396097</v>
       </c>
       <c r="DU46" s="1">
-        <f t="shared" si="212"/>
-        <v>384.50124198225745</v>
+        <f t="shared" si="210"/>
+        <v>476.17549285082134</v>
       </c>
       <c r="DV46" s="1">
-        <f t="shared" si="212"/>
-        <v>380.65622956243487</v>
+        <f t="shared" si="210"/>
+        <v>471.41373792231315</v>
       </c>
       <c r="DW46" s="1">
-        <f t="shared" si="212"/>
-        <v>376.84966726681051</v>
+        <f t="shared" si="210"/>
+        <v>466.69960054309001</v>
       </c>
       <c r="DX46" s="1">
-        <f t="shared" si="212"/>
-        <v>373.08117059414241</v>
+        <f t="shared" si="210"/>
+        <v>462.0326045376591</v>
       </c>
       <c r="DY46" s="1">
-        <f t="shared" si="212"/>
-        <v>369.35035888820096</v>
+        <f t="shared" si="210"/>
+        <v>457.4122784922825</v>
       </c>
       <c r="DZ46" s="1">
-        <f t="shared" si="212"/>
-        <v>365.65685529931892</v>
+        <f t="shared" si="210"/>
+        <v>452.83815570735965</v>
       </c>
       <c r="EA46" s="1">
-        <f t="shared" si="212"/>
-        <v>362.00028674632574</v>
+        <f t="shared" si="210"/>
+        <v>448.30977415028605</v>
       </c>
       <c r="EB46" s="1">
-        <f t="shared" si="212"/>
-        <v>358.38028387886249</v>
+        <f t="shared" si="210"/>
+        <v>443.82667640878316</v>
       </c>
       <c r="EC46" s="1">
-        <f t="shared" si="212"/>
-        <v>354.79648104007384</v>
+        <f t="shared" si="210"/>
+        <v>439.38840964469534</v>
       </c>
       <c r="ED46" s="1">
-        <f t="shared" si="212"/>
-        <v>351.2485162296731</v>
+        <f t="shared" si="210"/>
+        <v>434.99452554824836</v>
       </c>
       <c r="EE46" s="1">
-        <f t="shared" si="212"/>
-        <v>347.73603106737636</v>
+        <f t="shared" si="210"/>
+        <v>430.64458029276585</v>
       </c>
       <c r="EF46" s="1">
-        <f t="shared" si="212"/>
-        <v>344.2586707567026</v>
+        <f t="shared" si="210"/>
+        <v>426.33813448983818</v>
       </c>
       <c r="EG46" s="1">
-        <f t="shared" si="212"/>
-        <v>340.81608404913555</v>
+        <f t="shared" si="210"/>
+        <v>422.07475314493979</v>
       </c>
       <c r="EH46" s="1">
-        <f t="shared" si="212"/>
-        <v>337.40792320864421</v>
+        <f t="shared" si="210"/>
+        <v>417.85400561349041</v>
       </c>
       <c r="EI46" s="1">
-        <f t="shared" si="212"/>
-        <v>334.03384397655776</v>
+        <f t="shared" si="210"/>
+        <v>413.67546555735549</v>
       </c>
       <c r="EJ46" s="1">
-        <f t="shared" si="212"/>
-        <v>330.6935055367922</v>
+        <f t="shared" si="210"/>
+        <v>409.53871090178194</v>
       </c>
       <c r="EK46" s="1">
-        <f t="shared" si="212"/>
-        <v>327.38657048142426</v>
+        <f t="shared" si="210"/>
+        <v>405.44332379276409</v>
       </c>
       <c r="EL46" s="1">
-        <f t="shared" si="212"/>
-        <v>324.11270477661003</v>
+        <f t="shared" si="210"/>
+        <v>401.38889055483645</v>
       </c>
       <c r="EM46" s="1">
-        <f t="shared" si="212"/>
-        <v>320.87157772884393</v>
+        <f t="shared" si="210"/>
+        <v>397.37500164928809</v>
       </c>
       <c r="EN46" s="1">
-        <f t="shared" si="212"/>
-        <v>317.6628619515555</v>
+        <f t="shared" si="210"/>
+        <v>393.40125163279521</v>
       </c>
       <c r="EO46" s="1">
-        <f t="shared" si="212"/>
-        <v>314.48623333203994</v>
+        <f t="shared" si="210"/>
+        <v>389.46723911646723</v>
       </c>
       <c r="EP46" s="1">
-        <f t="shared" si="212"/>
-        <v>311.34137099871953</v>
+        <f t="shared" si="210"/>
+        <v>385.57256672530252</v>
       </c>
       <c r="EQ46" s="1">
-        <f t="shared" si="212"/>
-        <v>308.22795728873234</v>
+        <f t="shared" si="210"/>
+        <v>381.71684105804951</v>
       </c>
     </row>
     <row r="49" spans="57:57" x14ac:dyDescent="0.3">
       <c r="BE49" s="4">
         <f>NPV(BE22,AR46:EQ46)</f>
-        <v>8648.6546435549772</v>
+        <v>10209.227528518557</v>
       </c>
     </row>
     <row r="50" spans="57:57" x14ac:dyDescent="0.3">
@@ -7607,25 +7787,30 @@
     <row r="51" spans="57:57" x14ac:dyDescent="0.3">
       <c r="BE51" s="4">
         <f>BE49+BE50</f>
-        <v>7965.7546435549775</v>
+        <v>9526.3275285185573</v>
       </c>
     </row>
     <row r="52" spans="57:57" x14ac:dyDescent="0.3">
       <c r="BE52" s="5">
         <f>BE51/BB16</f>
-        <v>4.7559583518747255</v>
+        <v>5.6152829522655807</v>
       </c>
     </row>
     <row r="53" spans="57:57" x14ac:dyDescent="0.3">
       <c r="BE53" s="5">
         <f>Main!D3</f>
-        <v>7.86</v>
+        <v>8.58</v>
       </c>
     </row>
     <row r="54" spans="57:57" x14ac:dyDescent="0.3">
       <c r="BE54" s="10">
         <f>BE52/BE53-1</f>
-        <v>-0.39491624021950056</v>
+        <v>-0.34553811745156404</v>
+      </c>
+    </row>
+    <row r="55" spans="57:57" x14ac:dyDescent="0.3">
+      <c r="BE55" s="6" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/SNAP.xlsx
+++ b/Financial Analysis/SNAP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA26759E-6B0F-4EA5-BF70-C99FC6D48B53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C8F0344-E64F-491D-B847-B3D2AAA16782}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{48C45758-2500-4F87-8506-866CB0FEFDEC}"/>
   </bookViews>
@@ -25,8 +25,42 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Anton Mniszek</author>
+  </authors>
+  <commentList>
+    <comment ref="AI3" authorId="0" shapeId="0" xr:uid="{363ABB29-6B4E-4174-9FFA-A5F32C46D714}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Anton Mniszek:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+(Q425) our guidance range for revenue is 1.5 to 1.53 billion. Our Q1 revenue guidance range excludes any potential revenue from the perplexity integration as we have yet to mutually agree on a path to a broader rollout</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="94">
   <si>
     <t>SNAP</t>
   </si>
@@ -292,10 +326,22 @@
     <t>FCF</t>
   </si>
   <si>
-    <t>Q325 8K</t>
-  </si>
-  <si>
-    <t>Overvalued</t>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
+  </si>
+  <si>
+    <t>Q425 8K</t>
+  </si>
+  <si>
+    <t>Slightly undervalued</t>
   </si>
 </sst>
 </file>
@@ -305,7 +351,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$$-409]#,##0.00"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -334,6 +380,19 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -395,13 +454,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
+      <xdr:col>34</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>33</xdr:col>
+      <xdr:col>34</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
       <xdr:row>50</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
@@ -419,7 +478,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="20574000" y="0"/>
+          <a:off x="21183600" y="0"/>
           <a:ext cx="0" cy="9304020"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -445,14 +504,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>43</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>48</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>43</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>48</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
       <xdr:row>52</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
@@ -469,8 +528,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="26670000" y="0"/>
-          <a:ext cx="0" cy="9433560"/>
+          <a:off x="29725620" y="0"/>
+          <a:ext cx="0" cy="9616440"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -818,17 +877,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="5">
-        <v>8.58</v>
+        <v>5.12</v>
       </c>
       <c r="E3" s="3">
-        <v>45967</v>
+        <v>46059</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45967</v>
+        <v>46059</v>
       </c>
       <c r="G3" s="3">
-        <v>46063</v>
+        <v>46128</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -836,11 +895,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="4">
-        <f>1696.5</f>
-        <v>1696.5</v>
+        <f>1710.5</f>
+        <v>1710.5</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -849,7 +908,7 @@
       </c>
       <c r="D5" s="4">
         <f>D3*D4</f>
-        <v>14555.97</v>
+        <v>8757.76</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -857,11 +916,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="4">
-        <f>926+1967.1</f>
-        <v>2893.1</v>
+        <f>1030.5+1910.1</f>
+        <v>2940.6</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -869,11 +928,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="4">
-        <f>3576</f>
-        <v>3576</v>
+        <f>47+3489.9</f>
+        <v>3536.9</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -882,7 +941,7 @@
       </c>
       <c r="D8" s="4">
         <f>D6-D7</f>
-        <v>-682.90000000000009</v>
+        <v>-596.30000000000018</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -891,7 +950,7 @@
       </c>
       <c r="D9" s="4">
         <f>D5-D8</f>
-        <v>15238.869999999999</v>
+        <v>9354.0600000000013</v>
       </c>
     </row>
   </sheetData>
@@ -901,18 +960,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59D9429E-4E4D-4756-99DE-9A816F2CA7A1}">
-  <dimension ref="B2:FK55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59D9429E-4E4D-4756-99DE-9A816F2CA7A1}">
+  <dimension ref="B2:FO55"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="15.21875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="8.88671875" customWidth="1"/>
-    <col min="51" max="53" width="8.88671875" customWidth="1"/>
-    <col min="56" max="56" width="12" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="17.5546875" customWidth="1"/>
+    <col min="55" max="57" width="8.88671875" customWidth="1"/>
+    <col min="60" max="60" width="12" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="17.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:167" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:171" x14ac:dyDescent="0.3">
       <c r="C2" s="6" t="s">
         <v>12</v>
       </c>
@@ -1009,63 +1068,75 @@
       <c r="AH2" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="AI2" s="6"/>
-      <c r="AK2">
+      <c r="AI2" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="AJ2" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="AK2" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="AL2" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM2" s="6"/>
+      <c r="AO2">
         <v>2018</v>
       </c>
-      <c r="AL2">
+      <c r="AP2">
         <v>2019</v>
       </c>
-      <c r="AM2">
+      <c r="AQ2">
         <v>2020</v>
       </c>
-      <c r="AN2">
+      <c r="AR2">
         <v>2021</v>
       </c>
-      <c r="AO2">
+      <c r="AS2">
         <v>2022</v>
       </c>
-      <c r="AP2">
+      <c r="AT2">
         <v>2023</v>
       </c>
-      <c r="AQ2">
+      <c r="AU2">
         <v>2024</v>
       </c>
-      <c r="AR2">
+      <c r="AV2">
         <v>2025</v>
       </c>
-      <c r="AS2">
+      <c r="AW2">
         <v>2026</v>
       </c>
-      <c r="AT2">
+      <c r="AX2">
         <v>2027</v>
       </c>
-      <c r="AU2">
+      <c r="AY2">
         <v>2028</v>
       </c>
-      <c r="AV2">
+      <c r="AZ2">
         <v>2029</v>
       </c>
-      <c r="AW2">
+      <c r="BA2">
         <v>2030</v>
       </c>
-      <c r="AX2">
+      <c r="BB2">
         <v>2031</v>
       </c>
-      <c r="AY2">
+      <c r="BC2">
         <v>2032</v>
       </c>
-      <c r="AZ2">
+      <c r="BD2">
         <v>2033</v>
       </c>
-      <c r="BA2">
+      <c r="BE2">
         <v>2034</v>
       </c>
-      <c r="BB2">
+      <c r="BF2">
         <v>2035</v>
       </c>
     </row>
-    <row r="3" spans="2:167" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:171" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
@@ -1163,84 +1234,89 @@
         <v>1506.8</v>
       </c>
       <c r="AH3" s="8">
-        <f>AD3*1.08</f>
-        <v>1681.884</v>
-      </c>
-      <c r="AI3" s="8"/>
-      <c r="AK3" s="8">
+        <v>1716.5</v>
+      </c>
+      <c r="AI3" s="8">
+        <v>1515</v>
+      </c>
+      <c r="AJ3" s="8"/>
+      <c r="AK3" s="8"/>
+      <c r="AL3" s="8"/>
+      <c r="AM3" s="8"/>
+      <c r="AO3" s="8">
         <f>SUM(C3:F3)</f>
         <v>1180.5999999999999</v>
       </c>
-      <c r="AL3" s="8">
+      <c r="AP3" s="8">
         <f>SUM(G3:J3)</f>
         <v>1715.5</v>
       </c>
-      <c r="AM3" s="8">
+      <c r="AQ3" s="8">
         <f>SUM(K3:N3)</f>
         <v>2506.6999999999998</v>
       </c>
-      <c r="AN3" s="8">
+      <c r="AR3" s="8">
         <f>SUM(O3:R3)</f>
         <v>4117.1000000000004</v>
       </c>
-      <c r="AO3" s="8">
+      <c r="AS3" s="8">
         <f>SUM(S3:V3)</f>
         <v>4601.8</v>
       </c>
-      <c r="AP3" s="8">
+      <c r="AT3" s="8">
         <f>SUM(W3:Z3)</f>
         <v>4606.2</v>
       </c>
-      <c r="AQ3" s="8">
+      <c r="AU3" s="8">
         <f>SUM(AA3:AD3)</f>
         <v>5361.4</v>
       </c>
-      <c r="AR3" s="8">
+      <c r="AV3" s="8">
         <f>SUM(AE3:AH3)</f>
-        <v>5896.7840000000006</v>
-      </c>
-      <c r="AS3" s="8">
-        <f>AR3*1.07</f>
-        <v>6309.5588800000014</v>
-      </c>
-      <c r="AT3" s="8">
-        <f>AS3*1.06</f>
-        <v>6688.1324128000015</v>
-      </c>
-      <c r="AU3" s="8">
-        <f>AT3*1.05</f>
-        <v>7022.5390334400017</v>
-      </c>
-      <c r="AV3" s="8">
-        <f>AU3*1.04</f>
-        <v>7303.4405947776022</v>
+        <v>5931.4000000000005</v>
       </c>
       <c r="AW3" s="8">
-        <f>AV3*1.03</f>
-        <v>7522.5438126209301</v>
+        <f>AV3*1.09</f>
+        <v>6465.2260000000015</v>
       </c>
       <c r="AX3" s="8">
-        <f t="shared" ref="AX3:BB3" si="0">AW3*1.03</f>
-        <v>7748.2201269995585</v>
+        <f>AW3*1.06</f>
+        <v>6853.1395600000023</v>
       </c>
       <c r="AY3" s="8">
+        <f>AX3*1.05</f>
+        <v>7195.7965380000023</v>
+      </c>
+      <c r="AZ3" s="8">
+        <f>AY3*1.04</f>
+        <v>7483.6283995200029</v>
+      </c>
+      <c r="BA3" s="8">
+        <f>AZ3*1.03</f>
+        <v>7708.1372515056028</v>
+      </c>
+      <c r="BB3" s="8">
+        <f t="shared" ref="BB3:BF3" si="0">BA3*1.03</f>
+        <v>7939.3813690507714</v>
+      </c>
+      <c r="BC3" s="8">
         <f t="shared" si="0"/>
-        <v>7980.6667308095457</v>
-      </c>
-      <c r="AZ3" s="8">
+        <v>8177.5628101222946</v>
+      </c>
+      <c r="BD3" s="8">
         <f t="shared" si="0"/>
-        <v>8220.0867327338328</v>
-      </c>
-      <c r="BA3" s="8">
+        <v>8422.8896944259632</v>
+      </c>
+      <c r="BE3" s="8">
         <f t="shared" si="0"/>
-        <v>8466.6893347158475</v>
-      </c>
-      <c r="BB3" s="8">
+        <v>8675.5763852587424</v>
+      </c>
+      <c r="BF3" s="8">
         <f t="shared" si="0"/>
-        <v>8720.6900147573233</v>
+        <v>8935.8436768165047</v>
       </c>
     </row>
-    <row r="4" spans="2:167" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:171" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>23</v>
       </c>
@@ -1338,84 +1414,87 @@
         <v>674.2</v>
       </c>
       <c r="AH4" s="4">
-        <f>AH3-AH5</f>
-        <v>723.21012000000007</v>
+        <v>702.4</v>
       </c>
       <c r="AI4" s="4"/>
-      <c r="AK4" s="4">
+      <c r="AJ4" s="4"/>
+      <c r="AK4" s="4"/>
+      <c r="AL4" s="4"/>
+      <c r="AM4" s="4"/>
+      <c r="AO4" s="4">
         <f>SUM(C4:F4)</f>
         <v>799</v>
       </c>
-      <c r="AL4" s="4">
+      <c r="AP4" s="4">
         <f>SUM(G4:J4)</f>
         <v>895.8</v>
       </c>
-      <c r="AM4" s="4">
+      <c r="AQ4" s="4">
         <f>SUM(K4:N4)</f>
         <v>1182.5</v>
       </c>
-      <c r="AN4" s="4">
+      <c r="AR4" s="4">
         <f>SUM(O4:R4)</f>
         <v>1750.3</v>
       </c>
-      <c r="AO4" s="4">
+      <c r="AS4" s="4">
         <f>SUM(S4:V4)</f>
         <v>1815.3999999999999</v>
       </c>
-      <c r="AP4" s="4">
+      <c r="AT4" s="4">
         <f>SUM(W4:Z4)</f>
         <v>2114.1999999999998</v>
       </c>
-      <c r="AQ4" s="4">
+      <c r="AU4" s="4">
         <f>SUM(AA4:AD4)</f>
         <v>2474.1999999999998</v>
       </c>
-      <c r="AR4" s="4">
+      <c r="AV4" s="4">
         <f>SUM(AE4:AH4)</f>
-        <v>2690.3101200000001</v>
-      </c>
-      <c r="AS4" s="4">
-        <f t="shared" ref="AS4:AW4" si="1">AS3-AS5</f>
-        <v>2776.2059072000002</v>
-      </c>
-      <c r="AT4" s="4">
+        <v>2669.5</v>
+      </c>
+      <c r="AW4" s="4">
+        <f t="shared" ref="AW4:BA4" si="1">AW3-AW5</f>
+        <v>2844.6994400000003</v>
+      </c>
+      <c r="AX4" s="4">
         <f t="shared" si="1"/>
-        <v>2942.7782616320001</v>
-      </c>
-      <c r="AU4" s="4">
+        <v>2946.8500108000012</v>
+      </c>
+      <c r="AY4" s="4">
         <f t="shared" si="1"/>
-        <v>3089.9171747136002</v>
-      </c>
-      <c r="AV4" s="4">
+        <v>3094.1925113400011</v>
+      </c>
+      <c r="AZ4" s="4">
         <f t="shared" si="1"/>
-        <v>3213.5138617021444</v>
-      </c>
-      <c r="AW4" s="4">
+        <v>3217.960211793602</v>
+      </c>
+      <c r="BA4" s="4">
         <f t="shared" si="1"/>
-        <v>3309.9192775532092</v>
-      </c>
-      <c r="AX4" s="4">
-        <f t="shared" ref="AX4:BB4" si="2">AX3-AX5</f>
-        <v>3409.2168558798057</v>
-      </c>
-      <c r="AY4" s="4">
+        <v>3314.4990181474095</v>
+      </c>
+      <c r="BB4" s="4">
+        <f t="shared" ref="BB4:BF4" si="2">BB3-BB5</f>
+        <v>3413.9339886918324</v>
+      </c>
+      <c r="BC4" s="4">
         <f t="shared" si="2"/>
-        <v>3511.4933615561995</v>
-      </c>
-      <c r="AZ4" s="4">
+        <v>3516.3520083525873</v>
+      </c>
+      <c r="BD4" s="4">
         <f t="shared" si="2"/>
-        <v>3616.8381624028862</v>
-      </c>
-      <c r="BA4" s="4">
+        <v>3621.8425686031642</v>
+      </c>
+      <c r="BE4" s="4">
         <f t="shared" si="2"/>
-        <v>3725.3433072749722</v>
-      </c>
-      <c r="BB4" s="4">
+        <v>3730.4978456612598</v>
+      </c>
+      <c r="BF4" s="4">
         <f t="shared" si="2"/>
-        <v>3837.1036064932214</v>
+        <v>3842.4127810310974</v>
       </c>
     </row>
-    <row r="5" spans="2:167" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:171" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
         <v>24</v>
       </c>
@@ -1520,7 +1599,7 @@
         <v>620.09999999999991</v>
       </c>
       <c r="AB5" s="8">
-        <f t="shared" ref="AB5:AG5" si="11">AB3-AB4</f>
+        <f t="shared" ref="AB5:AH5" si="11">AB3-AB4</f>
         <v>647.9</v>
       </c>
       <c r="AC5" s="8">
@@ -1544,85 +1623,89 @@
         <v>832.59999999999991</v>
       </c>
       <c r="AH5" s="8">
-        <f>AH3*0.57</f>
-        <v>958.67387999999994</v>
+        <f t="shared" si="11"/>
+        <v>1014.1</v>
       </c>
       <c r="AI5" s="8"/>
       <c r="AJ5" s="8"/>
-      <c r="AK5" s="8">
-        <f>AK3-AK4</f>
+      <c r="AK5" s="8"/>
+      <c r="AL5" s="8"/>
+      <c r="AM5" s="8"/>
+      <c r="AN5" s="8"/>
+      <c r="AO5" s="8">
+        <f>AO3-AO4</f>
         <v>381.59999999999991</v>
       </c>
-      <c r="AL5" s="8">
-        <f>AL3-AL4</f>
+      <c r="AP5" s="8">
+        <f>AP3-AP4</f>
         <v>819.7</v>
       </c>
-      <c r="AM5" s="8">
-        <f>AM3-AM4</f>
+      <c r="AQ5" s="8">
+        <f>AQ3-AQ4</f>
         <v>1324.1999999999998</v>
       </c>
-      <c r="AN5" s="8">
-        <f t="shared" ref="AN5:AR5" si="12">AN3-AN4</f>
+      <c r="AR5" s="8">
+        <f t="shared" ref="AR5:AV5" si="12">AR3-AR4</f>
         <v>2366.8000000000002</v>
       </c>
-      <c r="AO5" s="8">
+      <c r="AS5" s="8">
         <f t="shared" si="12"/>
         <v>2786.4000000000005</v>
       </c>
-      <c r="AP5" s="8">
+      <c r="AT5" s="8">
         <f t="shared" si="12"/>
         <v>2492</v>
       </c>
-      <c r="AQ5" s="8">
+      <c r="AU5" s="8">
         <f t="shared" si="12"/>
         <v>2887.2</v>
       </c>
-      <c r="AR5" s="8">
+      <c r="AV5" s="8">
         <f t="shared" si="12"/>
-        <v>3206.4738800000005</v>
-      </c>
-      <c r="AS5" s="8">
-        <f>AS3*0.56</f>
-        <v>3533.3529728000012</v>
-      </c>
-      <c r="AT5" s="8">
-        <f t="shared" ref="AT5:BB5" si="13">AT3*0.56</f>
-        <v>3745.3541511680014</v>
-      </c>
-      <c r="AU5" s="8">
-        <f t="shared" si="13"/>
-        <v>3932.6218587264016</v>
-      </c>
-      <c r="AV5" s="8">
-        <f t="shared" si="13"/>
-        <v>4089.9267330754578</v>
+        <v>3261.9000000000005</v>
       </c>
       <c r="AW5" s="8">
-        <f t="shared" si="13"/>
-        <v>4212.6245350677209</v>
+        <f>AW3*0.56</f>
+        <v>3620.5265600000012</v>
       </c>
       <c r="AX5" s="8">
-        <f t="shared" si="13"/>
-        <v>4339.0032711197528</v>
+        <f>AX3*0.57</f>
+        <v>3906.2895492000011</v>
       </c>
       <c r="AY5" s="8">
-        <f t="shared" si="13"/>
-        <v>4469.1733692533462</v>
+        <f t="shared" ref="AY5:BF5" si="13">AY3*0.57</f>
+        <v>4101.6040266600012</v>
       </c>
       <c r="AZ5" s="8">
         <f t="shared" si="13"/>
-        <v>4603.2485703309467</v>
+        <v>4265.6681877264009</v>
       </c>
       <c r="BA5" s="8">
         <f t="shared" si="13"/>
-        <v>4741.3460274408753</v>
+        <v>4393.6382333581932</v>
       </c>
       <c r="BB5" s="8">
         <f t="shared" si="13"/>
-        <v>4883.5864082641019</v>
+        <v>4525.447380358939</v>
+      </c>
+      <c r="BC5" s="8">
+        <f t="shared" si="13"/>
+        <v>4661.2108017697074</v>
+      </c>
+      <c r="BD5" s="8">
+        <f t="shared" si="13"/>
+        <v>4801.047125822799</v>
+      </c>
+      <c r="BE5" s="8">
+        <f t="shared" si="13"/>
+        <v>4945.0785395974826</v>
+      </c>
+      <c r="BF5" s="8">
+        <f t="shared" si="13"/>
+        <v>5093.4308957854073</v>
       </c>
     </row>
-    <row r="6" spans="2:167" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:171" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>25</v>
       </c>
@@ -1720,85 +1803,88 @@
         <v>453.4</v>
       </c>
       <c r="AH6" s="4">
-        <f>AD6*1.1</f>
-        <v>465.19</v>
+        <v>472.7</v>
       </c>
       <c r="AI6" s="4"/>
       <c r="AJ6" s="4"/>
-      <c r="AK6" s="4">
+      <c r="AK6" s="4"/>
+      <c r="AL6" s="4"/>
+      <c r="AM6" s="4"/>
+      <c r="AN6" s="4"/>
+      <c r="AO6" s="4">
         <f>SUM(C6:F6)</f>
         <v>772.1</v>
       </c>
-      <c r="AL6" s="4">
+      <c r="AP6" s="4">
         <f>SUM(G6:J6)</f>
         <v>883.5</v>
       </c>
-      <c r="AM6" s="4">
-        <f t="shared" ref="AM6:AM8" si="14">SUM(K6:N6)</f>
+      <c r="AQ6" s="4">
+        <f t="shared" ref="AQ6:AQ8" si="14">SUM(K6:N6)</f>
         <v>1101.5</v>
       </c>
-      <c r="AN6" s="4">
+      <c r="AR6" s="4">
         <f>SUM(O6:R6)</f>
         <v>1565.5</v>
       </c>
-      <c r="AO6" s="4">
+      <c r="AS6" s="4">
         <f>SUM(S6:V6)</f>
         <v>2109.8000000000002</v>
       </c>
-      <c r="AP6" s="4">
+      <c r="AT6" s="4">
         <f>SUM(W6:Z6)</f>
         <v>1910.9</v>
       </c>
-      <c r="AQ6" s="4">
+      <c r="AU6" s="4">
         <f>SUM(AA6:AD6)</f>
         <v>1691.6999999999998</v>
       </c>
-      <c r="AR6" s="4">
+      <c r="AV6" s="4">
         <f>SUM(AE6:AH6)</f>
-        <v>1786.0900000000001</v>
-      </c>
-      <c r="AS6" s="4">
-        <f>AR6*1.01</f>
-        <v>1803.9509000000003</v>
-      </c>
-      <c r="AT6" s="4">
-        <f t="shared" ref="AT6:BB6" si="15">AS6*1.01</f>
-        <v>1821.9904090000002</v>
-      </c>
-      <c r="AU6" s="4">
-        <f t="shared" si="15"/>
-        <v>1840.2103130900002</v>
-      </c>
-      <c r="AV6" s="4">
-        <f t="shared" si="15"/>
-        <v>1858.6124162209003</v>
+        <v>1793.6000000000001</v>
       </c>
       <c r="AW6" s="4">
-        <f t="shared" si="15"/>
-        <v>1877.1985403831093</v>
+        <f>AV6*1.01</f>
+        <v>1811.5360000000001</v>
       </c>
       <c r="AX6" s="4">
-        <f t="shared" si="15"/>
-        <v>1895.9705257869405</v>
+        <f t="shared" ref="AX6:BF6" si="15">AW6*1.01</f>
+        <v>1829.6513600000001</v>
       </c>
       <c r="AY6" s="4">
         <f t="shared" si="15"/>
-        <v>1914.9302310448099</v>
+        <v>1847.9478736000001</v>
       </c>
       <c r="AZ6" s="4">
         <f t="shared" si="15"/>
-        <v>1934.079533355258</v>
+        <v>1866.427352336</v>
       </c>
       <c r="BA6" s="4">
         <f t="shared" si="15"/>
-        <v>1953.4203286888107</v>
+        <v>1885.09162585936</v>
       </c>
       <c r="BB6" s="4">
         <f t="shared" si="15"/>
-        <v>1972.954531975699</v>
+        <v>1903.9425421179535</v>
+      </c>
+      <c r="BC6" s="4">
+        <f t="shared" si="15"/>
+        <v>1922.9819675391332</v>
+      </c>
+      <c r="BD6" s="4">
+        <f t="shared" si="15"/>
+        <v>1942.2117872145245</v>
+      </c>
+      <c r="BE6" s="4">
+        <f t="shared" si="15"/>
+        <v>1961.6339050866698</v>
+      </c>
+      <c r="BF6" s="4">
+        <f t="shared" si="15"/>
+        <v>1981.2502441375366</v>
       </c>
     </row>
-    <row r="7" spans="2:167" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:171" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>26</v>
       </c>
@@ -1896,84 +1982,87 @@
         <v>256.2</v>
       </c>
       <c r="AH7" s="4">
-        <f>AH3*0.16</f>
-        <v>269.10144000000003</v>
+        <v>249.3</v>
       </c>
       <c r="AI7" s="4"/>
-      <c r="AK7" s="4">
+      <c r="AJ7" s="4"/>
+      <c r="AK7" s="4"/>
+      <c r="AL7" s="4"/>
+      <c r="AM7" s="4"/>
+      <c r="AO7" s="4">
         <f>SUM(C7:F7)</f>
         <v>400.9</v>
       </c>
-      <c r="AL7" s="4">
+      <c r="AP7" s="4">
         <f>SUM(G7:J7)</f>
         <v>458.6</v>
       </c>
-      <c r="AM7" s="4">
+      <c r="AQ7" s="4">
         <f t="shared" si="14"/>
         <v>555.4</v>
       </c>
-      <c r="AN7" s="4">
+      <c r="AR7" s="4">
         <f>SUM(O7:R7)</f>
         <v>792.7</v>
       </c>
-      <c r="AO7" s="4">
+      <c r="AS7" s="4">
         <f>SUM(S7:V7)</f>
         <v>1118.8</v>
       </c>
-      <c r="AP7" s="4">
+      <c r="AT7" s="4">
         <f>SUM(W7:Z7)</f>
         <v>1122.0999999999999</v>
       </c>
-      <c r="AQ7" s="4">
+      <c r="AU7" s="4">
         <f>SUM(AA7:AD7)</f>
         <v>1063.5999999999999</v>
       </c>
-      <c r="AR7" s="4">
+      <c r="AV7" s="4">
         <f>SUM(AE7:AH7)</f>
-        <v>1041.2014399999998</v>
-      </c>
-      <c r="AS7" s="4">
-        <f>AS3*0.17</f>
-        <v>1072.6250096000003</v>
-      </c>
-      <c r="AT7" s="4">
-        <f>AT3*0.16</f>
-        <v>1070.1011860480003</v>
-      </c>
-      <c r="AU7" s="4">
-        <f>AU3*0.16</f>
-        <v>1123.6062453504003</v>
-      </c>
-      <c r="AV7" s="4">
-        <f t="shared" ref="AV7:BB7" si="16">AV3*0.16</f>
-        <v>1168.5504951644164</v>
+        <v>1021.3999999999999</v>
       </c>
       <c r="AW7" s="4">
-        <f t="shared" si="16"/>
-        <v>1203.6070100193488</v>
+        <f>AW3*0.17</f>
+        <v>1099.0884200000003</v>
       </c>
       <c r="AX7" s="4">
-        <f t="shared" si="16"/>
-        <v>1239.7152203199294</v>
+        <f>AX3*0.16</f>
+        <v>1096.5023296000004</v>
       </c>
       <c r="AY7" s="4">
-        <f t="shared" si="16"/>
-        <v>1276.9066769295273</v>
+        <f>AY3*0.16</f>
+        <v>1151.3274460800003</v>
       </c>
       <c r="AZ7" s="4">
-        <f t="shared" si="16"/>
-        <v>1315.2138772374133</v>
+        <f t="shared" ref="AZ7:BF7" si="16">AZ3*0.16</f>
+        <v>1197.3805439232005</v>
       </c>
       <c r="BA7" s="4">
         <f t="shared" si="16"/>
-        <v>1354.6702935545356</v>
+        <v>1233.3019602408965</v>
       </c>
       <c r="BB7" s="4">
         <f t="shared" si="16"/>
-        <v>1395.3104023611718</v>
+        <v>1270.3010190481234</v>
+      </c>
+      <c r="BC7" s="4">
+        <f t="shared" si="16"/>
+        <v>1308.4100496195672</v>
+      </c>
+      <c r="BD7" s="4">
+        <f t="shared" si="16"/>
+        <v>1347.6623511081541</v>
+      </c>
+      <c r="BE7" s="4">
+        <f t="shared" si="16"/>
+        <v>1388.0922216413987</v>
+      </c>
+      <c r="BF7" s="4">
+        <f t="shared" si="16"/>
+        <v>1429.7349882906408</v>
       </c>
     </row>
-    <row r="8" spans="2:167" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:171" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>27</v>
       </c>
@@ -2071,84 +2160,87 @@
         <v>251.3</v>
       </c>
       <c r="AH8" s="4">
-        <f>AD8*1.1</f>
-        <v>265.43</v>
+        <v>242.3</v>
       </c>
       <c r="AI8" s="4"/>
-      <c r="AK8" s="4">
+      <c r="AJ8" s="4"/>
+      <c r="AK8" s="4"/>
+      <c r="AL8" s="4"/>
+      <c r="AM8" s="4"/>
+      <c r="AO8" s="4">
         <f>SUM(C8:F8)</f>
         <v>477.09999999999997</v>
       </c>
-      <c r="AL8" s="4">
+      <c r="AP8" s="4">
         <f>SUM(G8:J8)</f>
         <v>580.9</v>
       </c>
-      <c r="AM8" s="4">
+      <c r="AQ8" s="4">
         <f t="shared" si="14"/>
         <v>529.1</v>
       </c>
-      <c r="AN8" s="4">
+      <c r="AR8" s="4">
         <f>SUM(O8:R8)</f>
         <v>710.6</v>
       </c>
-      <c r="AO8" s="4">
+      <c r="AS8" s="4">
         <f>SUM(S8:V8)</f>
         <v>953.3</v>
       </c>
-      <c r="AP8" s="4">
+      <c r="AT8" s="4">
         <f>SUM(W8:Z8)</f>
         <v>857.5</v>
       </c>
-      <c r="AQ8" s="4">
+      <c r="AU8" s="4">
         <f>SUM(AA8:AD8)</f>
         <v>919.09999999999991</v>
       </c>
-      <c r="AR8" s="4">
+      <c r="AV8" s="4">
         <f>SUM(AE8:AH8)</f>
-        <v>1002.23</v>
-      </c>
-      <c r="AS8" s="4">
-        <f>AR8*1.04</f>
-        <v>1042.3192000000001</v>
-      </c>
-      <c r="AT8" s="4">
-        <f>AS8*1.03</f>
-        <v>1073.5887760000003</v>
-      </c>
-      <c r="AU8" s="4">
-        <f t="shared" ref="AU8:AW8" si="17">AT8*1.02</f>
-        <v>1095.0605515200002</v>
-      </c>
-      <c r="AV8" s="4">
+        <v>979.09999999999991</v>
+      </c>
+      <c r="AW8" s="4">
+        <f>AV8*1.04</f>
+        <v>1018.2639999999999</v>
+      </c>
+      <c r="AX8" s="4">
+        <f>AW8*1.03</f>
+        <v>1048.8119199999999</v>
+      </c>
+      <c r="AY8" s="4">
+        <f t="shared" ref="AY8:BA8" si="17">AX8*1.02</f>
+        <v>1069.7881583999999</v>
+      </c>
+      <c r="AZ8" s="4">
         <f t="shared" si="17"/>
-        <v>1116.9617625504002</v>
-      </c>
-      <c r="AW8" s="4">
+        <v>1091.183921568</v>
+      </c>
+      <c r="BA8" s="4">
         <f t="shared" si="17"/>
-        <v>1139.3009978014081</v>
-      </c>
-      <c r="AX8" s="4">
-        <f>AW8*1.01</f>
-        <v>1150.6940077794222</v>
-      </c>
-      <c r="AY8" s="4">
-        <f t="shared" ref="AY8:BB8" si="18">AX8*1.01</f>
-        <v>1162.2009478572165</v>
-      </c>
-      <c r="AZ8" s="4">
+        <v>1113.0075999993601</v>
+      </c>
+      <c r="BB8" s="4">
+        <f>BA8*1.01</f>
+        <v>1124.1376759993536</v>
+      </c>
+      <c r="BC8" s="4">
+        <f t="shared" ref="BC8:BF8" si="18">BB8*1.01</f>
+        <v>1135.3790527593471</v>
+      </c>
+      <c r="BD8" s="4">
         <f t="shared" si="18"/>
-        <v>1173.8229573357887</v>
-      </c>
-      <c r="BA8" s="4">
+        <v>1146.7328432869406</v>
+      </c>
+      <c r="BE8" s="4">
         <f t="shared" si="18"/>
-        <v>1185.5611869091465</v>
-      </c>
-      <c r="BB8" s="4">
+        <v>1158.20017171981</v>
+      </c>
+      <c r="BF8" s="4">
         <f t="shared" si="18"/>
-        <v>1197.416798778238</v>
+        <v>1169.7821734370082</v>
       </c>
     </row>
-    <row r="9" spans="2:167" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:171" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
         <v>28</v>
       </c>
@@ -2278,83 +2370,87 @@
       </c>
       <c r="AH9" s="8">
         <f t="shared" si="27"/>
-        <v>-41.04756000000009</v>
+        <v>49.800000000000068</v>
       </c>
       <c r="AI9" s="8"/>
-      <c r="AK9" s="8">
-        <f>AK5-AK6-AK7-AK8</f>
+      <c r="AJ9" s="8"/>
+      <c r="AK9" s="8"/>
+      <c r="AL9" s="8"/>
+      <c r="AM9" s="8"/>
+      <c r="AO9" s="8">
+        <f>AO5-AO6-AO7-AO8</f>
         <v>-1268.5</v>
       </c>
-      <c r="AL9" s="8">
-        <f>AL5-AL6-AL7-AL8</f>
+      <c r="AP9" s="8">
+        <f>AP5-AP6-AP7-AP8</f>
         <v>-1103.3</v>
       </c>
-      <c r="AM9" s="8">
-        <f>AM5-AM6-AM7-AM8</f>
+      <c r="AQ9" s="8">
+        <f>AQ5-AQ6-AQ7-AQ8</f>
         <v>-861.80000000000018</v>
       </c>
-      <c r="AN9" s="8">
-        <f t="shared" ref="AN9:AW9" si="28">AN5-AN6-AN7-AN8</f>
+      <c r="AR9" s="8">
+        <f t="shared" ref="AR9:BA9" si="28">AR5-AR6-AR7-AR8</f>
         <v>-701.99999999999989</v>
       </c>
-      <c r="AO9" s="8">
+      <c r="AS9" s="8">
         <f t="shared" si="28"/>
         <v>-1395.4999999999995</v>
       </c>
-      <c r="AP9" s="8">
+      <c r="AT9" s="8">
         <f t="shared" si="28"/>
         <v>-1398.5</v>
       </c>
-      <c r="AQ9" s="8">
+      <c r="AU9" s="8">
         <f t="shared" si="28"/>
         <v>-787.19999999999982</v>
       </c>
-      <c r="AR9" s="8">
-        <f t="shared" si="28"/>
-        <v>-623.04755999999952</v>
-      </c>
-      <c r="AS9" s="8">
-        <f t="shared" si="28"/>
-        <v>-385.54213679999953</v>
-      </c>
-      <c r="AT9" s="8">
-        <f t="shared" si="28"/>
-        <v>-220.32621987999937</v>
-      </c>
-      <c r="AU9" s="8">
-        <f t="shared" si="28"/>
-        <v>-126.25525123399893</v>
-      </c>
       <c r="AV9" s="8">
         <f t="shared" si="28"/>
-        <v>-54.197940860258996</v>
+        <v>-532.19999999999936</v>
       </c>
       <c r="AW9" s="8">
         <f t="shared" si="28"/>
-        <v>-7.4820131361454969</v>
+        <v>-308.36185999999907</v>
       </c>
       <c r="AX9" s="8">
-        <f t="shared" ref="AX9:BB9" si="29">AX5-AX6-AX7-AX8</f>
-        <v>52.623517233460689</v>
+        <f t="shared" si="28"/>
+        <v>-68.676060399999415</v>
       </c>
       <c r="AY9" s="8">
+        <f t="shared" si="28"/>
+        <v>32.540548580000859</v>
+      </c>
+      <c r="AZ9" s="8">
+        <f t="shared" si="28"/>
+        <v>110.67636989920061</v>
+      </c>
+      <c r="BA9" s="8">
+        <f t="shared" si="28"/>
+        <v>162.23704725857692</v>
+      </c>
+      <c r="BB9" s="8">
+        <f t="shared" ref="BB9:BF9" si="29">BB5-BB6-BB7-BB8</f>
+        <v>227.06614319350842</v>
+      </c>
+      <c r="BC9" s="8">
         <f t="shared" si="29"/>
-        <v>115.13551342179221</v>
-      </c>
-      <c r="AZ9" s="8">
+        <v>294.43973185165987</v>
+      </c>
+      <c r="BD9" s="8">
         <f t="shared" si="29"/>
-        <v>180.13220240248688</v>
-      </c>
-      <c r="BA9" s="8">
+        <v>364.44014421317979</v>
+      </c>
+      <c r="BE9" s="8">
         <f t="shared" si="29"/>
-        <v>247.69421828838267</v>
-      </c>
-      <c r="BB9" s="8">
+        <v>437.15224114960392</v>
+      </c>
+      <c r="BF9" s="8">
         <f t="shared" si="29"/>
-        <v>317.90467514899319</v>
+        <v>512.66348992022199</v>
       </c>
     </row>
-    <row r="10" spans="2:167" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:171" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>34</v>
       </c>
@@ -2452,84 +2548,87 @@
         <v>-32.299999999999997</v>
       </c>
       <c r="AH10" s="4">
-        <f t="shared" ref="AG10:AH10" si="30">AD10*1.01</f>
-        <v>-38.986000000000004</v>
+        <v>-31.7</v>
       </c>
       <c r="AI10" s="4"/>
-      <c r="AK10" s="4">
+      <c r="AJ10" s="4"/>
+      <c r="AK10" s="4"/>
+      <c r="AL10" s="4"/>
+      <c r="AM10" s="4"/>
+      <c r="AO10" s="4">
         <f>SUM(C10:F10)</f>
         <v>-27.2</v>
       </c>
-      <c r="AL10" s="4">
+      <c r="AP10" s="4">
         <f>SUM(G10:J10)</f>
         <v>-35.700000000000003</v>
       </c>
-      <c r="AM10" s="4">
-        <f t="shared" ref="AM10:AM12" si="31">SUM(K10:N10)</f>
+      <c r="AQ10" s="4">
+        <f t="shared" ref="AQ10:AQ12" si="30">SUM(K10:N10)</f>
         <v>-18.169</v>
       </c>
-      <c r="AN10" s="4">
+      <c r="AR10" s="4">
         <f>SUM(O10:R10)</f>
         <v>-5.3000000000000007</v>
       </c>
-      <c r="AO10" s="4">
+      <c r="AS10" s="4">
         <f>SUM(S10:V10)</f>
         <v>-58.5</v>
       </c>
-      <c r="AP10" s="4">
+      <c r="AT10" s="4">
         <f>SUM(W10:Z10)</f>
         <v>-168.4</v>
       </c>
-      <c r="AQ10" s="4">
+      <c r="AU10" s="4">
         <f>SUM(AA10:AD10)</f>
         <v>-153.5</v>
       </c>
-      <c r="AR10" s="4">
+      <c r="AV10" s="4">
         <f>SUM(AE10:AH10)</f>
-        <v>-141.48599999999999</v>
-      </c>
-      <c r="AS10" s="4">
-        <f t="shared" ref="AS10:BB10" si="32">AR10*1.02</f>
-        <v>-144.31572</v>
-      </c>
-      <c r="AT10" s="4">
-        <f t="shared" si="32"/>
-        <v>-147.2020344</v>
-      </c>
-      <c r="AU10" s="4">
-        <f t="shared" si="32"/>
-        <v>-150.146075088</v>
-      </c>
-      <c r="AV10" s="4">
-        <f t="shared" si="32"/>
-        <v>-153.14899658976</v>
+        <v>-134.19999999999999</v>
       </c>
       <c r="AW10" s="4">
-        <f t="shared" si="32"/>
-        <v>-156.21197652155521</v>
+        <f t="shared" ref="AW10:BF10" si="31">AV10*1.02</f>
+        <v>-136.88399999999999</v>
       </c>
       <c r="AX10" s="4">
-        <f t="shared" si="32"/>
-        <v>-159.33621605198633</v>
+        <f t="shared" si="31"/>
+        <v>-139.62168</v>
       </c>
       <c r="AY10" s="4">
-        <f t="shared" si="32"/>
-        <v>-162.52294037302605</v>
+        <f t="shared" si="31"/>
+        <v>-142.41411360000001</v>
       </c>
       <c r="AZ10" s="4">
-        <f t="shared" si="32"/>
-        <v>-165.77339918048656</v>
+        <f t="shared" si="31"/>
+        <v>-145.26239587200001</v>
       </c>
       <c r="BA10" s="4">
-        <f t="shared" si="32"/>
-        <v>-169.08886716409629</v>
+        <f t="shared" si="31"/>
+        <v>-148.16764378944001</v>
       </c>
       <c r="BB10" s="4">
-        <f t="shared" si="32"/>
-        <v>-172.47064450737821</v>
+        <f t="shared" si="31"/>
+        <v>-151.13099666522882</v>
+      </c>
+      <c r="BC10" s="4">
+        <f t="shared" si="31"/>
+        <v>-154.1536165985334</v>
+      </c>
+      <c r="BD10" s="4">
+        <f t="shared" si="31"/>
+        <v>-157.23668893050407</v>
+      </c>
+      <c r="BE10" s="4">
+        <f t="shared" si="31"/>
+        <v>-160.38142270911416</v>
+      </c>
+      <c r="BF10" s="4">
+        <f t="shared" si="31"/>
+        <v>-163.58905116329646</v>
       </c>
     </row>
-    <row r="11" spans="2:167" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:171" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>35</v>
       </c>
@@ -2627,83 +2726,87 @@
         <v>34.5</v>
       </c>
       <c r="AH11" s="4">
-        <v>6</v>
+        <v>36.5</v>
       </c>
       <c r="AI11" s="4"/>
-      <c r="AK11" s="4">
+      <c r="AJ11" s="4"/>
+      <c r="AK11" s="4"/>
+      <c r="AL11" s="4"/>
+      <c r="AM11" s="4"/>
+      <c r="AO11" s="4">
         <f>SUM(C11:F11)</f>
         <v>3.8000000000000003</v>
       </c>
-      <c r="AL11" s="4">
+      <c r="AP11" s="4">
         <f>SUM(G11:J11)</f>
         <v>25.1</v>
       </c>
-      <c r="AM11" s="4">
-        <f t="shared" si="31"/>
+      <c r="AQ11" s="4">
+        <f t="shared" si="30"/>
         <v>97.2</v>
       </c>
-      <c r="AN11" s="4">
+      <c r="AR11" s="4">
         <f>SUM(O11:R11)</f>
         <v>17.7</v>
       </c>
-      <c r="AO11" s="4">
+      <c r="AS11" s="4">
         <f>SUM(S11:V11)</f>
         <v>21.400000000000002</v>
       </c>
-      <c r="AP11" s="4">
+      <c r="AT11" s="4">
         <f>SUM(W11:Z11)</f>
         <v>22</v>
       </c>
-      <c r="AQ11" s="4">
+      <c r="AU11" s="4">
         <f>SUM(AA11:AD11)</f>
         <v>21.5</v>
       </c>
-      <c r="AR11" s="4">
+      <c r="AV11" s="4">
         <f>SUM(AE11:AH11)</f>
-        <v>91.5</v>
-      </c>
-      <c r="AS11" s="4">
-        <f>AR11*1.03</f>
-        <v>94.245000000000005</v>
-      </c>
-      <c r="AT11" s="4">
-        <f t="shared" ref="AT11:BB11" si="33">AS11*1.03</f>
-        <v>97.07235</v>
-      </c>
-      <c r="AU11" s="4">
-        <f t="shared" si="33"/>
-        <v>99.984520500000002</v>
-      </c>
-      <c r="AV11" s="4">
-        <f t="shared" si="33"/>
-        <v>102.984056115</v>
+        <v>122</v>
       </c>
       <c r="AW11" s="4">
-        <f t="shared" si="33"/>
-        <v>106.07357779845</v>
+        <f>AV11*1.03</f>
+        <v>125.66</v>
       </c>
       <c r="AX11" s="4">
-        <f t="shared" si="33"/>
-        <v>109.2557851324035</v>
+        <f t="shared" ref="AX11:BF11" si="32">AW11*1.03</f>
+        <v>129.4298</v>
       </c>
       <c r="AY11" s="4">
-        <f t="shared" si="33"/>
-        <v>112.53345868637561</v>
+        <f t="shared" si="32"/>
+        <v>133.31269399999999</v>
       </c>
       <c r="AZ11" s="4">
-        <f t="shared" si="33"/>
-        <v>115.90946244696688</v>
+        <f t="shared" si="32"/>
+        <v>137.31207481999999</v>
       </c>
       <c r="BA11" s="4">
-        <f t="shared" si="33"/>
-        <v>119.38674632037589</v>
+        <f t="shared" si="32"/>
+        <v>141.4314370646</v>
       </c>
       <c r="BB11" s="4">
-        <f t="shared" si="33"/>
-        <v>122.96834870998717</v>
+        <f t="shared" si="32"/>
+        <v>145.67438017653799</v>
+      </c>
+      <c r="BC11" s="4">
+        <f t="shared" si="32"/>
+        <v>150.04461158183415</v>
+      </c>
+      <c r="BD11" s="4">
+        <f t="shared" si="32"/>
+        <v>154.54594992928918</v>
+      </c>
+      <c r="BE11" s="4">
+        <f t="shared" si="32"/>
+        <v>159.18232842716785</v>
+      </c>
+      <c r="BF11" s="4">
+        <f t="shared" si="32"/>
+        <v>163.95779827998288</v>
       </c>
     </row>
-    <row r="12" spans="2:167" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:171" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>29</v>
       </c>
@@ -2801,289 +2904,297 @@
         <v>-27.6</v>
       </c>
       <c r="AH12" s="4">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="AI12" s="4"/>
-      <c r="AK12" s="4">
+      <c r="AJ12" s="4"/>
+      <c r="AK12" s="4"/>
+      <c r="AL12" s="4"/>
+      <c r="AM12" s="4"/>
+      <c r="AO12" s="4">
         <f>SUM(C12:F12)</f>
         <v>8.1999999999999993</v>
       </c>
-      <c r="AL12" s="4">
+      <c r="AP12" s="4">
         <f>SUM(G12:J12)</f>
         <v>-58.9</v>
       </c>
-      <c r="AM12" s="4">
-        <f t="shared" si="31"/>
+      <c r="AQ12" s="4">
+        <f t="shared" si="30"/>
         <v>-15</v>
       </c>
-      <c r="AN12" s="4">
+      <c r="AR12" s="4">
         <f>SUM(O12:R12)</f>
         <v>-240.2</v>
       </c>
-      <c r="AO12" s="4">
+      <c r="AS12" s="4">
         <f>SUM(S12:V12)</f>
         <v>186.4</v>
       </c>
-      <c r="AP12" s="4">
+      <c r="AT12" s="4">
         <f>SUM(W12:Z12)</f>
         <v>42.4</v>
       </c>
-      <c r="AQ12" s="4">
+      <c r="AU12" s="4">
         <f>SUM(AA12:AD12)</f>
         <v>16.900000000000006</v>
       </c>
-      <c r="AR12" s="4">
+      <c r="AV12" s="4">
         <f>SUM(AE12:AH12)</f>
-        <v>-75.900000000000006</v>
-      </c>
-      <c r="AS12" s="4">
-        <f t="shared" ref="AS12:AX12" si="34">-AR15*0.02</f>
-        <v>10.26716963999999</v>
-      </c>
-      <c r="AT12" s="4">
-        <f t="shared" si="34"/>
-        <v>5.5318173830399919</v>
-      </c>
-      <c r="AU12" s="4">
-        <f t="shared" si="34"/>
-        <v>2.8116536458086294</v>
-      </c>
-      <c r="AV12" s="4">
-        <f t="shared" si="34"/>
-        <v>1.262485604668921</v>
+        <v>-69</v>
       </c>
       <c r="AW12" s="4">
-        <f t="shared" si="34"/>
-        <v>8.4727775842686648E-2</v>
+        <f t="shared" ref="AW12:BB12" si="33">-AV15*0.02</f>
+        <v>9.207999999999986</v>
       </c>
       <c r="AX12" s="4">
-        <f t="shared" si="34"/>
-        <v>-0.68114652497787254</v>
+        <f t="shared" si="33"/>
+        <v>4.9015337599999853</v>
       </c>
       <c r="AY12" s="4">
-        <f t="shared" ref="AY12" si="35">-AX15*0.02</f>
-        <v>-1.6541615148483422</v>
+        <f t="shared" si="33"/>
+        <v>1.0141714265599904</v>
       </c>
       <c r="AZ12" s="4">
-        <f t="shared" ref="AZ12" si="36">-AY15*0.02</f>
-        <v>-2.6684665059726553</v>
+        <f t="shared" si="33"/>
+        <v>-0.65004474805505408</v>
       </c>
       <c r="BA12" s="4">
-        <f t="shared" ref="BA12" si="37">-AZ15*0.02</f>
-        <v>-3.7226336902716675</v>
+        <f t="shared" si="33"/>
+        <v>-1.908427771188091</v>
       </c>
       <c r="BB12" s="4">
-        <f t="shared" ref="BB12" si="38">-BA15*0.02</f>
-        <v>-4.8179035651579962</v>
+        <f t="shared" si="33"/>
+        <v>-2.7341069080736804</v>
+      </c>
+      <c r="BC12" s="4">
+        <f t="shared" ref="BC12" si="34">-BB15*0.02</f>
+        <v>-3.7641098654443672</v>
+      </c>
+      <c r="BD12" s="4">
+        <f t="shared" ref="BD12" si="35">-BC15*0.02</f>
+        <v>-4.8370055477408567</v>
+      </c>
+      <c r="BE12" s="4">
+        <f t="shared" ref="BE12" si="36">-BD15*0.02</f>
+        <v>-5.9514862201941687</v>
+      </c>
+      <c r="BF12" s="4">
+        <f t="shared" ref="BF12" si="37">-BE15*0.02</f>
+        <v>-7.1088451464279112</v>
       </c>
     </row>
-    <row r="13" spans="2:167" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:171" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="8">
-        <f t="shared" ref="C13:L13" si="39">C9-C10-C11-C12</f>
+        <f t="shared" ref="C13:L13" si="38">C9-C10-C11-C12</f>
         <v>-384.1</v>
       </c>
       <c r="D13" s="8">
+        <f t="shared" si="38"/>
+        <v>-352.19999999999993</v>
+      </c>
+      <c r="E13" s="8">
+        <f t="shared" si="38"/>
+        <v>-325</v>
+      </c>
+      <c r="F13" s="8">
+        <f t="shared" si="38"/>
+        <v>-192.00000000000003</v>
+      </c>
+      <c r="G13" s="8">
+        <f t="shared" si="38"/>
+        <v>-310.30000000000007</v>
+      </c>
+      <c r="H13" s="8">
+        <f t="shared" si="38"/>
+        <v>-254.2</v>
+      </c>
+      <c r="I13" s="8">
+        <f t="shared" si="38"/>
+        <v>-229</v>
+      </c>
+      <c r="J13" s="8">
+        <f t="shared" si="38"/>
+        <v>-240.3</v>
+      </c>
+      <c r="K13" s="8">
+        <f t="shared" si="38"/>
+        <v>-305.19999999999993</v>
+      </c>
+      <c r="L13" s="8">
+        <f t="shared" si="38"/>
+        <v>-326.89999999999992</v>
+      </c>
+      <c r="M13" s="8">
+        <f t="shared" ref="M13:Q13" si="39">M9-M10-M11-M12</f>
+        <v>-198.89999999999998</v>
+      </c>
+      <c r="N13" s="8">
         <f t="shared" si="39"/>
-        <v>-352.19999999999993</v>
-      </c>
-      <c r="E13" s="8">
+        <v>-94.831000000000031</v>
+      </c>
+      <c r="O13" s="8">
         <f t="shared" si="39"/>
-        <v>-325</v>
-      </c>
-      <c r="F13" s="8">
+        <v>-285.39999999999998</v>
+      </c>
+      <c r="P13" s="8">
         <f t="shared" si="39"/>
-        <v>-192.00000000000003</v>
-      </c>
-      <c r="G13" s="8">
+        <v>-153.49999999999994</v>
+      </c>
+      <c r="Q13" s="8">
         <f t="shared" si="39"/>
-        <v>-310.30000000000007</v>
-      </c>
-      <c r="H13" s="8">
-        <f t="shared" si="39"/>
-        <v>-254.2</v>
-      </c>
-      <c r="I13" s="8">
-        <f t="shared" si="39"/>
-        <v>-229</v>
-      </c>
-      <c r="J13" s="8">
-        <f t="shared" si="39"/>
-        <v>-240.3</v>
-      </c>
-      <c r="K13" s="8">
-        <f t="shared" si="39"/>
-        <v>-305.19999999999993</v>
-      </c>
-      <c r="L13" s="8">
-        <f t="shared" si="39"/>
-        <v>-326.89999999999992</v>
-      </c>
-      <c r="M13" s="8">
-        <f t="shared" ref="M13:Q13" si="40">M9-M10-M11-M12</f>
-        <v>-198.89999999999998</v>
-      </c>
-      <c r="N13" s="8">
+        <v>-70.900000000000006</v>
+      </c>
+      <c r="R13" s="8">
+        <f t="shared" ref="R13:S13" si="40">R9-R10-R11-R12</f>
+        <v>35.600000000000065</v>
+      </c>
+      <c r="S13" s="8">
         <f t="shared" si="40"/>
-        <v>-94.831000000000031</v>
-      </c>
-      <c r="O13" s="8">
-        <f t="shared" si="40"/>
-        <v>-285.39999999999998</v>
-      </c>
-      <c r="P13" s="8">
-        <f t="shared" si="40"/>
-        <v>-153.49999999999994</v>
-      </c>
-      <c r="Q13" s="8">
-        <f t="shared" si="40"/>
-        <v>-70.900000000000006</v>
-      </c>
-      <c r="R13" s="8">
-        <f t="shared" ref="R13:S13" si="41">R9-R10-R11-R12</f>
-        <v>35.600000000000065</v>
-      </c>
-      <c r="S13" s="8">
+        <v>-351.19999999999993</v>
+      </c>
+      <c r="T13" s="8">
+        <f t="shared" ref="T13:U13" si="41">T9-T10-T11-T12</f>
+        <v>-415.09999999999985</v>
+      </c>
+      <c r="U13" s="8">
         <f t="shared" si="41"/>
-        <v>-351.19999999999993</v>
-      </c>
-      <c r="T13" s="8">
-        <f t="shared" ref="T13:U13" si="42">T9-T10-T11-T12</f>
-        <v>-415.09999999999985</v>
-      </c>
-      <c r="U13" s="8">
-        <f t="shared" si="42"/>
         <v>-494.2999999999999</v>
       </c>
       <c r="V13" s="8">
-        <f t="shared" ref="V13" si="43">V9-V10-V11-V12</f>
+        <f t="shared" ref="V13" si="42">V9-V10-V11-V12</f>
         <v>-284.19999999999993</v>
       </c>
       <c r="W13" s="8">
-        <f t="shared" ref="W13" si="44">W9-W10-W11-W12</f>
+        <f t="shared" ref="W13" si="43">W9-W10-W11-W12</f>
         <v>-321.8</v>
       </c>
       <c r="X13" s="8">
-        <f t="shared" ref="X13:Y13" si="45">X9-X10-X11-X12</f>
+        <f t="shared" ref="X13:Y13" si="44">X9-X10-X11-X12</f>
         <v>-365.29999999999995</v>
       </c>
       <c r="Y13" s="8">
-        <f t="shared" si="45"/>
+        <f t="shared" si="44"/>
         <v>-362.50000000000006</v>
       </c>
       <c r="Z13" s="8">
-        <f t="shared" ref="Z13" si="46">Z9-Z10-Z11-Z12</f>
+        <f t="shared" ref="Z13" si="45">Z9-Z10-Z11-Z12</f>
         <v>-244.90000000000006</v>
       </c>
       <c r="AA13" s="8">
-        <f t="shared" ref="AA13" si="47">AA9-AA10-AA11-AA12</f>
+        <f t="shared" ref="AA13" si="46">AA9-AA10-AA11-AA12</f>
         <v>-298.10000000000014</v>
       </c>
       <c r="AB13" s="8">
-        <f t="shared" ref="AB13:AH13" si="48">AB9-AB10-AB11-AB12</f>
+        <f t="shared" ref="AB13:AH13" si="47">AB9-AB10-AB11-AB12</f>
         <v>-243.30000000000004</v>
       </c>
       <c r="AC13" s="8">
+        <f t="shared" si="47"/>
+        <v>-145.10000000000002</v>
+      </c>
+      <c r="AD13" s="8">
+        <f t="shared" si="47"/>
+        <v>14.399999999999935</v>
+      </c>
+      <c r="AE13" s="8">
+        <f t="shared" si="47"/>
+        <v>-131.29999999999998</v>
+      </c>
+      <c r="AF13" s="8">
+        <f t="shared" si="47"/>
+        <v>-254.89999999999984</v>
+      </c>
+      <c r="AG13" s="8">
+        <f t="shared" si="47"/>
+        <v>-102.90000000000006</v>
+      </c>
+      <c r="AH13" s="8">
+        <f t="shared" si="47"/>
+        <v>38.100000000000072</v>
+      </c>
+      <c r="AI13" s="8"/>
+      <c r="AJ13" s="8"/>
+      <c r="AK13" s="8"/>
+      <c r="AL13" s="8"/>
+      <c r="AM13" s="8"/>
+      <c r="AO13" s="8">
+        <f>AO9-AO10-AO11-AO12</f>
+        <v>-1253.3</v>
+      </c>
+      <c r="AP13" s="8">
+        <f>AP9-AP10-AP11-AP12</f>
+        <v>-1033.7999999999997</v>
+      </c>
+      <c r="AQ13" s="8">
+        <f>AQ9-AQ10-AQ11-AQ12</f>
+        <v>-925.83100000000024</v>
+      </c>
+      <c r="AR13" s="8">
+        <f t="shared" ref="AR13:BA13" si="48">AR9-AR10-AR11-AR12</f>
+        <v>-474.2</v>
+      </c>
+      <c r="AS13" s="8">
         <f t="shared" si="48"/>
-        <v>-145.10000000000002</v>
-      </c>
-      <c r="AD13" s="8">
+        <v>-1544.7999999999997</v>
+      </c>
+      <c r="AT13" s="8">
         <f t="shared" si="48"/>
-        <v>14.399999999999935</v>
-      </c>
-      <c r="AE13" s="8">
+        <v>-1294.5</v>
+      </c>
+      <c r="AU13" s="8">
         <f t="shared" si="48"/>
-        <v>-131.29999999999998</v>
-      </c>
-      <c r="AF13" s="8">
+        <v>-672.0999999999998</v>
+      </c>
+      <c r="AV13" s="8">
         <f t="shared" si="48"/>
-        <v>-254.89999999999984</v>
-      </c>
-      <c r="AG13" s="8">
+        <v>-450.99999999999932</v>
+      </c>
+      <c r="AW13" s="8">
         <f t="shared" si="48"/>
-        <v>-102.90000000000006</v>
-      </c>
-      <c r="AH13" s="8">
+        <v>-306.34585999999905</v>
+      </c>
+      <c r="AX13" s="8">
         <f t="shared" si="48"/>
-        <v>-8.0615600000000853</v>
-      </c>
-      <c r="AI13" s="8"/>
-      <c r="AK13" s="8">
-        <f>AK9-AK10-AK11-AK12</f>
-        <v>-1253.3</v>
-      </c>
-      <c r="AL13" s="8">
-        <f>AL9-AL10-AL11-AL12</f>
-        <v>-1033.7999999999997</v>
-      </c>
-      <c r="AM13" s="8">
-        <f>AM9-AM10-AM11-AM12</f>
-        <v>-925.83100000000024</v>
-      </c>
-      <c r="AN13" s="8">
-        <f t="shared" ref="AN13:AW13" si="49">AN9-AN10-AN11-AN12</f>
-        <v>-474.2</v>
-      </c>
-      <c r="AO13" s="8">
+        <v>-63.385714159999402</v>
+      </c>
+      <c r="AY13" s="8">
+        <f t="shared" si="48"/>
+        <v>40.627796753440883</v>
+      </c>
+      <c r="AZ13" s="8">
+        <f t="shared" si="48"/>
+        <v>119.27673569925568</v>
+      </c>
+      <c r="BA13" s="8">
+        <f t="shared" si="48"/>
+        <v>170.88168175460504</v>
+      </c>
+      <c r="BB13" s="8">
+        <f t="shared" ref="BB13:BF13" si="49">BB9-BB10-BB11-BB12</f>
+        <v>235.25686659027295</v>
+      </c>
+      <c r="BC13" s="8">
         <f t="shared" si="49"/>
-        <v>-1544.7999999999997</v>
-      </c>
-      <c r="AP13" s="8">
+        <v>302.3128467338035</v>
+      </c>
+      <c r="BD13" s="8">
         <f t="shared" si="49"/>
-        <v>-1294.5</v>
-      </c>
-      <c r="AQ13" s="8">
+        <v>371.96788876213554</v>
+      </c>
+      <c r="BE13" s="8">
         <f t="shared" si="49"/>
-        <v>-672.0999999999998</v>
-      </c>
-      <c r="AR13" s="8">
+        <v>444.30282165174447</v>
+      </c>
+      <c r="BF13" s="8">
         <f t="shared" si="49"/>
-        <v>-497.16155999999955</v>
-      </c>
-      <c r="AS13" s="8">
-        <f t="shared" si="49"/>
-        <v>-345.73858643999949</v>
-      </c>
-      <c r="AT13" s="8">
-        <f t="shared" si="49"/>
-        <v>-175.72835286303936</v>
-      </c>
-      <c r="AU13" s="8">
-        <f t="shared" si="49"/>
-        <v>-78.905350291807565</v>
-      </c>
-      <c r="AV13" s="8">
-        <f t="shared" si="49"/>
-        <v>-5.295485990167915</v>
-      </c>
-      <c r="AW13" s="8">
-        <f t="shared" si="49"/>
-        <v>42.571657811117028</v>
-      </c>
-      <c r="AX13" s="8">
-        <f t="shared" ref="AX13:BB13" si="50">AX9-AX10-AX11-AX12</f>
-        <v>103.38509467802139</v>
-      </c>
-      <c r="AY13" s="8">
-        <f t="shared" si="50"/>
-        <v>166.77915662329096</v>
-      </c>
-      <c r="AZ13" s="8">
-        <f t="shared" si="50"/>
-        <v>232.66460564197919</v>
-      </c>
-      <c r="BA13" s="8">
-        <f t="shared" si="50"/>
-        <v>301.11897282237476</v>
-      </c>
-      <c r="BB13" s="8">
-        <f t="shared" si="50"/>
-        <v>372.22487451154228</v>
+        <v>519.40358794996359</v>
       </c>
     </row>
-    <row r="14" spans="2:167" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:171" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>31</v>
       </c>
@@ -3181,787 +3292,794 @@
         <v>0.5</v>
       </c>
       <c r="AH14" s="4">
-        <f t="shared" ref="AG14:AH14" si="51">AH13*0.05</f>
-        <v>-0.40307800000000427</v>
+        <v>-7.2</v>
       </c>
       <c r="AI14" s="4"/>
-      <c r="AK14" s="4">
+      <c r="AJ14" s="4"/>
+      <c r="AK14" s="4"/>
+      <c r="AL14" s="4"/>
+      <c r="AM14" s="4"/>
+      <c r="AO14" s="4">
         <f>SUM(C14:F14)</f>
         <v>3.3000000000000003</v>
       </c>
-      <c r="AL14" s="4">
+      <c r="AP14" s="4">
         <f>SUM(G14:J14)</f>
         <v>-0.2</v>
       </c>
-      <c r="AM14" s="4">
+      <c r="AQ14" s="4">
         <f>SUM(K14:N14)</f>
         <v>17.8</v>
       </c>
-      <c r="AN14" s="4">
+      <c r="AR14" s="4">
         <f>SUM(O14:R14)</f>
         <v>13.5</v>
       </c>
-      <c r="AO14" s="4">
+      <c r="AS14" s="4">
         <f>SUM(S14:V14)</f>
         <v>28.9</v>
       </c>
-      <c r="AP14" s="4">
+      <c r="AT14" s="4">
         <f>SUM(W14:Z14)</f>
         <v>28</v>
       </c>
-      <c r="AQ14" s="4">
+      <c r="AU14" s="4">
         <f>SUM(AA14:AD14)</f>
         <v>25.6</v>
       </c>
-      <c r="AR14" s="4">
+      <c r="AV14" s="4">
         <f>SUM(AE14:AH14)</f>
-        <v>16.196921999999997</v>
-      </c>
-      <c r="AS14" s="4">
-        <f>AS13*0.2</f>
-        <v>-69.147717287999896</v>
-      </c>
-      <c r="AT14" s="4">
-        <f t="shared" ref="AT14:AW14" si="52">AT13*0.2</f>
-        <v>-35.145670572607877</v>
-      </c>
-      <c r="AU14" s="4">
-        <f t="shared" si="52"/>
-        <v>-15.781070058361514</v>
-      </c>
-      <c r="AV14" s="4">
-        <f t="shared" si="52"/>
-        <v>-1.059097198033583</v>
+        <v>9.4000000000000021</v>
       </c>
       <c r="AW14" s="4">
-        <f t="shared" si="52"/>
-        <v>8.5143315622234059</v>
+        <f>AW13*0.2</f>
+        <v>-61.269171999999813</v>
       </c>
       <c r="AX14" s="4">
-        <f t="shared" ref="AX14:BB14" si="53">AX13*0.2</f>
-        <v>20.677018935604281</v>
+        <f t="shared" ref="AX14:BA14" si="50">AX13*0.2</f>
+        <v>-12.67714283199988</v>
       </c>
       <c r="AY14" s="4">
-        <f t="shared" si="53"/>
-        <v>33.35583132465819</v>
+        <f t="shared" si="50"/>
+        <v>8.1255593506881763</v>
       </c>
       <c r="AZ14" s="4">
-        <f t="shared" si="53"/>
-        <v>46.532921128395841</v>
+        <f t="shared" si="50"/>
+        <v>23.855347139851137</v>
       </c>
       <c r="BA14" s="4">
-        <f t="shared" si="53"/>
-        <v>60.223794564474957</v>
+        <f t="shared" si="50"/>
+        <v>34.176336350921012</v>
       </c>
       <c r="BB14" s="4">
-        <f t="shared" si="53"/>
-        <v>74.444974902308459</v>
+        <f t="shared" ref="BB14:BF14" si="51">BB13*0.2</f>
+        <v>47.051373318054594</v>
+      </c>
+      <c r="BC14" s="4">
+        <f t="shared" si="51"/>
+        <v>60.462569346760702</v>
+      </c>
+      <c r="BD14" s="4">
+        <f t="shared" si="51"/>
+        <v>74.393577752427106</v>
+      </c>
+      <c r="BE14" s="4">
+        <f t="shared" si="51"/>
+        <v>88.860564330348893</v>
+      </c>
+      <c r="BF14" s="4">
+        <f t="shared" si="51"/>
+        <v>103.88071758999273</v>
       </c>
     </row>
-    <row r="15" spans="2:167" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:171" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C15" s="8">
-        <f t="shared" ref="C15:L15" si="54">C13-C14</f>
+        <f t="shared" ref="C15:L15" si="52">C13-C14</f>
         <v>-385.70000000000005</v>
       </c>
       <c r="D15" s="8">
+        <f t="shared" si="52"/>
+        <v>-353.29999999999995</v>
+      </c>
+      <c r="E15" s="8">
+        <f t="shared" si="52"/>
+        <v>-325.2</v>
+      </c>
+      <c r="F15" s="8">
+        <f t="shared" si="52"/>
+        <v>-192.40000000000003</v>
+      </c>
+      <c r="G15" s="8">
+        <f t="shared" si="52"/>
+        <v>-310.00000000000006</v>
+      </c>
+      <c r="H15" s="8">
+        <f t="shared" si="52"/>
+        <v>-255.29999999999998</v>
+      </c>
+      <c r="I15" s="8">
+        <f t="shared" si="52"/>
+        <v>-227.7</v>
+      </c>
+      <c r="J15" s="8">
+        <f t="shared" si="52"/>
+        <v>-240.60000000000002</v>
+      </c>
+      <c r="K15" s="8">
+        <f t="shared" si="52"/>
+        <v>-305.89999999999992</v>
+      </c>
+      <c r="L15" s="8">
+        <f t="shared" si="52"/>
+        <v>-325.89999999999992</v>
+      </c>
+      <c r="M15" s="8">
+        <f t="shared" ref="M15:N15" si="53">M13-M14</f>
+        <v>-198.89999999999998</v>
+      </c>
+      <c r="N15" s="8">
+        <f t="shared" si="53"/>
+        <v>-112.93100000000004</v>
+      </c>
+      <c r="O15" s="8">
+        <f t="shared" ref="O15:Q15" si="54">O13-O14</f>
+        <v>-286.79999999999995</v>
+      </c>
+      <c r="P15" s="8">
         <f t="shared" si="54"/>
-        <v>-353.29999999999995</v>
-      </c>
-      <c r="E15" s="8">
+        <v>-151.59999999999994</v>
+      </c>
+      <c r="Q15" s="8">
         <f t="shared" si="54"/>
-        <v>-325.2</v>
-      </c>
-      <c r="F15" s="8">
-        <f t="shared" si="54"/>
-        <v>-192.40000000000003</v>
-      </c>
-      <c r="G15" s="8">
-        <f t="shared" si="54"/>
-        <v>-310.00000000000006</v>
-      </c>
-      <c r="H15" s="8">
-        <f t="shared" si="54"/>
-        <v>-255.29999999999998</v>
-      </c>
-      <c r="I15" s="8">
-        <f t="shared" si="54"/>
-        <v>-227.7</v>
-      </c>
-      <c r="J15" s="8">
-        <f t="shared" si="54"/>
-        <v>-240.60000000000002</v>
-      </c>
-      <c r="K15" s="8">
-        <f t="shared" si="54"/>
-        <v>-305.89999999999992</v>
-      </c>
-      <c r="L15" s="8">
-        <f t="shared" si="54"/>
-        <v>-325.89999999999992</v>
-      </c>
-      <c r="M15" s="8">
-        <f t="shared" ref="M15:N15" si="55">M13-M14</f>
-        <v>-198.89999999999998</v>
-      </c>
-      <c r="N15" s="8">
+        <v>-71.900000000000006</v>
+      </c>
+      <c r="R15" s="8">
+        <f t="shared" ref="R15:S15" si="55">R13-R14</f>
+        <v>22.600000000000065</v>
+      </c>
+      <c r="S15" s="8">
         <f t="shared" si="55"/>
-        <v>-112.93100000000004</v>
-      </c>
-      <c r="O15" s="8">
-        <f t="shared" ref="O15:Q15" si="56">O13-O14</f>
-        <v>-286.79999999999995</v>
-      </c>
-      <c r="P15" s="8">
+        <v>-359.69999999999993</v>
+      </c>
+      <c r="T15" s="8">
+        <f t="shared" ref="T15:U15" si="56">T13-T14</f>
+        <v>-422.09999999999985</v>
+      </c>
+      <c r="U15" s="8">
         <f t="shared" si="56"/>
-        <v>-151.59999999999994</v>
-      </c>
-      <c r="Q15" s="8">
-        <f t="shared" si="56"/>
-        <v>-71.900000000000006</v>
-      </c>
-      <c r="R15" s="8">
-        <f t="shared" ref="R15:S15" si="57">R13-R14</f>
-        <v>22.600000000000065</v>
-      </c>
-      <c r="S15" s="8">
-        <f t="shared" si="57"/>
-        <v>-359.69999999999993</v>
-      </c>
-      <c r="T15" s="8">
-        <f t="shared" ref="T15:U15" si="58">T13-T14</f>
-        <v>-422.09999999999985</v>
-      </c>
-      <c r="U15" s="8">
-        <f t="shared" si="58"/>
         <v>-503.49999999999989</v>
       </c>
       <c r="V15" s="8">
-        <f t="shared" ref="V15" si="59">V13-V14</f>
+        <f t="shared" ref="V15" si="57">V13-V14</f>
         <v>-288.39999999999992</v>
       </c>
       <c r="W15" s="8">
-        <f t="shared" ref="W15" si="60">W13-W14</f>
+        <f t="shared" ref="W15" si="58">W13-W14</f>
         <v>-328.6</v>
       </c>
       <c r="X15" s="8">
-        <f t="shared" ref="X15:Y15" si="61">X13-X14</f>
+        <f t="shared" ref="X15:Y15" si="59">X13-X14</f>
         <v>-377.4</v>
       </c>
       <c r="Y15" s="8">
-        <f t="shared" si="61"/>
+        <f t="shared" si="59"/>
         <v>-368.30000000000007</v>
       </c>
       <c r="Z15" s="8">
-        <f t="shared" ref="Z15" si="62">Z13-Z14</f>
+        <f t="shared" ref="Z15" si="60">Z13-Z14</f>
         <v>-248.20000000000007</v>
       </c>
       <c r="AA15" s="8">
-        <f t="shared" ref="AA15" si="63">AA13-AA14</f>
+        <f t="shared" ref="AA15" si="61">AA13-AA14</f>
         <v>-305.00000000000011</v>
       </c>
       <c r="AB15" s="8">
-        <f t="shared" ref="AB15:AD15" si="64">AB13-AB14</f>
+        <f t="shared" ref="AB15:AD15" si="62">AB13-AB14</f>
         <v>-248.50000000000003</v>
       </c>
       <c r="AC15" s="8">
+        <f t="shared" si="62"/>
+        <v>-153.40000000000003</v>
+      </c>
+      <c r="AD15" s="8">
+        <f t="shared" si="62"/>
+        <v>9.1999999999999353</v>
+      </c>
+      <c r="AE15" s="8">
+        <f t="shared" ref="AE15:AH15" si="63">AE13-AE14</f>
+        <v>-139.69999999999999</v>
+      </c>
+      <c r="AF15" s="8">
+        <f t="shared" si="63"/>
+        <v>-262.59999999999985</v>
+      </c>
+      <c r="AG15" s="8">
+        <f t="shared" si="63"/>
+        <v>-103.40000000000006</v>
+      </c>
+      <c r="AH15" s="8">
+        <f t="shared" si="63"/>
+        <v>45.300000000000075</v>
+      </c>
+      <c r="AI15" s="8"/>
+      <c r="AJ15" s="8"/>
+      <c r="AK15" s="8"/>
+      <c r="AL15" s="8"/>
+      <c r="AM15" s="8"/>
+      <c r="AO15" s="8">
+        <f>AO13-AO14</f>
+        <v>-1256.5999999999999</v>
+      </c>
+      <c r="AP15" s="8">
+        <f>AP13-AP14</f>
+        <v>-1033.5999999999997</v>
+      </c>
+      <c r="AQ15" s="8">
+        <f>AQ13-AQ14</f>
+        <v>-943.6310000000002</v>
+      </c>
+      <c r="AR15" s="8">
+        <f t="shared" ref="AR15:BA15" si="64">AR13-AR14</f>
+        <v>-487.7</v>
+      </c>
+      <c r="AS15" s="8">
         <f t="shared" si="64"/>
-        <v>-153.40000000000003</v>
-      </c>
-      <c r="AD15" s="8">
+        <v>-1573.6999999999998</v>
+      </c>
+      <c r="AT15" s="8">
         <f t="shared" si="64"/>
-        <v>9.1999999999999353</v>
-      </c>
-      <c r="AE15" s="8">
-        <f t="shared" ref="AE15:AH15" si="65">AE13-AE14</f>
-        <v>-139.69999999999999</v>
-      </c>
-      <c r="AF15" s="8">
+        <v>-1322.5</v>
+      </c>
+      <c r="AU15" s="8">
+        <f t="shared" si="64"/>
+        <v>-697.69999999999982</v>
+      </c>
+      <c r="AV15" s="8">
+        <f t="shared" si="64"/>
+        <v>-460.3999999999993</v>
+      </c>
+      <c r="AW15" s="8">
+        <f t="shared" si="64"/>
+        <v>-245.07668799999925</v>
+      </c>
+      <c r="AX15" s="8">
+        <f t="shared" si="64"/>
+        <v>-50.708571327999522</v>
+      </c>
+      <c r="AY15" s="8">
+        <f t="shared" si="64"/>
+        <v>32.502237402752705</v>
+      </c>
+      <c r="AZ15" s="8">
+        <f t="shared" si="64"/>
+        <v>95.421388559404548</v>
+      </c>
+      <c r="BA15" s="8">
+        <f t="shared" si="64"/>
+        <v>136.70534540368402</v>
+      </c>
+      <c r="BB15" s="8">
+        <f t="shared" ref="BB15:BF15" si="65">BB13-BB14</f>
+        <v>188.20549327221835</v>
+      </c>
+      <c r="BC15" s="8">
         <f t="shared" si="65"/>
-        <v>-262.59999999999985</v>
-      </c>
-      <c r="AG15" s="8">
+        <v>241.85027738704281</v>
+      </c>
+      <c r="BD15" s="8">
         <f t="shared" si="65"/>
-        <v>-103.40000000000006</v>
-      </c>
-      <c r="AH15" s="8">
+        <v>297.57431100970842</v>
+      </c>
+      <c r="BE15" s="8">
         <f t="shared" si="65"/>
-        <v>-7.6584820000000811</v>
-      </c>
-      <c r="AI15" s="8"/>
-      <c r="AK15" s="8">
-        <f>AK13-AK14</f>
-        <v>-1256.5999999999999</v>
-      </c>
-      <c r="AL15" s="8">
-        <f>AL13-AL14</f>
-        <v>-1033.5999999999997</v>
-      </c>
-      <c r="AM15" s="8">
-        <f>AM13-AM14</f>
-        <v>-943.6310000000002</v>
-      </c>
-      <c r="AN15" s="8">
-        <f t="shared" ref="AN15:AW15" si="66">AN13-AN14</f>
-        <v>-487.7</v>
-      </c>
-      <c r="AO15" s="8">
+        <v>355.44225732139557</v>
+      </c>
+      <c r="BF15" s="8">
+        <f t="shared" si="65"/>
+        <v>415.52287035997085</v>
+      </c>
+      <c r="BG15" s="1">
+        <f t="shared" ref="BG15:CL15" si="66">BF15*(1+$BI$21)</f>
+        <v>411.36764165637112</v>
+      </c>
+      <c r="BH15" s="1">
         <f t="shared" si="66"/>
-        <v>-1573.6999999999998</v>
-      </c>
-      <c r="AP15" s="8">
+        <v>407.25396523980743</v>
+      </c>
+      <c r="BI15" s="1">
         <f t="shared" si="66"/>
-        <v>-1322.5</v>
-      </c>
-      <c r="AQ15" s="8">
+        <v>403.18142558740936</v>
+      </c>
+      <c r="BJ15" s="1">
         <f t="shared" si="66"/>
-        <v>-697.69999999999982</v>
-      </c>
-      <c r="AR15" s="8">
+        <v>399.14961133153525</v>
+      </c>
+      <c r="BK15" s="1">
         <f t="shared" si="66"/>
-        <v>-513.35848199999953</v>
-      </c>
-      <c r="AS15" s="8">
+        <v>395.1581152182199</v>
+      </c>
+      <c r="BL15" s="1">
         <f t="shared" si="66"/>
-        <v>-276.59086915199958</v>
-      </c>
-      <c r="AT15" s="8">
+        <v>391.2065340660377</v>
+      </c>
+      <c r="BM15" s="1">
         <f t="shared" si="66"/>
-        <v>-140.58268229043148</v>
-      </c>
-      <c r="AU15" s="8">
+        <v>387.29446872537733</v>
+      </c>
+      <c r="BN15" s="1">
         <f t="shared" si="66"/>
-        <v>-63.124280233446051</v>
-      </c>
-      <c r="AV15" s="8">
+        <v>383.42152403812355</v>
+      </c>
+      <c r="BO15" s="1">
         <f t="shared" si="66"/>
-        <v>-4.2363887921343322</v>
-      </c>
-      <c r="AW15" s="8">
+        <v>379.58730879774231</v>
+      </c>
+      <c r="BP15" s="1">
         <f t="shared" si="66"/>
-        <v>34.057326248893624</v>
-      </c>
-      <c r="AX15" s="8">
-        <f t="shared" ref="AX15:BB15" si="67">AX13-AX14</f>
-        <v>82.708075742417108</v>
-      </c>
-      <c r="AY15" s="8">
+        <v>375.79143570976487</v>
+      </c>
+      <c r="BQ15" s="1">
+        <f t="shared" si="66"/>
+        <v>372.03352135266721</v>
+      </c>
+      <c r="BR15" s="1">
+        <f t="shared" si="66"/>
+        <v>368.31318613914056</v>
+      </c>
+      <c r="BS15" s="1">
+        <f t="shared" si="66"/>
+        <v>364.63005427774914</v>
+      </c>
+      <c r="BT15" s="1">
+        <f t="shared" si="66"/>
+        <v>360.98375373497163</v>
+      </c>
+      <c r="BU15" s="1">
+        <f t="shared" si="66"/>
+        <v>357.3739161976219</v>
+      </c>
+      <c r="BV15" s="1">
+        <f t="shared" si="66"/>
+        <v>353.80017703564567</v>
+      </c>
+      <c r="BW15" s="1">
+        <f t="shared" si="66"/>
+        <v>350.26217526528922</v>
+      </c>
+      <c r="BX15" s="1">
+        <f t="shared" si="66"/>
+        <v>346.75955351263633</v>
+      </c>
+      <c r="BY15" s="1">
+        <f t="shared" si="66"/>
+        <v>343.29195797750998</v>
+      </c>
+      <c r="BZ15" s="1">
+        <f t="shared" si="66"/>
+        <v>339.85903839773488</v>
+      </c>
+      <c r="CA15" s="1">
+        <f t="shared" si="66"/>
+        <v>336.46044801375751</v>
+      </c>
+      <c r="CB15" s="1">
+        <f t="shared" si="66"/>
+        <v>333.09584353361993</v>
+      </c>
+      <c r="CC15" s="1">
+        <f t="shared" si="66"/>
+        <v>329.76488509828374</v>
+      </c>
+      <c r="CD15" s="1">
+        <f t="shared" si="66"/>
+        <v>326.46723624730089</v>
+      </c>
+      <c r="CE15" s="1">
+        <f t="shared" si="66"/>
+        <v>323.2025638848279</v>
+      </c>
+      <c r="CF15" s="1">
+        <f t="shared" si="66"/>
+        <v>319.97053824597964</v>
+      </c>
+      <c r="CG15" s="1">
+        <f t="shared" si="66"/>
+        <v>316.77083286351984</v>
+      </c>
+      <c r="CH15" s="1">
+        <f t="shared" si="66"/>
+        <v>313.60312453488461</v>
+      </c>
+      <c r="CI15" s="1">
+        <f t="shared" si="66"/>
+        <v>310.46709328953574</v>
+      </c>
+      <c r="CJ15" s="1">
+        <f t="shared" si="66"/>
+        <v>307.36242235664037</v>
+      </c>
+      <c r="CK15" s="1">
+        <f t="shared" si="66"/>
+        <v>304.28879813307395</v>
+      </c>
+      <c r="CL15" s="1">
+        <f t="shared" si="66"/>
+        <v>301.2459101517432</v>
+      </c>
+      <c r="CM15" s="1">
+        <f t="shared" ref="CM15:DR15" si="67">CL15*(1+$BI$21)</f>
+        <v>298.23345105022577</v>
+      </c>
+      <c r="CN15" s="1">
         <f t="shared" si="67"/>
-        <v>133.42332529863276</v>
-      </c>
-      <c r="AZ15" s="8">
+        <v>295.25111653972351</v>
+      </c>
+      <c r="CO15" s="1">
         <f t="shared" si="67"/>
-        <v>186.13168451358337</v>
-      </c>
-      <c r="BA15" s="8">
+        <v>292.29860537432626</v>
+      </c>
+      <c r="CP15" s="1">
         <f t="shared" si="67"/>
-        <v>240.8951782578998</v>
-      </c>
-      <c r="BB15" s="8">
+        <v>289.37561932058298</v>
+      </c>
+      <c r="CQ15" s="1">
         <f t="shared" si="67"/>
-        <v>297.77989960923384</v>
-      </c>
-      <c r="BC15" s="1">
-        <f t="shared" ref="BC15:CH15" si="68">BB15*(1+$BE$21)</f>
-        <v>294.80210061314148</v>
-      </c>
-      <c r="BD15" s="1">
+        <v>286.48186312737715</v>
+      </c>
+      <c r="CR15" s="1">
+        <f t="shared" si="67"/>
+        <v>283.6170444961034</v>
+      </c>
+      <c r="CS15" s="1">
+        <f t="shared" si="67"/>
+        <v>280.78087405114235</v>
+      </c>
+      <c r="CT15" s="1">
+        <f t="shared" si="67"/>
+        <v>277.97306531063094</v>
+      </c>
+      <c r="CU15" s="1">
+        <f t="shared" si="67"/>
+        <v>275.19333465752464</v>
+      </c>
+      <c r="CV15" s="1">
+        <f t="shared" si="67"/>
+        <v>272.4414013109494</v>
+      </c>
+      <c r="CW15" s="1">
+        <f t="shared" si="67"/>
+        <v>269.71698729783992</v>
+      </c>
+      <c r="CX15" s="1">
+        <f t="shared" si="67"/>
+        <v>267.01981742486151</v>
+      </c>
+      <c r="CY15" s="1">
+        <f t="shared" si="67"/>
+        <v>264.34961925061288</v>
+      </c>
+      <c r="CZ15" s="1">
+        <f t="shared" si="67"/>
+        <v>261.70612305810675</v>
+      </c>
+      <c r="DA15" s="1">
+        <f t="shared" si="67"/>
+        <v>259.08906182752571</v>
+      </c>
+      <c r="DB15" s="1">
+        <f t="shared" si="67"/>
+        <v>256.49817120925047</v>
+      </c>
+      <c r="DC15" s="1">
+        <f t="shared" si="67"/>
+        <v>253.93318949715797</v>
+      </c>
+      <c r="DD15" s="1">
+        <f t="shared" si="67"/>
+        <v>251.39385760218639</v>
+      </c>
+      <c r="DE15" s="1">
+        <f t="shared" si="67"/>
+        <v>248.87991902616452</v>
+      </c>
+      <c r="DF15" s="1">
+        <f t="shared" si="67"/>
+        <v>246.39111983590286</v>
+      </c>
+      <c r="DG15" s="1">
+        <f t="shared" si="67"/>
+        <v>243.92720863754383</v>
+      </c>
+      <c r="DH15" s="1">
+        <f t="shared" si="67"/>
+        <v>241.48793655116839</v>
+      </c>
+      <c r="DI15" s="1">
+        <f t="shared" si="67"/>
+        <v>239.07305718565669</v>
+      </c>
+      <c r="DJ15" s="1">
+        <f t="shared" si="67"/>
+        <v>236.68232661380011</v>
+      </c>
+      <c r="DK15" s="1">
+        <f t="shared" si="67"/>
+        <v>234.31550334766212</v>
+      </c>
+      <c r="DL15" s="1">
+        <f t="shared" si="67"/>
+        <v>231.9723483141855</v>
+      </c>
+      <c r="DM15" s="1">
+        <f t="shared" si="67"/>
+        <v>229.65262483104362</v>
+      </c>
+      <c r="DN15" s="1">
+        <f t="shared" si="67"/>
+        <v>227.35609858273318</v>
+      </c>
+      <c r="DO15" s="1">
+        <f t="shared" si="67"/>
+        <v>225.08253759690584</v>
+      </c>
+      <c r="DP15" s="1">
+        <f t="shared" si="67"/>
+        <v>222.83171222093677</v>
+      </c>
+      <c r="DQ15" s="1">
+        <f t="shared" si="67"/>
+        <v>220.60339509872739</v>
+      </c>
+      <c r="DR15" s="1">
+        <f t="shared" si="67"/>
+        <v>218.39736114774013</v>
+      </c>
+      <c r="DS15" s="1">
+        <f t="shared" ref="DS15:EX15" si="68">DR15*(1+$BI$21)</f>
+        <v>216.21338753626273</v>
+      </c>
+      <c r="DT15" s="1">
         <f t="shared" si="68"/>
-        <v>291.85407960701008</v>
-      </c>
-      <c r="BE15" s="1">
+        <v>214.0512536609001</v>
+      </c>
+      <c r="DU15" s="1">
         <f t="shared" si="68"/>
-        <v>288.93553881093999</v>
-      </c>
-      <c r="BF15" s="1">
+        <v>211.91074112429109</v>
+      </c>
+      <c r="DV15" s="1">
         <f t="shared" si="68"/>
-        <v>286.04618342283061</v>
-      </c>
-      <c r="BG15" s="1">
+        <v>209.79163371304818</v>
+      </c>
+      <c r="DW15" s="1">
         <f t="shared" si="68"/>
-        <v>283.18572158860229</v>
-      </c>
-      <c r="BH15" s="1">
+        <v>207.69371737591771</v>
+      </c>
+      <c r="DX15" s="1">
         <f t="shared" si="68"/>
-        <v>280.35386437271626</v>
-      </c>
-      <c r="BI15" s="1">
+        <v>205.61678020215854</v>
+      </c>
+      <c r="DY15" s="1">
         <f t="shared" si="68"/>
-        <v>277.55032572898909</v>
-      </c>
-      <c r="BJ15" s="1">
+        <v>203.56061240013696</v>
+      </c>
+      <c r="DZ15" s="1">
         <f t="shared" si="68"/>
-        <v>274.77482247169922</v>
-      </c>
-      <c r="BK15" s="1">
+        <v>201.5250062761356</v>
+      </c>
+      <c r="EA15" s="1">
         <f t="shared" si="68"/>
-        <v>272.02707424698224</v>
-      </c>
-      <c r="BL15" s="1">
+        <v>199.50975621337423</v>
+      </c>
+      <c r="EB15" s="1">
         <f t="shared" si="68"/>
-        <v>269.3068035045124</v>
-      </c>
-      <c r="BM15" s="1">
+        <v>197.5146586512405</v>
+      </c>
+      <c r="EC15" s="1">
         <f t="shared" si="68"/>
-        <v>266.61373546946726</v>
-      </c>
-      <c r="BN15" s="1">
+        <v>195.53951206472809</v>
+      </c>
+      <c r="ED15" s="1">
         <f t="shared" si="68"/>
-        <v>263.94759811477257</v>
-      </c>
-      <c r="BO15" s="1">
+        <v>193.58411694408079</v>
+      </c>
+      <c r="EE15" s="1">
         <f t="shared" si="68"/>
-        <v>261.30812213362486</v>
-      </c>
-      <c r="BP15" s="1">
+        <v>191.64827577463998</v>
+      </c>
+      <c r="EF15" s="1">
         <f t="shared" si="68"/>
-        <v>258.69504091228862</v>
-      </c>
-      <c r="BQ15" s="1">
+        <v>189.73179301689359</v>
+      </c>
+      <c r="EG15" s="1">
         <f t="shared" si="68"/>
-        <v>256.10809050316573</v>
-      </c>
-      <c r="BR15" s="1">
+        <v>187.83447508672467</v>
+      </c>
+      <c r="EH15" s="1">
         <f t="shared" si="68"/>
-        <v>253.54700959813405</v>
-      </c>
-      <c r="BS15" s="1">
+        <v>185.95613033585741</v>
+      </c>
+      <c r="EI15" s="1">
         <f t="shared" si="68"/>
-        <v>251.01153950215271</v>
-      </c>
-      <c r="BT15" s="1">
+        <v>184.09656903249882</v>
+      </c>
+      <c r="EJ15" s="1">
         <f t="shared" si="68"/>
-        <v>248.50142410713119</v>
-      </c>
-      <c r="BU15" s="1">
+        <v>182.25560334217383</v>
+      </c>
+      <c r="EK15" s="1">
         <f t="shared" si="68"/>
-        <v>246.01640986605986</v>
-      </c>
-      <c r="BV15" s="1">
+        <v>180.43304730875209</v>
+      </c>
+      <c r="EL15" s="1">
         <f t="shared" si="68"/>
-        <v>243.55624576739925</v>
-      </c>
-      <c r="BW15" s="1">
+        <v>178.62871683566456</v>
+      </c>
+      <c r="EM15" s="1">
         <f t="shared" si="68"/>
-        <v>241.12068330972525</v>
-      </c>
-      <c r="BX15" s="1">
+        <v>176.84242966730793</v>
+      </c>
+      <c r="EN15" s="1">
         <f t="shared" si="68"/>
-        <v>238.709476476628</v>
-      </c>
-      <c r="BY15" s="1">
+        <v>175.07400537063484</v>
+      </c>
+      <c r="EO15" s="1">
         <f t="shared" si="68"/>
-        <v>236.32238171186171</v>
-      </c>
-      <c r="BZ15" s="1">
+        <v>173.32326531692848</v>
+      </c>
+      <c r="EP15" s="1">
         <f t="shared" si="68"/>
-        <v>233.9591578947431</v>
-      </c>
-      <c r="CA15" s="1">
+        <v>171.59003266375919</v>
+      </c>
+      <c r="EQ15" s="1">
         <f t="shared" si="68"/>
-        <v>231.61956631579568</v>
-      </c>
-      <c r="CB15" s="1">
+        <v>169.87413233712161</v>
+      </c>
+      <c r="ER15" s="1">
         <f t="shared" si="68"/>
-        <v>229.30337065263771</v>
-      </c>
-      <c r="CC15" s="1">
+        <v>168.17539101375039</v>
+      </c>
+      <c r="ES15" s="1">
         <f t="shared" si="68"/>
-        <v>227.01033694611132</v>
-      </c>
-      <c r="CD15" s="1">
+        <v>166.49363710361288</v>
+      </c>
+      <c r="ET15" s="1">
         <f t="shared" si="68"/>
-        <v>224.74023357665021</v>
-      </c>
-      <c r="CE15" s="1">
+        <v>164.82870073257675</v>
+      </c>
+      <c r="EU15" s="1">
         <f t="shared" si="68"/>
-        <v>222.4928312408837</v>
-      </c>
-      <c r="CF15" s="1">
+        <v>163.18041372525099</v>
+      </c>
+      <c r="EV15" s="1">
         <f t="shared" si="68"/>
-        <v>220.26790292847485</v>
-      </c>
-      <c r="CG15" s="1">
+        <v>161.54860958799847</v>
+      </c>
+      <c r="EW15" s="1">
         <f t="shared" si="68"/>
-        <v>218.0652238991901</v>
-      </c>
-      <c r="CH15" s="1">
+        <v>159.93312349211848</v>
+      </c>
+      <c r="EX15" s="1">
         <f t="shared" si="68"/>
-        <v>215.88457166019819</v>
-      </c>
-      <c r="CI15" s="1">
-        <f t="shared" ref="CI15:DN15" si="69">CH15*(1+$BE$21)</f>
-        <v>213.72572594359622</v>
-      </c>
-      <c r="CJ15" s="1">
+        <v>158.3337922571973</v>
+      </c>
+      <c r="EY15" s="1">
+        <f t="shared" ref="EY15:FO15" si="69">EX15*(1+$BI$21)</f>
+        <v>156.75045433462532</v>
+      </c>
+      <c r="EZ15" s="1">
         <f t="shared" si="69"/>
-        <v>211.58846868416026</v>
-      </c>
-      <c r="CK15" s="1">
+        <v>155.18294979127907</v>
+      </c>
+      <c r="FA15" s="1">
         <f t="shared" si="69"/>
-        <v>209.47258399731865</v>
-      </c>
-      <c r="CL15" s="1">
+        <v>153.63112029336628</v>
+      </c>
+      <c r="FB15" s="1">
         <f t="shared" si="69"/>
-        <v>207.37785815734546</v>
-      </c>
-      <c r="CM15" s="1">
+        <v>152.09480909043262</v>
+      </c>
+      <c r="FC15" s="1">
         <f t="shared" si="69"/>
-        <v>205.30407957577199</v>
-      </c>
-      <c r="CN15" s="1">
+        <v>150.57386099952828</v>
+      </c>
+      <c r="FD15" s="1">
         <f t="shared" si="69"/>
-        <v>203.25103878001428</v>
-      </c>
-      <c r="CO15" s="1">
+        <v>149.06812238953299</v>
+      </c>
+      <c r="FE15" s="1">
         <f t="shared" si="69"/>
-        <v>201.21852839221413</v>
-      </c>
-      <c r="CP15" s="1">
+        <v>147.57744116563765</v>
+      </c>
+      <c r="FF15" s="1">
         <f t="shared" si="69"/>
-        <v>199.20634310829197</v>
-      </c>
-      <c r="CQ15" s="1">
+        <v>146.10166675398128</v>
+      </c>
+      <c r="FG15" s="1">
         <f t="shared" si="69"/>
-        <v>197.21427967720905</v>
-      </c>
-      <c r="CR15" s="1">
+        <v>144.64065008644147</v>
+      </c>
+      <c r="FH15" s="1">
         <f t="shared" si="69"/>
-        <v>195.24213688043696</v>
-      </c>
-      <c r="CS15" s="1">
+        <v>143.19424358557706</v>
+      </c>
+      <c r="FI15" s="1">
         <f t="shared" si="69"/>
-        <v>193.28971551163258</v>
-      </c>
-      <c r="CT15" s="1">
+        <v>141.76230114972128</v>
+      </c>
+      <c r="FJ15" s="1">
         <f t="shared" si="69"/>
-        <v>191.35681835651624</v>
-      </c>
-      <c r="CU15" s="1">
+        <v>140.34467813822405</v>
+      </c>
+      <c r="FK15" s="1">
         <f t="shared" si="69"/>
-        <v>189.44325017295108</v>
-      </c>
-      <c r="CV15" s="1">
+        <v>138.94123135684183</v>
+      </c>
+      <c r="FL15" s="1">
         <f t="shared" si="69"/>
-        <v>187.54881767122157</v>
-      </c>
-      <c r="CW15" s="1">
+        <v>137.55181904327341</v>
+      </c>
+      <c r="FM15" s="1">
         <f t="shared" si="69"/>
-        <v>185.67332949450935</v>
-      </c>
-      <c r="CX15" s="1">
+        <v>136.17630085284068</v>
+      </c>
+      <c r="FN15" s="1">
         <f t="shared" si="69"/>
-        <v>183.81659619956426</v>
-      </c>
-      <c r="CY15" s="1">
+        <v>134.81453784431227</v>
+      </c>
+      <c r="FO15" s="1">
         <f t="shared" si="69"/>
-        <v>181.9784302375686</v>
-      </c>
-      <c r="CZ15" s="1">
-        <f t="shared" si="69"/>
-        <v>180.15864593519291</v>
-      </c>
-      <c r="DA15" s="1">
-        <f t="shared" si="69"/>
-        <v>178.35705947584097</v>
-      </c>
-      <c r="DB15" s="1">
-        <f t="shared" si="69"/>
-        <v>176.57348888108257</v>
-      </c>
-      <c r="DC15" s="1">
-        <f t="shared" si="69"/>
-        <v>174.80775399227173</v>
-      </c>
-      <c r="DD15" s="1">
-        <f t="shared" si="69"/>
-        <v>173.05967645234901</v>
-      </c>
-      <c r="DE15" s="1">
-        <f t="shared" si="69"/>
-        <v>171.32907968782553</v>
-      </c>
-      <c r="DF15" s="1">
-        <f t="shared" si="69"/>
-        <v>169.61578889094727</v>
-      </c>
-      <c r="DG15" s="1">
-        <f t="shared" si="69"/>
-        <v>167.91963100203779</v>
-      </c>
-      <c r="DH15" s="1">
-        <f t="shared" si="69"/>
-        <v>166.2404346920174</v>
-      </c>
-      <c r="DI15" s="1">
-        <f t="shared" si="69"/>
-        <v>164.57803034509723</v>
-      </c>
-      <c r="DJ15" s="1">
-        <f t="shared" si="69"/>
-        <v>162.93225004164626</v>
-      </c>
-      <c r="DK15" s="1">
-        <f t="shared" si="69"/>
-        <v>161.30292754122979</v>
-      </c>
-      <c r="DL15" s="1">
-        <f t="shared" si="69"/>
-        <v>159.6898982658175</v>
-      </c>
-      <c r="DM15" s="1">
-        <f t="shared" si="69"/>
-        <v>158.09299928315932</v>
-      </c>
-      <c r="DN15" s="1">
-        <f t="shared" si="69"/>
-        <v>156.51206929032773</v>
-      </c>
-      <c r="DO15" s="1">
-        <f t="shared" ref="DO15:ET15" si="70">DN15*(1+$BE$21)</f>
-        <v>154.94694859742444</v>
-      </c>
-      <c r="DP15" s="1">
-        <f t="shared" si="70"/>
-        <v>153.3974791114502</v>
-      </c>
-      <c r="DQ15" s="1">
-        <f t="shared" si="70"/>
-        <v>151.86350432033569</v>
-      </c>
-      <c r="DR15" s="1">
-        <f t="shared" si="70"/>
-        <v>150.34486927713235</v>
-      </c>
-      <c r="DS15" s="1">
-        <f t="shared" si="70"/>
-        <v>148.84142058436103</v>
-      </c>
-      <c r="DT15" s="1">
-        <f t="shared" si="70"/>
-        <v>147.35300637851742</v>
-      </c>
-      <c r="DU15" s="1">
-        <f t="shared" si="70"/>
-        <v>145.87947631473224</v>
-      </c>
-      <c r="DV15" s="1">
-        <f t="shared" si="70"/>
-        <v>144.42068155158492</v>
-      </c>
-      <c r="DW15" s="1">
-        <f t="shared" si="70"/>
-        <v>142.97647473606906</v>
-      </c>
-      <c r="DX15" s="1">
-        <f t="shared" si="70"/>
-        <v>141.54670998870839</v>
-      </c>
-      <c r="DY15" s="1">
-        <f t="shared" si="70"/>
-        <v>140.1312428888213</v>
-      </c>
-      <c r="DZ15" s="1">
-        <f t="shared" si="70"/>
-        <v>138.72993045993309</v>
-      </c>
-      <c r="EA15" s="1">
-        <f t="shared" si="70"/>
-        <v>137.34263115533375</v>
-      </c>
-      <c r="EB15" s="1">
-        <f t="shared" si="70"/>
-        <v>135.9692048437804</v>
-      </c>
-      <c r="EC15" s="1">
-        <f t="shared" si="70"/>
-        <v>134.6095127953426</v>
-      </c>
-      <c r="ED15" s="1">
-        <f t="shared" si="70"/>
-        <v>133.26341766738918</v>
-      </c>
-      <c r="EE15" s="1">
-        <f t="shared" si="70"/>
-        <v>131.93078349071527</v>
-      </c>
-      <c r="EF15" s="1">
-        <f t="shared" si="70"/>
-        <v>130.61147565580811</v>
-      </c>
-      <c r="EG15" s="1">
-        <f t="shared" si="70"/>
-        <v>129.30536089925002</v>
-      </c>
-      <c r="EH15" s="1">
-        <f t="shared" si="70"/>
-        <v>128.01230729025752</v>
-      </c>
-      <c r="EI15" s="1">
-        <f t="shared" si="70"/>
-        <v>126.73218421735494</v>
-      </c>
-      <c r="EJ15" s="1">
-        <f t="shared" si="70"/>
-        <v>125.4648623751814</v>
-      </c>
-      <c r="EK15" s="1">
-        <f t="shared" si="70"/>
-        <v>124.21021375142958</v>
-      </c>
-      <c r="EL15" s="1">
-        <f t="shared" si="70"/>
-        <v>122.96811161391528</v>
-      </c>
-      <c r="EM15" s="1">
-        <f t="shared" si="70"/>
-        <v>121.73843049777614</v>
-      </c>
-      <c r="EN15" s="1">
-        <f t="shared" si="70"/>
-        <v>120.52104619279838</v>
-      </c>
-      <c r="EO15" s="1">
-        <f t="shared" si="70"/>
-        <v>119.31583573087039</v>
-      </c>
-      <c r="EP15" s="1">
-        <f t="shared" si="70"/>
-        <v>118.12267737356169</v>
-      </c>
-      <c r="EQ15" s="1">
-        <f t="shared" si="70"/>
-        <v>116.94145059982607</v>
-      </c>
-      <c r="ER15" s="1">
-        <f t="shared" si="70"/>
-        <v>115.77203609382781</v>
-      </c>
-      <c r="ES15" s="1">
-        <f t="shared" si="70"/>
-        <v>114.61431573288952</v>
-      </c>
-      <c r="ET15" s="1">
-        <f t="shared" si="70"/>
-        <v>113.46817257556063</v>
-      </c>
-      <c r="EU15" s="1">
-        <f t="shared" ref="EU15:FK15" si="71">ET15*(1+$BE$21)</f>
-        <v>112.33349084980502</v>
-      </c>
-      <c r="EV15" s="1">
-        <f t="shared" si="71"/>
-        <v>111.21015594130697</v>
-      </c>
-      <c r="EW15" s="1">
-        <f t="shared" si="71"/>
-        <v>110.09805438189389</v>
-      </c>
-      <c r="EX15" s="1">
-        <f t="shared" si="71"/>
-        <v>108.99707383807495</v>
-      </c>
-      <c r="EY15" s="1">
-        <f t="shared" si="71"/>
-        <v>107.9071030996942</v>
-      </c>
-      <c r="EZ15" s="1">
-        <f t="shared" si="71"/>
-        <v>106.82803206869725</v>
-      </c>
-      <c r="FA15" s="1">
-        <f t="shared" si="71"/>
-        <v>105.75975174801029</v>
-      </c>
-      <c r="FB15" s="1">
-        <f t="shared" si="71"/>
-        <v>104.70215423053018</v>
-      </c>
-      <c r="FC15" s="1">
-        <f t="shared" si="71"/>
-        <v>103.65513268822488</v>
-      </c>
-      <c r="FD15" s="1">
-        <f t="shared" si="71"/>
-        <v>102.61858136134263</v>
-      </c>
-      <c r="FE15" s="1">
-        <f t="shared" si="71"/>
-        <v>101.59239554772921</v>
-      </c>
-      <c r="FF15" s="1">
-        <f t="shared" si="71"/>
-        <v>100.57647159225192</v>
-      </c>
-      <c r="FG15" s="1">
-        <f t="shared" si="71"/>
-        <v>99.570706876329396</v>
-      </c>
-      <c r="FH15" s="1">
-        <f t="shared" si="71"/>
-        <v>98.574999807566101</v>
-      </c>
-      <c r="FI15" s="1">
-        <f t="shared" si="71"/>
-        <v>97.58924980949044</v>
-      </c>
-      <c r="FJ15" s="1">
-        <f t="shared" si="71"/>
-        <v>96.613357311395532</v>
-      </c>
-      <c r="FK15" s="1">
-        <f t="shared" si="71"/>
-        <v>95.647223738281582</v>
+        <v>133.46639246586915</v>
       </c>
     </row>
-    <row r="16" spans="2:167" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:171" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>2</v>
       </c>
       <c r="C16" s="4">
-        <f t="shared" ref="C16:L16" si="72">1211.1+23.7+234.4</f>
+        <f t="shared" ref="C16:L16" si="70">1211.1+23.7+234.4</f>
         <v>1469.2</v>
       </c>
       <c r="D16" s="4">
-        <f t="shared" si="72"/>
+        <f t="shared" si="70"/>
         <v>1469.2</v>
       </c>
       <c r="E16" s="4">
-        <f t="shared" si="72"/>
+        <f t="shared" si="70"/>
         <v>1469.2</v>
       </c>
       <c r="F16" s="4">
-        <f t="shared" si="72"/>
+        <f t="shared" si="70"/>
         <v>1469.2</v>
       </c>
       <c r="G16" s="4">
-        <f t="shared" si="72"/>
+        <f t="shared" si="70"/>
         <v>1469.2</v>
       </c>
       <c r="H16" s="4">
-        <f t="shared" si="72"/>
+        <f t="shared" si="70"/>
         <v>1469.2</v>
       </c>
       <c r="I16" s="4">
-        <f t="shared" si="72"/>
+        <f t="shared" si="70"/>
         <v>1469.2</v>
       </c>
       <c r="J16" s="4">
-        <f t="shared" si="72"/>
+        <f t="shared" si="70"/>
         <v>1469.2</v>
       </c>
       <c r="K16" s="4">
-        <f t="shared" si="72"/>
+        <f t="shared" si="70"/>
         <v>1469.2</v>
       </c>
       <c r="L16" s="4">
-        <f t="shared" si="72"/>
+        <f t="shared" si="70"/>
         <v>1469.2</v>
       </c>
       <c r="M16" s="4">
-        <f t="shared" ref="M16" si="73">1211.1+23.7+234.4</f>
+        <f t="shared" ref="M16" si="71">1211.1+23.7+234.4</f>
         <v>1469.2</v>
       </c>
       <c r="N16" s="4">
@@ -4031,287 +4149,295 @@
         <v>1696.5</v>
       </c>
       <c r="AH16" s="4">
-        <f>1696.5</f>
-        <v>1696.5</v>
+        <f>1710.5</f>
+        <v>1710.5</v>
       </c>
       <c r="AI16" s="4"/>
-      <c r="AK16" s="4">
+      <c r="AJ16" s="4"/>
+      <c r="AK16" s="4"/>
+      <c r="AL16" s="4"/>
+      <c r="AM16" s="4"/>
+      <c r="AO16" s="4">
         <f>1211.1+23.7+234.4</f>
         <v>1469.2</v>
       </c>
-      <c r="AL16" s="4">
+      <c r="AP16" s="4">
         <f>1211.1+23.7+234.4</f>
         <v>1469.2</v>
       </c>
-      <c r="AM16" s="4">
+      <c r="AQ16" s="4">
         <f>1211.1+23.7+234.4</f>
         <v>1469.2</v>
       </c>
-      <c r="AN16" s="4">
+      <c r="AR16" s="4">
         <v>1508</v>
       </c>
-      <c r="AO16" s="4">
+      <c r="AS16" s="4">
         <v>1508</v>
       </c>
-      <c r="AP16" s="4">
+      <c r="AT16" s="4">
         <v>1508</v>
       </c>
-      <c r="AQ16" s="4">
-        <f t="shared" ref="AQ16" si="74">1442.2+22.5+231.6</f>
+      <c r="AU16" s="4">
+        <f t="shared" ref="AU16" si="72">1442.2+22.5+231.6</f>
         <v>1696.3</v>
       </c>
-      <c r="AR16" s="4">
-        <f>1696.5</f>
+      <c r="AV16" s="4">
+        <f t="shared" ref="AV16:BF16" si="73">1696.5</f>
         <v>1696.5</v>
       </c>
-      <c r="AS16" s="4">
-        <f>1696.5</f>
+      <c r="AW16" s="4">
+        <f t="shared" si="73"/>
         <v>1696.5</v>
       </c>
-      <c r="AT16" s="4">
-        <f>1696.5</f>
+      <c r="AX16" s="4">
+        <f t="shared" si="73"/>
         <v>1696.5</v>
       </c>
-      <c r="AU16" s="4">
-        <f>1696.5</f>
+      <c r="AY16" s="4">
+        <f t="shared" si="73"/>
         <v>1696.5</v>
       </c>
-      <c r="AV16" s="4">
-        <f>1696.5</f>
+      <c r="AZ16" s="4">
+        <f t="shared" si="73"/>
         <v>1696.5</v>
       </c>
-      <c r="AW16" s="4">
-        <f>1696.5</f>
+      <c r="BA16" s="4">
+        <f t="shared" si="73"/>
         <v>1696.5</v>
       </c>
-      <c r="AX16" s="4">
-        <f>1696.5</f>
+      <c r="BB16" s="4">
+        <f t="shared" si="73"/>
         <v>1696.5</v>
       </c>
-      <c r="AY16" s="4">
-        <f>1696.5</f>
+      <c r="BC16" s="4">
+        <f t="shared" si="73"/>
         <v>1696.5</v>
       </c>
-      <c r="AZ16" s="4">
-        <f>1696.5</f>
+      <c r="BD16" s="4">
+        <f t="shared" si="73"/>
         <v>1696.5</v>
       </c>
-      <c r="BA16" s="4">
-        <f>1696.5</f>
+      <c r="BE16" s="4">
+        <f t="shared" si="73"/>
         <v>1696.5</v>
       </c>
-      <c r="BB16" s="4">
-        <f>1696.5</f>
+      <c r="BF16" s="4">
+        <f t="shared" si="73"/>
         <v>1696.5</v>
       </c>
     </row>
-    <row r="17" spans="2:57" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:61" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B17" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C17" s="7">
-        <f t="shared" ref="C17:L17" si="75">C15/C16</f>
+        <f t="shared" ref="C17:L17" si="74">C15/C16</f>
         <v>-0.26252382248842909</v>
       </c>
       <c r="D17" s="7">
+        <f t="shared" si="74"/>
+        <v>-0.24047100462836915</v>
+      </c>
+      <c r="E17" s="7">
+        <f t="shared" si="74"/>
+        <v>-0.22134494963245302</v>
+      </c>
+      <c r="F17" s="7">
+        <f t="shared" si="74"/>
+        <v>-0.13095562210726927</v>
+      </c>
+      <c r="G17" s="7">
+        <f t="shared" si="74"/>
+        <v>-0.21099918322896818</v>
+      </c>
+      <c r="H17" s="7">
+        <f t="shared" si="74"/>
+        <v>-0.17376803702695343</v>
+      </c>
+      <c r="I17" s="7">
+        <f t="shared" si="74"/>
+        <v>-0.15498230329430981</v>
+      </c>
+      <c r="J17" s="7">
+        <f t="shared" si="74"/>
+        <v>-0.16376259188674108</v>
+      </c>
+      <c r="K17" s="7">
+        <f t="shared" si="74"/>
+        <v>-0.20820854887013335</v>
+      </c>
+      <c r="L17" s="7">
+        <f t="shared" si="74"/>
+        <v>-0.22182139940103451</v>
+      </c>
+      <c r="M17" s="7">
+        <f t="shared" ref="M17:N17" si="75">M15/M16</f>
+        <v>-0.13537979852981213</v>
+      </c>
+      <c r="N17" s="7">
         <f t="shared" si="75"/>
-        <v>-0.24047100462836915</v>
-      </c>
-      <c r="E17" s="7">
-        <f t="shared" si="75"/>
-        <v>-0.22134494963245302</v>
-      </c>
-      <c r="F17" s="7">
-        <f t="shared" si="75"/>
-        <v>-0.13095562210726927</v>
-      </c>
-      <c r="G17" s="7">
-        <f t="shared" si="75"/>
-        <v>-0.21099918322896818</v>
-      </c>
-      <c r="H17" s="7">
-        <f t="shared" si="75"/>
-        <v>-0.17376803702695343</v>
-      </c>
-      <c r="I17" s="7">
-        <f t="shared" si="75"/>
-        <v>-0.15498230329430981</v>
-      </c>
-      <c r="J17" s="7">
-        <f t="shared" si="75"/>
-        <v>-0.16376259188674108</v>
-      </c>
-      <c r="K17" s="7">
-        <f t="shared" si="75"/>
-        <v>-0.20820854887013335</v>
-      </c>
-      <c r="L17" s="7">
-        <f t="shared" si="75"/>
-        <v>-0.22182139940103451</v>
-      </c>
-      <c r="M17" s="7">
-        <f t="shared" ref="M17:N17" si="76">M15/M16</f>
-        <v>-0.13537979852981213</v>
-      </c>
-      <c r="N17" s="7">
+        <v>-7.4887931034482783E-2</v>
+      </c>
+      <c r="O17" s="7">
+        <f t="shared" ref="O17:Q17" si="76">O15/O16</f>
+        <v>-0.19018567639257292</v>
+      </c>
+      <c r="P17" s="7">
         <f t="shared" si="76"/>
-        <v>-7.4887931034482783E-2</v>
-      </c>
-      <c r="O17" s="7">
-        <f t="shared" ref="O17:Q17" si="77">O15/O16</f>
-        <v>-0.19018567639257292</v>
-      </c>
-      <c r="P17" s="7">
+        <v>-0.1005305039787798</v>
+      </c>
+      <c r="Q17" s="7">
+        <f t="shared" si="76"/>
+        <v>-4.7679045092838199E-2</v>
+      </c>
+      <c r="R17" s="7">
+        <f t="shared" ref="R17:S17" si="77">R15/R16</f>
+        <v>1.4986737400530548E-2</v>
+      </c>
+      <c r="S17" s="7">
         <f t="shared" si="77"/>
-        <v>-0.1005305039787798</v>
-      </c>
-      <c r="Q17" s="7">
-        <f t="shared" si="77"/>
-        <v>-4.7679045092838199E-2</v>
-      </c>
-      <c r="R17" s="7">
-        <f t="shared" ref="R17:S17" si="78">R15/R16</f>
-        <v>1.4986737400530548E-2</v>
-      </c>
-      <c r="S17" s="7">
+        <v>-0.23852785145888589</v>
+      </c>
+      <c r="T17" s="7">
+        <f t="shared" ref="T17:U17" si="78">T15/T16</f>
+        <v>-0.27990716180371344</v>
+      </c>
+      <c r="U17" s="7">
         <f t="shared" si="78"/>
-        <v>-0.23852785145888589</v>
-      </c>
-      <c r="T17" s="7">
-        <f t="shared" ref="T17:U17" si="79">T15/T16</f>
-        <v>-0.27990716180371344</v>
-      </c>
-      <c r="U17" s="7">
-        <f t="shared" si="79"/>
         <v>-0.33388594164456226</v>
       </c>
       <c r="V17" s="7">
-        <f t="shared" ref="V17" si="80">V15/V16</f>
+        <f t="shared" ref="V17" si="79">V15/V16</f>
         <v>-0.19124668435013256</v>
       </c>
       <c r="W17" s="7">
-        <f t="shared" ref="W17" si="81">W15/W16</f>
+        <f t="shared" ref="W17" si="80">W15/W16</f>
         <v>-0.21790450928381963</v>
       </c>
       <c r="X17" s="7">
-        <f t="shared" ref="X17:Y17" si="82">X15/X16</f>
+        <f t="shared" ref="X17:Y17" si="81">X15/X16</f>
         <v>-0.25026525198938993</v>
       </c>
       <c r="Y17" s="7">
-        <f t="shared" si="82"/>
+        <f t="shared" si="81"/>
         <v>-0.24423076923076928</v>
       </c>
       <c r="Z17" s="7">
-        <f t="shared" ref="Z17" si="83">Z15/Z16</f>
+        <f t="shared" ref="Z17" si="82">Z15/Z16</f>
         <v>-0.16458885941644566</v>
       </c>
       <c r="AA17" s="7">
-        <f t="shared" ref="AA17" si="84">AA15/AA16</f>
+        <f t="shared" ref="AA17" si="83">AA15/AA16</f>
         <v>-0.2022546419098144</v>
       </c>
       <c r="AB17" s="7">
-        <f t="shared" ref="AB17:AD17" si="85">AB15/AB16</f>
+        <f t="shared" ref="AB17:AD17" si="84">AB15/AB16</f>
         <v>-0.14975292274316021</v>
       </c>
       <c r="AC17" s="7">
+        <f t="shared" si="84"/>
+        <v>-9.1461960410207516E-2</v>
+      </c>
+      <c r="AD17" s="7">
+        <f t="shared" si="84"/>
+        <v>5.4235689441725727E-3</v>
+      </c>
+      <c r="AE17" s="7">
+        <f t="shared" ref="AE17:AH17" si="85">AE15/AE16</f>
+        <v>-8.23557153805341E-2</v>
+      </c>
+      <c r="AF17" s="7">
         <f t="shared" si="85"/>
-        <v>-9.1461960410207516E-2</v>
-      </c>
-      <c r="AD17" s="7">
+        <v>-0.15678547973013304</v>
+      </c>
+      <c r="AG17" s="7">
         <f t="shared" si="85"/>
-        <v>5.4235689441725727E-3</v>
-      </c>
-      <c r="AE17" s="7">
-        <f t="shared" ref="AE17:AH17" si="86">AE15/AE16</f>
-        <v>-8.23557153805341E-2</v>
-      </c>
-      <c r="AF17" s="7">
+        <v>-6.0949012673150643E-2</v>
+      </c>
+      <c r="AH17" s="7">
+        <f t="shared" si="85"/>
+        <v>2.648348436129791E-2</v>
+      </c>
+      <c r="AI17" s="7"/>
+      <c r="AJ17" s="7"/>
+      <c r="AK17" s="7"/>
+      <c r="AL17" s="7"/>
+      <c r="AM17" s="7"/>
+      <c r="AO17" s="7">
+        <f>AO15/AO16</f>
+        <v>-0.85529539885652051</v>
+      </c>
+      <c r="AP17" s="7">
+        <f>AP15/AP16</f>
+        <v>-0.70351211543697223</v>
+      </c>
+      <c r="AQ17" s="7">
+        <f>AQ15/AQ16</f>
+        <v>-0.64227538796624029</v>
+      </c>
+      <c r="AR17" s="7">
+        <f t="shared" ref="AR17:BA17" si="86">AR15/AR16</f>
+        <v>-0.32340848806366046</v>
+      </c>
+      <c r="AS17" s="7">
         <f t="shared" si="86"/>
-        <v>-0.15678547973013304</v>
-      </c>
-      <c r="AG17" s="7">
+        <v>-1.0435676392572943</v>
+      </c>
+      <c r="AT17" s="7">
         <f t="shared" si="86"/>
-        <v>-6.0949012673150643E-2</v>
-      </c>
-      <c r="AH17" s="7">
+        <v>-0.87698938992042441</v>
+      </c>
+      <c r="AU17" s="7">
         <f t="shared" si="86"/>
-        <v>-4.5142835249042624E-3</v>
-      </c>
-      <c r="AI17" s="7"/>
-      <c r="AK17" s="7">
-        <f>AK15/AK16</f>
-        <v>-0.85529539885652051</v>
-      </c>
-      <c r="AL17" s="7">
-        <f>AL15/AL16</f>
-        <v>-0.70351211543697223</v>
-      </c>
-      <c r="AM17" s="7">
-        <f>AM15/AM16</f>
-        <v>-0.64227538796624029</v>
-      </c>
-      <c r="AN17" s="7">
-        <f t="shared" ref="AN17:AW17" si="87">AN15/AN16</f>
-        <v>-0.32340848806366046</v>
-      </c>
-      <c r="AO17" s="7">
+        <v>-0.4113069622118728</v>
+      </c>
+      <c r="AV17" s="7">
+        <f t="shared" si="86"/>
+        <v>-0.27138225758915374</v>
+      </c>
+      <c r="AW17" s="7">
+        <f t="shared" si="86"/>
+        <v>-0.14446017565576141</v>
+      </c>
+      <c r="AX17" s="7">
+        <f t="shared" si="86"/>
+        <v>-2.9890109830827894E-2</v>
+      </c>
+      <c r="AY17" s="7">
+        <f t="shared" si="86"/>
+        <v>1.9158406957119189E-2</v>
+      </c>
+      <c r="AZ17" s="7">
+        <f t="shared" si="86"/>
+        <v>5.6246029212734777E-2</v>
+      </c>
+      <c r="BA17" s="7">
+        <f t="shared" si="86"/>
+        <v>8.0580810730140895E-2</v>
+      </c>
+      <c r="BB17" s="7">
+        <f t="shared" ref="BB17:BF17" si="87">BB15/BB16</f>
+        <v>0.11093751445459378</v>
+      </c>
+      <c r="BC17" s="7">
         <f t="shared" si="87"/>
-        <v>-1.0435676392572943</v>
-      </c>
-      <c r="AP17" s="7">
+        <v>0.1425583715809271</v>
+      </c>
+      <c r="BD17" s="7">
         <f t="shared" si="87"/>
-        <v>-0.87698938992042441</v>
-      </c>
-      <c r="AQ17" s="7">
+        <v>0.17540483997035569</v>
+      </c>
+      <c r="BE17" s="7">
         <f t="shared" si="87"/>
-        <v>-0.4113069622118728</v>
-      </c>
-      <c r="AR17" s="7">
+        <v>0.20951503526165374</v>
+      </c>
+      <c r="BF17" s="7">
         <f t="shared" si="87"/>
-        <v>-0.3025985747126434</v>
-      </c>
-      <c r="AS17" s="7">
-        <f t="shared" si="87"/>
-        <v>-0.16303617397701126</v>
-      </c>
-      <c r="AT17" s="7">
-        <f t="shared" si="87"/>
-        <v>-8.2866302558462404E-2</v>
-      </c>
-      <c r="AU17" s="7">
-        <f t="shared" si="87"/>
-        <v>-3.7208535357174215E-2</v>
-      </c>
-      <c r="AV17" s="7">
-        <f t="shared" si="87"/>
-        <v>-2.4971345665395417E-3</v>
-      </c>
-      <c r="AW17" s="7">
-        <f t="shared" si="87"/>
-        <v>2.0075052312934643E-2</v>
-      </c>
-      <c r="AX17" s="7">
-        <f t="shared" ref="AX17:BB17" si="88">AX15/AX16</f>
-        <v>4.8752181398418575E-2</v>
-      </c>
-      <c r="AY17" s="7">
-        <f t="shared" si="88"/>
-        <v>7.8646227703290758E-2</v>
-      </c>
-      <c r="AZ17" s="7">
-        <f t="shared" si="88"/>
-        <v>0.10971511023494451</v>
-      </c>
-      <c r="BA17" s="7">
-        <f t="shared" si="88"/>
-        <v>0.14199538948299428</v>
-      </c>
-      <c r="BB17" s="7">
-        <f t="shared" si="88"/>
-        <v>0.17552602393706682</v>
+        <v>0.24492948444442728</v>
       </c>
     </row>
-    <row r="19" spans="2:57" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:61" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
         <v>36</v>
       </c>
@@ -4320,185 +4446,192 @@
         <v>0.388816644993498</v>
       </c>
       <c r="H19" s="9">
-        <f t="shared" ref="H19:N19" si="89">H3/D3-1</f>
+        <f t="shared" ref="H19:N19" si="88">H3/D3-1</f>
         <v>0.47922226458253903</v>
       </c>
       <c r="I19" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="88"/>
         <v>0.4988243197850184</v>
       </c>
       <c r="J19" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="88"/>
         <v>0.4385739933316235</v>
       </c>
       <c r="K19" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="88"/>
         <v>0.44350811485642949</v>
       </c>
       <c r="L19" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="88"/>
         <v>0.17061855670103099</v>
       </c>
       <c r="M19" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="88"/>
         <v>0.52106678619453173</v>
       </c>
       <c r="N19" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="88"/>
         <v>0.62471028703868781</v>
       </c>
       <c r="O19" s="9">
-        <f t="shared" ref="O19" si="90">O3/K3-1</f>
+        <f t="shared" ref="O19" si="89">O3/K3-1</f>
         <v>0.66400000000000015</v>
       </c>
       <c r="P19" s="9">
-        <f t="shared" ref="P19" si="91">P3/L3-1</f>
+        <f t="shared" ref="P19" si="90">P3/L3-1</f>
         <v>1.1622633201232939</v>
       </c>
       <c r="Q19" s="9">
-        <f t="shared" ref="Q19" si="92">Q3/M3-1</f>
+        <f t="shared" ref="Q19" si="91">Q3/M3-1</f>
         <v>0.57285987918078662</v>
       </c>
       <c r="R19" s="9">
-        <f t="shared" ref="R19" si="93">R3/N3-1</f>
+        <f t="shared" ref="R19" si="92">R3/N3-1</f>
         <v>0.42422912323054995</v>
       </c>
       <c r="S19" s="9">
-        <f t="shared" ref="S19" si="94">S3/O3-1</f>
+        <f t="shared" ref="S19" si="93">S3/O3-1</f>
         <v>0.3808471933471933</v>
       </c>
       <c r="T19" s="9">
-        <f t="shared" ref="T19" si="95">T3/P3-1</f>
+        <f t="shared" ref="T19" si="94">T3/P3-1</f>
         <v>0.1311475409836067</v>
       </c>
       <c r="U19" s="9">
-        <f t="shared" ref="U19" si="96">U3/Q3-1</f>
+        <f t="shared" ref="U19" si="95">U3/Q3-1</f>
         <v>5.7142857142857162E-2</v>
       </c>
       <c r="V19" s="9">
-        <f t="shared" ref="V19" si="97">V3/R3-1</f>
+        <f t="shared" ref="V19" si="96">V3/R3-1</f>
         <v>1.3868556899607754E-3</v>
       </c>
       <c r="W19" s="9">
-        <f t="shared" ref="W19" si="98">W3/S3-1</f>
+        <f t="shared" ref="W19" si="97">W3/S3-1</f>
         <v>-6.9728051190364182E-2</v>
       </c>
       <c r="X19" s="9">
-        <f t="shared" ref="X19" si="99">X3/T3-1</f>
+        <f t="shared" ref="X19" si="98">X3/T3-1</f>
         <v>-3.8887388603834783E-2</v>
       </c>
       <c r="Y19" s="9">
-        <f t="shared" ref="Y19" si="100">Y3/U3-1</f>
+        <f t="shared" ref="Y19" si="99">Y3/U3-1</f>
         <v>5.325653522374818E-2</v>
       </c>
       <c r="Z19" s="9">
-        <f t="shared" ref="Z19" si="101">Z3/V3-1</f>
+        <f t="shared" ref="Z19" si="100">Z3/V3-1</f>
         <v>4.7395552819881503E-2</v>
       </c>
       <c r="AA19" s="9">
-        <f t="shared" ref="AA19" si="102">AA3/W3-1</f>
+        <f t="shared" ref="AA19" si="101">AA3/W3-1</f>
         <v>0.20857778676916849</v>
       </c>
       <c r="AB19" s="9">
-        <f t="shared" ref="AB19" si="103">AB3/X3-1</f>
+        <f t="shared" ref="AB19" si="102">AB3/X3-1</f>
         <v>0.15837782148543589</v>
       </c>
       <c r="AC19" s="9">
-        <f t="shared" ref="AC19" si="104">AC3/Y3-1</f>
+        <f t="shared" ref="AC19" si="103">AC3/Y3-1</f>
         <v>0.15471983846542159</v>
       </c>
       <c r="AD19" s="9">
-        <f t="shared" ref="AD19" si="105">AD3/Z3-1</f>
+        <f t="shared" ref="AD19" si="104">AD3/Z3-1</f>
         <v>0.14398001909939029</v>
       </c>
       <c r="AE19" s="9">
-        <f t="shared" ref="AE19" si="106">AE3/AA3-1</f>
+        <f t="shared" ref="AE19" si="105">AE3/AA3-1</f>
         <v>0.1409440910612656</v>
       </c>
       <c r="AF19" s="9">
-        <f t="shared" ref="AF19" si="107">AF3/AB3-1</f>
+        <f t="shared" ref="AF19" si="106">AF3/AB3-1</f>
         <v>8.7402975420439954E-2</v>
       </c>
       <c r="AG19" s="9">
-        <f t="shared" ref="AG19" si="108">AG3/AC3-1</f>
+        <f t="shared" ref="AG19" si="107">AG3/AC3-1</f>
         <v>9.7850637522768569E-2</v>
       </c>
       <c r="AH19" s="9">
-        <f t="shared" ref="AH19" si="109">AH3/AD3-1</f>
-        <v>8.0000000000000071E-2</v>
-      </c>
-      <c r="AI19" s="9"/>
+        <f t="shared" ref="AH19:AI19" si="108">AH3/AD3-1</f>
+        <v>0.10222821550118799</v>
+      </c>
+      <c r="AI19" s="9">
+        <f t="shared" si="108"/>
+        <v>0.11135563380281677</v>
+      </c>
+      <c r="AJ19" s="9"/>
       <c r="AK19" s="9"/>
-      <c r="AL19" s="9">
-        <f>AL3/AK3-1</f>
+      <c r="AL19" s="9"/>
+      <c r="AM19" s="9"/>
+      <c r="AO19" s="9"/>
+      <c r="AP19" s="9">
+        <f>AP3/AO3-1</f>
         <v>0.45307470777570735</v>
       </c>
-      <c r="AM19" s="9">
-        <f>AM3/AL3-1</f>
+      <c r="AQ19" s="9">
+        <f>AQ3/AP3-1</f>
         <v>0.46120664529291733</v>
       </c>
-      <c r="AN19" s="9">
-        <f t="shared" ref="AN19:AX19" si="110">AN3/AM3-1</f>
+      <c r="AR19" s="9">
+        <f t="shared" ref="AR19:BB19" si="109">AR3/AQ3-1</f>
         <v>0.64243826544859806</v>
       </c>
-      <c r="AO19" s="9">
-        <f t="shared" si="110"/>
+      <c r="AS19" s="9">
+        <f t="shared" si="109"/>
         <v>0.11772849821476283</v>
       </c>
-      <c r="AP19" s="9">
-        <f t="shared" si="110"/>
+      <c r="AT19" s="9">
+        <f t="shared" si="109"/>
         <v>9.561475944195319E-4</v>
       </c>
-      <c r="AQ19" s="9">
-        <f t="shared" si="110"/>
+      <c r="AU19" s="9">
+        <f t="shared" si="109"/>
         <v>0.16395293300334335</v>
       </c>
-      <c r="AR19" s="9">
-        <f t="shared" si="110"/>
-        <v>9.9858992054314255E-2</v>
-      </c>
-      <c r="AS19" s="9">
-        <f t="shared" si="110"/>
-        <v>7.0000000000000062E-2</v>
-      </c>
-      <c r="AT19" s="9">
-        <f t="shared" si="110"/>
+      <c r="AV19" s="9">
+        <f t="shared" si="109"/>
+        <v>0.10631551460439459</v>
+      </c>
+      <c r="AW19" s="9">
+        <f t="shared" si="109"/>
+        <v>9.000000000000008E-2</v>
+      </c>
+      <c r="AX19" s="9">
+        <f t="shared" si="109"/>
         <v>6.0000000000000053E-2</v>
       </c>
-      <c r="AU19" s="9">
-        <f t="shared" si="110"/>
+      <c r="AY19" s="9">
+        <f t="shared" si="109"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AV19" s="9">
-        <f t="shared" si="110"/>
+      <c r="AZ19" s="9">
+        <f t="shared" si="109"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AW19" s="9">
-        <f t="shared" si="110"/>
+      <c r="BA19" s="9">
+        <f t="shared" si="109"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AX19" s="9">
-        <f t="shared" si="110"/>
+      <c r="BB19" s="9">
+        <f t="shared" si="109"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AY19" s="9">
-        <f t="shared" ref="AY19" si="111">AY3/AX3-1</f>
+      <c r="BC19" s="9">
+        <f t="shared" ref="BC19" si="110">BC3/BB3-1</f>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AZ19" s="9">
-        <f t="shared" ref="AZ19" si="112">AZ3/AY3-1</f>
+      <c r="BD19" s="9">
+        <f t="shared" ref="BD19" si="111">BD3/BC3-1</f>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="BA19" s="9">
-        <f t="shared" ref="BA19" si="113">BA3/AZ3-1</f>
+      <c r="BE19" s="9">
+        <f t="shared" ref="BE19" si="112">BE3/BD3-1</f>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="BB19" s="9">
-        <f t="shared" ref="BB19" si="114">BB3/BA3-1</f>
+      <c r="BF19" s="9">
+        <f t="shared" ref="BF19" si="113">BF3/BE3-1</f>
         <v>3.0000000000000027E-2</v>
       </c>
     </row>
-    <row r="20" spans="2:57" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:61" x14ac:dyDescent="0.3">
       <c r="B20" s="1" t="s">
         <v>37</v>
       </c>
@@ -4507,204 +4640,208 @@
         <v>0.14694408322496741</v>
       </c>
       <c r="D20" s="9">
-        <f t="shared" ref="D20:N20" si="115">D5/D3</f>
+        <f t="shared" ref="D20:N20" si="114">D5/D3</f>
         <v>0.26953869614944725</v>
       </c>
       <c r="E20" s="9">
+        <f t="shared" si="114"/>
+        <v>0.33624454148471616</v>
+      </c>
+      <c r="F20" s="9">
+        <f t="shared" si="114"/>
+        <v>0.45370607848166195</v>
+      </c>
+      <c r="G20" s="9">
+        <f t="shared" si="114"/>
+        <v>0.363920099875156</v>
+      </c>
+      <c r="H20" s="9">
+        <f t="shared" si="114"/>
+        <v>0.44458762886597936</v>
+      </c>
+      <c r="I20" s="9">
+        <f t="shared" si="114"/>
+        <v>0.5</v>
+      </c>
+      <c r="J20" s="9">
+        <f t="shared" si="114"/>
+        <v>0.54822606525227313</v>
+      </c>
+      <c r="K20" s="9">
+        <f t="shared" si="114"/>
+        <v>0.45210810810810809</v>
+      </c>
+      <c r="L20" s="9">
+        <f t="shared" si="114"/>
+        <v>0.4484808454425363</v>
+      </c>
+      <c r="M20" s="9">
+        <f t="shared" si="114"/>
+        <v>0.56814498305584205</v>
+      </c>
+      <c r="N20" s="9">
+        <f t="shared" si="114"/>
+        <v>0.57697794359705912</v>
+      </c>
+      <c r="O20" s="9">
+        <f t="shared" ref="O20:R20" si="115">O5/O3</f>
+        <v>0.46387733887733884</v>
+      </c>
+      <c r="P20" s="9">
         <f t="shared" si="115"/>
-        <v>0.33624454148471616</v>
-      </c>
-      <c r="F20" s="9">
+        <v>0.54688931880663882</v>
+      </c>
+      <c r="Q20" s="9">
         <f t="shared" si="115"/>
-        <v>0.45370607848166195</v>
-      </c>
-      <c r="G20" s="9">
+        <v>0.58454332552693211</v>
+      </c>
+      <c r="R20" s="9">
         <f t="shared" si="115"/>
-        <v>0.363920099875156</v>
-      </c>
-      <c r="H20" s="9">
-        <f t="shared" si="115"/>
-        <v>0.44458762886597936</v>
-      </c>
-      <c r="I20" s="9">
-        <f t="shared" si="115"/>
-        <v>0.5</v>
-      </c>
-      <c r="J20" s="9">
-        <f t="shared" si="115"/>
-        <v>0.54822606525227313</v>
-      </c>
-      <c r="K20" s="9">
-        <f t="shared" si="115"/>
-        <v>0.45210810810810809</v>
-      </c>
-      <c r="L20" s="9">
-        <f t="shared" si="115"/>
-        <v>0.4484808454425363</v>
-      </c>
-      <c r="M20" s="9">
-        <f t="shared" si="115"/>
-        <v>0.56814498305584205</v>
-      </c>
-      <c r="N20" s="9">
-        <f t="shared" si="115"/>
-        <v>0.57697794359705912</v>
-      </c>
-      <c r="O20" s="9">
-        <f t="shared" ref="O20:R20" si="116">O5/O3</f>
-        <v>0.46387733887733884</v>
-      </c>
-      <c r="P20" s="9">
+        <v>0.65390245781647272</v>
+      </c>
+      <c r="S20" s="9">
+        <f t="shared" ref="S20:AD20" si="116">S5/S3</f>
+        <v>0.60393337724663598</v>
+      </c>
+      <c r="T20" s="9">
         <f t="shared" si="116"/>
-        <v>0.54688931880663882</v>
-      </c>
-      <c r="Q20" s="9">
+        <v>0.59816365109370784</v>
+      </c>
+      <c r="U20" s="9">
         <f t="shared" si="116"/>
-        <v>0.58454332552693211</v>
-      </c>
-      <c r="R20" s="9">
+        <v>0.58635356668143557</v>
+      </c>
+      <c r="V20" s="9">
         <f t="shared" si="116"/>
-        <v>0.65390245781647272</v>
-      </c>
-      <c r="S20" s="9">
-        <f t="shared" ref="S20:AD20" si="117">S5/S3</f>
-        <v>0.60393337724663598</v>
-      </c>
-      <c r="T20" s="9">
+        <v>0.62968377317842583</v>
+      </c>
+      <c r="W20" s="9">
+        <f t="shared" si="116"/>
+        <v>0.55492615820352009</v>
+      </c>
+      <c r="X20" s="9">
+        <f t="shared" si="116"/>
+        <v>0.53460709937248296</v>
+      </c>
+      <c r="Y20" s="9">
+        <f t="shared" si="116"/>
+        <v>0.53239104829210837</v>
+      </c>
+      <c r="Z20" s="9">
+        <f t="shared" si="116"/>
+        <v>0.54345111290678028</v>
+      </c>
+      <c r="AA20" s="9">
+        <f t="shared" si="116"/>
+        <v>0.51899899564780716</v>
+      </c>
+      <c r="AB20" s="9">
+        <f t="shared" si="116"/>
+        <v>0.5238518758085382</v>
+      </c>
+      <c r="AC20" s="9">
+        <f t="shared" si="116"/>
+        <v>0.53449908925318768</v>
+      </c>
+      <c r="AD20" s="9">
+        <f t="shared" si="116"/>
+        <v>0.56867655557696006</v>
+      </c>
+      <c r="AE20" s="9">
+        <f t="shared" ref="AE20:AH20" si="117">AE5/AE3</f>
+        <v>0.53080985915492962</v>
+      </c>
+      <c r="AF20" s="9">
         <f t="shared" si="117"/>
-        <v>0.59816365109370784</v>
-      </c>
-      <c r="U20" s="9">
+        <v>0.51423897687560416</v>
+      </c>
+      <c r="AG20" s="9">
         <f t="shared" si="117"/>
-        <v>0.58635356668143557</v>
-      </c>
-      <c r="V20" s="9">
+        <v>0.55256172020175198</v>
+      </c>
+      <c r="AH20" s="9">
         <f t="shared" si="117"/>
-        <v>0.62968377317842583</v>
-      </c>
-      <c r="W20" s="9">
-        <f t="shared" si="117"/>
-        <v>0.55492615820352009</v>
-      </c>
-      <c r="X20" s="9">
-        <f t="shared" si="117"/>
-        <v>0.53460709937248296</v>
-      </c>
-      <c r="Y20" s="9">
-        <f t="shared" si="117"/>
-        <v>0.53239104829210837</v>
-      </c>
-      <c r="Z20" s="9">
-        <f t="shared" si="117"/>
-        <v>0.54345111290678028</v>
-      </c>
-      <c r="AA20" s="9">
-        <f t="shared" si="117"/>
-        <v>0.51899899564780716</v>
-      </c>
-      <c r="AB20" s="9">
-        <f t="shared" si="117"/>
-        <v>0.5238518758085382</v>
-      </c>
-      <c r="AC20" s="9">
-        <f t="shared" si="117"/>
-        <v>0.53449908925318768</v>
-      </c>
-      <c r="AD20" s="9">
-        <f t="shared" si="117"/>
-        <v>0.56867655557696006</v>
-      </c>
-      <c r="AE20" s="9">
-        <f t="shared" ref="AE20:AH20" si="118">AE5/AE3</f>
-        <v>0.53080985915492962</v>
-      </c>
-      <c r="AF20" s="9">
+        <v>0.59079522283716868</v>
+      </c>
+      <c r="AI20" s="9"/>
+      <c r="AJ20" s="9"/>
+      <c r="AK20" s="9"/>
+      <c r="AL20" s="9"/>
+      <c r="AM20" s="9"/>
+      <c r="AO20" s="9">
+        <f t="shared" ref="AO20:AQ20" si="118">AO5/AO3</f>
+        <v>0.32322547857021849</v>
+      </c>
+      <c r="AP20" s="9">
         <f t="shared" si="118"/>
-        <v>0.51423897687560416</v>
-      </c>
-      <c r="AG20" s="9">
+        <v>0.47781987758670946</v>
+      </c>
+      <c r="AQ20" s="9">
         <f t="shared" si="118"/>
-        <v>0.55256172020175198</v>
-      </c>
-      <c r="AH20" s="9">
-        <f t="shared" si="118"/>
+        <v>0.52826425180516212</v>
+      </c>
+      <c r="AR20" s="9">
+        <f t="shared" ref="AR20:BA20" si="119">AR5/AR3</f>
+        <v>0.57487066138787013</v>
+      </c>
+      <c r="AS20" s="9">
+        <f t="shared" si="119"/>
+        <v>0.60550219479334189</v>
+      </c>
+      <c r="AT20" s="9">
+        <f t="shared" si="119"/>
+        <v>0.54100994312014239</v>
+      </c>
+      <c r="AU20" s="9">
+        <f t="shared" si="119"/>
+        <v>0.53851605923825863</v>
+      </c>
+      <c r="AV20" s="9">
+        <f t="shared" si="119"/>
+        <v>0.54993762012341108</v>
+      </c>
+      <c r="AW20" s="9">
+        <f t="shared" si="119"/>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="AX20" s="9">
+        <f t="shared" si="119"/>
         <v>0.56999999999999995</v>
       </c>
-      <c r="AI20" s="9"/>
-      <c r="AK20" s="9">
-        <f t="shared" ref="AK20:AM20" si="119">AK5/AK3</f>
-        <v>0.32322547857021849</v>
-      </c>
-      <c r="AL20" s="9">
+      <c r="AY20" s="9">
         <f t="shared" si="119"/>
-        <v>0.47781987758670946</v>
-      </c>
-      <c r="AM20" s="9">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="AZ20" s="9">
         <f t="shared" si="119"/>
-        <v>0.52826425180516212</v>
-      </c>
-      <c r="AN20" s="9">
-        <f t="shared" ref="AN20:AW20" si="120">AN5/AN3</f>
-        <v>0.57487066138787013</v>
-      </c>
-      <c r="AO20" s="9">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="BA20" s="9">
+        <f t="shared" si="119"/>
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="BB20" s="9">
+        <f t="shared" ref="BB20:BF20" si="120">BB5/BB3</f>
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="BC20" s="9">
         <f t="shared" si="120"/>
-        <v>0.60550219479334189</v>
-      </c>
-      <c r="AP20" s="9">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="BD20" s="9">
         <f t="shared" si="120"/>
-        <v>0.54100994312014239</v>
-      </c>
-      <c r="AQ20" s="9">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="BE20" s="9">
         <f t="shared" si="120"/>
-        <v>0.53851605923825863</v>
-      </c>
-      <c r="AR20" s="9">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="BF20" s="9">
         <f t="shared" si="120"/>
-        <v>0.54376654800311497</v>
-      </c>
-      <c r="AS20" s="9">
-        <f t="shared" si="120"/>
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="AT20" s="9">
-        <f t="shared" si="120"/>
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="AU20" s="9">
-        <f t="shared" si="120"/>
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="AV20" s="9">
-        <f t="shared" si="120"/>
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="AW20" s="9">
-        <f t="shared" si="120"/>
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="AX20" s="9">
-        <f t="shared" ref="AX20:BB20" si="121">AX5/AX3</f>
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="AY20" s="9">
-        <f t="shared" si="121"/>
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="AZ20" s="9">
-        <f t="shared" si="121"/>
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="BA20" s="9">
-        <f t="shared" si="121"/>
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="BB20" s="9">
-        <f t="shared" si="121"/>
-        <v>0.56000000000000005</v>
+        <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="21" spans="2:57" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:61" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>38</v>
       </c>
@@ -4713,210 +4850,214 @@
         <v>-1.7013437364542698</v>
       </c>
       <c r="D21" s="9">
-        <f t="shared" ref="D21:N21" si="122">D9/D3</f>
+        <f t="shared" ref="D21:N21" si="121">D9/D3</f>
         <v>-1.3640869233701867</v>
       </c>
       <c r="E21" s="9">
+        <f t="shared" si="121"/>
+        <v>-1.0866644272757811</v>
+      </c>
+      <c r="F21" s="9">
+        <f t="shared" si="121"/>
+        <v>-0.49935880995126969</v>
+      </c>
+      <c r="G21" s="9">
+        <f t="shared" si="121"/>
+        <v>-0.98689138576779045</v>
+      </c>
+      <c r="H21" s="9">
+        <f t="shared" si="121"/>
+        <v>-0.78556701030927822</v>
+      </c>
+      <c r="I21" s="9">
+        <f t="shared" si="121"/>
+        <v>-0.51277454056476923</v>
+      </c>
+      <c r="J21" s="9">
+        <f t="shared" si="121"/>
+        <v>-0.45195221964699595</v>
+      </c>
+      <c r="K21" s="9">
+        <f t="shared" si="121"/>
+        <v>-0.61902702702702694</v>
+      </c>
+      <c r="L21" s="9">
+        <f t="shared" si="121"/>
+        <v>-0.68383971818582112</v>
+      </c>
+      <c r="M21" s="9">
+        <f t="shared" si="121"/>
+        <v>-0.24723736555179018</v>
+      </c>
+      <c r="N21" s="9">
+        <f t="shared" si="121"/>
+        <v>-0.10655108087347748</v>
+      </c>
+      <c r="O21" s="9">
+        <f t="shared" ref="O21:R21" si="122">O9/O3</f>
+        <v>-0.39449064449064453</v>
+      </c>
+      <c r="P21" s="9">
         <f t="shared" si="122"/>
-        <v>-1.0866644272757811</v>
-      </c>
-      <c r="F21" s="9">
+        <v>-0.19600855310049886</v>
+      </c>
+      <c r="Q21" s="9">
         <f t="shared" si="122"/>
-        <v>-0.49935880995126969</v>
-      </c>
-      <c r="G21" s="9">
+        <v>-0.16936768149882905</v>
+      </c>
+      <c r="R21" s="9">
         <f t="shared" si="122"/>
-        <v>-0.98689138576779045</v>
-      </c>
-      <c r="H21" s="9">
-        <f t="shared" si="122"/>
-        <v>-0.78556701030927822</v>
-      </c>
-      <c r="I21" s="9">
-        <f t="shared" si="122"/>
-        <v>-0.51277454056476923</v>
-      </c>
-      <c r="J21" s="9">
-        <f t="shared" si="122"/>
-        <v>-0.45195221964699595</v>
-      </c>
-      <c r="K21" s="9">
-        <f t="shared" si="122"/>
-        <v>-0.61902702702702694</v>
-      </c>
-      <c r="L21" s="9">
-        <f t="shared" si="122"/>
-        <v>-0.68383971818582112</v>
-      </c>
-      <c r="M21" s="9">
-        <f t="shared" si="122"/>
-        <v>-0.24723736555179018</v>
-      </c>
-      <c r="N21" s="9">
-        <f t="shared" si="122"/>
-        <v>-0.10655108087347748</v>
-      </c>
-      <c r="O21" s="9">
-        <f t="shared" ref="O21:R21" si="123">O9/O3</f>
-        <v>-0.39449064449064453</v>
-      </c>
-      <c r="P21" s="9">
+        <v>-1.9338932121118681E-2</v>
+      </c>
+      <c r="S21" s="9">
+        <f t="shared" ref="S21:AD21" si="123">S9/S3</f>
+        <v>-0.25557542109720521</v>
+      </c>
+      <c r="T21" s="9">
         <f t="shared" si="123"/>
-        <v>-0.19600855310049886</v>
-      </c>
-      <c r="Q21" s="9">
+        <v>-0.36096858403096577</v>
+      </c>
+      <c r="U21" s="9">
         <f t="shared" si="123"/>
-        <v>-0.16936768149882905</v>
-      </c>
-      <c r="R21" s="9">
+        <v>-0.38573327425786436</v>
+      </c>
+      <c r="V21" s="9">
         <f t="shared" si="123"/>
-        <v>-1.9338932121118681E-2</v>
-      </c>
-      <c r="S21" s="9">
-        <f t="shared" ref="S21:AD21" si="124">S9/S3</f>
-        <v>-0.25557542109720521</v>
-      </c>
-      <c r="T21" s="9">
+        <v>-0.22128183426944673</v>
+      </c>
+      <c r="W21" s="9">
+        <f t="shared" si="123"/>
+        <v>-0.36941128869107825</v>
+      </c>
+      <c r="X21" s="9">
+        <f t="shared" si="123"/>
+        <v>-0.37875807811182916</v>
+      </c>
+      <c r="Y21" s="9">
+        <f t="shared" si="123"/>
+        <v>-0.31987211845869096</v>
+      </c>
+      <c r="Z21" s="9">
+        <f t="shared" si="123"/>
+        <v>-0.18269301403070598</v>
+      </c>
+      <c r="AA21" s="9">
+        <f t="shared" si="123"/>
+        <v>-0.27887512554402422</v>
+      </c>
+      <c r="AB21" s="9">
+        <f t="shared" si="123"/>
+        <v>-0.2052878395860285</v>
+      </c>
+      <c r="AC21" s="9">
+        <f t="shared" si="123"/>
+        <v>-0.12626593806921677</v>
+      </c>
+      <c r="AD21" s="9">
+        <f t="shared" si="123"/>
+        <v>-1.7209272458742739E-2</v>
+      </c>
+      <c r="AE21" s="9">
+        <f t="shared" ref="AE21:AH21" si="124">AE9/AE3</f>
+        <v>-0.14231220657276994</v>
+      </c>
+      <c r="AF21" s="9">
         <f t="shared" si="124"/>
-        <v>-0.36096858403096577</v>
-      </c>
-      <c r="U21" s="9">
+        <v>-0.19309985872555566</v>
+      </c>
+      <c r="AG21" s="9">
         <f t="shared" si="124"/>
-        <v>-0.38573327425786436</v>
-      </c>
-      <c r="V21" s="9">
+        <v>-8.5147332094504966E-2</v>
+      </c>
+      <c r="AH21" s="9">
         <f t="shared" si="124"/>
-        <v>-0.22128183426944673</v>
-      </c>
-      <c r="W21" s="9">
-        <f t="shared" si="124"/>
-        <v>-0.36941128869107825</v>
-      </c>
-      <c r="X21" s="9">
-        <f t="shared" si="124"/>
-        <v>-0.37875807811182916</v>
-      </c>
-      <c r="Y21" s="9">
-        <f t="shared" si="124"/>
-        <v>-0.31987211845869096</v>
-      </c>
-      <c r="Z21" s="9">
-        <f t="shared" si="124"/>
-        <v>-0.18269301403070598</v>
-      </c>
-      <c r="AA21" s="9">
-        <f t="shared" si="124"/>
-        <v>-0.27887512554402422</v>
-      </c>
-      <c r="AB21" s="9">
-        <f t="shared" si="124"/>
-        <v>-0.2052878395860285</v>
-      </c>
-      <c r="AC21" s="9">
-        <f t="shared" si="124"/>
-        <v>-0.12626593806921677</v>
-      </c>
-      <c r="AD21" s="9">
-        <f t="shared" si="124"/>
-        <v>-1.7209272458742739E-2</v>
-      </c>
-      <c r="AE21" s="9">
-        <f t="shared" ref="AE21:AH21" si="125">AE9/AE3</f>
-        <v>-0.14231220657276994</v>
-      </c>
-      <c r="AF21" s="9">
+        <v>2.9012525487911486E-2</v>
+      </c>
+      <c r="AI21" s="9"/>
+      <c r="AJ21" s="9"/>
+      <c r="AK21" s="9"/>
+      <c r="AL21" s="9"/>
+      <c r="AM21" s="9"/>
+      <c r="AO21" s="9">
+        <f t="shared" ref="AO21:AQ21" si="125">AO9/AO3</f>
+        <v>-1.0744536676266305</v>
+      </c>
+      <c r="AP21" s="9">
         <f t="shared" si="125"/>
-        <v>-0.19309985872555566</v>
-      </c>
-      <c r="AG21" s="9">
+        <v>-0.64313611192072284</v>
+      </c>
+      <c r="AQ21" s="9">
         <f t="shared" si="125"/>
-        <v>-8.5147332094504966E-2</v>
-      </c>
-      <c r="AH21" s="9">
-        <f t="shared" si="125"/>
-        <v>-2.4405702176844592E-2</v>
-      </c>
-      <c r="AI21" s="9"/>
-      <c r="AK21" s="9">
-        <f t="shared" ref="AK21:AM21" si="126">AK9/AK3</f>
-        <v>-1.0744536676266305</v>
-      </c>
-      <c r="AL21" s="9">
+        <v>-0.34379861969920622</v>
+      </c>
+      <c r="AR21" s="9">
+        <f t="shared" ref="AR21:BA21" si="126">AR9/AR3</f>
+        <v>-0.17050836754025889</v>
+      </c>
+      <c r="AS21" s="9">
         <f t="shared" si="126"/>
-        <v>-0.64313611192072284</v>
-      </c>
-      <c r="AM21" s="9">
+        <v>-0.30325090182102643</v>
+      </c>
+      <c r="AT21" s="9">
         <f t="shared" si="126"/>
-        <v>-0.34379861969920622</v>
-      </c>
-      <c r="AN21" s="9">
-        <f t="shared" ref="AN21:AW21" si="127">AN9/AN3</f>
-        <v>-0.17050836754025889</v>
-      </c>
-      <c r="AO21" s="9">
+        <v>-0.30361252225261603</v>
+      </c>
+      <c r="AU21" s="9">
+        <f t="shared" si="126"/>
+        <v>-0.14682732122206885</v>
+      </c>
+      <c r="AV21" s="9">
+        <f t="shared" si="126"/>
+        <v>-8.972586573153038E-2</v>
+      </c>
+      <c r="AW21" s="9">
+        <f t="shared" si="126"/>
+        <v>-4.7695449470753069E-2</v>
+      </c>
+      <c r="AX21" s="9">
+        <f t="shared" si="126"/>
+        <v>-1.0021109273893058E-2</v>
+      </c>
+      <c r="AY21" s="9">
+        <f t="shared" si="126"/>
+        <v>4.522160737613792E-3</v>
+      </c>
+      <c r="AZ21" s="9">
+        <f t="shared" si="126"/>
+        <v>1.4789132221784202E-2</v>
+      </c>
+      <c r="BA21" s="9">
+        <f t="shared" si="126"/>
+        <v>2.1047503691879351E-2</v>
+      </c>
+      <c r="BB21" s="9">
+        <f t="shared" ref="BB21:BF21" si="127">BB9/BB3</f>
+        <v>2.8599979348347685E-2</v>
+      </c>
+      <c r="BC21" s="9">
         <f t="shared" si="127"/>
-        <v>-0.30325090182102643</v>
-      </c>
-      <c r="AP21" s="9">
+        <v>3.6005804992069089E-2</v>
+      </c>
+      <c r="BD21" s="9">
         <f t="shared" si="127"/>
-        <v>-0.30361252225261603</v>
-      </c>
-      <c r="AQ21" s="9">
+        <v>4.3267828196106646E-2</v>
+      </c>
+      <c r="BE21" s="9">
         <f t="shared" si="127"/>
-        <v>-0.14682732122206885</v>
-      </c>
-      <c r="AR21" s="9">
+        <v>5.0388841240842371E-2</v>
+      </c>
+      <c r="BF21" s="9">
         <f t="shared" si="127"/>
-        <v>-0.10565887439662017</v>
-      </c>
-      <c r="AS21" s="9">
-        <f t="shared" si="127"/>
-        <v>-6.110445185353424E-2</v>
-      </c>
-      <c r="AT21" s="9">
-        <f t="shared" si="127"/>
-        <v>-3.2942861516666554E-2</v>
-      </c>
-      <c r="AU21" s="9">
-        <f t="shared" si="127"/>
-        <v>-1.7978575929987049E-2</v>
-      </c>
-      <c r="AV21" s="9">
-        <f t="shared" si="127"/>
-        <v>-7.4208778940454134E-3</v>
-      </c>
-      <c r="AW21" s="9">
-        <f t="shared" si="127"/>
-        <v>-9.9461210496276111E-4</v>
-      </c>
-      <c r="AX21" s="9">
-        <f t="shared" ref="AX21:BB21" si="128">AX9/AX3</f>
-        <v>6.7916910427064442E-3</v>
-      </c>
-      <c r="AY21" s="9">
-        <f t="shared" si="128"/>
-        <v>1.4426803837993753E-2</v>
-      </c>
-      <c r="AZ21" s="9">
-        <f t="shared" si="128"/>
-        <v>2.1913662015896833E-2</v>
-      </c>
-      <c r="BA21" s="9">
-        <f t="shared" si="128"/>
-        <v>2.9255144306850323E-2</v>
-      </c>
-      <c r="BB21" s="9">
-        <f t="shared" si="128"/>
-        <v>3.64540735436105E-2</v>
-      </c>
-      <c r="BD21" t="s">
+        <v>5.7371582187622172E-2</v>
+      </c>
+      <c r="BH21" t="s">
         <v>40</v>
       </c>
-      <c r="BE21" s="9">
+      <c r="BI21" s="9">
         <v>-0.01</v>
       </c>
     </row>
-    <row r="22" spans="2:57" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:61" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>55</v>
       </c>
@@ -4925,195 +5066,199 @@
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
       <c r="G22" s="9">
-        <f t="shared" ref="G22:R22" si="129">G6/C6-1</f>
+        <f t="shared" ref="G22:R22" si="128">G6/C6-1</f>
         <v>7.5621890547263648E-2</v>
       </c>
       <c r="H22" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="128"/>
         <v>0.16240157480314954</v>
       </c>
       <c r="I22" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="128"/>
         <v>3.98034398034397E-2</v>
       </c>
       <c r="J22" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="128"/>
         <v>0.33515815085158152</v>
       </c>
       <c r="K22" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="128"/>
         <v>0.1036077705827938</v>
       </c>
       <c r="L22" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="128"/>
         <v>0.10457239627434367</v>
       </c>
       <c r="M22" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="128"/>
         <v>0.34026465028355402</v>
       </c>
       <c r="N22" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="128"/>
         <v>0.45056947608200448</v>
       </c>
       <c r="O22" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="128"/>
         <v>0.4610226320201174</v>
       </c>
       <c r="P22" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="128"/>
         <v>0.42085090072824838</v>
       </c>
       <c r="Q22" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="128"/>
         <v>0.45275035260930885</v>
       </c>
       <c r="R22" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="128"/>
         <v>0.3636934673366834</v>
       </c>
       <c r="S22" s="9">
-        <f t="shared" ref="S22" si="130">S6/O6-1</f>
+        <f t="shared" ref="S22" si="129">S6/O6-1</f>
         <v>0.30694205393000562</v>
       </c>
       <c r="T22" s="9">
-        <f t="shared" ref="T22" si="131">T6/P6-1</f>
+        <f t="shared" ref="T22" si="130">T6/P6-1</f>
         <v>0.36228756406797946</v>
       </c>
       <c r="U22" s="9">
-        <f t="shared" ref="U22" si="132">U6/Q6-1</f>
+        <f t="shared" ref="U22" si="131">U6/Q6-1</f>
         <v>0.36966019417475726</v>
       </c>
       <c r="V22" s="9">
-        <f t="shared" ref="V22" si="133">V6/R6-1</f>
+        <f t="shared" ref="V22" si="132">V6/R6-1</f>
         <v>0.34707508060801473</v>
       </c>
       <c r="W22" s="9">
-        <f t="shared" ref="W22" si="134">W6/S6-1</f>
+        <f t="shared" ref="W22" si="133">W6/S6-1</f>
         <v>-1.0974539069359412E-3</v>
       </c>
       <c r="X22" s="9">
-        <f t="shared" ref="X22" si="135">X6/T6-1</f>
+        <f t="shared" ref="X22" si="134">X6/T6-1</f>
         <v>-5.4059405940594107E-2</v>
       </c>
       <c r="Y22" s="9">
-        <f t="shared" ref="Y22" si="136">Y6/U6-1</f>
+        <f t="shared" ref="Y22" si="135">Y6/U6-1</f>
         <v>-0.12351586035796547</v>
       </c>
       <c r="Z22" s="9">
-        <f t="shared" ref="Z22" si="137">Z6/V6-1</f>
+        <f t="shared" ref="Z22" si="136">Z6/V6-1</f>
         <v>-0.17336296802872286</v>
       </c>
       <c r="AA22" s="9">
-        <f t="shared" ref="AA22" si="138">AA6/W6-1</f>
+        <f t="shared" ref="AA22" si="137">AA6/W6-1</f>
         <v>-1.1645792133597066E-2</v>
       </c>
       <c r="AB22" s="9">
-        <f t="shared" ref="AB22" si="139">AB6/X6-1</f>
+        <f t="shared" ref="AB22" si="138">AB6/X6-1</f>
         <v>-0.14967552857441913</v>
       </c>
       <c r="AC22" s="9">
-        <f t="shared" ref="AC22" si="140">AC6/Y6-1</f>
+        <f t="shared" ref="AC22" si="139">AC6/Y6-1</f>
         <v>-0.16538617064294381</v>
       </c>
       <c r="AD22" s="9">
-        <f t="shared" ref="AD22" si="141">AD6/Z6-1</f>
+        <f t="shared" ref="AD22" si="140">AD6/Z6-1</f>
         <v>-0.12533609100310239</v>
       </c>
       <c r="AE22" s="9">
-        <f t="shared" ref="AE22" si="142">AE6/AA6-1</f>
+        <f t="shared" ref="AE22" si="141">AE6/AA6-1</f>
         <v>-5.6914184081814145E-2</v>
       </c>
       <c r="AF22" s="9">
-        <f t="shared" ref="AF22" si="143">AF6/AB6-1</f>
+        <f t="shared" ref="AF22" si="142">AF6/AB6-1</f>
         <v>9.1334318069916431E-2</v>
       </c>
       <c r="AG22" s="9">
-        <f t="shared" ref="AG22" si="144">AG6/AC6-1</f>
+        <f t="shared" ref="AG22" si="143">AG6/AC6-1</f>
         <v>9.8352713178294415E-2</v>
       </c>
       <c r="AH22" s="9">
-        <f t="shared" ref="AH22" si="145">AH6/AD6-1</f>
-        <v>0.10000000000000009</v>
+        <f t="shared" ref="AH22" si="144">AH6/AD6-1</f>
+        <v>0.11775833530385427</v>
       </c>
       <c r="AI22" s="9"/>
+      <c r="AJ22" s="9"/>
       <c r="AK22" s="9"/>
-      <c r="AL22" s="9">
-        <f t="shared" ref="AL22:AX24" si="146">AL6/AK6-1</f>
+      <c r="AL22" s="9"/>
+      <c r="AM22" s="9"/>
+      <c r="AO22" s="9"/>
+      <c r="AP22" s="9">
+        <f t="shared" ref="AP22:BB24" si="145">AP6/AO6-1</f>
         <v>0.14428182877865559</v>
       </c>
-      <c r="AM22" s="9">
-        <f t="shared" si="146"/>
+      <c r="AQ22" s="9">
+        <f t="shared" si="145"/>
         <v>0.24674589700056604</v>
       </c>
-      <c r="AN22" s="9">
-        <f t="shared" si="146"/>
+      <c r="AR22" s="9">
+        <f t="shared" si="145"/>
         <v>0.42124375851112128</v>
       </c>
-      <c r="AO22" s="9">
-        <f t="shared" si="146"/>
+      <c r="AS22" s="9">
+        <f t="shared" si="145"/>
         <v>0.34768444586394143</v>
       </c>
-      <c r="AP22" s="9">
-        <f t="shared" si="146"/>
+      <c r="AT22" s="9">
+        <f t="shared" si="145"/>
         <v>-9.4274338799886226E-2</v>
       </c>
-      <c r="AQ22" s="9">
-        <f t="shared" si="146"/>
+      <c r="AU22" s="9">
+        <f t="shared" si="145"/>
         <v>-0.11471034591030416</v>
       </c>
-      <c r="AR22" s="9">
-        <f t="shared" si="146"/>
-        <v>5.5795944907489625E-2</v>
-      </c>
-      <c r="AS22" s="9">
-        <f t="shared" si="146"/>
+      <c r="AV22" s="9">
+        <f t="shared" si="145"/>
+        <v>6.023526630017173E-2</v>
+      </c>
+      <c r="AW22" s="9">
+        <f t="shared" si="145"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AT22" s="9">
-        <f t="shared" si="146"/>
+      <c r="AX22" s="9">
+        <f t="shared" si="145"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AU22" s="9">
-        <f t="shared" si="146"/>
+      <c r="AY22" s="9">
+        <f t="shared" si="145"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AV22" s="9">
-        <f t="shared" si="146"/>
+      <c r="AZ22" s="9">
+        <f t="shared" si="145"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AW22" s="9">
-        <f t="shared" si="146"/>
+      <c r="BA22" s="9">
+        <f t="shared" si="145"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AX22" s="9">
-        <f t="shared" si="146"/>
+      <c r="BB22" s="9">
+        <f t="shared" si="145"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AY22" s="9">
-        <f t="shared" ref="AY22" si="147">AY6/AX6-1</f>
+      <c r="BC22" s="9">
+        <f t="shared" ref="BC22" si="146">BC6/BB6-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AZ22" s="9">
-        <f t="shared" ref="AZ22" si="148">AZ6/AY6-1</f>
+      <c r="BD22" s="9">
+        <f t="shared" ref="BD22" si="147">BD6/BC6-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BA22" s="9">
-        <f t="shared" ref="BA22" si="149">BA6/AZ6-1</f>
+      <c r="BE22" s="9">
+        <f t="shared" ref="BE22" si="148">BE6/BD6-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BB22" s="9">
-        <f t="shared" ref="BB22" si="150">BB6/BA6-1</f>
+      <c r="BF22" s="9">
+        <f t="shared" ref="BF22" si="149">BF6/BE6-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BD22" t="s">
+      <c r="BH22" t="s">
         <v>41</v>
       </c>
-      <c r="BE22" s="9">
-        <v>0.08</v>
+      <c r="BI22" s="9">
+        <v>0.09</v>
       </c>
     </row>
-    <row r="23" spans="2:57" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:61" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>39</v>
       </c>
@@ -5122,211 +5267,215 @@
         <v>0.44256610316428263</v>
       </c>
       <c r="D23" s="9">
-        <f t="shared" ref="D23:N23" si="151">D7/D3</f>
+        <f t="shared" ref="D23:N23" si="150">D7/D3</f>
         <v>0.38772398017537169</v>
       </c>
       <c r="E23" s="9">
+        <f t="shared" si="150"/>
+        <v>0.32784682566341955</v>
+      </c>
+      <c r="F23" s="9">
+        <f t="shared" si="150"/>
+        <v>0.25519363939471662</v>
+      </c>
+      <c r="G23" s="9">
+        <f t="shared" si="150"/>
+        <v>0.30555555555555558</v>
+      </c>
+      <c r="H23" s="9">
+        <f t="shared" si="150"/>
+        <v>0.28737113402061853</v>
+      </c>
+      <c r="I23" s="9">
+        <f t="shared" si="150"/>
+        <v>0.27610936799641417</v>
+      </c>
+      <c r="J23" s="9">
+        <f t="shared" si="150"/>
+        <v>0.22463897307898023</v>
+      </c>
+      <c r="K23" s="9">
+        <f t="shared" si="150"/>
+        <v>0.26421621621621622</v>
+      </c>
+      <c r="L23" s="9">
+        <f t="shared" si="150"/>
+        <v>0.29084103918978421</v>
+      </c>
+      <c r="M23" s="9">
+        <f t="shared" si="150"/>
+        <v>0.21143362310299099</v>
+      </c>
+      <c r="N23" s="9">
+        <f t="shared" si="150"/>
+        <v>0.17293975639196751</v>
+      </c>
+      <c r="O23" s="9">
+        <f t="shared" ref="O23:R23" si="151">O7/O3</f>
+        <v>0.19529625779625781</v>
+      </c>
+      <c r="P23" s="9">
         <f t="shared" si="151"/>
-        <v>0.32784682566341955</v>
-      </c>
-      <c r="F23" s="9">
+        <v>0.18297525710212809</v>
+      </c>
+      <c r="Q23" s="9">
         <f t="shared" si="151"/>
-        <v>0.25519363939471662</v>
-      </c>
-      <c r="G23" s="9">
+        <v>0.20374707259953162</v>
+      </c>
+      <c r="R23" s="9">
         <f t="shared" si="151"/>
-        <v>0.30555555555555558</v>
-      </c>
-      <c r="H23" s="9">
-        <f t="shared" si="151"/>
-        <v>0.28737113402061853</v>
-      </c>
-      <c r="I23" s="9">
-        <f t="shared" si="151"/>
-        <v>0.27610936799641417</v>
-      </c>
-      <c r="J23" s="9">
-        <f t="shared" si="151"/>
-        <v>0.22463897307898023</v>
-      </c>
-      <c r="K23" s="9">
-        <f t="shared" si="151"/>
-        <v>0.26421621621621622</v>
-      </c>
-      <c r="L23" s="9">
-        <f t="shared" si="151"/>
-        <v>0.29084103918978421</v>
-      </c>
-      <c r="M23" s="9">
-        <f t="shared" si="151"/>
-        <v>0.21143362310299099</v>
-      </c>
-      <c r="N23" s="9">
-        <f t="shared" si="151"/>
-        <v>0.17293975639196751</v>
-      </c>
-      <c r="O23" s="9">
-        <f t="shared" ref="O23:R23" si="152">O7/O3</f>
-        <v>0.19529625779625781</v>
-      </c>
-      <c r="P23" s="9">
+        <v>0.18892056398798057</v>
+      </c>
+      <c r="S23" s="9">
+        <f t="shared" ref="S23:AD23" si="152">S7/S3</f>
+        <v>0.22762774066058153</v>
+      </c>
+      <c r="T23" s="9">
         <f t="shared" si="152"/>
-        <v>0.18297525710212809</v>
-      </c>
-      <c r="Q23" s="9">
+        <v>0.28031325951930863</v>
+      </c>
+      <c r="U23" s="9">
         <f t="shared" si="152"/>
-        <v>0.20374707259953162</v>
-      </c>
-      <c r="R23" s="9">
+        <v>0.23952148870181658</v>
+      </c>
+      <c r="V23" s="9">
         <f t="shared" si="152"/>
-        <v>0.18892056398798057</v>
-      </c>
-      <c r="S23" s="9">
-        <f t="shared" ref="S23:AD23" si="153">S7/S3</f>
-        <v>0.22762774066058153</v>
-      </c>
-      <c r="T23" s="9">
+        <v>0.22712933753943215</v>
+      </c>
+      <c r="W23" s="9">
+        <f t="shared" si="152"/>
+        <v>0.27149504349585268</v>
+      </c>
+      <c r="X23" s="9">
+        <f t="shared" si="152"/>
+        <v>0.26280790484218414</v>
+      </c>
+      <c r="Y23" s="9">
+        <f t="shared" si="152"/>
+        <v>0.25012619888944981</v>
+      </c>
+      <c r="Z23" s="9">
+        <f t="shared" si="152"/>
+        <v>0.2026004554469992</v>
+      </c>
+      <c r="AA23" s="9">
+        <f t="shared" si="152"/>
+        <v>0.23100100435219284</v>
+      </c>
+      <c r="AB23" s="9">
+        <f t="shared" si="152"/>
+        <v>0.21531371280724451</v>
+      </c>
+      <c r="AC23" s="9">
+        <f t="shared" si="152"/>
+        <v>0.19897996357012751</v>
+      </c>
+      <c r="AD23" s="9">
+        <f t="shared" si="152"/>
+        <v>0.15937841135298272</v>
+      </c>
+      <c r="AE23" s="9">
+        <f t="shared" ref="AE23:AH23" si="153">AE7/AE3</f>
+        <v>0.18926056338028169</v>
+      </c>
+      <c r="AF23" s="9">
         <f t="shared" si="153"/>
-        <v>0.28031325951930863</v>
-      </c>
-      <c r="U23" s="9">
+        <v>0.19176146925421961</v>
+      </c>
+      <c r="AG23" s="9">
         <f t="shared" si="153"/>
-        <v>0.23952148870181658</v>
-      </c>
-      <c r="V23" s="9">
+        <v>0.17002920095566765</v>
+      </c>
+      <c r="AH23" s="9">
         <f t="shared" si="153"/>
-        <v>0.22712933753943215</v>
-      </c>
-      <c r="W23" s="9">
-        <f t="shared" si="153"/>
-        <v>0.27149504349585268</v>
-      </c>
-      <c r="X23" s="9">
-        <f t="shared" si="153"/>
-        <v>0.26280790484218414</v>
-      </c>
-      <c r="Y23" s="9">
-        <f t="shared" si="153"/>
-        <v>0.25012619888944981</v>
-      </c>
-      <c r="Z23" s="9">
-        <f t="shared" si="153"/>
-        <v>0.2026004554469992</v>
-      </c>
-      <c r="AA23" s="9">
-        <f t="shared" si="153"/>
-        <v>0.23100100435219284</v>
-      </c>
-      <c r="AB23" s="9">
-        <f t="shared" si="153"/>
-        <v>0.21531371280724451</v>
-      </c>
-      <c r="AC23" s="9">
-        <f t="shared" si="153"/>
-        <v>0.19897996357012751</v>
-      </c>
-      <c r="AD23" s="9">
-        <f t="shared" si="153"/>
-        <v>0.15937841135298272</v>
-      </c>
-      <c r="AE23" s="9">
-        <f t="shared" ref="AE23:AH23" si="154">AE7/AE3</f>
-        <v>0.18926056338028169</v>
-      </c>
-      <c r="AF23" s="9">
+        <v>0.14523740168948443</v>
+      </c>
+      <c r="AI23" s="9"/>
+      <c r="AJ23" s="9"/>
+      <c r="AK23" s="9"/>
+      <c r="AL23" s="9"/>
+      <c r="AM23" s="9"/>
+      <c r="AO23" s="9">
+        <f t="shared" ref="AO23:BA23" si="154">AO7/AO3</f>
+        <v>0.33957309842452993</v>
+      </c>
+      <c r="AP23" s="9">
         <f t="shared" si="154"/>
-        <v>0.19176146925421961</v>
-      </c>
-      <c r="AG23" s="9">
+        <v>0.26732730982220926</v>
+      </c>
+      <c r="AQ23" s="9">
         <f t="shared" si="154"/>
-        <v>0.17002920095566765</v>
-      </c>
-      <c r="AH23" s="9">
+        <v>0.22156620257709339</v>
+      </c>
+      <c r="AR23" s="9">
+        <f t="shared" si="154"/>
+        <v>0.1925384372495203</v>
+      </c>
+      <c r="AS23" s="9">
+        <f t="shared" si="154"/>
+        <v>0.24312225650832281</v>
+      </c>
+      <c r="AT23" s="9">
+        <f t="shared" si="154"/>
+        <v>0.24360644348921018</v>
+      </c>
+      <c r="AU23" s="9">
+        <f t="shared" si="154"/>
+        <v>0.19838101988286641</v>
+      </c>
+      <c r="AV23" s="9">
+        <f t="shared" si="154"/>
+        <v>0.17220217823785275</v>
+      </c>
+      <c r="AW23" s="9">
+        <f t="shared" si="154"/>
+        <v>0.17</v>
+      </c>
+      <c r="AX23" s="9">
         <f t="shared" si="154"/>
         <v>0.16</v>
       </c>
-      <c r="AI23" s="9"/>
-      <c r="AK23" s="9">
-        <f t="shared" ref="AK23:AW23" si="155">AK7/AK3</f>
-        <v>0.33957309842452993</v>
-      </c>
-      <c r="AL23" s="9">
-        <f t="shared" si="155"/>
-        <v>0.26732730982220926</v>
-      </c>
-      <c r="AM23" s="9">
-        <f t="shared" si="155"/>
-        <v>0.22156620257709339</v>
-      </c>
-      <c r="AN23" s="9">
-        <f t="shared" si="155"/>
-        <v>0.1925384372495203</v>
-      </c>
-      <c r="AO23" s="9">
-        <f t="shared" si="155"/>
-        <v>0.24312225650832281</v>
-      </c>
-      <c r="AP23" s="9">
-        <f t="shared" si="155"/>
-        <v>0.24360644348921018</v>
-      </c>
-      <c r="AQ23" s="9">
-        <f t="shared" si="155"/>
-        <v>0.19838101988286641</v>
-      </c>
-      <c r="AR23" s="9">
-        <f t="shared" si="155"/>
-        <v>0.17657106653389368</v>
-      </c>
-      <c r="AS23" s="9">
-        <f t="shared" si="155"/>
-        <v>0.17</v>
-      </c>
-      <c r="AT23" s="9">
+      <c r="AY23" s="9">
+        <f t="shared" si="154"/>
+        <v>0.16</v>
+      </c>
+      <c r="AZ23" s="9">
+        <f t="shared" si="154"/>
+        <v>0.16</v>
+      </c>
+      <c r="BA23" s="9">
+        <f t="shared" si="154"/>
+        <v>0.16</v>
+      </c>
+      <c r="BB23" s="9">
+        <f t="shared" ref="BB23:BF23" si="155">BB7/BB3</f>
+        <v>0.16</v>
+      </c>
+      <c r="BC23" s="9">
         <f t="shared" si="155"/>
         <v>0.16</v>
       </c>
-      <c r="AU23" s="9">
+      <c r="BD23" s="9">
         <f t="shared" si="155"/>
         <v>0.16</v>
       </c>
-      <c r="AV23" s="9">
+      <c r="BE23" s="9">
         <f t="shared" si="155"/>
         <v>0.16</v>
       </c>
-      <c r="AW23" s="9">
+      <c r="BF23" s="9">
         <f t="shared" si="155"/>
         <v>0.16</v>
       </c>
-      <c r="AX23" s="9">
-        <f t="shared" ref="AX23:BB23" si="156">AX7/AX3</f>
-        <v>0.16</v>
-      </c>
-      <c r="AY23" s="9">
-        <f t="shared" si="156"/>
-        <v>0.16</v>
-      </c>
-      <c r="AZ23" s="9">
-        <f t="shared" si="156"/>
-        <v>0.16</v>
-      </c>
-      <c r="BA23" s="9">
-        <f t="shared" si="156"/>
-        <v>0.16</v>
-      </c>
-      <c r="BB23" s="9">
-        <f t="shared" si="156"/>
-        <v>0.16</v>
-      </c>
-      <c r="BD23" t="s">
+      <c r="BH23" t="s">
         <v>42</v>
       </c>
-      <c r="BE23" s="4">
-        <f>NPV(BE22,AR15:FK15)</f>
-        <v>1005.6313757734623</v>
+      <c r="BI23" s="4">
+        <f>NPV(BI22,AW15:FO15)</f>
+        <v>2384.693285248045</v>
       </c>
     </row>
-    <row r="24" spans="2:57" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:61" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>56</v>
       </c>
@@ -5335,196 +5484,200 @@
       <c r="E24" s="9"/>
       <c r="F24" s="9"/>
       <c r="G24" s="9">
-        <f t="shared" ref="G24" si="157">G8/C8-1</f>
+        <f t="shared" ref="G24" si="156">G8/C8-1</f>
         <v>-3.7307380373073795E-2</v>
       </c>
       <c r="H24" s="9">
-        <f t="shared" ref="H24" si="158">H8/D8-1</f>
+        <f t="shared" ref="H24" si="157">H8/D8-1</f>
         <v>4.8543689320388328E-2</v>
       </c>
       <c r="I24" s="9">
-        <f t="shared" ref="I24" si="159">I8/E8-1</f>
+        <f t="shared" ref="I24" si="158">I8/E8-1</f>
         <v>-4.4081632653061309E-2</v>
       </c>
       <c r="J24" s="9">
-        <f t="shared" ref="J24" si="160">J8/F8-1</f>
+        <f t="shared" ref="J24" si="159">J8/F8-1</f>
         <v>1.0009285051067782</v>
       </c>
       <c r="K24" s="9">
-        <f t="shared" ref="K24" si="161">K8/G8-1</f>
+        <f t="shared" ref="K24" si="160">K8/G8-1</f>
         <v>0.13395113732097719</v>
       </c>
       <c r="L24" s="9">
-        <f t="shared" ref="L24" si="162">L8/H8-1</f>
+        <f t="shared" ref="L24" si="161">L8/H8-1</f>
         <v>-6.4043209876543217E-2</v>
       </c>
       <c r="M24" s="9">
-        <f t="shared" ref="M24" si="163">M8/I8-1</f>
+        <f t="shared" ref="M24" si="162">M8/I8-1</f>
         <v>7.8565328778821497E-2</v>
       </c>
       <c r="N24" s="9">
-        <f t="shared" ref="N24" si="164">N8/J8-1</f>
+        <f t="shared" ref="N24" si="163">N8/J8-1</f>
         <v>-0.31832946635730852</v>
       </c>
       <c r="O24" s="9">
-        <f t="shared" ref="O24" si="165">O8/K8-1</f>
+        <f t="shared" ref="O24" si="164">O8/K8-1</f>
         <v>0.20133729569093606</v>
       </c>
       <c r="P24" s="9">
-        <f t="shared" ref="P24" si="166">P8/L8-1</f>
+        <f t="shared" ref="P24" si="165">P8/L8-1</f>
         <v>0.47732893652102226</v>
       </c>
       <c r="Q24" s="9">
-        <f t="shared" ref="Q24" si="167">Q8/M8-1</f>
+        <f t="shared" ref="Q24" si="166">Q8/M8-1</f>
         <v>0.38796516231195577</v>
       </c>
       <c r="R24" s="9">
-        <f t="shared" ref="R24" si="168">R8/N8-1</f>
+        <f t="shared" ref="R24" si="167">R8/N8-1</f>
         <v>0.32334921715452691</v>
       </c>
       <c r="S24" s="9">
-        <f t="shared" ref="S24" si="169">S8/O8-1</f>
+        <f t="shared" ref="S24" si="168">S8/O8-1</f>
         <v>0.33518862090290669</v>
       </c>
       <c r="T24" s="9">
-        <f t="shared" ref="T24" si="170">T8/P8-1</f>
+        <f t="shared" ref="T24" si="169">T8/P8-1</f>
         <v>0.39006696428571441</v>
       </c>
       <c r="U24" s="9">
-        <f t="shared" ref="U24" si="171">U8/Q8-1</f>
+        <f t="shared" ref="U24" si="170">U8/Q8-1</f>
         <v>0.49686252139189935</v>
       </c>
       <c r="V24" s="9">
-        <f t="shared" ref="V24" si="172">V8/R8-1</f>
+        <f t="shared" ref="V24" si="171">V8/R8-1</f>
         <v>0.16203703703703698</v>
       </c>
       <c r="W24" s="9">
-        <f t="shared" ref="W24" si="173">W8/S8-1</f>
+        <f t="shared" ref="W24" si="172">W8/S8-1</f>
         <v>-0.11857341361741547</v>
       </c>
       <c r="X24" s="9">
-        <f t="shared" ref="X24" si="174">X8/T8-1</f>
+        <f t="shared" ref="X24" si="173">X8/T8-1</f>
         <v>-0.1292653552790044</v>
       </c>
       <c r="Y24" s="9">
-        <f t="shared" ref="Y24" si="175">Y8/U8-1</f>
+        <f t="shared" ref="Y24" si="174">Y8/U8-1</f>
         <v>-0.15739329268292679</v>
       </c>
       <c r="Z24" s="9">
-        <f t="shared" ref="Z24" si="176">Z8/V8-1</f>
+        <f t="shared" ref="Z24" si="175">Z8/V8-1</f>
         <v>1.4608233731739695E-2</v>
       </c>
       <c r="AA24" s="9">
-        <f t="shared" ref="AA24" si="177">AA8/W8-1</f>
+        <f t="shared" ref="AA24" si="176">AA8/W8-1</f>
         <v>0.19548081975827625</v>
       </c>
       <c r="AB24" s="9">
-        <f t="shared" ref="AB24" si="178">AB8/X8-1</f>
+        <f t="shared" ref="AB24" si="177">AB8/X8-1</f>
         <v>5.7169202397418184E-2</v>
       </c>
       <c r="AC24" s="9">
-        <f t="shared" ref="AC24" si="179">AC8/Y8-1</f>
+        <f t="shared" ref="AC24" si="178">AC8/Y8-1</f>
         <v>-4.5228403437358455E-4</v>
       </c>
       <c r="AD24" s="9">
-        <f t="shared" ref="AD24" si="180">AD8/Z8-1</f>
+        <f t="shared" ref="AD24" si="179">AD8/Z8-1</f>
         <v>5.2792321116928553E-2</v>
       </c>
       <c r="AE24" s="9">
-        <f t="shared" ref="AE24" si="181">AE8/AA8-1</f>
+        <f t="shared" ref="AE24" si="180">AE8/AA8-1</f>
         <v>3.4725274725274646E-2</v>
       </c>
       <c r="AF24" s="9">
-        <f t="shared" ref="AF24" si="182">AF8/AB8-1</f>
+        <f t="shared" ref="AF24" si="181">AF8/AB8-1</f>
         <v>9.0710859136502231E-2</v>
       </c>
       <c r="AG24" s="9">
-        <f t="shared" ref="AG24" si="183">AG8/AC8-1</f>
+        <f t="shared" ref="AG24" si="182">AG8/AC8-1</f>
         <v>0.13710407239819</v>
       </c>
       <c r="AH24" s="9">
-        <f t="shared" ref="AH24" si="184">AH8/AD8-1</f>
-        <v>9.9999999999999867E-2</v>
+        <f t="shared" ref="AH24" si="183">AH8/AD8-1</f>
+        <v>4.1442188147533532E-3</v>
       </c>
       <c r="AI24" s="9"/>
+      <c r="AJ24" s="9"/>
       <c r="AK24" s="9"/>
-      <c r="AL24" s="9">
-        <f t="shared" si="146"/>
+      <c r="AL24" s="9"/>
+      <c r="AM24" s="9"/>
+      <c r="AO24" s="9"/>
+      <c r="AP24" s="9">
+        <f t="shared" si="145"/>
         <v>0.2175644518968769</v>
       </c>
-      <c r="AM24" s="9">
-        <f t="shared" si="146"/>
+      <c r="AQ24" s="9">
+        <f t="shared" si="145"/>
         <v>-8.9171974522292974E-2</v>
       </c>
-      <c r="AN24" s="9">
-        <f t="shared" si="146"/>
+      <c r="AR24" s="9">
+        <f t="shared" si="145"/>
         <v>0.343035343035343</v>
       </c>
-      <c r="AO24" s="9">
-        <f t="shared" si="146"/>
+      <c r="AS24" s="9">
+        <f t="shared" si="145"/>
         <v>0.34154235857022219</v>
       </c>
-      <c r="AP24" s="9">
-        <f t="shared" si="146"/>
+      <c r="AT24" s="9">
+        <f t="shared" si="145"/>
         <v>-0.10049302423161643</v>
       </c>
-      <c r="AQ24" s="9">
-        <f t="shared" si="146"/>
+      <c r="AU24" s="9">
+        <f t="shared" si="145"/>
         <v>7.1836734693877524E-2</v>
       </c>
-      <c r="AR24" s="9">
-        <f t="shared" si="146"/>
-        <v>9.0447176585790601E-2</v>
-      </c>
-      <c r="AS24" s="9">
-        <f t="shared" si="146"/>
+      <c r="AV24" s="9">
+        <f t="shared" si="145"/>
+        <v>6.5281253400065298E-2</v>
+      </c>
+      <c r="AW24" s="9">
+        <f t="shared" si="145"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AT24" s="9">
-        <f t="shared" si="146"/>
+      <c r="AX24" s="9">
+        <f t="shared" si="145"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AU24" s="9">
-        <f t="shared" si="146"/>
+      <c r="AY24" s="9">
+        <f t="shared" si="145"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AV24" s="9">
-        <f t="shared" si="146"/>
+      <c r="AZ24" s="9">
+        <f t="shared" si="145"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AW24" s="9">
-        <f t="shared" si="146"/>
+      <c r="BA24" s="9">
+        <f t="shared" si="145"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AX24" s="9">
-        <f t="shared" si="146"/>
+      <c r="BB24" s="9">
+        <f t="shared" si="145"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AY24" s="9">
-        <f t="shared" ref="AY24" si="185">AY8/AX8-1</f>
+      <c r="BC24" s="9">
+        <f t="shared" ref="BC24" si="184">BC8/BB8-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AZ24" s="9">
-        <f t="shared" ref="AZ24" si="186">AZ8/AY8-1</f>
+      <c r="BD24" s="9">
+        <f t="shared" ref="BD24" si="185">BD8/BC8-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BA24" s="9">
-        <f t="shared" ref="BA24" si="187">BA8/AZ8-1</f>
+      <c r="BE24" s="9">
+        <f t="shared" ref="BE24" si="186">BE8/BD8-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BB24" s="9">
-        <f t="shared" ref="BB24" si="188">BB8/BA8-1</f>
+      <c r="BF24" s="9">
+        <f t="shared" ref="BF24" si="187">BF8/BE8-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BD24" t="s">
+      <c r="BH24" t="s">
         <v>43</v>
       </c>
-      <c r="BE24" s="4">
+      <c r="BI24" s="4">
         <f>Main!D8</f>
-        <v>-682.90000000000009</v>
+        <v>-596.30000000000018</v>
       </c>
     </row>
-    <row r="25" spans="2:57" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:61" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>31</v>
       </c>
@@ -5533,211 +5686,215 @@
         <v>-4.1655818797188236E-3</v>
       </c>
       <c r="D25" s="9">
-        <f t="shared" ref="D25:N25" si="189">D14/D13</f>
+        <f t="shared" ref="D25:N25" si="188">D14/D13</f>
         <v>-3.1232254400908582E-3</v>
       </c>
       <c r="E25" s="9">
+        <f t="shared" si="188"/>
+        <v>-6.1538461538461541E-4</v>
+      </c>
+      <c r="F25" s="9">
+        <f t="shared" si="188"/>
+        <v>-2.0833333333333333E-3</v>
+      </c>
+      <c r="G25" s="9">
+        <f t="shared" si="188"/>
+        <v>9.6680631646793396E-4</v>
+      </c>
+      <c r="H25" s="9">
+        <f t="shared" si="188"/>
+        <v>-4.3273013375295048E-3</v>
+      </c>
+      <c r="I25" s="9">
+        <f t="shared" si="188"/>
+        <v>5.6768558951965069E-3</v>
+      </c>
+      <c r="J25" s="9">
+        <f t="shared" si="188"/>
+        <v>-1.2484394506866415E-3</v>
+      </c>
+      <c r="K25" s="9">
+        <f t="shared" si="188"/>
+        <v>-2.2935779816513767E-3</v>
+      </c>
+      <c r="L25" s="9">
+        <f t="shared" si="188"/>
+        <v>3.0590394616090556E-3</v>
+      </c>
+      <c r="M25" s="9">
+        <f t="shared" si="188"/>
+        <v>0</v>
+      </c>
+      <c r="N25" s="9">
+        <f t="shared" si="188"/>
+        <v>-0.19086585610190757</v>
+      </c>
+      <c r="O25" s="9">
+        <f t="shared" ref="O25:R25" si="189">O14/O13</f>
+        <v>-4.905395935529082E-3</v>
+      </c>
+      <c r="P25" s="9">
         <f t="shared" si="189"/>
-        <v>-6.1538461538461541E-4</v>
-      </c>
-      <c r="F25" s="9">
+        <v>1.2377850162866454E-2</v>
+      </c>
+      <c r="Q25" s="9">
         <f t="shared" si="189"/>
-        <v>-2.0833333333333333E-3</v>
-      </c>
-      <c r="G25" s="9">
+        <v>-1.4104372355430182E-2</v>
+      </c>
+      <c r="R25" s="9">
         <f t="shared" si="189"/>
-        <v>9.6680631646793396E-4</v>
-      </c>
-      <c r="H25" s="9">
-        <f t="shared" si="189"/>
-        <v>-4.3273013375295048E-3</v>
-      </c>
-      <c r="I25" s="9">
-        <f t="shared" si="189"/>
-        <v>5.6768558951965069E-3</v>
-      </c>
-      <c r="J25" s="9">
-        <f t="shared" si="189"/>
-        <v>-1.2484394506866415E-3</v>
-      </c>
-      <c r="K25" s="9">
-        <f t="shared" si="189"/>
-        <v>-2.2935779816513767E-3</v>
-      </c>
-      <c r="L25" s="9">
-        <f t="shared" si="189"/>
-        <v>3.0590394616090556E-3</v>
-      </c>
-      <c r="M25" s="9">
-        <f t="shared" si="189"/>
-        <v>0</v>
-      </c>
-      <c r="N25" s="9">
-        <f t="shared" si="189"/>
-        <v>-0.19086585610190757</v>
-      </c>
-      <c r="O25" s="9">
-        <f t="shared" ref="O25:R25" si="190">O14/O13</f>
-        <v>-4.905395935529082E-3</v>
-      </c>
-      <c r="P25" s="9">
+        <v>0.36516853932584203</v>
+      </c>
+      <c r="S25" s="9">
+        <f t="shared" ref="S25:AD25" si="190">S14/S13</f>
+        <v>-2.4202733485193625E-2</v>
+      </c>
+      <c r="T25" s="9">
         <f t="shared" si="190"/>
-        <v>1.2377850162866454E-2</v>
-      </c>
-      <c r="Q25" s="9">
+        <v>-1.6863406408094441E-2</v>
+      </c>
+      <c r="U25" s="9">
         <f t="shared" si="190"/>
-        <v>-1.4104372355430182E-2</v>
-      </c>
-      <c r="R25" s="9">
+        <v>-1.8612178838761886E-2</v>
+      </c>
+      <c r="V25" s="9">
         <f t="shared" si="190"/>
-        <v>0.36516853932584203</v>
-      </c>
-      <c r="S25" s="9">
-        <f t="shared" ref="S25:AD25" si="191">S14/S13</f>
-        <v>-2.4202733485193625E-2</v>
-      </c>
-      <c r="T25" s="9">
+        <v>-1.4778325123152714E-2</v>
+      </c>
+      <c r="W25" s="9">
+        <f t="shared" si="190"/>
+        <v>-2.113113735239279E-2</v>
+      </c>
+      <c r="X25" s="9">
+        <f t="shared" si="190"/>
+        <v>-3.312346016972352E-2</v>
+      </c>
+      <c r="Y25" s="9">
+        <f t="shared" si="190"/>
+        <v>-1.5999999999999997E-2</v>
+      </c>
+      <c r="Z25" s="9">
+        <f t="shared" si="190"/>
+        <v>-1.3474887709269086E-2</v>
+      </c>
+      <c r="AA25" s="9">
+        <f t="shared" si="190"/>
+        <v>-2.3146595102314649E-2</v>
+      </c>
+      <c r="AB25" s="9">
+        <f t="shared" si="190"/>
+        <v>-2.1372790793259346E-2</v>
+      </c>
+      <c r="AC25" s="9">
+        <f t="shared" si="190"/>
+        <v>-5.7201929703652649E-2</v>
+      </c>
+      <c r="AD25" s="9">
+        <f t="shared" si="190"/>
+        <v>0.36111111111111277</v>
+      </c>
+      <c r="AE25" s="9">
+        <f t="shared" ref="AE25:AH25" si="191">AE14/AE13</f>
+        <v>-6.397562833206398E-2</v>
+      </c>
+      <c r="AF25" s="9">
         <f t="shared" si="191"/>
-        <v>-1.6863406408094441E-2</v>
-      </c>
-      <c r="U25" s="9">
+        <v>-3.0207924676343683E-2</v>
+      </c>
+      <c r="AG25" s="9">
         <f t="shared" si="191"/>
-        <v>-1.8612178838761886E-2</v>
-      </c>
-      <c r="V25" s="9">
+        <v>-4.8590864917395504E-3</v>
+      </c>
+      <c r="AH25" s="9">
         <f t="shared" si="191"/>
-        <v>-1.4778325123152714E-2</v>
-      </c>
-      <c r="W25" s="9">
-        <f t="shared" si="191"/>
-        <v>-2.113113735239279E-2</v>
-      </c>
-      <c r="X25" s="9">
-        <f t="shared" si="191"/>
-        <v>-3.312346016972352E-2</v>
-      </c>
-      <c r="Y25" s="9">
-        <f t="shared" si="191"/>
-        <v>-1.5999999999999997E-2</v>
-      </c>
-      <c r="Z25" s="9">
-        <f t="shared" si="191"/>
-        <v>-1.3474887709269086E-2</v>
-      </c>
-      <c r="AA25" s="9">
-        <f t="shared" si="191"/>
-        <v>-2.3146595102314649E-2</v>
-      </c>
-      <c r="AB25" s="9">
-        <f t="shared" si="191"/>
-        <v>-2.1372790793259346E-2</v>
-      </c>
-      <c r="AC25" s="9">
-        <f t="shared" si="191"/>
-        <v>-5.7201929703652649E-2</v>
-      </c>
-      <c r="AD25" s="9">
-        <f t="shared" si="191"/>
-        <v>0.36111111111111277</v>
-      </c>
-      <c r="AE25" s="9">
-        <f t="shared" ref="AE25:AH25" si="192">AE14/AE13</f>
-        <v>-6.397562833206398E-2</v>
-      </c>
-      <c r="AF25" s="9">
+        <v>-0.18897637795275554</v>
+      </c>
+      <c r="AI25" s="9"/>
+      <c r="AJ25" s="9"/>
+      <c r="AK25" s="9"/>
+      <c r="AL25" s="9"/>
+      <c r="AM25" s="9"/>
+      <c r="AO25" s="9">
+        <f t="shared" ref="AO25:AQ25" si="192">AO14/AO13</f>
+        <v>-2.6330487512965773E-3</v>
+      </c>
+      <c r="AP25" s="9">
         <f t="shared" si="192"/>
-        <v>-3.0207924676343683E-2</v>
-      </c>
-      <c r="AG25" s="9">
+        <v>1.9346101760495268E-4</v>
+      </c>
+      <c r="AQ25" s="9">
         <f t="shared" si="192"/>
-        <v>-4.8590864917395504E-3</v>
-      </c>
-      <c r="AH25" s="9">
-        <f t="shared" si="192"/>
-        <v>0.05</v>
-      </c>
-      <c r="AI25" s="9"/>
-      <c r="AK25" s="9">
-        <f t="shared" ref="AK25:AM25" si="193">AK14/AK13</f>
-        <v>-2.6330487512965773E-3</v>
-      </c>
-      <c r="AL25" s="9">
+        <v>-1.9225971046551688E-2</v>
+      </c>
+      <c r="AR25" s="9">
+        <f t="shared" ref="AR25:BA25" si="193">AR14/AR13</f>
+        <v>-2.846900042176297E-2</v>
+      </c>
+      <c r="AS25" s="9">
         <f t="shared" si="193"/>
-        <v>1.9346101760495268E-4</v>
-      </c>
-      <c r="AM25" s="9">
+        <v>-1.8707923355774213E-2</v>
+      </c>
+      <c r="AT25" s="9">
         <f t="shared" si="193"/>
-        <v>-1.9225971046551688E-2</v>
-      </c>
-      <c r="AN25" s="9">
-        <f t="shared" ref="AN25:AW25" si="194">AN14/AN13</f>
-        <v>-2.846900042176297E-2</v>
-      </c>
-      <c r="AO25" s="9">
+        <v>-2.1629972962533797E-2</v>
+      </c>
+      <c r="AU25" s="9">
+        <f t="shared" si="193"/>
+        <v>-3.8089570004463634E-2</v>
+      </c>
+      <c r="AV25" s="9">
+        <f t="shared" si="193"/>
+        <v>-2.0842572062084293E-2</v>
+      </c>
+      <c r="AW25" s="9">
+        <f t="shared" si="193"/>
+        <v>0.2</v>
+      </c>
+      <c r="AX25" s="9">
+        <f t="shared" si="193"/>
+        <v>0.2</v>
+      </c>
+      <c r="AY25" s="9">
+        <f t="shared" si="193"/>
+        <v>0.19999999999999998</v>
+      </c>
+      <c r="AZ25" s="9">
+        <f t="shared" si="193"/>
+        <v>0.2</v>
+      </c>
+      <c r="BA25" s="9">
+        <f t="shared" si="193"/>
+        <v>0.2</v>
+      </c>
+      <c r="BB25" s="9">
+        <f t="shared" ref="BB25:BF25" si="194">BB14/BB13</f>
+        <v>0.2</v>
+      </c>
+      <c r="BC25" s="9">
         <f t="shared" si="194"/>
-        <v>-1.8707923355774213E-2</v>
-      </c>
-      <c r="AP25" s="9">
-        <f t="shared" si="194"/>
-        <v>-2.1629972962533797E-2</v>
-      </c>
-      <c r="AQ25" s="9">
-        <f t="shared" si="194"/>
-        <v>-3.8089570004463634E-2</v>
-      </c>
-      <c r="AR25" s="9">
-        <f t="shared" si="194"/>
-        <v>-3.2578789880697963E-2</v>
-      </c>
-      <c r="AS25" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="BD25" s="9">
         <f t="shared" si="194"/>
         <v>0.19999999999999998</v>
       </c>
-      <c r="AT25" s="9">
+      <c r="BE25" s="9">
         <f t="shared" si="194"/>
         <v>0.2</v>
       </c>
-      <c r="AU25" s="9">
+      <c r="BF25" s="9">
         <f t="shared" si="194"/>
         <v>0.2</v>
       </c>
-      <c r="AV25" s="9">
-        <f t="shared" si="194"/>
-        <v>0.2</v>
-      </c>
-      <c r="AW25" s="9">
-        <f t="shared" si="194"/>
-        <v>0.2</v>
-      </c>
-      <c r="AX25" s="9">
-        <f t="shared" ref="AX25:BB25" si="195">AX14/AX13</f>
-        <v>0.20000000000000004</v>
-      </c>
-      <c r="AY25" s="9">
-        <f t="shared" si="195"/>
-        <v>0.19999999999999998</v>
-      </c>
-      <c r="AZ25" s="9">
-        <f t="shared" si="195"/>
-        <v>0.2</v>
-      </c>
-      <c r="BA25" s="9">
-        <f t="shared" si="195"/>
-        <v>0.2</v>
-      </c>
-      <c r="BB25" s="9">
-        <f t="shared" si="195"/>
-        <v>0.2</v>
-      </c>
-      <c r="BD25" t="s">
+      <c r="BH25" t="s">
         <v>44</v>
       </c>
-      <c r="BE25" s="4">
-        <f>BE23+BE24</f>
-        <v>322.73137577346222</v>
+      <c r="BI25" s="4">
+        <f>BI23+BI24</f>
+        <v>1788.3932852480448</v>
       </c>
     </row>
-    <row r="26" spans="2:57" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:61" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>57</v>
       </c>
@@ -5746,332 +5903,340 @@
         <v>-1.6718682271348073</v>
       </c>
       <c r="D26" s="9">
-        <f t="shared" ref="D26:R26" si="196">D15/D3</f>
+        <f t="shared" ref="D26:R26" si="195">D15/D3</f>
         <v>-1.3469309950438426</v>
       </c>
       <c r="E26" s="9">
+        <f t="shared" si="195"/>
+        <v>-1.0923748740342627</v>
+      </c>
+      <c r="F26" s="9">
+        <f t="shared" si="195"/>
+        <v>-0.49345986150294957</v>
+      </c>
+      <c r="G26" s="9">
+        <f t="shared" si="195"/>
+        <v>-0.96754057428214757</v>
+      </c>
+      <c r="H26" s="9">
+        <f t="shared" si="195"/>
+        <v>-0.65798969072164948</v>
+      </c>
+      <c r="I26" s="9">
+        <f t="shared" si="195"/>
+        <v>-0.51030927835051543</v>
+      </c>
+      <c r="J26" s="9">
+        <f t="shared" si="195"/>
+        <v>-0.42895346764129083</v>
+      </c>
+      <c r="K26" s="9">
+        <f t="shared" si="195"/>
+        <v>-0.66140540540540527</v>
+      </c>
+      <c r="L26" s="9">
+        <f t="shared" si="195"/>
+        <v>-0.71752531924262419</v>
+      </c>
+      <c r="M26" s="9">
+        <f t="shared" si="195"/>
+        <v>-0.29306026226609688</v>
+      </c>
+      <c r="N26" s="9">
+        <f t="shared" si="195"/>
+        <v>-0.12392296718972901</v>
+      </c>
+      <c r="O26" s="9">
+        <f t="shared" si="195"/>
+        <v>-0.37266112266112261</v>
+      </c>
+      <c r="P26" s="9">
+        <f t="shared" si="195"/>
+        <v>-0.15436309948070454</v>
+      </c>
+      <c r="Q26" s="9">
+        <f t="shared" si="195"/>
+        <v>-6.7353629976580801E-2</v>
+      </c>
+      <c r="R26" s="9">
+        <f t="shared" si="195"/>
+        <v>1.741274366284002E-2</v>
+      </c>
+      <c r="S26" s="9">
+        <f t="shared" ref="S26:AD26" si="196">S15/S3</f>
+        <v>-0.33847746306577575</v>
+      </c>
+      <c r="T26" s="9">
         <f t="shared" si="196"/>
-        <v>-1.0923748740342627</v>
-      </c>
-      <c r="F26" s="9">
+        <v>-0.37996219281663501</v>
+      </c>
+      <c r="U26" s="9">
         <f t="shared" si="196"/>
-        <v>-0.49345986150294957</v>
-      </c>
-      <c r="G26" s="9">
+        <v>-0.44616747895436409</v>
+      </c>
+      <c r="V26" s="9">
         <f t="shared" si="196"/>
-        <v>-0.96754057428214757</v>
-      </c>
-      <c r="H26" s="9">
+        <v>-0.22189736092944518</v>
+      </c>
+      <c r="W26" s="9">
         <f t="shared" si="196"/>
-        <v>-0.65798969072164948</v>
-      </c>
-      <c r="I26" s="9">
+        <v>-0.33238923730528019</v>
+      </c>
+      <c r="X26" s="9">
         <f t="shared" si="196"/>
-        <v>-0.51030927835051543</v>
-      </c>
-      <c r="J26" s="9">
+        <v>-0.35347007586400669</v>
+      </c>
+      <c r="Y26" s="9">
         <f t="shared" si="196"/>
-        <v>-0.42895346764129083</v>
-      </c>
-      <c r="K26" s="9">
+        <v>-0.30986033989567568</v>
+      </c>
+      <c r="Z26" s="9">
         <f t="shared" si="196"/>
-        <v>-0.66140540540540527</v>
-      </c>
-      <c r="L26" s="9">
+        <v>-0.18232571806361572</v>
+      </c>
+      <c r="AA26" s="9">
         <f t="shared" si="196"/>
-        <v>-0.71752531924262419</v>
-      </c>
-      <c r="M26" s="9">
+        <v>-0.25527284901238712</v>
+      </c>
+      <c r="AB26" s="9">
         <f t="shared" si="196"/>
-        <v>-0.29306026226609688</v>
-      </c>
-      <c r="N26" s="9">
+        <v>-0.20092173350582151</v>
+      </c>
+      <c r="AC26" s="9">
         <f t="shared" si="196"/>
-        <v>-0.12392296718972901</v>
-      </c>
-      <c r="O26" s="9">
+        <v>-0.11176684881602916</v>
+      </c>
+      <c r="AD26" s="9">
         <f t="shared" si="196"/>
-        <v>-0.37266112266112261</v>
-      </c>
-      <c r="P26" s="9">
-        <f t="shared" si="196"/>
-        <v>-0.15436309948070454</v>
-      </c>
-      <c r="Q26" s="9">
-        <f t="shared" si="196"/>
-        <v>-6.7353629976580801E-2</v>
-      </c>
-      <c r="R26" s="9">
-        <f t="shared" si="196"/>
-        <v>1.741274366284002E-2</v>
-      </c>
-      <c r="S26" s="9">
-        <f t="shared" ref="S26:AD26" si="197">S15/S3</f>
-        <v>-0.33847746306577575</v>
-      </c>
-      <c r="T26" s="9">
+        <v>5.9076606947922276E-3</v>
+      </c>
+      <c r="AE26" s="9">
+        <f t="shared" ref="AE26:AH26" si="197">AE15/AE3</f>
+        <v>-0.1024794600938967</v>
+      </c>
+      <c r="AF26" s="9">
         <f t="shared" si="197"/>
-        <v>-0.37996219281663501</v>
-      </c>
-      <c r="U26" s="9">
+        <v>-0.19525615287381951</v>
+      </c>
+      <c r="AG26" s="9">
         <f t="shared" si="197"/>
-        <v>-0.44616747895436409</v>
-      </c>
-      <c r="V26" s="9">
+        <v>-6.8622245818954125E-2</v>
+      </c>
+      <c r="AH26" s="9">
         <f t="shared" si="197"/>
-        <v>-0.22189736092944518</v>
-      </c>
-      <c r="W26" s="9">
-        <f t="shared" si="197"/>
-        <v>-0.33238923730528019</v>
-      </c>
-      <c r="X26" s="9">
-        <f t="shared" si="197"/>
-        <v>-0.35347007586400669</v>
-      </c>
-      <c r="Y26" s="9">
-        <f t="shared" si="197"/>
-        <v>-0.30986033989567568</v>
-      </c>
-      <c r="Z26" s="9">
-        <f t="shared" si="197"/>
-        <v>-0.18232571806361572</v>
-      </c>
-      <c r="AA26" s="9">
-        <f t="shared" si="197"/>
-        <v>-0.25527284901238712</v>
-      </c>
-      <c r="AB26" s="9">
-        <f t="shared" si="197"/>
-        <v>-0.20092173350582151</v>
-      </c>
-      <c r="AC26" s="9">
-        <f t="shared" si="197"/>
-        <v>-0.11176684881602916</v>
-      </c>
-      <c r="AD26" s="9">
-        <f t="shared" si="197"/>
-        <v>5.9076606947922276E-3</v>
-      </c>
-      <c r="AE26" s="9">
-        <f t="shared" ref="AE26:AH26" si="198">AE15/AE3</f>
-        <v>-0.1024794600938967</v>
-      </c>
-      <c r="AF26" s="9">
+        <v>2.639091173900383E-2</v>
+      </c>
+      <c r="AI26" s="9"/>
+      <c r="AJ26" s="9"/>
+      <c r="AK26" s="9"/>
+      <c r="AL26" s="9"/>
+      <c r="AM26" s="9"/>
+      <c r="AO26" s="9">
+        <f t="shared" ref="AO26:BA26" si="198">AO15/AO3</f>
+        <v>-1.0643740470946976</v>
+      </c>
+      <c r="AP26" s="9">
         <f t="shared" si="198"/>
-        <v>-0.19525615287381951</v>
-      </c>
-      <c r="AG26" s="9">
+        <v>-0.60250655785485263</v>
+      </c>
+      <c r="AQ26" s="9">
         <f t="shared" si="198"/>
-        <v>-6.8622245818954125E-2</v>
-      </c>
-      <c r="AH26" s="9">
+        <v>-0.3764435313360196</v>
+      </c>
+      <c r="AR26" s="9">
         <f t="shared" si="198"/>
-        <v>-4.5535137976222386E-3</v>
-      </c>
-      <c r="AI26" s="9"/>
-      <c r="AK26" s="9">
-        <f t="shared" ref="AK26:AW26" si="199">AK15/AK3</f>
-        <v>-1.0643740470946976</v>
-      </c>
-      <c r="AL26" s="9">
+        <v>-0.11845716645211433</v>
+      </c>
+      <c r="AS26" s="9">
+        <f t="shared" si="198"/>
+        <v>-0.3419748793950193</v>
+      </c>
+      <c r="AT26" s="9">
+        <f t="shared" si="198"/>
+        <v>-0.28711302157961011</v>
+      </c>
+      <c r="AU26" s="9">
+        <f t="shared" si="198"/>
+        <v>-0.13013392024471218</v>
+      </c>
+      <c r="AV26" s="9">
+        <f t="shared" si="198"/>
+        <v>-7.7620797788043164E-2</v>
+      </c>
+      <c r="AW26" s="9">
+        <f t="shared" si="198"/>
+        <v>-3.7906901939700047E-2</v>
+      </c>
+      <c r="AX26" s="9">
+        <f t="shared" si="198"/>
+        <v>-7.3993198130638252E-3</v>
+      </c>
+      <c r="AY26" s="9">
+        <f t="shared" si="198"/>
+        <v>4.5168366324857719E-3</v>
+      </c>
+      <c r="AZ26" s="9">
+        <f t="shared" si="198"/>
+        <v>1.2750685024061971E-2</v>
+      </c>
+      <c r="BA26" s="9">
+        <f t="shared" si="198"/>
+        <v>1.7735198653472582E-2</v>
+      </c>
+      <c r="BB26" s="9">
+        <f t="shared" ref="BB26:BF26" si="199">BB15/BB3</f>
+        <v>2.3705309585691323E-2</v>
+      </c>
+      <c r="BC26" s="9">
         <f t="shared" si="199"/>
-        <v>-0.60250655785485263</v>
-      </c>
-      <c r="AM26" s="9">
+        <v>2.9574860261259914E-2</v>
+      </c>
+      <c r="BD26" s="9">
         <f t="shared" si="199"/>
-        <v>-0.3764435313360196</v>
-      </c>
-      <c r="AN26" s="9">
+        <v>3.5329242315334478E-2</v>
+      </c>
+      <c r="BE26" s="9">
         <f t="shared" si="199"/>
-        <v>-0.11845716645211433</v>
-      </c>
-      <c r="AO26" s="9">
+        <v>4.0970448709938337E-2</v>
+      </c>
+      <c r="BF26" s="9">
         <f t="shared" si="199"/>
-        <v>-0.3419748793950193</v>
-      </c>
-      <c r="AP26" s="9">
-        <f t="shared" si="199"/>
-        <v>-0.28711302157961011</v>
-      </c>
-      <c r="AQ26" s="9">
-        <f t="shared" si="199"/>
-        <v>-0.13013392024471218</v>
-      </c>
-      <c r="AR26" s="9">
-        <f t="shared" si="199"/>
-        <v>-8.7057365845518417E-2</v>
-      </c>
-      <c r="AS26" s="9">
-        <f t="shared" si="199"/>
-        <v>-4.3836799752948741E-2</v>
-      </c>
-      <c r="AT26" s="9">
-        <f t="shared" si="199"/>
-        <v>-2.1019721741958788E-2</v>
-      </c>
-      <c r="AU26" s="9">
-        <f t="shared" si="199"/>
-        <v>-8.9888115869289128E-3</v>
-      </c>
-      <c r="AV26" s="9">
-        <f t="shared" si="199"/>
-        <v>-5.8005384409693208E-4</v>
-      </c>
-      <c r="AW26" s="9">
-        <f t="shared" si="199"/>
-        <v>4.5273682808937617E-3</v>
-      </c>
-      <c r="AX26" s="9">
-        <f t="shared" ref="AX26:BB26" si="200">AX15/AX3</f>
-        <v>1.0674461281012316E-2</v>
-      </c>
-      <c r="AY26" s="9">
-        <f t="shared" si="200"/>
-        <v>1.6718318130432508E-2</v>
-      </c>
-      <c r="AZ26" s="9">
-        <f t="shared" si="200"/>
-        <v>2.2643518318654014E-2</v>
-      </c>
-      <c r="BA26" s="9">
-        <f t="shared" si="200"/>
-        <v>2.8452110232763672E-2</v>
-      </c>
-      <c r="BB26" s="9">
-        <f t="shared" si="200"/>
-        <v>3.4146369049389995E-2</v>
-      </c>
-      <c r="BD26" t="s">
+        <v>4.6500687051858274E-2</v>
+      </c>
+      <c r="BH26" t="s">
         <v>45</v>
       </c>
-      <c r="BE26" s="5">
-        <f>BE25/BB16</f>
-        <v>0.19023364324990405</v>
+      <c r="BI26" s="5">
+        <f>BI25/BF16</f>
+        <v>1.054166392719154</v>
       </c>
     </row>
-    <row r="27" spans="2:57" x14ac:dyDescent="0.3">
-      <c r="BD27" t="s">
+    <row r="27" spans="2:61" x14ac:dyDescent="0.3">
+      <c r="BH27" t="s">
         <v>46</v>
       </c>
-      <c r="BE27" s="5">
+      <c r="BI27" s="5">
         <f>Main!D3</f>
-        <v>8.58</v>
+        <v>5.12</v>
       </c>
     </row>
-    <row r="28" spans="2:57" x14ac:dyDescent="0.3">
-      <c r="BD28" s="1" t="s">
+    <row r="28" spans="2:61" x14ac:dyDescent="0.3">
+      <c r="BH28" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="BE28" s="10">
-        <f>BE26/BE27-1</f>
-        <v>-0.97782824670747037</v>
+      <c r="BI28" s="10">
+        <f>BI26/BI27-1</f>
+        <v>-0.79410812642204021</v>
       </c>
     </row>
-    <row r="29" spans="2:57" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:61" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B29" s="1" t="s">
         <v>74</v>
       </c>
       <c r="Z29" s="8">
-        <f>Z15</f>
+        <f t="shared" ref="Z29:AH29" si="200">Z15</f>
         <v>-248.20000000000007</v>
       </c>
       <c r="AA29" s="8">
-        <f>AA15</f>
+        <f t="shared" si="200"/>
         <v>-305.00000000000011</v>
       </c>
       <c r="AB29" s="8">
-        <f>AB15</f>
+        <f t="shared" si="200"/>
         <v>-248.50000000000003</v>
       </c>
       <c r="AC29" s="8">
-        <f>AC15</f>
+        <f t="shared" si="200"/>
         <v>-153.40000000000003</v>
       </c>
       <c r="AD29" s="8">
-        <f>AD15</f>
+        <f t="shared" si="200"/>
         <v>9.1999999999999353</v>
       </c>
       <c r="AE29" s="8">
-        <f>AE15</f>
+        <f t="shared" si="200"/>
         <v>-139.69999999999999</v>
       </c>
       <c r="AF29" s="8">
-        <f>AF15</f>
+        <f t="shared" si="200"/>
         <v>-262.59999999999985</v>
       </c>
       <c r="AG29" s="8">
-        <f>AG15</f>
+        <f t="shared" si="200"/>
         <v>-103.40000000000006</v>
       </c>
       <c r="AH29" s="8">
-        <f>AH15</f>
-        <v>-7.6584820000000811</v>
-      </c>
-      <c r="AO29" s="8">
-        <f>AO15</f>
+        <f t="shared" si="200"/>
+        <v>45.300000000000075</v>
+      </c>
+      <c r="AI29" s="8"/>
+      <c r="AJ29" s="8"/>
+      <c r="AK29" s="8"/>
+      <c r="AL29" s="8"/>
+      <c r="AS29" s="8">
+        <f>AS15</f>
         <v>-1573.6999999999998</v>
       </c>
-      <c r="AP29" s="8">
-        <f>AP15</f>
+      <c r="AT29" s="8">
+        <f>AT15</f>
         <v>-1322.5</v>
       </c>
-      <c r="AQ29" s="8">
-        <f>AQ15</f>
+      <c r="AU29" s="8">
+        <f>AU15</f>
         <v>-697.69999999999982</v>
       </c>
-      <c r="AR29" s="8">
-        <f t="shared" ref="AR29:BB29" si="201">AR15</f>
-        <v>-513.35848199999953</v>
-      </c>
-      <c r="AS29" s="8">
-        <f t="shared" si="201"/>
-        <v>-276.59086915199958</v>
-      </c>
-      <c r="AT29" s="8">
-        <f t="shared" si="201"/>
-        <v>-140.58268229043148</v>
-      </c>
-      <c r="AU29" s="8">
-        <f t="shared" si="201"/>
-        <v>-63.124280233446051</v>
-      </c>
       <c r="AV29" s="8">
-        <f t="shared" si="201"/>
-        <v>-4.2363887921343322</v>
+        <f t="shared" ref="AV29:BF29" si="201">AV15</f>
+        <v>-460.3999999999993</v>
       </c>
       <c r="AW29" s="8">
         <f t="shared" si="201"/>
-        <v>34.057326248893624</v>
+        <v>-245.07668799999925</v>
       </c>
       <c r="AX29" s="8">
         <f t="shared" si="201"/>
-        <v>82.708075742417108</v>
+        <v>-50.708571327999522</v>
       </c>
       <c r="AY29" s="8">
         <f t="shared" si="201"/>
-        <v>133.42332529863276</v>
+        <v>32.502237402752705</v>
       </c>
       <c r="AZ29" s="8">
         <f t="shared" si="201"/>
-        <v>186.13168451358337</v>
+        <v>95.421388559404548</v>
       </c>
       <c r="BA29" s="8">
         <f t="shared" si="201"/>
-        <v>240.8951782578998</v>
+        <v>136.70534540368402</v>
       </c>
       <c r="BB29" s="8">
         <f t="shared" si="201"/>
-        <v>297.77989960923384</v>
-      </c>
-      <c r="BD29" t="s">
+        <v>188.20549327221835</v>
+      </c>
+      <c r="BC29" s="8">
+        <f t="shared" si="201"/>
+        <v>241.85027738704281</v>
+      </c>
+      <c r="BD29" s="8">
+        <f t="shared" si="201"/>
+        <v>297.57431100970842</v>
+      </c>
+      <c r="BE29" s="8">
+        <f t="shared" si="201"/>
+        <v>355.44225732139557</v>
+      </c>
+      <c r="BF29" s="8">
+        <f t="shared" si="201"/>
+        <v>415.52287035997085</v>
+      </c>
+      <c r="BH29" t="s">
         <v>48</v>
       </c>
-      <c r="BE29" s="6" t="s">
+      <c r="BI29" s="6" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="30" spans="2:57" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:61" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>75</v>
       </c>
@@ -6100,63 +6265,67 @@
         <v>42.5</v>
       </c>
       <c r="AH30" s="4">
-        <v>44</v>
-      </c>
-      <c r="AO30" s="4">
+        <v>43.4</v>
+      </c>
+      <c r="AI30" s="4"/>
+      <c r="AJ30" s="4"/>
+      <c r="AK30" s="4"/>
+      <c r="AL30" s="4"/>
+      <c r="AS30" s="4">
         <v>202.2</v>
       </c>
-      <c r="AP30" s="4">
+      <c r="AT30" s="4">
         <v>168.4</v>
       </c>
-      <c r="AQ30" s="4">
+      <c r="AU30" s="4">
         <v>158.1</v>
       </c>
-      <c r="AR30" s="4">
+      <c r="AV30" s="4">
         <f>SUM(AE30:AH30)</f>
-        <v>164.2</v>
-      </c>
-      <c r="AS30" s="4">
-        <f t="shared" ref="AS30:BB30" si="202">AR30*1.01</f>
-        <v>165.84199999999998</v>
-      </c>
-      <c r="AT30" s="4">
-        <f t="shared" si="202"/>
-        <v>167.50041999999999</v>
-      </c>
-      <c r="AU30" s="4">
-        <f t="shared" si="202"/>
-        <v>169.17542419999998</v>
-      </c>
-      <c r="AV30" s="4">
-        <f t="shared" si="202"/>
-        <v>170.86717844199998</v>
+        <v>163.6</v>
       </c>
       <c r="AW30" s="4">
-        <f t="shared" si="202"/>
-        <v>172.57585022641999</v>
+        <f t="shared" ref="AW30:BF30" si="202">AV30*1.01</f>
+        <v>165.23599999999999</v>
       </c>
       <c r="AX30" s="4">
         <f t="shared" si="202"/>
-        <v>174.30160872868419</v>
+        <v>166.88835999999998</v>
       </c>
       <c r="AY30" s="4">
         <f t="shared" si="202"/>
-        <v>176.04462481597102</v>
+        <v>168.55724359999999</v>
       </c>
       <c r="AZ30" s="4">
         <f t="shared" si="202"/>
-        <v>177.80507106413074</v>
+        <v>170.24281603599999</v>
       </c>
       <c r="BA30" s="4">
         <f t="shared" si="202"/>
-        <v>179.58312177477205</v>
+        <v>171.94524419635999</v>
       </c>
       <c r="BB30" s="4">
         <f t="shared" si="202"/>
-        <v>181.37895299251977</v>
+        <v>173.66469663832359</v>
+      </c>
+      <c r="BC30" s="4">
+        <f t="shared" si="202"/>
+        <v>175.40134360470682</v>
+      </c>
+      <c r="BD30" s="4">
+        <f t="shared" si="202"/>
+        <v>177.1553570407539</v>
+      </c>
+      <c r="BE30" s="4">
+        <f t="shared" si="202"/>
+        <v>178.92691061116145</v>
+      </c>
+      <c r="BF30" s="4">
+        <f t="shared" si="202"/>
+        <v>180.71617971727306</v>
       </c>
     </row>
-    <row r="31" spans="2:57" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:61" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>76</v>
       </c>
@@ -6185,63 +6354,67 @@
         <v>260.39999999999998</v>
       </c>
       <c r="AH31" s="4">
-        <v>260.39999999999998</v>
-      </c>
-      <c r="AO31" s="4">
+        <v>257.2</v>
+      </c>
+      <c r="AI31" s="4"/>
+      <c r="AJ31" s="4"/>
+      <c r="AK31" s="4"/>
+      <c r="AL31" s="4"/>
+      <c r="AS31" s="4">
         <v>1387.8</v>
       </c>
-      <c r="AP31" s="4">
+      <c r="AT31" s="4">
         <v>1324</v>
       </c>
-      <c r="AQ31" s="4">
+      <c r="AU31" s="4">
         <v>1041</v>
       </c>
-      <c r="AR31" s="4">
-        <f t="shared" ref="AR31:AR43" si="203">SUM(AE31:AH31)</f>
-        <v>1020</v>
-      </c>
-      <c r="AS31" s="4">
-        <f>AR31*0.97</f>
-        <v>989.4</v>
-      </c>
-      <c r="AT31" s="4">
-        <f t="shared" ref="AT31:BB31" si="204">AS31*0.97</f>
-        <v>959.71799999999996</v>
-      </c>
-      <c r="AU31" s="4">
-        <f t="shared" si="204"/>
-        <v>930.92645999999991</v>
-      </c>
       <c r="AV31" s="4">
-        <f t="shared" si="204"/>
-        <v>902.99866619999989</v>
+        <f t="shared" ref="AV31:AV43" si="203">SUM(AE31:AH31)</f>
+        <v>1016.8</v>
       </c>
       <c r="AW31" s="4">
-        <f t="shared" si="204"/>
-        <v>875.90870621399984</v>
+        <f>AV31*0.97</f>
+        <v>986.29599999999994</v>
       </c>
       <c r="AX31" s="4">
-        <f t="shared" si="204"/>
-        <v>849.63144502757984</v>
+        <f t="shared" ref="AX31:BF31" si="204">AW31*0.97</f>
+        <v>956.70711999999992</v>
       </c>
       <c r="AY31" s="4">
         <f t="shared" si="204"/>
-        <v>824.14250167675243</v>
+        <v>928.00590639999984</v>
       </c>
       <c r="AZ31" s="4">
         <f t="shared" si="204"/>
-        <v>799.41822662644984</v>
+        <v>900.16572920799979</v>
       </c>
       <c r="BA31" s="4">
         <f t="shared" si="204"/>
-        <v>775.43567982765637</v>
+        <v>873.16075733175978</v>
       </c>
       <c r="BB31" s="4">
         <f t="shared" si="204"/>
-        <v>752.17260943282668</v>
+        <v>846.96593461180692</v>
+      </c>
+      <c r="BC31" s="4">
+        <f t="shared" si="204"/>
+        <v>821.55695657345268</v>
+      </c>
+      <c r="BD31" s="4">
+        <f t="shared" si="204"/>
+        <v>796.91024787624906</v>
+      </c>
+      <c r="BE31" s="4">
+        <f t="shared" si="204"/>
+        <v>773.00294043996155</v>
+      </c>
+      <c r="BF31" s="4">
+        <f t="shared" si="204"/>
+        <v>749.81285222676263</v>
       </c>
     </row>
-    <row r="32" spans="2:57" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:61" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>77</v>
       </c>
@@ -6270,63 +6443,67 @@
         <v>0.7</v>
       </c>
       <c r="AH32" s="4">
-        <v>0.7</v>
-      </c>
-      <c r="AO32" s="4">
+        <v>-0.9</v>
+      </c>
+      <c r="AI32" s="4"/>
+      <c r="AJ32" s="4"/>
+      <c r="AK32" s="4"/>
+      <c r="AL32" s="4"/>
+      <c r="AS32" s="4">
         <v>6.9</v>
       </c>
-      <c r="AP32" s="4">
+      <c r="AT32" s="4">
         <v>7.4</v>
       </c>
-      <c r="AQ32" s="4">
+      <c r="AU32" s="4">
         <v>9.4</v>
       </c>
-      <c r="AR32" s="4">
+      <c r="AV32" s="4">
         <f t="shared" si="203"/>
-        <v>8.4</v>
-      </c>
-      <c r="AS32" s="4">
-        <f t="shared" ref="AS32:BB32" si="205">AR32*1.01</f>
-        <v>8.484</v>
-      </c>
-      <c r="AT32" s="4">
-        <f t="shared" si="205"/>
-        <v>8.5688399999999998</v>
-      </c>
-      <c r="AU32" s="4">
-        <f t="shared" si="205"/>
-        <v>8.6545284000000002</v>
-      </c>
-      <c r="AV32" s="4">
-        <f t="shared" si="205"/>
-        <v>8.7410736839999998</v>
+        <v>6.8</v>
       </c>
       <c r="AW32" s="4">
-        <f t="shared" si="205"/>
-        <v>8.8284844208400006</v>
+        <f t="shared" ref="AW32:BF32" si="205">AV32*1.01</f>
+        <v>6.8679999999999994</v>
       </c>
       <c r="AX32" s="4">
         <f t="shared" si="205"/>
-        <v>8.9167692650484014</v>
+        <v>6.9366799999999991</v>
       </c>
       <c r="AY32" s="4">
         <f t="shared" si="205"/>
-        <v>9.0059369576988857</v>
+        <v>7.0060467999999991</v>
       </c>
       <c r="AZ32" s="4">
         <f t="shared" si="205"/>
-        <v>9.0959963272758753</v>
+        <v>7.0761072679999995</v>
       </c>
       <c r="BA32" s="4">
         <f t="shared" si="205"/>
-        <v>9.1869562905486344</v>
+        <v>7.1468683406799993</v>
       </c>
       <c r="BB32" s="4">
         <f t="shared" si="205"/>
-        <v>9.278825853454121</v>
+        <v>7.2183370240867992</v>
+      </c>
+      <c r="BC32" s="4">
+        <f t="shared" si="205"/>
+        <v>7.2905203943276673</v>
+      </c>
+      <c r="BD32" s="4">
+        <f t="shared" si="205"/>
+        <v>7.3634255982709442</v>
+      </c>
+      <c r="BE32" s="4">
+        <f t="shared" si="205"/>
+        <v>7.4370598542536541</v>
+      </c>
+      <c r="BF32" s="4">
+        <f t="shared" si="205"/>
+        <v>7.5114304527961906</v>
       </c>
     </row>
-    <row r="33" spans="2:147" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:151" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
         <v>78</v>
       </c>
@@ -6357,31 +6534,23 @@
       <c r="AH33" s="4">
         <v>1.2</v>
       </c>
-      <c r="AO33" s="4">
+      <c r="AI33" s="4"/>
+      <c r="AJ33" s="4"/>
+      <c r="AK33" s="4"/>
+      <c r="AL33" s="4"/>
+      <c r="AS33" s="4">
         <v>36.799999999999997</v>
       </c>
-      <c r="AP33" s="4">
+      <c r="AT33" s="4">
         <v>33</v>
       </c>
-      <c r="AQ33" s="4">
+      <c r="AU33" s="4">
         <v>8.5</v>
       </c>
-      <c r="AR33" s="4">
+      <c r="AV33" s="4">
         <f t="shared" si="203"/>
         <v>17</v>
       </c>
-      <c r="AS33" s="4">
-        <v>0</v>
-      </c>
-      <c r="AT33" s="4">
-        <v>0</v>
-      </c>
-      <c r="AU33" s="4">
-        <v>0</v>
-      </c>
-      <c r="AV33" s="4">
-        <v>0</v>
-      </c>
       <c r="AW33" s="4">
         <v>0</v>
       </c>
@@ -6400,8 +6569,20 @@
       <c r="BB33" s="4">
         <v>0</v>
       </c>
+      <c r="BC33" s="4">
+        <v>0</v>
+      </c>
+      <c r="BD33" s="4">
+        <v>0</v>
+      </c>
+      <c r="BE33" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF33" s="4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="34" spans="2:147" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:151" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
         <v>5</v>
       </c>
@@ -6428,25 +6609,29 @@
       <c r="AH34" s="4">
         <v>0</v>
       </c>
-      <c r="AO34" s="4"/>
-      <c r="AP34" s="4"/>
-      <c r="AQ34" s="4"/>
-      <c r="AR34" s="4">
-        <f t="shared" si="203"/>
-        <v>-96.7</v>
-      </c>
+      <c r="AI34" s="4"/>
+      <c r="AJ34" s="4"/>
+      <c r="AK34" s="4"/>
+      <c r="AL34" s="4"/>
       <c r="AS34" s="4"/>
       <c r="AT34" s="4"/>
       <c r="AU34" s="4"/>
-      <c r="AV34" s="4"/>
+      <c r="AV34" s="4">
+        <f t="shared" si="203"/>
+        <v>-96.7</v>
+      </c>
       <c r="AW34" s="4"/>
       <c r="AX34" s="4"/>
       <c r="AY34" s="4"/>
       <c r="AZ34" s="4"/>
       <c r="BA34" s="4"/>
       <c r="BB34" s="4"/>
+      <c r="BC34" s="4"/>
+      <c r="BD34" s="4"/>
+      <c r="BE34" s="4"/>
+      <c r="BF34" s="4"/>
     </row>
-    <row r="35" spans="2:147" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:151" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
         <v>79</v>
       </c>
@@ -6475,32 +6660,24 @@
         <v>3</v>
       </c>
       <c r="AH35" s="4">
-        <v>0</v>
-      </c>
-      <c r="AO35" s="4">
+        <v>11.6</v>
+      </c>
+      <c r="AI35" s="4"/>
+      <c r="AJ35" s="4"/>
+      <c r="AK35" s="4"/>
+      <c r="AL35" s="4"/>
+      <c r="AS35" s="4">
         <v>15.6</v>
       </c>
-      <c r="AP35" s="4">
+      <c r="AT35" s="4">
         <v>-27</v>
       </c>
-      <c r="AQ35" s="4">
+      <c r="AU35" s="4">
         <v>-14.2</v>
       </c>
-      <c r="AR35" s="4">
+      <c r="AV35" s="4">
         <f t="shared" si="203"/>
-        <v>14.6</v>
-      </c>
-      <c r="AS35" s="4">
-        <v>0</v>
-      </c>
-      <c r="AT35" s="4">
-        <v>0</v>
-      </c>
-      <c r="AU35" s="4">
-        <v>0</v>
-      </c>
-      <c r="AV35" s="4">
-        <v>0</v>
+        <v>26.2</v>
       </c>
       <c r="AW35" s="4">
         <v>0</v>
@@ -6520,8 +6697,20 @@
       <c r="BB35" s="4">
         <v>0</v>
       </c>
+      <c r="BC35" s="4">
+        <v>0</v>
+      </c>
+      <c r="BD35" s="4">
+        <v>0</v>
+      </c>
+      <c r="BE35" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF35" s="4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="36" spans="2:147" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:151" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
         <v>80</v>
       </c>
@@ -6550,32 +6739,24 @@
         <v>-89.1</v>
       </c>
       <c r="AH36" s="4">
-        <v>0</v>
-      </c>
-      <c r="AO36" s="4">
+        <v>-133.9</v>
+      </c>
+      <c r="AI36" s="4"/>
+      <c r="AJ36" s="4"/>
+      <c r="AK36" s="4"/>
+      <c r="AL36" s="4"/>
+      <c r="AS36" s="4">
         <v>-119.8</v>
       </c>
-      <c r="AP36" s="4">
+      <c r="AT36" s="4">
         <v>-98.1</v>
       </c>
-      <c r="AQ36" s="4">
+      <c r="AU36" s="4">
         <v>-94</v>
       </c>
-      <c r="AR36" s="4">
+      <c r="AV36" s="4">
         <f t="shared" si="203"/>
-        <v>102</v>
-      </c>
-      <c r="AS36" s="4">
-        <v>0</v>
-      </c>
-      <c r="AT36" s="4">
-        <v>0</v>
-      </c>
-      <c r="AU36" s="4">
-        <v>0</v>
-      </c>
-      <c r="AV36" s="4">
-        <v>0</v>
+        <v>-31.900000000000006</v>
       </c>
       <c r="AW36" s="4">
         <v>0</v>
@@ -6595,8 +6776,20 @@
       <c r="BB36" s="4">
         <v>0</v>
       </c>
+      <c r="BC36" s="4">
+        <v>0</v>
+      </c>
+      <c r="BD36" s="4">
+        <v>0</v>
+      </c>
+      <c r="BE36" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF36" s="4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="37" spans="2:147" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:151" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
         <v>81</v>
       </c>
@@ -6625,32 +6818,24 @@
         <v>-16.3</v>
       </c>
       <c r="AH37" s="4">
-        <v>0</v>
-      </c>
-      <c r="AO37" s="4">
+        <v>-20.5</v>
+      </c>
+      <c r="AI37" s="4"/>
+      <c r="AJ37" s="4"/>
+      <c r="AK37" s="4"/>
+      <c r="AL37" s="4"/>
+      <c r="AS37" s="4">
         <v>-40.9</v>
       </c>
-      <c r="AP37" s="4">
+      <c r="AT37" s="4">
         <v>-9.9</v>
       </c>
-      <c r="AQ37" s="4">
+      <c r="AU37" s="4">
         <v>-36.5</v>
       </c>
-      <c r="AR37" s="4">
+      <c r="AV37" s="4">
         <f t="shared" si="203"/>
-        <v>-46.2</v>
-      </c>
-      <c r="AS37" s="4">
-        <v>0</v>
-      </c>
-      <c r="AT37" s="4">
-        <v>0</v>
-      </c>
-      <c r="AU37" s="4">
-        <v>0</v>
-      </c>
-      <c r="AV37" s="4">
-        <v>0</v>
+        <v>-66.7</v>
       </c>
       <c r="AW37" s="4">
         <v>0</v>
@@ -6670,8 +6855,20 @@
       <c r="BB37" s="4">
         <v>0</v>
       </c>
+      <c r="BC37" s="4">
+        <v>0</v>
+      </c>
+      <c r="BD37" s="4">
+        <v>0</v>
+      </c>
+      <c r="BE37" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF37" s="4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="38" spans="2:147" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:151" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
         <v>82</v>
       </c>
@@ -6700,32 +6897,24 @@
         <v>14.9</v>
       </c>
       <c r="AH38" s="4">
-        <v>0</v>
-      </c>
-      <c r="AO38" s="4">
+        <v>14.4</v>
+      </c>
+      <c r="AI38" s="4"/>
+      <c r="AJ38" s="4"/>
+      <c r="AK38" s="4"/>
+      <c r="AL38" s="4"/>
+      <c r="AS38" s="4">
         <v>71.400000000000006</v>
       </c>
-      <c r="AP38" s="4">
+      <c r="AT38" s="4">
         <v>70.7</v>
       </c>
-      <c r="AQ38" s="4">
+      <c r="AU38" s="4">
         <v>54.1</v>
       </c>
-      <c r="AR38" s="4">
+      <c r="AV38" s="4">
         <f t="shared" si="203"/>
-        <v>42.8</v>
-      </c>
-      <c r="AS38" s="4">
-        <v>0</v>
-      </c>
-      <c r="AT38" s="4">
-        <v>0</v>
-      </c>
-      <c r="AU38" s="4">
-        <v>0</v>
-      </c>
-      <c r="AV38" s="4">
-        <v>0</v>
+        <v>57.199999999999996</v>
       </c>
       <c r="AW38" s="4">
         <v>0</v>
@@ -6745,8 +6934,20 @@
       <c r="BB38" s="4">
         <v>0</v>
       </c>
+      <c r="BC38" s="4">
+        <v>0</v>
+      </c>
+      <c r="BD38" s="4">
+        <v>0</v>
+      </c>
+      <c r="BE38" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF38" s="4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="39" spans="2:147" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:151" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
         <v>79</v>
       </c>
@@ -6775,32 +6976,24 @@
         <v>0.2</v>
       </c>
       <c r="AH39" s="4">
-        <v>0</v>
-      </c>
-      <c r="AO39" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="AI39" s="4"/>
+      <c r="AJ39" s="4"/>
+      <c r="AK39" s="4"/>
+      <c r="AL39" s="4"/>
+      <c r="AS39" s="4">
         <v>-0.5</v>
       </c>
-      <c r="AP39" s="4">
+      <c r="AT39" s="4">
         <v>2.2000000000000002</v>
       </c>
-      <c r="AQ39" s="4">
+      <c r="AU39" s="4">
         <v>-10</v>
       </c>
-      <c r="AR39" s="4">
+      <c r="AV39" s="4">
         <f t="shared" si="203"/>
-        <v>7.1000000000000005</v>
-      </c>
-      <c r="AS39" s="4">
-        <v>0</v>
-      </c>
-      <c r="AT39" s="4">
-        <v>0</v>
-      </c>
-      <c r="AU39" s="4">
-        <v>0</v>
-      </c>
-      <c r="AV39" s="4">
-        <v>0</v>
+        <v>7.8000000000000007</v>
       </c>
       <c r="AW39" s="4">
         <v>0</v>
@@ -6820,8 +7013,20 @@
       <c r="BB39" s="4">
         <v>0</v>
       </c>
+      <c r="BC39" s="4">
+        <v>0</v>
+      </c>
+      <c r="BD39" s="4">
+        <v>0</v>
+      </c>
+      <c r="BE39" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF39" s="4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="40" spans="2:147" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:151" x14ac:dyDescent="0.3">
       <c r="B40" t="s">
         <v>83</v>
       </c>
@@ -6850,32 +7055,24 @@
         <v>38.1</v>
       </c>
       <c r="AH40" s="4">
-        <v>0</v>
-      </c>
-      <c r="AO40" s="4">
+        <v>67.7</v>
+      </c>
+      <c r="AI40" s="4"/>
+      <c r="AJ40" s="4"/>
+      <c r="AK40" s="4"/>
+      <c r="AL40" s="4"/>
+      <c r="AS40" s="4">
         <v>46.5</v>
       </c>
-      <c r="AP40" s="4">
+      <c r="AT40" s="4">
         <v>95</v>
       </c>
-      <c r="AQ40" s="4">
+      <c r="AU40" s="4">
         <v>-100.7</v>
       </c>
-      <c r="AR40" s="4">
+      <c r="AV40" s="4">
         <f t="shared" si="203"/>
-        <v>-21.800000000000004</v>
-      </c>
-      <c r="AS40" s="4">
-        <v>0</v>
-      </c>
-      <c r="AT40" s="4">
-        <v>0</v>
-      </c>
-      <c r="AU40" s="4">
-        <v>0</v>
-      </c>
-      <c r="AV40" s="4">
-        <v>0</v>
+        <v>45.9</v>
       </c>
       <c r="AW40" s="4">
         <v>0</v>
@@ -6895,8 +7092,20 @@
       <c r="BB40" s="4">
         <v>0</v>
       </c>
+      <c r="BC40" s="4">
+        <v>0</v>
+      </c>
+      <c r="BD40" s="4">
+        <v>0</v>
+      </c>
+      <c r="BE40" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF40" s="4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="41" spans="2:147" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:151" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
         <v>84</v>
       </c>
@@ -6925,32 +7134,24 @@
         <v>23.9</v>
       </c>
       <c r="AH41" s="4">
-        <v>0</v>
-      </c>
-      <c r="AO41" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="AI41" s="4"/>
+      <c r="AJ41" s="4"/>
+      <c r="AK41" s="4"/>
+      <c r="AL41" s="4"/>
+      <c r="AS41" s="4">
         <v>71.7</v>
       </c>
-      <c r="AP41" s="4">
+      <c r="AT41" s="4">
         <v>62.1</v>
       </c>
-      <c r="AQ41" s="4">
+      <c r="AU41" s="4">
         <v>150.4</v>
       </c>
-      <c r="AR41" s="4">
+      <c r="AV41" s="4">
         <f t="shared" si="203"/>
-        <v>8.9999999999999929</v>
-      </c>
-      <c r="AS41" s="4">
-        <v>0</v>
-      </c>
-      <c r="AT41" s="4">
-        <v>0</v>
-      </c>
-      <c r="AU41" s="4">
-        <v>0</v>
-      </c>
-      <c r="AV41" s="4">
-        <v>0</v>
+        <v>12.799999999999994</v>
       </c>
       <c r="AW41" s="4">
         <v>0</v>
@@ -6970,8 +7171,20 @@
       <c r="BB41" s="4">
         <v>0</v>
       </c>
+      <c r="BC41" s="4">
+        <v>0</v>
+      </c>
+      <c r="BD41" s="4">
+        <v>0</v>
+      </c>
+      <c r="BE41" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF41" s="4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="2:147" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:151" x14ac:dyDescent="0.3">
       <c r="B42" t="s">
         <v>82</v>
       </c>
@@ -7000,32 +7213,24 @@
         <v>1.3</v>
       </c>
       <c r="AH42" s="4">
-        <v>0</v>
-      </c>
-      <c r="AO42" s="4">
+        <v>-10.3</v>
+      </c>
+      <c r="AI42" s="4"/>
+      <c r="AJ42" s="4"/>
+      <c r="AK42" s="4"/>
+      <c r="AL42" s="4"/>
+      <c r="AS42" s="4">
         <v>-68.900000000000006</v>
       </c>
-      <c r="AP42" s="4">
+      <c r="AT42" s="4">
         <v>-68</v>
       </c>
-      <c r="AQ42" s="4">
+      <c r="AU42" s="4">
         <v>-62.7</v>
       </c>
-      <c r="AR42" s="4">
+      <c r="AV42" s="4">
         <f t="shared" si="203"/>
-        <v>-24.2</v>
-      </c>
-      <c r="AS42" s="4">
-        <v>0</v>
-      </c>
-      <c r="AT42" s="4">
-        <v>0</v>
-      </c>
-      <c r="AU42" s="4">
-        <v>0</v>
-      </c>
-      <c r="AV42" s="4">
-        <v>0</v>
+        <v>-34.5</v>
       </c>
       <c r="AW42" s="4">
         <v>0</v>
@@ -7045,8 +7250,20 @@
       <c r="BB42" s="4">
         <v>0</v>
       </c>
+      <c r="BC42" s="4">
+        <v>0</v>
+      </c>
+      <c r="BD42" s="4">
+        <v>0</v>
+      </c>
+      <c r="BE42" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF42" s="4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:147" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:151" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
         <v>79</v>
       </c>
@@ -7075,32 +7292,24 @@
         <v>-0.9</v>
       </c>
       <c r="AH43" s="4">
-        <v>0</v>
-      </c>
-      <c r="AO43" s="4">
+        <v>-10</v>
+      </c>
+      <c r="AI43" s="4"/>
+      <c r="AJ43" s="4"/>
+      <c r="AK43" s="4"/>
+      <c r="AL43" s="4"/>
+      <c r="AS43" s="4">
         <v>5.5</v>
       </c>
-      <c r="AP43" s="4">
+      <c r="AT43" s="4">
         <v>9.1999999999999993</v>
       </c>
-      <c r="AQ43" s="4">
+      <c r="AU43" s="4">
         <v>7.9</v>
       </c>
-      <c r="AR43" s="4">
+      <c r="AV43" s="4">
         <f t="shared" si="203"/>
-        <v>2.3000000000000003</v>
-      </c>
-      <c r="AS43" s="4">
-        <v>0</v>
-      </c>
-      <c r="AT43" s="4">
-        <v>0</v>
-      </c>
-      <c r="AU43" s="4">
-        <v>0</v>
-      </c>
-      <c r="AV43" s="4">
-        <v>0</v>
+        <v>-7.6999999999999993</v>
       </c>
       <c r="AW43" s="4">
         <v>0</v>
@@ -7120,105 +7329,121 @@
       <c r="BB43" s="4">
         <v>0</v>
       </c>
+      <c r="BC43" s="4">
+        <v>0</v>
+      </c>
+      <c r="BD43" s="4">
+        <v>0</v>
+      </c>
+      <c r="BE43" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF43" s="4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:147" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:151" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B44" s="1" t="s">
         <v>85</v>
       </c>
       <c r="Z44" s="8">
-        <f>Z29+SUM(Z30:Z43)</f>
+        <f t="shared" ref="Z44:AH44" si="206">Z29+SUM(Z30:Z43)</f>
         <v>164.39999999999989</v>
       </c>
       <c r="AA44" s="8">
-        <f>AA29+SUM(AA30:AA43)</f>
+        <f t="shared" si="206"/>
         <v>88.499999999999886</v>
       </c>
       <c r="AB44" s="8">
-        <f>AB29+SUM(AB30:AB43)</f>
+        <f t="shared" si="206"/>
         <v>102.49999999999986</v>
       </c>
       <c r="AC44" s="8">
-        <f>AC29+SUM(AC30:AC43)</f>
+        <f t="shared" si="206"/>
         <v>115.69999999999993</v>
       </c>
       <c r="AD44" s="8">
-        <f>AD29+SUM(AD30:AD43)</f>
+        <f t="shared" si="206"/>
         <v>230.7999999999999</v>
       </c>
       <c r="AE44" s="8">
-        <f>AE29+SUM(AE30:AE43)</f>
+        <f t="shared" si="206"/>
         <v>151.39999999999998</v>
       </c>
       <c r="AF44" s="8">
-        <f>AF29+SUM(AF30:AF43)</f>
+        <f t="shared" si="206"/>
         <v>88.400000000000034</v>
       </c>
       <c r="AG44" s="8">
-        <f>AG29+SUM(AG30:AG43)</f>
+        <f t="shared" si="206"/>
         <v>146.69999999999987</v>
       </c>
       <c r="AH44" s="8">
-        <f>AH29+SUM(AH30:AH43)</f>
-        <v>298.64151799999985</v>
-      </c>
-      <c r="AO44" s="8">
-        <f>AO29+SUM(AO30:AO43)</f>
+        <f t="shared" si="206"/>
+        <v>269.70000000000005</v>
+      </c>
+      <c r="AI44" s="8"/>
+      <c r="AJ44" s="8"/>
+      <c r="AK44" s="8"/>
+      <c r="AL44" s="8"/>
+      <c r="AS44" s="8">
+        <f>AS29+SUM(AS30:AS43)</f>
         <v>40.600000000000136</v>
       </c>
-      <c r="AP44" s="8">
-        <f>AP29+SUM(AP30:AP43)</f>
+      <c r="AT44" s="8">
+        <f>AT29+SUM(AT30:AT43)</f>
         <v>246.50000000000023</v>
       </c>
-      <c r="AQ44" s="8">
-        <f>AQ29+SUM(AQ30:AQ43)</f>
+      <c r="AU44" s="8">
+        <f>AU29+SUM(AU30:AU43)</f>
         <v>413.60000000000014</v>
       </c>
-      <c r="AR44" s="8">
-        <f>AR29+SUM(AR30:AR43)</f>
-        <v>685.14151800000025</v>
-      </c>
-      <c r="AS44" s="8">
-        <f t="shared" ref="AS44:BB44" si="206">AS29+SUM(AS30:AS43)</f>
-        <v>887.13513084800024</v>
-      </c>
-      <c r="AT44" s="8">
-        <f t="shared" si="206"/>
-        <v>995.20457770956841</v>
-      </c>
-      <c r="AU44" s="8">
-        <f t="shared" si="206"/>
-        <v>1045.6321323665536</v>
-      </c>
       <c r="AV44" s="8">
-        <f t="shared" si="206"/>
-        <v>1078.3705295338657</v>
+        <f>AV29+SUM(AV30:AV43)</f>
+        <v>656.20000000000039</v>
       </c>
       <c r="AW44" s="8">
-        <f t="shared" si="206"/>
-        <v>1091.3703671101532</v>
+        <f t="shared" ref="AW44:BF44" si="207">AW29+SUM(AW30:AW43)</f>
+        <v>913.32331200000067</v>
       </c>
       <c r="AX44" s="8">
-        <f t="shared" si="206"/>
-        <v>1115.5578987637296</v>
+        <f t="shared" si="207"/>
+        <v>1079.8235886720004</v>
       </c>
       <c r="AY44" s="8">
-        <f t="shared" si="206"/>
-        <v>1142.616388749055</v>
+        <f t="shared" si="207"/>
+        <v>1136.0714342027525</v>
       </c>
       <c r="AZ44" s="8">
-        <f t="shared" si="206"/>
-        <v>1172.4509785314399</v>
+        <f t="shared" si="207"/>
+        <v>1172.9060410714042</v>
       </c>
       <c r="BA44" s="8">
-        <f t="shared" si="206"/>
-        <v>1205.1009361508768</v>
+        <f t="shared" si="207"/>
+        <v>1188.9582152724838</v>
       </c>
       <c r="BB44" s="8">
-        <f t="shared" si="206"/>
-        <v>1240.6102878880345</v>
+        <f t="shared" si="207"/>
+        <v>1216.0544615464355</v>
+      </c>
+      <c r="BC44" s="8">
+        <f t="shared" si="207"/>
+        <v>1246.0990979595301</v>
+      </c>
+      <c r="BD44" s="8">
+        <f t="shared" si="207"/>
+        <v>1279.0033415249823</v>
+      </c>
+      <c r="BE44" s="8">
+        <f t="shared" si="207"/>
+        <v>1314.8091682267723</v>
+      </c>
+      <c r="BF44" s="8">
+        <f t="shared" si="207"/>
+        <v>1353.5633327568028</v>
       </c>
     </row>
-    <row r="45" spans="2:147" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:151" x14ac:dyDescent="0.3">
       <c r="B45" t="s">
         <v>86</v>
       </c>
@@ -7247,570 +7472,578 @@
         <v>53</v>
       </c>
       <c r="AH45" s="4">
-        <v>53</v>
-      </c>
-      <c r="AO45" s="4">
+        <v>64</v>
+      </c>
+      <c r="AI45" s="4"/>
+      <c r="AJ45" s="4"/>
+      <c r="AK45" s="4"/>
+      <c r="AL45" s="4"/>
+      <c r="AS45" s="4">
         <v>129.30000000000001</v>
       </c>
-      <c r="AP45" s="4">
+      <c r="AT45" s="4">
         <v>211.7</v>
       </c>
-      <c r="AQ45" s="4">
+      <c r="AU45" s="4">
         <v>194.8</v>
       </c>
-      <c r="AR45" s="4">
+      <c r="AV45" s="4">
         <f>SUM(AE45:AH45)</f>
-        <v>207.9</v>
-      </c>
-      <c r="AS45" s="4">
-        <f>AR45*1.05</f>
-        <v>218.29500000000002</v>
-      </c>
-      <c r="AT45" s="4">
-        <f>AS45*1.04</f>
-        <v>227.02680000000004</v>
-      </c>
-      <c r="AU45" s="4">
-        <f>AT45*1.03</f>
-        <v>233.83760400000006</v>
-      </c>
-      <c r="AV45" s="4">
-        <f>AU45*1.02</f>
-        <v>238.51435608000006</v>
+        <v>218.9</v>
       </c>
       <c r="AW45" s="4">
-        <f t="shared" ref="AW45:BB45" si="207">AV45*1.02</f>
-        <v>243.28464320160006</v>
+        <f>AV45*1.05</f>
+        <v>229.84500000000003</v>
       </c>
       <c r="AX45" s="4">
-        <f t="shared" si="207"/>
-        <v>248.15033606563208</v>
+        <f>AW45*1.04</f>
+        <v>239.03880000000004</v>
       </c>
       <c r="AY45" s="4">
-        <f t="shared" si="207"/>
-        <v>253.11334278694471</v>
+        <f>AX45*1.03</f>
+        <v>246.20996400000004</v>
       </c>
       <c r="AZ45" s="4">
-        <f t="shared" si="207"/>
-        <v>258.17560964268364</v>
+        <f>AY45*1.02</f>
+        <v>251.13416328000005</v>
       </c>
       <c r="BA45" s="4">
-        <f t="shared" si="207"/>
-        <v>263.3391218355373</v>
+        <f t="shared" ref="BA45:BF45" si="208">AZ45*1.02</f>
+        <v>256.15684654560005</v>
       </c>
       <c r="BB45" s="4">
-        <f t="shared" si="207"/>
-        <v>268.60590427224804</v>
+        <f t="shared" si="208"/>
+        <v>261.27998347651203</v>
+      </c>
+      <c r="BC45" s="4">
+        <f t="shared" si="208"/>
+        <v>266.50558314604228</v>
+      </c>
+      <c r="BD45" s="4">
+        <f t="shared" si="208"/>
+        <v>271.83569480896313</v>
+      </c>
+      <c r="BE45" s="4">
+        <f t="shared" si="208"/>
+        <v>277.27240870514237</v>
+      </c>
+      <c r="BF45" s="4">
+        <f t="shared" si="208"/>
+        <v>282.8178568792452</v>
       </c>
     </row>
-    <row r="46" spans="2:147" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:151" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B46" s="1" t="s">
         <v>87</v>
       </c>
       <c r="Z46" s="8">
-        <f>Z44-Z45</f>
+        <f t="shared" ref="Z46:AH46" si="209">Z44-Z45</f>
         <v>110.69999999999989</v>
       </c>
       <c r="AA46" s="8">
-        <f>AA44-AA45</f>
+        <f t="shared" si="209"/>
         <v>38.099999999999888</v>
       </c>
       <c r="AB46" s="8">
-        <f>AB44-AB45</f>
+        <f t="shared" si="209"/>
         <v>37.799999999999855</v>
       </c>
       <c r="AC46" s="8">
-        <f>AC44-AC45</f>
+        <f t="shared" si="209"/>
         <v>71.699999999999932</v>
       </c>
       <c r="AD46" s="8">
-        <f>AD44-AD45</f>
+        <f t="shared" si="209"/>
         <v>182.49999999999989</v>
       </c>
       <c r="AE46" s="8">
-        <f>AE44-AE45</f>
+        <f t="shared" si="209"/>
         <v>114.19999999999997</v>
       </c>
       <c r="AF46" s="8">
-        <f>AF44-AF45</f>
+        <f t="shared" si="209"/>
         <v>23.700000000000031</v>
       </c>
       <c r="AG46" s="8">
-        <f>AG44-AG45</f>
+        <f t="shared" si="209"/>
         <v>93.699999999999875</v>
       </c>
       <c r="AH46" s="8">
-        <f>AH44-AH45</f>
-        <v>245.64151799999985</v>
-      </c>
-      <c r="AO46" s="8">
-        <f>AO44-AO45</f>
+        <f t="shared" si="209"/>
+        <v>205.70000000000005</v>
+      </c>
+      <c r="AI46" s="8"/>
+      <c r="AJ46" s="8"/>
+      <c r="AK46" s="8"/>
+      <c r="AL46" s="8"/>
+      <c r="AS46" s="8">
+        <f>AS44-AS45</f>
         <v>-88.699999999999875</v>
       </c>
-      <c r="AP46" s="8">
-        <f>AP44-AP45</f>
+      <c r="AT46" s="8">
+        <f>AT44-AT45</f>
         <v>34.800000000000239</v>
       </c>
-      <c r="AQ46" s="8">
-        <f>AQ44-AQ45</f>
+      <c r="AU46" s="8">
+        <f>AU44-AU45</f>
         <v>218.80000000000013</v>
       </c>
-      <c r="AR46" s="8">
-        <f>AR44-AR45</f>
-        <v>477.24151800000027</v>
-      </c>
-      <c r="AS46" s="8">
-        <f t="shared" ref="AS46:BB46" si="208">AS44-AS45</f>
-        <v>668.84013084800017</v>
-      </c>
-      <c r="AT46" s="8">
-        <f t="shared" si="208"/>
-        <v>768.17777770956832</v>
-      </c>
-      <c r="AU46" s="8">
-        <f t="shared" si="208"/>
-        <v>811.79452836655355</v>
-      </c>
       <c r="AV46" s="8">
-        <f t="shared" si="208"/>
-        <v>839.85617345386561</v>
+        <f>AV44-AV45</f>
+        <v>437.30000000000041</v>
       </c>
       <c r="AW46" s="8">
-        <f t="shared" si="208"/>
-        <v>848.08572390855318</v>
+        <f t="shared" ref="AW46:BF46" si="210">AW44-AW45</f>
+        <v>683.47831200000064</v>
       </c>
       <c r="AX46" s="8">
-        <f t="shared" si="208"/>
-        <v>867.40756269809754</v>
+        <f t="shared" si="210"/>
+        <v>840.78478867200033</v>
       </c>
       <c r="AY46" s="8">
-        <f t="shared" si="208"/>
-        <v>889.50304596211026</v>
+        <f t="shared" si="210"/>
+        <v>889.86147020275246</v>
       </c>
       <c r="AZ46" s="8">
-        <f t="shared" si="208"/>
-        <v>914.27536888875625</v>
+        <f t="shared" si="210"/>
+        <v>921.77187779140411</v>
       </c>
       <c r="BA46" s="8">
-        <f t="shared" si="208"/>
-        <v>941.76181431533951</v>
+        <f t="shared" si="210"/>
+        <v>932.80136872688377</v>
       </c>
       <c r="BB46" s="8">
-        <f t="shared" si="208"/>
-        <v>972.00438361578642</v>
-      </c>
-      <c r="BC46" s="1">
-        <f>BB46*(1+$BE$21)</f>
-        <v>962.28433977962857</v>
-      </c>
-      <c r="BD46" s="1">
-        <f t="shared" ref="BD46:DO46" si="209">BC46*(1+$BE$21)</f>
-        <v>952.66149638183231</v>
-      </c>
-      <c r="BE46" s="1">
-        <f t="shared" si="209"/>
-        <v>943.13488141801395</v>
-      </c>
-      <c r="BF46" s="1">
-        <f t="shared" si="209"/>
-        <v>933.70353260383376</v>
+        <f t="shared" si="210"/>
+        <v>954.77447806992348</v>
+      </c>
+      <c r="BC46" s="8">
+        <f t="shared" si="210"/>
+        <v>979.5935148134879</v>
+      </c>
+      <c r="BD46" s="8">
+        <f t="shared" si="210"/>
+        <v>1007.1676467160191</v>
+      </c>
+      <c r="BE46" s="8">
+        <f t="shared" si="210"/>
+        <v>1037.5367595216298</v>
+      </c>
+      <c r="BF46" s="8">
+        <f t="shared" si="210"/>
+        <v>1070.7454758775575</v>
       </c>
       <c r="BG46" s="1">
-        <f t="shared" si="209"/>
-        <v>924.36649727779547</v>
+        <f>BF46*(1+$BI$21)</f>
+        <v>1060.0380211187819</v>
       </c>
       <c r="BH46" s="1">
-        <f t="shared" si="209"/>
-        <v>915.12283230501748</v>
+        <f t="shared" ref="BH46:DS46" si="211">BG46*(1+$BI$21)</f>
+        <v>1049.437640907594</v>
       </c>
       <c r="BI46" s="1">
-        <f t="shared" si="209"/>
-        <v>905.97160398196729</v>
+        <f t="shared" si="211"/>
+        <v>1038.9432644985179</v>
       </c>
       <c r="BJ46" s="1">
-        <f t="shared" si="209"/>
-        <v>896.91188794214759</v>
+        <f t="shared" si="211"/>
+        <v>1028.5538318535328</v>
       </c>
       <c r="BK46" s="1">
-        <f t="shared" si="209"/>
-        <v>887.94276906272614</v>
+        <f t="shared" si="211"/>
+        <v>1018.2682935349974</v>
       </c>
       <c r="BL46" s="1">
-        <f t="shared" si="209"/>
-        <v>879.06334137209888</v>
+        <f t="shared" si="211"/>
+        <v>1008.0856105996475</v>
       </c>
       <c r="BM46" s="1">
-        <f t="shared" si="209"/>
-        <v>870.27270795837785</v>
+        <f t="shared" si="211"/>
+        <v>998.00475449365092</v>
       </c>
       <c r="BN46" s="1">
-        <f t="shared" si="209"/>
-        <v>861.56998087879401</v>
+        <f t="shared" si="211"/>
+        <v>988.02470694871442</v>
       </c>
       <c r="BO46" s="1">
-        <f t="shared" si="209"/>
-        <v>852.95428107000612</v>
+        <f t="shared" si="211"/>
+        <v>978.14445987922727</v>
       </c>
       <c r="BP46" s="1">
-        <f t="shared" si="209"/>
-        <v>844.42473825930608</v>
+        <f t="shared" si="211"/>
+        <v>968.36301528043498</v>
       </c>
       <c r="BQ46" s="1">
-        <f t="shared" si="209"/>
-        <v>835.98049087671302</v>
+        <f t="shared" si="211"/>
+        <v>958.67938512763067</v>
       </c>
       <c r="BR46" s="1">
-        <f t="shared" si="209"/>
-        <v>827.62068596794586</v>
+        <f t="shared" si="211"/>
+        <v>949.09259127635437</v>
       </c>
       <c r="BS46" s="1">
-        <f t="shared" si="209"/>
-        <v>819.34447910826634</v>
+        <f t="shared" si="211"/>
+        <v>939.60166536359077</v>
       </c>
       <c r="BT46" s="1">
-        <f t="shared" si="209"/>
-        <v>811.15103431718364</v>
+        <f t="shared" si="211"/>
+        <v>930.20564870995486</v>
       </c>
       <c r="BU46" s="1">
-        <f t="shared" si="209"/>
-        <v>803.03952397401179</v>
+        <f t="shared" si="211"/>
+        <v>920.90359222285531</v>
       </c>
       <c r="BV46" s="1">
-        <f t="shared" si="209"/>
-        <v>795.00912873427171</v>
+        <f t="shared" si="211"/>
+        <v>911.6945563006268</v>
       </c>
       <c r="BW46" s="1">
-        <f t="shared" si="209"/>
-        <v>787.05903744692898</v>
+        <f t="shared" si="211"/>
+        <v>902.57761073762049</v>
       </c>
       <c r="BX46" s="1">
-        <f t="shared" si="209"/>
-        <v>779.18844707245967</v>
+        <f t="shared" si="211"/>
+        <v>893.55183463024423</v>
       </c>
       <c r="BY46" s="1">
-        <f t="shared" si="209"/>
-        <v>771.39656260173501</v>
+        <f t="shared" si="211"/>
+        <v>884.61631628394173</v>
       </c>
       <c r="BZ46" s="1">
-        <f t="shared" si="209"/>
-        <v>763.68259697571762</v>
+        <f t="shared" si="211"/>
+        <v>875.77015312110234</v>
       </c>
       <c r="CA46" s="1">
-        <f t="shared" si="209"/>
-        <v>756.04577100596043</v>
+        <f t="shared" si="211"/>
+        <v>867.01245158989127</v>
       </c>
       <c r="CB46" s="1">
-        <f t="shared" si="209"/>
-        <v>748.48531329590082</v>
+        <f t="shared" si="211"/>
+        <v>858.34232707399235</v>
       </c>
       <c r="CC46" s="1">
-        <f t="shared" si="209"/>
-        <v>741.00046016294186</v>
+        <f t="shared" si="211"/>
+        <v>849.75890380325245</v>
       </c>
       <c r="CD46" s="1">
-        <f t="shared" si="209"/>
-        <v>733.59045556131241</v>
+        <f t="shared" si="211"/>
+        <v>841.26131476521994</v>
       </c>
       <c r="CE46" s="1">
-        <f t="shared" si="209"/>
-        <v>726.25455100569923</v>
+        <f t="shared" si="211"/>
+        <v>832.84870161756771</v>
       </c>
       <c r="CF46" s="1">
-        <f t="shared" si="209"/>
-        <v>718.99200549564227</v>
+        <f t="shared" si="211"/>
+        <v>824.52021460139201</v>
       </c>
       <c r="CG46" s="1">
-        <f t="shared" si="209"/>
-        <v>711.8020854406858</v>
+        <f t="shared" si="211"/>
+        <v>816.27501245537803</v>
       </c>
       <c r="CH46" s="1">
-        <f t="shared" si="209"/>
-        <v>704.68406458627896</v>
+        <f t="shared" si="211"/>
+        <v>808.11226233082425</v>
       </c>
       <c r="CI46" s="1">
-        <f t="shared" si="209"/>
-        <v>697.63722394041622</v>
+        <f t="shared" si="211"/>
+        <v>800.03113970751599</v>
       </c>
       <c r="CJ46" s="1">
-        <f t="shared" si="209"/>
-        <v>690.66085170101201</v>
+        <f t="shared" si="211"/>
+        <v>792.03082831044082</v>
       </c>
       <c r="CK46" s="1">
-        <f t="shared" si="209"/>
-        <v>683.75424318400189</v>
+        <f t="shared" si="211"/>
+        <v>784.11052002733641</v>
       </c>
       <c r="CL46" s="1">
-        <f t="shared" si="209"/>
-        <v>676.91670075216189</v>
+        <f t="shared" si="211"/>
+        <v>776.26941482706309</v>
       </c>
       <c r="CM46" s="1">
-        <f t="shared" si="209"/>
-        <v>670.14753374464021</v>
+        <f t="shared" si="211"/>
+        <v>768.50672067879248</v>
       </c>
       <c r="CN46" s="1">
-        <f t="shared" si="209"/>
-        <v>663.44605840719385</v>
+        <f t="shared" si="211"/>
+        <v>760.82165347200453</v>
       </c>
       <c r="CO46" s="1">
-        <f t="shared" si="209"/>
-        <v>656.81159782312193</v>
+        <f t="shared" si="211"/>
+        <v>753.21343693728443</v>
       </c>
       <c r="CP46" s="1">
-        <f t="shared" si="209"/>
-        <v>650.24348184489065</v>
+        <f t="shared" si="211"/>
+        <v>745.68130256791153</v>
       </c>
       <c r="CQ46" s="1">
-        <f t="shared" si="209"/>
-        <v>643.74104702644172</v>
+        <f t="shared" si="211"/>
+        <v>738.22448954223239</v>
       </c>
       <c r="CR46" s="1">
-        <f t="shared" si="209"/>
-        <v>637.30363655617725</v>
+        <f t="shared" si="211"/>
+        <v>730.84224464681006</v>
       </c>
       <c r="CS46" s="1">
-        <f t="shared" si="209"/>
-        <v>630.93060019061545</v>
+        <f t="shared" si="211"/>
+        <v>723.533822200342</v>
       </c>
       <c r="CT46" s="1">
-        <f t="shared" si="209"/>
-        <v>624.62129418870927</v>
+        <f t="shared" si="211"/>
+        <v>716.2984839783386</v>
       </c>
       <c r="CU46" s="1">
-        <f t="shared" si="209"/>
-        <v>618.37508124682222</v>
+        <f t="shared" si="211"/>
+        <v>709.13549913855525</v>
       </c>
       <c r="CV46" s="1">
-        <f t="shared" si="209"/>
-        <v>612.19133043435397</v>
+        <f t="shared" si="211"/>
+        <v>702.04414414716973</v>
       </c>
       <c r="CW46" s="1">
-        <f t="shared" si="209"/>
-        <v>606.06941713001038</v>
+        <f t="shared" si="211"/>
+        <v>695.02370270569804</v>
       </c>
       <c r="CX46" s="1">
-        <f t="shared" si="209"/>
-        <v>600.00872295871022</v>
+        <f t="shared" si="211"/>
+        <v>688.07346567864101</v>
       </c>
       <c r="CY46" s="1">
-        <f t="shared" si="209"/>
-        <v>594.00863572912317</v>
+        <f t="shared" si="211"/>
+        <v>681.19273102185457</v>
       </c>
       <c r="CZ46" s="1">
-        <f t="shared" si="209"/>
-        <v>588.06854937183198</v>
+        <f t="shared" si="211"/>
+        <v>674.38080371163596</v>
       </c>
       <c r="DA46" s="1">
-        <f t="shared" si="209"/>
-        <v>582.1878638781136</v>
+        <f t="shared" si="211"/>
+        <v>667.63699567451965</v>
       </c>
       <c r="DB46" s="1">
-        <f t="shared" si="209"/>
-        <v>576.36598523933242</v>
+        <f t="shared" si="211"/>
+        <v>660.96062571777441</v>
       </c>
       <c r="DC46" s="1">
-        <f t="shared" si="209"/>
-        <v>570.60232538693913</v>
+        <f t="shared" si="211"/>
+        <v>654.3510194605966</v>
       </c>
       <c r="DD46" s="1">
-        <f t="shared" si="209"/>
-        <v>564.89630213306975</v>
+        <f t="shared" si="211"/>
+        <v>647.80750926599057</v>
       </c>
       <c r="DE46" s="1">
-        <f t="shared" si="209"/>
-        <v>559.24733911173905</v>
+        <f t="shared" si="211"/>
+        <v>641.3294341733307</v>
       </c>
       <c r="DF46" s="1">
-        <f t="shared" si="209"/>
-        <v>553.65486572062161</v>
+        <f t="shared" si="211"/>
+        <v>634.91613983159743</v>
       </c>
       <c r="DG46" s="1">
-        <f t="shared" si="209"/>
-        <v>548.11831706341536</v>
+        <f t="shared" si="211"/>
+        <v>628.56697843328141</v>
       </c>
       <c r="DH46" s="1">
-        <f t="shared" si="209"/>
-        <v>542.63713389278121</v>
+        <f t="shared" si="211"/>
+        <v>622.28130864894854</v>
       </c>
       <c r="DI46" s="1">
-        <f t="shared" si="209"/>
-        <v>537.21076255385344</v>
+        <f t="shared" si="211"/>
+        <v>616.05849556245903</v>
       </c>
       <c r="DJ46" s="1">
-        <f t="shared" si="209"/>
-        <v>531.8386549283149</v>
+        <f t="shared" si="211"/>
+        <v>609.89791060683444</v>
       </c>
       <c r="DK46" s="1">
-        <f t="shared" si="209"/>
-        <v>526.52026837903179</v>
+        <f t="shared" si="211"/>
+        <v>603.79893150076612</v>
       </c>
       <c r="DL46" s="1">
-        <f t="shared" si="209"/>
-        <v>521.25506569524146</v>
+        <f t="shared" si="211"/>
+        <v>597.76094218575849</v>
       </c>
       <c r="DM46" s="1">
-        <f t="shared" si="209"/>
-        <v>516.04251503828903</v>
+        <f t="shared" si="211"/>
+        <v>591.78333276390094</v>
       </c>
       <c r="DN46" s="1">
-        <f t="shared" si="209"/>
-        <v>510.88208988790615</v>
+        <f t="shared" si="211"/>
+        <v>585.86549943626198</v>
       </c>
       <c r="DO46" s="1">
-        <f t="shared" si="209"/>
-        <v>505.77326898902709</v>
+        <f t="shared" si="211"/>
+        <v>580.00684444189937</v>
       </c>
       <c r="DP46" s="1">
-        <f t="shared" ref="DP46:EQ46" si="210">DO46*(1+$BE$21)</f>
-        <v>500.71553629913683</v>
+        <f t="shared" si="211"/>
+        <v>574.20677599748035</v>
       </c>
       <c r="DQ46" s="1">
-        <f t="shared" si="210"/>
-        <v>495.70838093614543</v>
+        <f t="shared" si="211"/>
+        <v>568.46470823750553</v>
       </c>
       <c r="DR46" s="1">
-        <f t="shared" si="210"/>
-        <v>490.75129712678398</v>
+        <f t="shared" si="211"/>
+        <v>562.78006115513051</v>
       </c>
       <c r="DS46" s="1">
-        <f t="shared" si="210"/>
-        <v>485.84378415551612</v>
+        <f t="shared" si="211"/>
+        <v>557.15226054357925</v>
       </c>
       <c r="DT46" s="1">
-        <f t="shared" si="210"/>
-        <v>480.98534631396097</v>
+        <f t="shared" ref="DT46:EU46" si="212">DS46*(1+$BI$21)</f>
+        <v>551.58073793814344</v>
       </c>
       <c r="DU46" s="1">
-        <f t="shared" si="210"/>
-        <v>476.17549285082134</v>
+        <f t="shared" si="212"/>
+        <v>546.06493055876206</v>
       </c>
       <c r="DV46" s="1">
-        <f t="shared" si="210"/>
-        <v>471.41373792231315</v>
+        <f t="shared" si="212"/>
+        <v>540.60428125317446</v>
       </c>
       <c r="DW46" s="1">
-        <f t="shared" si="210"/>
-        <v>466.69960054309001</v>
+        <f t="shared" si="212"/>
+        <v>535.19823844064274</v>
       </c>
       <c r="DX46" s="1">
-        <f t="shared" si="210"/>
-        <v>462.0326045376591</v>
+        <f t="shared" si="212"/>
+        <v>529.84625605623626</v>
       </c>
       <c r="DY46" s="1">
-        <f t="shared" si="210"/>
-        <v>457.4122784922825</v>
+        <f t="shared" si="212"/>
+        <v>524.54779349567389</v>
       </c>
       <c r="DZ46" s="1">
-        <f t="shared" si="210"/>
-        <v>452.83815570735965</v>
+        <f t="shared" si="212"/>
+        <v>519.30231556071715</v>
       </c>
       <c r="EA46" s="1">
-        <f t="shared" si="210"/>
-        <v>448.30977415028605</v>
+        <f t="shared" si="212"/>
+        <v>514.10929240510995</v>
       </c>
       <c r="EB46" s="1">
-        <f t="shared" si="210"/>
-        <v>443.82667640878316</v>
+        <f t="shared" si="212"/>
+        <v>508.96819948105883</v>
       </c>
       <c r="EC46" s="1">
-        <f t="shared" si="210"/>
-        <v>439.38840964469534</v>
+        <f t="shared" si="212"/>
+        <v>503.87851748624826</v>
       </c>
       <c r="ED46" s="1">
-        <f t="shared" si="210"/>
-        <v>434.99452554824836</v>
+        <f t="shared" si="212"/>
+        <v>498.83973231138577</v>
       </c>
       <c r="EE46" s="1">
-        <f t="shared" si="210"/>
-        <v>430.64458029276585</v>
+        <f t="shared" si="212"/>
+        <v>493.8513349882719</v>
       </c>
       <c r="EF46" s="1">
-        <f t="shared" si="210"/>
-        <v>426.33813448983818</v>
+        <f t="shared" si="212"/>
+        <v>488.91282163838918</v>
       </c>
       <c r="EG46" s="1">
-        <f t="shared" si="210"/>
-        <v>422.07475314493979</v>
+        <f t="shared" si="212"/>
+        <v>484.02369342200529</v>
       </c>
       <c r="EH46" s="1">
-        <f t="shared" si="210"/>
-        <v>417.85400561349041</v>
+        <f t="shared" si="212"/>
+        <v>479.18345648778524</v>
       </c>
       <c r="EI46" s="1">
-        <f t="shared" si="210"/>
-        <v>413.67546555735549</v>
+        <f t="shared" si="212"/>
+        <v>474.3916219229074</v>
       </c>
       <c r="EJ46" s="1">
-        <f t="shared" si="210"/>
-        <v>409.53871090178194</v>
+        <f t="shared" si="212"/>
+        <v>469.6477057036783</v>
       </c>
       <c r="EK46" s="1">
-        <f t="shared" si="210"/>
-        <v>405.44332379276409</v>
+        <f t="shared" si="212"/>
+        <v>464.95122864664154</v>
       </c>
       <c r="EL46" s="1">
-        <f t="shared" si="210"/>
-        <v>401.38889055483645</v>
+        <f t="shared" si="212"/>
+        <v>460.30171636017513</v>
       </c>
       <c r="EM46" s="1">
-        <f t="shared" si="210"/>
-        <v>397.37500164928809</v>
+        <f t="shared" si="212"/>
+        <v>455.69869919657339</v>
       </c>
       <c r="EN46" s="1">
-        <f t="shared" si="210"/>
-        <v>393.40125163279521</v>
+        <f t="shared" si="212"/>
+        <v>451.14171220460764</v>
       </c>
       <c r="EO46" s="1">
-        <f t="shared" si="210"/>
-        <v>389.46723911646723</v>
+        <f t="shared" si="212"/>
+        <v>446.63029508256159</v>
       </c>
       <c r="EP46" s="1">
-        <f t="shared" si="210"/>
-        <v>385.57256672530252</v>
+        <f t="shared" si="212"/>
+        <v>442.16399213173599</v>
       </c>
       <c r="EQ46" s="1">
-        <f t="shared" si="210"/>
-        <v>381.71684105804951</v>
+        <f t="shared" si="212"/>
+        <v>437.74235221041863</v>
+      </c>
+      <c r="ER46" s="1">
+        <f t="shared" si="212"/>
+        <v>433.36492868831442</v>
+      </c>
+      <c r="ES46" s="1">
+        <f t="shared" si="212"/>
+        <v>429.03127940143128</v>
+      </c>
+      <c r="ET46" s="1">
+        <f t="shared" si="212"/>
+        <v>424.74096660741696</v>
+      </c>
+      <c r="EU46" s="1">
+        <f t="shared" si="212"/>
+        <v>420.49355694134277</v>
       </c>
     </row>
-    <row r="49" spans="57:57" x14ac:dyDescent="0.3">
-      <c r="BE49" s="4">
-        <f>NPV(BE22,AR46:EQ46)</f>
-        <v>10209.227528518557</v>
+    <row r="49" spans="61:61" x14ac:dyDescent="0.3">
+      <c r="BI49" s="4">
+        <f>NPV(BI22,AW46:EU46)</f>
+        <v>10298.890191431381</v>
       </c>
     </row>
-    <row r="50" spans="57:57" x14ac:dyDescent="0.3">
-      <c r="BE50" s="4">
+    <row r="50" spans="61:61" x14ac:dyDescent="0.3">
+      <c r="BI50" s="4">
         <f>Main!D8</f>
-        <v>-682.90000000000009</v>
+        <v>-596.30000000000018</v>
       </c>
     </row>
-    <row r="51" spans="57:57" x14ac:dyDescent="0.3">
-      <c r="BE51" s="4">
-        <f>BE49+BE50</f>
-        <v>9526.3275285185573</v>
+    <row r="51" spans="61:61" x14ac:dyDescent="0.3">
+      <c r="BI51" s="4">
+        <f>BI49+BI50</f>
+        <v>9702.5901914313799</v>
       </c>
     </row>
-    <row r="52" spans="57:57" x14ac:dyDescent="0.3">
-      <c r="BE52" s="5">
-        <f>BE51/BB16</f>
-        <v>5.6152829522655807</v>
+    <row r="52" spans="61:61" x14ac:dyDescent="0.3">
+      <c r="BI52" s="5">
+        <f>BI51/BF16</f>
+        <v>5.7191807789162272</v>
       </c>
     </row>
-    <row r="53" spans="57:57" x14ac:dyDescent="0.3">
-      <c r="BE53" s="5">
+    <row r="53" spans="61:61" x14ac:dyDescent="0.3">
+      <c r="BI53" s="5">
         <f>Main!D3</f>
-        <v>8.58</v>
+        <v>5.12</v>
       </c>
     </row>
-    <row r="54" spans="57:57" x14ac:dyDescent="0.3">
-      <c r="BE54" s="10">
-        <f>BE52/BE53-1</f>
-        <v>-0.34553811745156404</v>
+    <row r="54" spans="61:61" x14ac:dyDescent="0.3">
+      <c r="BI54" s="10">
+        <f>BI52/BI53-1</f>
+        <v>0.11702749588207562</v>
       </c>
     </row>
-    <row r="55" spans="57:57" x14ac:dyDescent="0.3">
-      <c r="BE55" s="6" t="s">
-        <v>89</v>
+    <row r="55" spans="61:61" x14ac:dyDescent="0.3">
+      <c r="BI55" s="6" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -7818,5 +8051,6 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>